--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -297,7 +297,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1099,7 +1098,7 @@
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
     <col width="38" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
@@ -1233,8 +1232,8 @@
       </c>
       <c r="J5" s="19" t="inlineStr">
         <is>
-          <t>มูลค่าความเสียหาย/ของเสีย
-ต่อปี (บาท) - ถ้าประเมินได้</t>
+          <t>มูลค่าความเสียหาย/ของเสียต่อปี
+(ของเสีย เคลม งานแก้ ค่าปรับ)</t>
         </is>
       </c>
       <c r="K5" s="19" t="inlineStr">
@@ -1352,8 +1351,10 @@
           <t>มากกว่า 40 ชม./สัปดาห์  (มากกว่า 1 คนเต็มเวลา)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="n">
-        <v>850000</v>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>5 แสน - 2 ล้านบาท/ปี</t>
+        </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
         <is>
@@ -2182,12 +2183,15 @@
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="K4:O4"/>
   </mergeCells>
-  <dataValidations count="11">
+  <dataValidations count="12">
     <dataValidation sqref="C7:C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="บริษัท" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$A$4:$A$8</formula1>
     </dataValidation>
     <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="เวลาที่ใช้กับงานนี้ตอนนี้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$R$4:$R$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มูลค่าความเสียหาย/ของเสียต่อปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$S$4:$S$8</formula1>
     </dataValidation>
     <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="รูปแบบข้อมูลที่มี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$B$4:$B$9</formula1>
@@ -2234,12 +2238,12 @@
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
@@ -2342,13 +2346,12 @@
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
-          <t>ขนาดข้อมูล Input/วัน
-(GB)</t>
+          <t>ขนาดข้อมูล Input/วัน</t>
         </is>
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>ขนาดคลังเอกสารทั้งหมด (GB)
+          <t>ขนาดคลังเอกสารทั้งหมด
 (สำหรับงานค้นหา/RAG)</t>
         </is>
       </c>
@@ -2423,23 +2426,35 @@
           <t>รูปภาพ</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>600</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="20" t="n">
-        <v>600</v>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>1 - 10 คน</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>1 - 2 คน</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>100 - 1,000 ครั้ง</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>1 - 10 GB</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>ไม่เกี่ยวข้อง - ไม่ใช่งานค้นหาเอกสาร</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>100 - 1,000 รูป</t>
+        </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
         <is>
@@ -3394,9 +3409,27 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:S2"/>
   </mergeCells>
-  <dataValidations count="7">
+  <dataValidations count="13">
     <dataValidation sqref="D7:D36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ประเภทข้อมูล Input" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$K$4:$K$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="E7:E36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวน Users/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$T$4:$T$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนใช้พร้อมกันสูงสุด)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$U$4:$U$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Requests/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$V$4:$V$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดข้อมูล Input/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$W$4:$W$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดคลังเอกสารทั้งหมด (RAG)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$X$4:$X$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวนรูป/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$Y$4:$Y$8</formula1>
     </dataValidation>
     <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความละเอียดรูป" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$O$4:$O$8</formula1>
@@ -3427,7 +3460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U45"/>
+  <dimension ref="A1:U46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3651,11 +3684,11 @@
         <v/>
       </c>
       <c r="E6" s="29">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF('1-UseCase ทั้งหมด'!J6="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J6,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J6,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F6" s="30">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(D6="",IF(E6="","",E6),IF(E6="",D6,ROUND((D6+E6)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(D6="",IF(AND(E6&lt;&gt;"",E6&lt;&gt;"-"),E6,""),IF(AND(E6&lt;&gt;"",E6&lt;&gt;"-"),ROUND((D6+E6)/2,0),D6)))</f>
         <v/>
       </c>
       <c r="G6" s="29">
@@ -3703,11 +3736,11 @@
         <v/>
       </c>
       <c r="R6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(U6&gt;0,"",IFERROR(ROUND((F6*DATA!$T$4+M6*DATA!$T$5+J6*DATA!$T$6+(6-Q6)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(U6&gt;0,"",IFERROR(ROUND((F6*DATA!$AC$4+M6*DATA!$AC$5+J6*DATA!$AC$6+(6-Q6)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S6" s="30">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(U6&gt;0,"ข้อมูลไม่ครบ",IF(R6="","",IF(R6&gt;=DATA!$T$10,"สูง",IF(R6&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(U6&gt;0,"ข้อมูลไม่ครบ",IF(R6="","",IF(R6&gt;=DATA!$AC$10,"สูง",IF(R6&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T6" s="29" t="inlineStr">
@@ -3716,7 +3749,7 @@
         </is>
       </c>
       <c r="U6" s="29">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",COUNTBLANK('1-UseCase ทั้งหมด'!I6)+COUNTBLANK('1-UseCase ทั้งหมด'!L6)+COUNTBLANK('1-UseCase ทั้งหมด'!M6)+COUNTBLANK('1-UseCase ทั้งหมด'!O6)+COUNTBLANK('1-UseCase ทั้งหมด'!P6)+COUNTBLANK('1-UseCase ทั้งหมด'!Q6)+COUNTBLANK('1-UseCase ทั้งหมด'!R6)+COUNTBLANK('1-UseCase ทั้งหมด'!S6)+COUNTBLANK('1-UseCase ทั้งหมด'!T6))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",COUNTBLANK('1-UseCase ทั้งหมด'!I6)+COUNTBLANK('1-UseCase ทั้งหมด'!J6)+COUNTBLANK('1-UseCase ทั้งหมด'!L6)+COUNTBLANK('1-UseCase ทั้งหมด'!M6)+COUNTBLANK('1-UseCase ทั้งหมด'!O6)+COUNTBLANK('1-UseCase ทั้งหมด'!P6)+COUNTBLANK('1-UseCase ทั้งหมด'!Q6)+COUNTBLANK('1-UseCase ทั้งหมด'!R6)+COUNTBLANK('1-UseCase ทั้งหมด'!S6)+COUNTBLANK('1-UseCase ทั้งหมด'!T6))</f>
         <v/>
       </c>
     </row>
@@ -3738,11 +3771,11 @@
         <v/>
       </c>
       <c r="E7" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF('1-UseCase ทั้งหมด'!J7="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J7,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J7,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F7" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(D7="",IF(E7="","",E7),IF(E7="",D7,ROUND((D7+E7)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(D7="",IF(AND(E7&lt;&gt;"",E7&lt;&gt;"-"),E7,""),IF(AND(E7&lt;&gt;"",E7&lt;&gt;"-"),ROUND((D7+E7)/2,0),D7)))</f>
         <v/>
       </c>
       <c r="G7" s="32">
@@ -3790,11 +3823,11 @@
         <v/>
       </c>
       <c r="R7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(U7&gt;0,"",IFERROR(ROUND((F7*DATA!$T$4+M7*DATA!$T$5+J7*DATA!$T$6+(6-Q7)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(U7&gt;0,"",IFERROR(ROUND((F7*DATA!$AC$4+M7*DATA!$AC$5+J7*DATA!$AC$6+(6-Q7)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S7" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(U7&gt;0,"ข้อมูลไม่ครบ",IF(R7="","",IF(R7&gt;=DATA!$T$10,"สูง",IF(R7&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(U7&gt;0,"ข้อมูลไม่ครบ",IF(R7="","",IF(R7&gt;=DATA!$AC$10,"สูง",IF(R7&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T7" s="33">
@@ -3802,7 +3835,7 @@
         <v/>
       </c>
       <c r="U7" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",COUNTBLANK('1-UseCase ทั้งหมด'!I7)+COUNTBLANK('1-UseCase ทั้งหมด'!L7)+COUNTBLANK('1-UseCase ทั้งหมด'!M7)+COUNTBLANK('1-UseCase ทั้งหมด'!O7)+COUNTBLANK('1-UseCase ทั้งหมด'!P7)+COUNTBLANK('1-UseCase ทั้งหมด'!Q7)+COUNTBLANK('1-UseCase ทั้งหมด'!R7)+COUNTBLANK('1-UseCase ทั้งหมด'!S7)+COUNTBLANK('1-UseCase ทั้งหมด'!T7))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",COUNTBLANK('1-UseCase ทั้งหมด'!I7)+COUNTBLANK('1-UseCase ทั้งหมด'!J7)+COUNTBLANK('1-UseCase ทั้งหมด'!L7)+COUNTBLANK('1-UseCase ทั้งหมด'!M7)+COUNTBLANK('1-UseCase ทั้งหมด'!O7)+COUNTBLANK('1-UseCase ทั้งหมด'!P7)+COUNTBLANK('1-UseCase ทั้งหมด'!Q7)+COUNTBLANK('1-UseCase ทั้งหมด'!R7)+COUNTBLANK('1-UseCase ทั้งหมด'!S7)+COUNTBLANK('1-UseCase ทั้งหมด'!T7))</f>
         <v/>
       </c>
     </row>
@@ -3824,11 +3857,11 @@
         <v/>
       </c>
       <c r="E8" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF('1-UseCase ทั้งหมด'!J8="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J8,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J8,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F8" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(D8="",IF(E8="","",E8),IF(E8="",D8,ROUND((D8+E8)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(D8="",IF(AND(E8&lt;&gt;"",E8&lt;&gt;"-"),E8,""),IF(AND(E8&lt;&gt;"",E8&lt;&gt;"-"),ROUND((D8+E8)/2,0),D8)))</f>
         <v/>
       </c>
       <c r="G8" s="32">
@@ -3876,11 +3909,11 @@
         <v/>
       </c>
       <c r="R8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(U8&gt;0,"",IFERROR(ROUND((F8*DATA!$T$4+M8*DATA!$T$5+J8*DATA!$T$6+(6-Q8)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(U8&gt;0,"",IFERROR(ROUND((F8*DATA!$AC$4+M8*DATA!$AC$5+J8*DATA!$AC$6+(6-Q8)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S8" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(U8&gt;0,"ข้อมูลไม่ครบ",IF(R8="","",IF(R8&gt;=DATA!$T$10,"สูง",IF(R8&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(U8&gt;0,"ข้อมูลไม่ครบ",IF(R8="","",IF(R8&gt;=DATA!$AC$10,"สูง",IF(R8&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T8" s="33">
@@ -3888,7 +3921,7 @@
         <v/>
       </c>
       <c r="U8" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",COUNTBLANK('1-UseCase ทั้งหมด'!I8)+COUNTBLANK('1-UseCase ทั้งหมด'!L8)+COUNTBLANK('1-UseCase ทั้งหมด'!M8)+COUNTBLANK('1-UseCase ทั้งหมด'!O8)+COUNTBLANK('1-UseCase ทั้งหมด'!P8)+COUNTBLANK('1-UseCase ทั้งหมด'!Q8)+COUNTBLANK('1-UseCase ทั้งหมด'!R8)+COUNTBLANK('1-UseCase ทั้งหมด'!S8)+COUNTBLANK('1-UseCase ทั้งหมด'!T8))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",COUNTBLANK('1-UseCase ทั้งหมด'!I8)+COUNTBLANK('1-UseCase ทั้งหมด'!J8)+COUNTBLANK('1-UseCase ทั้งหมด'!L8)+COUNTBLANK('1-UseCase ทั้งหมด'!M8)+COUNTBLANK('1-UseCase ทั้งหมด'!O8)+COUNTBLANK('1-UseCase ทั้งหมด'!P8)+COUNTBLANK('1-UseCase ทั้งหมด'!Q8)+COUNTBLANK('1-UseCase ทั้งหมด'!R8)+COUNTBLANK('1-UseCase ทั้งหมด'!S8)+COUNTBLANK('1-UseCase ทั้งหมด'!T8))</f>
         <v/>
       </c>
     </row>
@@ -3910,11 +3943,11 @@
         <v/>
       </c>
       <c r="E9" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF('1-UseCase ทั้งหมด'!J9="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J9,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J9,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F9" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(D9="",IF(E9="","",E9),IF(E9="",D9,ROUND((D9+E9)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(D9="",IF(AND(E9&lt;&gt;"",E9&lt;&gt;"-"),E9,""),IF(AND(E9&lt;&gt;"",E9&lt;&gt;"-"),ROUND((D9+E9)/2,0),D9)))</f>
         <v/>
       </c>
       <c r="G9" s="32">
@@ -3962,11 +3995,11 @@
         <v/>
       </c>
       <c r="R9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(U9&gt;0,"",IFERROR(ROUND((F9*DATA!$T$4+M9*DATA!$T$5+J9*DATA!$T$6+(6-Q9)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(U9&gt;0,"",IFERROR(ROUND((F9*DATA!$AC$4+M9*DATA!$AC$5+J9*DATA!$AC$6+(6-Q9)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S9" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(U9&gt;0,"ข้อมูลไม่ครบ",IF(R9="","",IF(R9&gt;=DATA!$T$10,"สูง",IF(R9&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(U9&gt;0,"ข้อมูลไม่ครบ",IF(R9="","",IF(R9&gt;=DATA!$AC$10,"สูง",IF(R9&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T9" s="33">
@@ -3974,7 +4007,7 @@
         <v/>
       </c>
       <c r="U9" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",COUNTBLANK('1-UseCase ทั้งหมด'!I9)+COUNTBLANK('1-UseCase ทั้งหมด'!L9)+COUNTBLANK('1-UseCase ทั้งหมด'!M9)+COUNTBLANK('1-UseCase ทั้งหมด'!O9)+COUNTBLANK('1-UseCase ทั้งหมด'!P9)+COUNTBLANK('1-UseCase ทั้งหมด'!Q9)+COUNTBLANK('1-UseCase ทั้งหมด'!R9)+COUNTBLANK('1-UseCase ทั้งหมด'!S9)+COUNTBLANK('1-UseCase ทั้งหมด'!T9))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",COUNTBLANK('1-UseCase ทั้งหมด'!I9)+COUNTBLANK('1-UseCase ทั้งหมด'!J9)+COUNTBLANK('1-UseCase ทั้งหมด'!L9)+COUNTBLANK('1-UseCase ทั้งหมด'!M9)+COUNTBLANK('1-UseCase ทั้งหมด'!O9)+COUNTBLANK('1-UseCase ทั้งหมด'!P9)+COUNTBLANK('1-UseCase ทั้งหมด'!Q9)+COUNTBLANK('1-UseCase ทั้งหมด'!R9)+COUNTBLANK('1-UseCase ทั้งหมด'!S9)+COUNTBLANK('1-UseCase ทั้งหมด'!T9))</f>
         <v/>
       </c>
     </row>
@@ -3996,11 +4029,11 @@
         <v/>
       </c>
       <c r="E10" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF('1-UseCase ทั้งหมด'!J10="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J10,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J10,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F10" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(D10="",IF(E10="","",E10),IF(E10="",D10,ROUND((D10+E10)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(D10="",IF(AND(E10&lt;&gt;"",E10&lt;&gt;"-"),E10,""),IF(AND(E10&lt;&gt;"",E10&lt;&gt;"-"),ROUND((D10+E10)/2,0),D10)))</f>
         <v/>
       </c>
       <c r="G10" s="32">
@@ -4048,11 +4081,11 @@
         <v/>
       </c>
       <c r="R10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(U10&gt;0,"",IFERROR(ROUND((F10*DATA!$T$4+M10*DATA!$T$5+J10*DATA!$T$6+(6-Q10)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(U10&gt;0,"",IFERROR(ROUND((F10*DATA!$AC$4+M10*DATA!$AC$5+J10*DATA!$AC$6+(6-Q10)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S10" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(U10&gt;0,"ข้อมูลไม่ครบ",IF(R10="","",IF(R10&gt;=DATA!$T$10,"สูง",IF(R10&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(U10&gt;0,"ข้อมูลไม่ครบ",IF(R10="","",IF(R10&gt;=DATA!$AC$10,"สูง",IF(R10&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T10" s="33">
@@ -4060,7 +4093,7 @@
         <v/>
       </c>
       <c r="U10" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",COUNTBLANK('1-UseCase ทั้งหมด'!I10)+COUNTBLANK('1-UseCase ทั้งหมด'!L10)+COUNTBLANK('1-UseCase ทั้งหมด'!M10)+COUNTBLANK('1-UseCase ทั้งหมด'!O10)+COUNTBLANK('1-UseCase ทั้งหมด'!P10)+COUNTBLANK('1-UseCase ทั้งหมด'!Q10)+COUNTBLANK('1-UseCase ทั้งหมด'!R10)+COUNTBLANK('1-UseCase ทั้งหมด'!S10)+COUNTBLANK('1-UseCase ทั้งหมด'!T10))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",COUNTBLANK('1-UseCase ทั้งหมด'!I10)+COUNTBLANK('1-UseCase ทั้งหมด'!J10)+COUNTBLANK('1-UseCase ทั้งหมด'!L10)+COUNTBLANK('1-UseCase ทั้งหมด'!M10)+COUNTBLANK('1-UseCase ทั้งหมด'!O10)+COUNTBLANK('1-UseCase ทั้งหมด'!P10)+COUNTBLANK('1-UseCase ทั้งหมด'!Q10)+COUNTBLANK('1-UseCase ทั้งหมด'!R10)+COUNTBLANK('1-UseCase ทั้งหมด'!S10)+COUNTBLANK('1-UseCase ทั้งหมด'!T10))</f>
         <v/>
       </c>
     </row>
@@ -4082,11 +4115,11 @@
         <v/>
       </c>
       <c r="E11" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF('1-UseCase ทั้งหมด'!J11="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J11,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J11,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F11" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(D11="",IF(E11="","",E11),IF(E11="",D11,ROUND((D11+E11)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(D11="",IF(AND(E11&lt;&gt;"",E11&lt;&gt;"-"),E11,""),IF(AND(E11&lt;&gt;"",E11&lt;&gt;"-"),ROUND((D11+E11)/2,0),D11)))</f>
         <v/>
       </c>
       <c r="G11" s="32">
@@ -4134,11 +4167,11 @@
         <v/>
       </c>
       <c r="R11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(U11&gt;0,"",IFERROR(ROUND((F11*DATA!$T$4+M11*DATA!$T$5+J11*DATA!$T$6+(6-Q11)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(U11&gt;0,"",IFERROR(ROUND((F11*DATA!$AC$4+M11*DATA!$AC$5+J11*DATA!$AC$6+(6-Q11)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S11" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(U11&gt;0,"ข้อมูลไม่ครบ",IF(R11="","",IF(R11&gt;=DATA!$T$10,"สูง",IF(R11&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(U11&gt;0,"ข้อมูลไม่ครบ",IF(R11="","",IF(R11&gt;=DATA!$AC$10,"สูง",IF(R11&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T11" s="33">
@@ -4146,7 +4179,7 @@
         <v/>
       </c>
       <c r="U11" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",COUNTBLANK('1-UseCase ทั้งหมด'!I11)+COUNTBLANK('1-UseCase ทั้งหมด'!L11)+COUNTBLANK('1-UseCase ทั้งหมด'!M11)+COUNTBLANK('1-UseCase ทั้งหมด'!O11)+COUNTBLANK('1-UseCase ทั้งหมด'!P11)+COUNTBLANK('1-UseCase ทั้งหมด'!Q11)+COUNTBLANK('1-UseCase ทั้งหมด'!R11)+COUNTBLANK('1-UseCase ทั้งหมด'!S11)+COUNTBLANK('1-UseCase ทั้งหมด'!T11))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",COUNTBLANK('1-UseCase ทั้งหมด'!I11)+COUNTBLANK('1-UseCase ทั้งหมด'!J11)+COUNTBLANK('1-UseCase ทั้งหมด'!L11)+COUNTBLANK('1-UseCase ทั้งหมด'!M11)+COUNTBLANK('1-UseCase ทั้งหมด'!O11)+COUNTBLANK('1-UseCase ทั้งหมด'!P11)+COUNTBLANK('1-UseCase ทั้งหมด'!Q11)+COUNTBLANK('1-UseCase ทั้งหมด'!R11)+COUNTBLANK('1-UseCase ทั้งหมด'!S11)+COUNTBLANK('1-UseCase ทั้งหมด'!T11))</f>
         <v/>
       </c>
     </row>
@@ -4168,11 +4201,11 @@
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF('1-UseCase ทั้งหมด'!J12="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J12,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J12,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F12" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(D12="",IF(E12="","",E12),IF(E12="",D12,ROUND((D12+E12)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(D12="",IF(AND(E12&lt;&gt;"",E12&lt;&gt;"-"),E12,""),IF(AND(E12&lt;&gt;"",E12&lt;&gt;"-"),ROUND((D12+E12)/2,0),D12)))</f>
         <v/>
       </c>
       <c r="G12" s="32">
@@ -4220,11 +4253,11 @@
         <v/>
       </c>
       <c r="R12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(U12&gt;0,"",IFERROR(ROUND((F12*DATA!$T$4+M12*DATA!$T$5+J12*DATA!$T$6+(6-Q12)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(U12&gt;0,"",IFERROR(ROUND((F12*DATA!$AC$4+M12*DATA!$AC$5+J12*DATA!$AC$6+(6-Q12)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S12" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(U12&gt;0,"ข้อมูลไม่ครบ",IF(R12="","",IF(R12&gt;=DATA!$T$10,"สูง",IF(R12&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(U12&gt;0,"ข้อมูลไม่ครบ",IF(R12="","",IF(R12&gt;=DATA!$AC$10,"สูง",IF(R12&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T12" s="33">
@@ -4232,7 +4265,7 @@
         <v/>
       </c>
       <c r="U12" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",COUNTBLANK('1-UseCase ทั้งหมด'!I12)+COUNTBLANK('1-UseCase ทั้งหมด'!L12)+COUNTBLANK('1-UseCase ทั้งหมด'!M12)+COUNTBLANK('1-UseCase ทั้งหมด'!O12)+COUNTBLANK('1-UseCase ทั้งหมด'!P12)+COUNTBLANK('1-UseCase ทั้งหมด'!Q12)+COUNTBLANK('1-UseCase ทั้งหมด'!R12)+COUNTBLANK('1-UseCase ทั้งหมด'!S12)+COUNTBLANK('1-UseCase ทั้งหมด'!T12))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",COUNTBLANK('1-UseCase ทั้งหมด'!I12)+COUNTBLANK('1-UseCase ทั้งหมด'!J12)+COUNTBLANK('1-UseCase ทั้งหมด'!L12)+COUNTBLANK('1-UseCase ทั้งหมด'!M12)+COUNTBLANK('1-UseCase ทั้งหมด'!O12)+COUNTBLANK('1-UseCase ทั้งหมด'!P12)+COUNTBLANK('1-UseCase ทั้งหมด'!Q12)+COUNTBLANK('1-UseCase ทั้งหมด'!R12)+COUNTBLANK('1-UseCase ทั้งหมด'!S12)+COUNTBLANK('1-UseCase ทั้งหมด'!T12))</f>
         <v/>
       </c>
     </row>
@@ -4254,11 +4287,11 @@
         <v/>
       </c>
       <c r="E13" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF('1-UseCase ทั้งหมด'!J13="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J13,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J13,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F13" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(D13="",IF(E13="","",E13),IF(E13="",D13,ROUND((D13+E13)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(D13="",IF(AND(E13&lt;&gt;"",E13&lt;&gt;"-"),E13,""),IF(AND(E13&lt;&gt;"",E13&lt;&gt;"-"),ROUND((D13+E13)/2,0),D13)))</f>
         <v/>
       </c>
       <c r="G13" s="32">
@@ -4306,11 +4339,11 @@
         <v/>
       </c>
       <c r="R13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(U13&gt;0,"",IFERROR(ROUND((F13*DATA!$T$4+M13*DATA!$T$5+J13*DATA!$T$6+(6-Q13)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(U13&gt;0,"",IFERROR(ROUND((F13*DATA!$AC$4+M13*DATA!$AC$5+J13*DATA!$AC$6+(6-Q13)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S13" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(U13&gt;0,"ข้อมูลไม่ครบ",IF(R13="","",IF(R13&gt;=DATA!$T$10,"สูง",IF(R13&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(U13&gt;0,"ข้อมูลไม่ครบ",IF(R13="","",IF(R13&gt;=DATA!$AC$10,"สูง",IF(R13&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T13" s="33">
@@ -4318,7 +4351,7 @@
         <v/>
       </c>
       <c r="U13" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",COUNTBLANK('1-UseCase ทั้งหมด'!I13)+COUNTBLANK('1-UseCase ทั้งหมด'!L13)+COUNTBLANK('1-UseCase ทั้งหมด'!M13)+COUNTBLANK('1-UseCase ทั้งหมด'!O13)+COUNTBLANK('1-UseCase ทั้งหมด'!P13)+COUNTBLANK('1-UseCase ทั้งหมด'!Q13)+COUNTBLANK('1-UseCase ทั้งหมด'!R13)+COUNTBLANK('1-UseCase ทั้งหมด'!S13)+COUNTBLANK('1-UseCase ทั้งหมด'!T13))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",COUNTBLANK('1-UseCase ทั้งหมด'!I13)+COUNTBLANK('1-UseCase ทั้งหมด'!J13)+COUNTBLANK('1-UseCase ทั้งหมด'!L13)+COUNTBLANK('1-UseCase ทั้งหมด'!M13)+COUNTBLANK('1-UseCase ทั้งหมด'!O13)+COUNTBLANK('1-UseCase ทั้งหมด'!P13)+COUNTBLANK('1-UseCase ทั้งหมด'!Q13)+COUNTBLANK('1-UseCase ทั้งหมด'!R13)+COUNTBLANK('1-UseCase ทั้งหมด'!S13)+COUNTBLANK('1-UseCase ทั้งหมด'!T13))</f>
         <v/>
       </c>
     </row>
@@ -4340,11 +4373,11 @@
         <v/>
       </c>
       <c r="E14" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF('1-UseCase ทั้งหมด'!J14="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J14,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J14,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F14" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(D14="",IF(E14="","",E14),IF(E14="",D14,ROUND((D14+E14)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(D14="",IF(AND(E14&lt;&gt;"",E14&lt;&gt;"-"),E14,""),IF(AND(E14&lt;&gt;"",E14&lt;&gt;"-"),ROUND((D14+E14)/2,0),D14)))</f>
         <v/>
       </c>
       <c r="G14" s="32">
@@ -4392,11 +4425,11 @@
         <v/>
       </c>
       <c r="R14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(U14&gt;0,"",IFERROR(ROUND((F14*DATA!$T$4+M14*DATA!$T$5+J14*DATA!$T$6+(6-Q14)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(U14&gt;0,"",IFERROR(ROUND((F14*DATA!$AC$4+M14*DATA!$AC$5+J14*DATA!$AC$6+(6-Q14)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S14" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(U14&gt;0,"ข้อมูลไม่ครบ",IF(R14="","",IF(R14&gt;=DATA!$T$10,"สูง",IF(R14&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(U14&gt;0,"ข้อมูลไม่ครบ",IF(R14="","",IF(R14&gt;=DATA!$AC$10,"สูง",IF(R14&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T14" s="33">
@@ -4404,7 +4437,7 @@
         <v/>
       </c>
       <c r="U14" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",COUNTBLANK('1-UseCase ทั้งหมด'!I14)+COUNTBLANK('1-UseCase ทั้งหมด'!L14)+COUNTBLANK('1-UseCase ทั้งหมด'!M14)+COUNTBLANK('1-UseCase ทั้งหมด'!O14)+COUNTBLANK('1-UseCase ทั้งหมด'!P14)+COUNTBLANK('1-UseCase ทั้งหมด'!Q14)+COUNTBLANK('1-UseCase ทั้งหมด'!R14)+COUNTBLANK('1-UseCase ทั้งหมด'!S14)+COUNTBLANK('1-UseCase ทั้งหมด'!T14))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",COUNTBLANK('1-UseCase ทั้งหมด'!I14)+COUNTBLANK('1-UseCase ทั้งหมด'!J14)+COUNTBLANK('1-UseCase ทั้งหมด'!L14)+COUNTBLANK('1-UseCase ทั้งหมด'!M14)+COUNTBLANK('1-UseCase ทั้งหมด'!O14)+COUNTBLANK('1-UseCase ทั้งหมด'!P14)+COUNTBLANK('1-UseCase ทั้งหมด'!Q14)+COUNTBLANK('1-UseCase ทั้งหมด'!R14)+COUNTBLANK('1-UseCase ทั้งหมด'!S14)+COUNTBLANK('1-UseCase ทั้งหมด'!T14))</f>
         <v/>
       </c>
     </row>
@@ -4426,11 +4459,11 @@
         <v/>
       </c>
       <c r="E15" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF('1-UseCase ทั้งหมด'!J15="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J15,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J15,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F15" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(D15="",IF(E15="","",E15),IF(E15="",D15,ROUND((D15+E15)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(D15="",IF(AND(E15&lt;&gt;"",E15&lt;&gt;"-"),E15,""),IF(AND(E15&lt;&gt;"",E15&lt;&gt;"-"),ROUND((D15+E15)/2,0),D15)))</f>
         <v/>
       </c>
       <c r="G15" s="32">
@@ -4478,11 +4511,11 @@
         <v/>
       </c>
       <c r="R15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(U15&gt;0,"",IFERROR(ROUND((F15*DATA!$T$4+M15*DATA!$T$5+J15*DATA!$T$6+(6-Q15)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(U15&gt;0,"",IFERROR(ROUND((F15*DATA!$AC$4+M15*DATA!$AC$5+J15*DATA!$AC$6+(6-Q15)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S15" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(U15&gt;0,"ข้อมูลไม่ครบ",IF(R15="","",IF(R15&gt;=DATA!$T$10,"สูง",IF(R15&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(U15&gt;0,"ข้อมูลไม่ครบ",IF(R15="","",IF(R15&gt;=DATA!$AC$10,"สูง",IF(R15&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T15" s="33">
@@ -4490,7 +4523,7 @@
         <v/>
       </c>
       <c r="U15" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",COUNTBLANK('1-UseCase ทั้งหมด'!I15)+COUNTBLANK('1-UseCase ทั้งหมด'!L15)+COUNTBLANK('1-UseCase ทั้งหมด'!M15)+COUNTBLANK('1-UseCase ทั้งหมด'!O15)+COUNTBLANK('1-UseCase ทั้งหมด'!P15)+COUNTBLANK('1-UseCase ทั้งหมด'!Q15)+COUNTBLANK('1-UseCase ทั้งหมด'!R15)+COUNTBLANK('1-UseCase ทั้งหมด'!S15)+COUNTBLANK('1-UseCase ทั้งหมด'!T15))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",COUNTBLANK('1-UseCase ทั้งหมด'!I15)+COUNTBLANK('1-UseCase ทั้งหมด'!J15)+COUNTBLANK('1-UseCase ทั้งหมด'!L15)+COUNTBLANK('1-UseCase ทั้งหมด'!M15)+COUNTBLANK('1-UseCase ทั้งหมด'!O15)+COUNTBLANK('1-UseCase ทั้งหมด'!P15)+COUNTBLANK('1-UseCase ทั้งหมด'!Q15)+COUNTBLANK('1-UseCase ทั้งหมด'!R15)+COUNTBLANK('1-UseCase ทั้งหมด'!S15)+COUNTBLANK('1-UseCase ทั้งหมด'!T15))</f>
         <v/>
       </c>
     </row>
@@ -4512,11 +4545,11 @@
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF('1-UseCase ทั้งหมด'!J16="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J16,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J16,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F16" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(D16="",IF(E16="","",E16),IF(E16="",D16,ROUND((D16+E16)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(D16="",IF(AND(E16&lt;&gt;"",E16&lt;&gt;"-"),E16,""),IF(AND(E16&lt;&gt;"",E16&lt;&gt;"-"),ROUND((D16+E16)/2,0),D16)))</f>
         <v/>
       </c>
       <c r="G16" s="32">
@@ -4564,11 +4597,11 @@
         <v/>
       </c>
       <c r="R16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(U16&gt;0,"",IFERROR(ROUND((F16*DATA!$T$4+M16*DATA!$T$5+J16*DATA!$T$6+(6-Q16)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(U16&gt;0,"",IFERROR(ROUND((F16*DATA!$AC$4+M16*DATA!$AC$5+J16*DATA!$AC$6+(6-Q16)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S16" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(U16&gt;0,"ข้อมูลไม่ครบ",IF(R16="","",IF(R16&gt;=DATA!$T$10,"สูง",IF(R16&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(U16&gt;0,"ข้อมูลไม่ครบ",IF(R16="","",IF(R16&gt;=DATA!$AC$10,"สูง",IF(R16&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T16" s="33">
@@ -4576,7 +4609,7 @@
         <v/>
       </c>
       <c r="U16" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",COUNTBLANK('1-UseCase ทั้งหมด'!I16)+COUNTBLANK('1-UseCase ทั้งหมด'!L16)+COUNTBLANK('1-UseCase ทั้งหมด'!M16)+COUNTBLANK('1-UseCase ทั้งหมด'!O16)+COUNTBLANK('1-UseCase ทั้งหมด'!P16)+COUNTBLANK('1-UseCase ทั้งหมด'!Q16)+COUNTBLANK('1-UseCase ทั้งหมด'!R16)+COUNTBLANK('1-UseCase ทั้งหมด'!S16)+COUNTBLANK('1-UseCase ทั้งหมด'!T16))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",COUNTBLANK('1-UseCase ทั้งหมด'!I16)+COUNTBLANK('1-UseCase ทั้งหมด'!J16)+COUNTBLANK('1-UseCase ทั้งหมด'!L16)+COUNTBLANK('1-UseCase ทั้งหมด'!M16)+COUNTBLANK('1-UseCase ทั้งหมด'!O16)+COUNTBLANK('1-UseCase ทั้งหมด'!P16)+COUNTBLANK('1-UseCase ทั้งหมด'!Q16)+COUNTBLANK('1-UseCase ทั้งหมด'!R16)+COUNTBLANK('1-UseCase ทั้งหมด'!S16)+COUNTBLANK('1-UseCase ทั้งหมด'!T16))</f>
         <v/>
       </c>
     </row>
@@ -4598,11 +4631,11 @@
         <v/>
       </c>
       <c r="E17" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF('1-UseCase ทั้งหมด'!J17="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J17,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J17,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F17" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(D17="",IF(E17="","",E17),IF(E17="",D17,ROUND((D17+E17)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(D17="",IF(AND(E17&lt;&gt;"",E17&lt;&gt;"-"),E17,""),IF(AND(E17&lt;&gt;"",E17&lt;&gt;"-"),ROUND((D17+E17)/2,0),D17)))</f>
         <v/>
       </c>
       <c r="G17" s="32">
@@ -4650,11 +4683,11 @@
         <v/>
       </c>
       <c r="R17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(U17&gt;0,"",IFERROR(ROUND((F17*DATA!$T$4+M17*DATA!$T$5+J17*DATA!$T$6+(6-Q17)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(U17&gt;0,"",IFERROR(ROUND((F17*DATA!$AC$4+M17*DATA!$AC$5+J17*DATA!$AC$6+(6-Q17)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S17" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(U17&gt;0,"ข้อมูลไม่ครบ",IF(R17="","",IF(R17&gt;=DATA!$T$10,"สูง",IF(R17&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(U17&gt;0,"ข้อมูลไม่ครบ",IF(R17="","",IF(R17&gt;=DATA!$AC$10,"สูง",IF(R17&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T17" s="33">
@@ -4662,7 +4695,7 @@
         <v/>
       </c>
       <c r="U17" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",COUNTBLANK('1-UseCase ทั้งหมด'!I17)+COUNTBLANK('1-UseCase ทั้งหมด'!L17)+COUNTBLANK('1-UseCase ทั้งหมด'!M17)+COUNTBLANK('1-UseCase ทั้งหมด'!O17)+COUNTBLANK('1-UseCase ทั้งหมด'!P17)+COUNTBLANK('1-UseCase ทั้งหมด'!Q17)+COUNTBLANK('1-UseCase ทั้งหมด'!R17)+COUNTBLANK('1-UseCase ทั้งหมด'!S17)+COUNTBLANK('1-UseCase ทั้งหมด'!T17))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",COUNTBLANK('1-UseCase ทั้งหมด'!I17)+COUNTBLANK('1-UseCase ทั้งหมด'!J17)+COUNTBLANK('1-UseCase ทั้งหมด'!L17)+COUNTBLANK('1-UseCase ทั้งหมด'!M17)+COUNTBLANK('1-UseCase ทั้งหมด'!O17)+COUNTBLANK('1-UseCase ทั้งหมด'!P17)+COUNTBLANK('1-UseCase ทั้งหมด'!Q17)+COUNTBLANK('1-UseCase ทั้งหมด'!R17)+COUNTBLANK('1-UseCase ทั้งหมด'!S17)+COUNTBLANK('1-UseCase ทั้งหมด'!T17))</f>
         <v/>
       </c>
     </row>
@@ -4684,11 +4717,11 @@
         <v/>
       </c>
       <c r="E18" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF('1-UseCase ทั้งหมด'!J18="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J18,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J18,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F18" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(D18="",IF(E18="","",E18),IF(E18="",D18,ROUND((D18+E18)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(D18="",IF(AND(E18&lt;&gt;"",E18&lt;&gt;"-"),E18,""),IF(AND(E18&lt;&gt;"",E18&lt;&gt;"-"),ROUND((D18+E18)/2,0),D18)))</f>
         <v/>
       </c>
       <c r="G18" s="32">
@@ -4736,11 +4769,11 @@
         <v/>
       </c>
       <c r="R18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(U18&gt;0,"",IFERROR(ROUND((F18*DATA!$T$4+M18*DATA!$T$5+J18*DATA!$T$6+(6-Q18)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(U18&gt;0,"",IFERROR(ROUND((F18*DATA!$AC$4+M18*DATA!$AC$5+J18*DATA!$AC$6+(6-Q18)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S18" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(U18&gt;0,"ข้อมูลไม่ครบ",IF(R18="","",IF(R18&gt;=DATA!$T$10,"สูง",IF(R18&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(U18&gt;0,"ข้อมูลไม่ครบ",IF(R18="","",IF(R18&gt;=DATA!$AC$10,"สูง",IF(R18&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T18" s="33">
@@ -4748,7 +4781,7 @@
         <v/>
       </c>
       <c r="U18" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",COUNTBLANK('1-UseCase ทั้งหมด'!I18)+COUNTBLANK('1-UseCase ทั้งหมด'!L18)+COUNTBLANK('1-UseCase ทั้งหมด'!M18)+COUNTBLANK('1-UseCase ทั้งหมด'!O18)+COUNTBLANK('1-UseCase ทั้งหมด'!P18)+COUNTBLANK('1-UseCase ทั้งหมด'!Q18)+COUNTBLANK('1-UseCase ทั้งหมด'!R18)+COUNTBLANK('1-UseCase ทั้งหมด'!S18)+COUNTBLANK('1-UseCase ทั้งหมด'!T18))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",COUNTBLANK('1-UseCase ทั้งหมด'!I18)+COUNTBLANK('1-UseCase ทั้งหมด'!J18)+COUNTBLANK('1-UseCase ทั้งหมด'!L18)+COUNTBLANK('1-UseCase ทั้งหมด'!M18)+COUNTBLANK('1-UseCase ทั้งหมด'!O18)+COUNTBLANK('1-UseCase ทั้งหมด'!P18)+COUNTBLANK('1-UseCase ทั้งหมด'!Q18)+COUNTBLANK('1-UseCase ทั้งหมด'!R18)+COUNTBLANK('1-UseCase ทั้งหมด'!S18)+COUNTBLANK('1-UseCase ทั้งหมด'!T18))</f>
         <v/>
       </c>
     </row>
@@ -4770,11 +4803,11 @@
         <v/>
       </c>
       <c r="E19" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF('1-UseCase ทั้งหมด'!J19="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J19,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J19,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F19" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(D19="",IF(E19="","",E19),IF(E19="",D19,ROUND((D19+E19)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(D19="",IF(AND(E19&lt;&gt;"",E19&lt;&gt;"-"),E19,""),IF(AND(E19&lt;&gt;"",E19&lt;&gt;"-"),ROUND((D19+E19)/2,0),D19)))</f>
         <v/>
       </c>
       <c r="G19" s="32">
@@ -4822,11 +4855,11 @@
         <v/>
       </c>
       <c r="R19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(U19&gt;0,"",IFERROR(ROUND((F19*DATA!$T$4+M19*DATA!$T$5+J19*DATA!$T$6+(6-Q19)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(U19&gt;0,"",IFERROR(ROUND((F19*DATA!$AC$4+M19*DATA!$AC$5+J19*DATA!$AC$6+(6-Q19)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S19" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(U19&gt;0,"ข้อมูลไม่ครบ",IF(R19="","",IF(R19&gt;=DATA!$T$10,"สูง",IF(R19&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(U19&gt;0,"ข้อมูลไม่ครบ",IF(R19="","",IF(R19&gt;=DATA!$AC$10,"สูง",IF(R19&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T19" s="33">
@@ -4834,7 +4867,7 @@
         <v/>
       </c>
       <c r="U19" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",COUNTBLANK('1-UseCase ทั้งหมด'!I19)+COUNTBLANK('1-UseCase ทั้งหมด'!L19)+COUNTBLANK('1-UseCase ทั้งหมด'!M19)+COUNTBLANK('1-UseCase ทั้งหมด'!O19)+COUNTBLANK('1-UseCase ทั้งหมด'!P19)+COUNTBLANK('1-UseCase ทั้งหมด'!Q19)+COUNTBLANK('1-UseCase ทั้งหมด'!R19)+COUNTBLANK('1-UseCase ทั้งหมด'!S19)+COUNTBLANK('1-UseCase ทั้งหมด'!T19))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",COUNTBLANK('1-UseCase ทั้งหมด'!I19)+COUNTBLANK('1-UseCase ทั้งหมด'!J19)+COUNTBLANK('1-UseCase ทั้งหมด'!L19)+COUNTBLANK('1-UseCase ทั้งหมด'!M19)+COUNTBLANK('1-UseCase ทั้งหมด'!O19)+COUNTBLANK('1-UseCase ทั้งหมด'!P19)+COUNTBLANK('1-UseCase ทั้งหมด'!Q19)+COUNTBLANK('1-UseCase ทั้งหมด'!R19)+COUNTBLANK('1-UseCase ทั้งหมด'!S19)+COUNTBLANK('1-UseCase ทั้งหมด'!T19))</f>
         <v/>
       </c>
     </row>
@@ -4856,11 +4889,11 @@
         <v/>
       </c>
       <c r="E20" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF('1-UseCase ทั้งหมด'!J20="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J20,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J20,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F20" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(D20="",IF(E20="","",E20),IF(E20="",D20,ROUND((D20+E20)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(D20="",IF(AND(E20&lt;&gt;"",E20&lt;&gt;"-"),E20,""),IF(AND(E20&lt;&gt;"",E20&lt;&gt;"-"),ROUND((D20+E20)/2,0),D20)))</f>
         <v/>
       </c>
       <c r="G20" s="32">
@@ -4908,11 +4941,11 @@
         <v/>
       </c>
       <c r="R20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(U20&gt;0,"",IFERROR(ROUND((F20*DATA!$T$4+M20*DATA!$T$5+J20*DATA!$T$6+(6-Q20)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(U20&gt;0,"",IFERROR(ROUND((F20*DATA!$AC$4+M20*DATA!$AC$5+J20*DATA!$AC$6+(6-Q20)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S20" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(U20&gt;0,"ข้อมูลไม่ครบ",IF(R20="","",IF(R20&gt;=DATA!$T$10,"สูง",IF(R20&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(U20&gt;0,"ข้อมูลไม่ครบ",IF(R20="","",IF(R20&gt;=DATA!$AC$10,"สูง",IF(R20&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T20" s="33">
@@ -4920,7 +4953,7 @@
         <v/>
       </c>
       <c r="U20" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",COUNTBLANK('1-UseCase ทั้งหมด'!I20)+COUNTBLANK('1-UseCase ทั้งหมด'!L20)+COUNTBLANK('1-UseCase ทั้งหมด'!M20)+COUNTBLANK('1-UseCase ทั้งหมด'!O20)+COUNTBLANK('1-UseCase ทั้งหมด'!P20)+COUNTBLANK('1-UseCase ทั้งหมด'!Q20)+COUNTBLANK('1-UseCase ทั้งหมด'!R20)+COUNTBLANK('1-UseCase ทั้งหมด'!S20)+COUNTBLANK('1-UseCase ทั้งหมด'!T20))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",COUNTBLANK('1-UseCase ทั้งหมด'!I20)+COUNTBLANK('1-UseCase ทั้งหมด'!J20)+COUNTBLANK('1-UseCase ทั้งหมด'!L20)+COUNTBLANK('1-UseCase ทั้งหมด'!M20)+COUNTBLANK('1-UseCase ทั้งหมด'!O20)+COUNTBLANK('1-UseCase ทั้งหมด'!P20)+COUNTBLANK('1-UseCase ทั้งหมด'!Q20)+COUNTBLANK('1-UseCase ทั้งหมด'!R20)+COUNTBLANK('1-UseCase ทั้งหมด'!S20)+COUNTBLANK('1-UseCase ทั้งหมด'!T20))</f>
         <v/>
       </c>
     </row>
@@ -4942,11 +4975,11 @@
         <v/>
       </c>
       <c r="E21" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF('1-UseCase ทั้งหมด'!J21="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J21,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J21,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F21" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(D21="",IF(E21="","",E21),IF(E21="",D21,ROUND((D21+E21)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(D21="",IF(AND(E21&lt;&gt;"",E21&lt;&gt;"-"),E21,""),IF(AND(E21&lt;&gt;"",E21&lt;&gt;"-"),ROUND((D21+E21)/2,0),D21)))</f>
         <v/>
       </c>
       <c r="G21" s="32">
@@ -4994,11 +5027,11 @@
         <v/>
       </c>
       <c r="R21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(U21&gt;0,"",IFERROR(ROUND((F21*DATA!$T$4+M21*DATA!$T$5+J21*DATA!$T$6+(6-Q21)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(U21&gt;0,"",IFERROR(ROUND((F21*DATA!$AC$4+M21*DATA!$AC$5+J21*DATA!$AC$6+(6-Q21)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S21" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(U21&gt;0,"ข้อมูลไม่ครบ",IF(R21="","",IF(R21&gt;=DATA!$T$10,"สูง",IF(R21&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(U21&gt;0,"ข้อมูลไม่ครบ",IF(R21="","",IF(R21&gt;=DATA!$AC$10,"สูง",IF(R21&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T21" s="33">
@@ -5006,7 +5039,7 @@
         <v/>
       </c>
       <c r="U21" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",COUNTBLANK('1-UseCase ทั้งหมด'!I21)+COUNTBLANK('1-UseCase ทั้งหมด'!L21)+COUNTBLANK('1-UseCase ทั้งหมด'!M21)+COUNTBLANK('1-UseCase ทั้งหมด'!O21)+COUNTBLANK('1-UseCase ทั้งหมด'!P21)+COUNTBLANK('1-UseCase ทั้งหมด'!Q21)+COUNTBLANK('1-UseCase ทั้งหมด'!R21)+COUNTBLANK('1-UseCase ทั้งหมด'!S21)+COUNTBLANK('1-UseCase ทั้งหมด'!T21))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",COUNTBLANK('1-UseCase ทั้งหมด'!I21)+COUNTBLANK('1-UseCase ทั้งหมด'!J21)+COUNTBLANK('1-UseCase ทั้งหมด'!L21)+COUNTBLANK('1-UseCase ทั้งหมด'!M21)+COUNTBLANK('1-UseCase ทั้งหมด'!O21)+COUNTBLANK('1-UseCase ทั้งหมด'!P21)+COUNTBLANK('1-UseCase ทั้งหมด'!Q21)+COUNTBLANK('1-UseCase ทั้งหมด'!R21)+COUNTBLANK('1-UseCase ทั้งหมด'!S21)+COUNTBLANK('1-UseCase ทั้งหมด'!T21))</f>
         <v/>
       </c>
     </row>
@@ -5028,11 +5061,11 @@
         <v/>
       </c>
       <c r="E22" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF('1-UseCase ทั้งหมด'!J22="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J22,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J22,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F22" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(D22="",IF(E22="","",E22),IF(E22="",D22,ROUND((D22+E22)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(D22="",IF(AND(E22&lt;&gt;"",E22&lt;&gt;"-"),E22,""),IF(AND(E22&lt;&gt;"",E22&lt;&gt;"-"),ROUND((D22+E22)/2,0),D22)))</f>
         <v/>
       </c>
       <c r="G22" s="32">
@@ -5080,11 +5113,11 @@
         <v/>
       </c>
       <c r="R22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(U22&gt;0,"",IFERROR(ROUND((F22*DATA!$T$4+M22*DATA!$T$5+J22*DATA!$T$6+(6-Q22)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(U22&gt;0,"",IFERROR(ROUND((F22*DATA!$AC$4+M22*DATA!$AC$5+J22*DATA!$AC$6+(6-Q22)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S22" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(U22&gt;0,"ข้อมูลไม่ครบ",IF(R22="","",IF(R22&gt;=DATA!$T$10,"สูง",IF(R22&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(U22&gt;0,"ข้อมูลไม่ครบ",IF(R22="","",IF(R22&gt;=DATA!$AC$10,"สูง",IF(R22&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T22" s="33">
@@ -5092,7 +5125,7 @@
         <v/>
       </c>
       <c r="U22" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",COUNTBLANK('1-UseCase ทั้งหมด'!I22)+COUNTBLANK('1-UseCase ทั้งหมด'!L22)+COUNTBLANK('1-UseCase ทั้งหมด'!M22)+COUNTBLANK('1-UseCase ทั้งหมด'!O22)+COUNTBLANK('1-UseCase ทั้งหมด'!P22)+COUNTBLANK('1-UseCase ทั้งหมด'!Q22)+COUNTBLANK('1-UseCase ทั้งหมด'!R22)+COUNTBLANK('1-UseCase ทั้งหมด'!S22)+COUNTBLANK('1-UseCase ทั้งหมด'!T22))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",COUNTBLANK('1-UseCase ทั้งหมด'!I22)+COUNTBLANK('1-UseCase ทั้งหมด'!J22)+COUNTBLANK('1-UseCase ทั้งหมด'!L22)+COUNTBLANK('1-UseCase ทั้งหมด'!M22)+COUNTBLANK('1-UseCase ทั้งหมด'!O22)+COUNTBLANK('1-UseCase ทั้งหมด'!P22)+COUNTBLANK('1-UseCase ทั้งหมด'!Q22)+COUNTBLANK('1-UseCase ทั้งหมด'!R22)+COUNTBLANK('1-UseCase ทั้งหมด'!S22)+COUNTBLANK('1-UseCase ทั้งหมด'!T22))</f>
         <v/>
       </c>
     </row>
@@ -5114,11 +5147,11 @@
         <v/>
       </c>
       <c r="E23" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF('1-UseCase ทั้งหมด'!J23="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J23,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J23,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F23" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(D23="",IF(E23="","",E23),IF(E23="",D23,ROUND((D23+E23)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(D23="",IF(AND(E23&lt;&gt;"",E23&lt;&gt;"-"),E23,""),IF(AND(E23&lt;&gt;"",E23&lt;&gt;"-"),ROUND((D23+E23)/2,0),D23)))</f>
         <v/>
       </c>
       <c r="G23" s="32">
@@ -5166,11 +5199,11 @@
         <v/>
       </c>
       <c r="R23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(U23&gt;0,"",IFERROR(ROUND((F23*DATA!$T$4+M23*DATA!$T$5+J23*DATA!$T$6+(6-Q23)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(U23&gt;0,"",IFERROR(ROUND((F23*DATA!$AC$4+M23*DATA!$AC$5+J23*DATA!$AC$6+(6-Q23)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S23" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(U23&gt;0,"ข้อมูลไม่ครบ",IF(R23="","",IF(R23&gt;=DATA!$T$10,"สูง",IF(R23&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(U23&gt;0,"ข้อมูลไม่ครบ",IF(R23="","",IF(R23&gt;=DATA!$AC$10,"สูง",IF(R23&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T23" s="33">
@@ -5178,7 +5211,7 @@
         <v/>
       </c>
       <c r="U23" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",COUNTBLANK('1-UseCase ทั้งหมด'!I23)+COUNTBLANK('1-UseCase ทั้งหมด'!L23)+COUNTBLANK('1-UseCase ทั้งหมด'!M23)+COUNTBLANK('1-UseCase ทั้งหมด'!O23)+COUNTBLANK('1-UseCase ทั้งหมด'!P23)+COUNTBLANK('1-UseCase ทั้งหมด'!Q23)+COUNTBLANK('1-UseCase ทั้งหมด'!R23)+COUNTBLANK('1-UseCase ทั้งหมด'!S23)+COUNTBLANK('1-UseCase ทั้งหมด'!T23))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",COUNTBLANK('1-UseCase ทั้งหมด'!I23)+COUNTBLANK('1-UseCase ทั้งหมด'!J23)+COUNTBLANK('1-UseCase ทั้งหมด'!L23)+COUNTBLANK('1-UseCase ทั้งหมด'!M23)+COUNTBLANK('1-UseCase ทั้งหมด'!O23)+COUNTBLANK('1-UseCase ทั้งหมด'!P23)+COUNTBLANK('1-UseCase ทั้งหมด'!Q23)+COUNTBLANK('1-UseCase ทั้งหมด'!R23)+COUNTBLANK('1-UseCase ทั้งหมด'!S23)+COUNTBLANK('1-UseCase ทั้งหมด'!T23))</f>
         <v/>
       </c>
     </row>
@@ -5200,11 +5233,11 @@
         <v/>
       </c>
       <c r="E24" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF('1-UseCase ทั้งหมด'!J24="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J24,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J24,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F24" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(D24="",IF(E24="","",E24),IF(E24="",D24,ROUND((D24+E24)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(D24="",IF(AND(E24&lt;&gt;"",E24&lt;&gt;"-"),E24,""),IF(AND(E24&lt;&gt;"",E24&lt;&gt;"-"),ROUND((D24+E24)/2,0),D24)))</f>
         <v/>
       </c>
       <c r="G24" s="32">
@@ -5252,11 +5285,11 @@
         <v/>
       </c>
       <c r="R24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(U24&gt;0,"",IFERROR(ROUND((F24*DATA!$T$4+M24*DATA!$T$5+J24*DATA!$T$6+(6-Q24)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(U24&gt;0,"",IFERROR(ROUND((F24*DATA!$AC$4+M24*DATA!$AC$5+J24*DATA!$AC$6+(6-Q24)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S24" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(U24&gt;0,"ข้อมูลไม่ครบ",IF(R24="","",IF(R24&gt;=DATA!$T$10,"สูง",IF(R24&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(U24&gt;0,"ข้อมูลไม่ครบ",IF(R24="","",IF(R24&gt;=DATA!$AC$10,"สูง",IF(R24&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T24" s="33">
@@ -5264,7 +5297,7 @@
         <v/>
       </c>
       <c r="U24" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",COUNTBLANK('1-UseCase ทั้งหมด'!I24)+COUNTBLANK('1-UseCase ทั้งหมด'!L24)+COUNTBLANK('1-UseCase ทั้งหมด'!M24)+COUNTBLANK('1-UseCase ทั้งหมด'!O24)+COUNTBLANK('1-UseCase ทั้งหมด'!P24)+COUNTBLANK('1-UseCase ทั้งหมด'!Q24)+COUNTBLANK('1-UseCase ทั้งหมด'!R24)+COUNTBLANK('1-UseCase ทั้งหมด'!S24)+COUNTBLANK('1-UseCase ทั้งหมด'!T24))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",COUNTBLANK('1-UseCase ทั้งหมด'!I24)+COUNTBLANK('1-UseCase ทั้งหมด'!J24)+COUNTBLANK('1-UseCase ทั้งหมด'!L24)+COUNTBLANK('1-UseCase ทั้งหมด'!M24)+COUNTBLANK('1-UseCase ทั้งหมด'!O24)+COUNTBLANK('1-UseCase ทั้งหมด'!P24)+COUNTBLANK('1-UseCase ทั้งหมด'!Q24)+COUNTBLANK('1-UseCase ทั้งหมด'!R24)+COUNTBLANK('1-UseCase ทั้งหมด'!S24)+COUNTBLANK('1-UseCase ทั้งหมด'!T24))</f>
         <v/>
       </c>
     </row>
@@ -5286,11 +5319,11 @@
         <v/>
       </c>
       <c r="E25" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF('1-UseCase ทั้งหมด'!J25="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J25,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J25,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F25" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(D25="",IF(E25="","",E25),IF(E25="",D25,ROUND((D25+E25)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(D25="",IF(AND(E25&lt;&gt;"",E25&lt;&gt;"-"),E25,""),IF(AND(E25&lt;&gt;"",E25&lt;&gt;"-"),ROUND((D25+E25)/2,0),D25)))</f>
         <v/>
       </c>
       <c r="G25" s="32">
@@ -5338,11 +5371,11 @@
         <v/>
       </c>
       <c r="R25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(U25&gt;0,"",IFERROR(ROUND((F25*DATA!$T$4+M25*DATA!$T$5+J25*DATA!$T$6+(6-Q25)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(U25&gt;0,"",IFERROR(ROUND((F25*DATA!$AC$4+M25*DATA!$AC$5+J25*DATA!$AC$6+(6-Q25)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S25" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(U25&gt;0,"ข้อมูลไม่ครบ",IF(R25="","",IF(R25&gt;=DATA!$T$10,"สูง",IF(R25&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(U25&gt;0,"ข้อมูลไม่ครบ",IF(R25="","",IF(R25&gt;=DATA!$AC$10,"สูง",IF(R25&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T25" s="33">
@@ -5350,7 +5383,7 @@
         <v/>
       </c>
       <c r="U25" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",COUNTBLANK('1-UseCase ทั้งหมด'!I25)+COUNTBLANK('1-UseCase ทั้งหมด'!L25)+COUNTBLANK('1-UseCase ทั้งหมด'!M25)+COUNTBLANK('1-UseCase ทั้งหมด'!O25)+COUNTBLANK('1-UseCase ทั้งหมด'!P25)+COUNTBLANK('1-UseCase ทั้งหมด'!Q25)+COUNTBLANK('1-UseCase ทั้งหมด'!R25)+COUNTBLANK('1-UseCase ทั้งหมด'!S25)+COUNTBLANK('1-UseCase ทั้งหมด'!T25))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",COUNTBLANK('1-UseCase ทั้งหมด'!I25)+COUNTBLANK('1-UseCase ทั้งหมด'!J25)+COUNTBLANK('1-UseCase ทั้งหมด'!L25)+COUNTBLANK('1-UseCase ทั้งหมด'!M25)+COUNTBLANK('1-UseCase ทั้งหมด'!O25)+COUNTBLANK('1-UseCase ทั้งหมด'!P25)+COUNTBLANK('1-UseCase ทั้งหมด'!Q25)+COUNTBLANK('1-UseCase ทั้งหมด'!R25)+COUNTBLANK('1-UseCase ทั้งหมด'!S25)+COUNTBLANK('1-UseCase ทั้งหมด'!T25))</f>
         <v/>
       </c>
     </row>
@@ -5372,11 +5405,11 @@
         <v/>
       </c>
       <c r="E26" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF('1-UseCase ทั้งหมด'!J26="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J26,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J26,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F26" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(D26="",IF(E26="","",E26),IF(E26="",D26,ROUND((D26+E26)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(D26="",IF(AND(E26&lt;&gt;"",E26&lt;&gt;"-"),E26,""),IF(AND(E26&lt;&gt;"",E26&lt;&gt;"-"),ROUND((D26+E26)/2,0),D26)))</f>
         <v/>
       </c>
       <c r="G26" s="32">
@@ -5424,11 +5457,11 @@
         <v/>
       </c>
       <c r="R26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(U26&gt;0,"",IFERROR(ROUND((F26*DATA!$T$4+M26*DATA!$T$5+J26*DATA!$T$6+(6-Q26)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(U26&gt;0,"",IFERROR(ROUND((F26*DATA!$AC$4+M26*DATA!$AC$5+J26*DATA!$AC$6+(6-Q26)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S26" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(U26&gt;0,"ข้อมูลไม่ครบ",IF(R26="","",IF(R26&gt;=DATA!$T$10,"สูง",IF(R26&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(U26&gt;0,"ข้อมูลไม่ครบ",IF(R26="","",IF(R26&gt;=DATA!$AC$10,"สูง",IF(R26&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T26" s="33">
@@ -5436,7 +5469,7 @@
         <v/>
       </c>
       <c r="U26" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",COUNTBLANK('1-UseCase ทั้งหมด'!I26)+COUNTBLANK('1-UseCase ทั้งหมด'!L26)+COUNTBLANK('1-UseCase ทั้งหมด'!M26)+COUNTBLANK('1-UseCase ทั้งหมด'!O26)+COUNTBLANK('1-UseCase ทั้งหมด'!P26)+COUNTBLANK('1-UseCase ทั้งหมด'!Q26)+COUNTBLANK('1-UseCase ทั้งหมด'!R26)+COUNTBLANK('1-UseCase ทั้งหมด'!S26)+COUNTBLANK('1-UseCase ทั้งหมด'!T26))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",COUNTBLANK('1-UseCase ทั้งหมด'!I26)+COUNTBLANK('1-UseCase ทั้งหมด'!J26)+COUNTBLANK('1-UseCase ทั้งหมด'!L26)+COUNTBLANK('1-UseCase ทั้งหมด'!M26)+COUNTBLANK('1-UseCase ทั้งหมด'!O26)+COUNTBLANK('1-UseCase ทั้งหมด'!P26)+COUNTBLANK('1-UseCase ทั้งหมด'!Q26)+COUNTBLANK('1-UseCase ทั้งหมด'!R26)+COUNTBLANK('1-UseCase ทั้งหมด'!S26)+COUNTBLANK('1-UseCase ทั้งหมด'!T26))</f>
         <v/>
       </c>
     </row>
@@ -5458,11 +5491,11 @@
         <v/>
       </c>
       <c r="E27" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF('1-UseCase ทั้งหมด'!J27="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J27,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J27,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F27" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(D27="",IF(E27="","",E27),IF(E27="",D27,ROUND((D27+E27)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(D27="",IF(AND(E27&lt;&gt;"",E27&lt;&gt;"-"),E27,""),IF(AND(E27&lt;&gt;"",E27&lt;&gt;"-"),ROUND((D27+E27)/2,0),D27)))</f>
         <v/>
       </c>
       <c r="G27" s="32">
@@ -5510,11 +5543,11 @@
         <v/>
       </c>
       <c r="R27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(U27&gt;0,"",IFERROR(ROUND((F27*DATA!$T$4+M27*DATA!$T$5+J27*DATA!$T$6+(6-Q27)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(U27&gt;0,"",IFERROR(ROUND((F27*DATA!$AC$4+M27*DATA!$AC$5+J27*DATA!$AC$6+(6-Q27)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S27" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(U27&gt;0,"ข้อมูลไม่ครบ",IF(R27="","",IF(R27&gt;=DATA!$T$10,"สูง",IF(R27&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(U27&gt;0,"ข้อมูลไม่ครบ",IF(R27="","",IF(R27&gt;=DATA!$AC$10,"สูง",IF(R27&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T27" s="33">
@@ -5522,7 +5555,7 @@
         <v/>
       </c>
       <c r="U27" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",COUNTBLANK('1-UseCase ทั้งหมด'!I27)+COUNTBLANK('1-UseCase ทั้งหมด'!L27)+COUNTBLANK('1-UseCase ทั้งหมด'!M27)+COUNTBLANK('1-UseCase ทั้งหมด'!O27)+COUNTBLANK('1-UseCase ทั้งหมด'!P27)+COUNTBLANK('1-UseCase ทั้งหมด'!Q27)+COUNTBLANK('1-UseCase ทั้งหมด'!R27)+COUNTBLANK('1-UseCase ทั้งหมด'!S27)+COUNTBLANK('1-UseCase ทั้งหมด'!T27))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",COUNTBLANK('1-UseCase ทั้งหมด'!I27)+COUNTBLANK('1-UseCase ทั้งหมด'!J27)+COUNTBLANK('1-UseCase ทั้งหมด'!L27)+COUNTBLANK('1-UseCase ทั้งหมด'!M27)+COUNTBLANK('1-UseCase ทั้งหมด'!O27)+COUNTBLANK('1-UseCase ทั้งหมด'!P27)+COUNTBLANK('1-UseCase ทั้งหมด'!Q27)+COUNTBLANK('1-UseCase ทั้งหมด'!R27)+COUNTBLANK('1-UseCase ทั้งหมด'!S27)+COUNTBLANK('1-UseCase ทั้งหมด'!T27))</f>
         <v/>
       </c>
     </row>
@@ -5544,11 +5577,11 @@
         <v/>
       </c>
       <c r="E28" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF('1-UseCase ทั้งหมด'!J28="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J28,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J28,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F28" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(D28="",IF(E28="","",E28),IF(E28="",D28,ROUND((D28+E28)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(D28="",IF(AND(E28&lt;&gt;"",E28&lt;&gt;"-"),E28,""),IF(AND(E28&lt;&gt;"",E28&lt;&gt;"-"),ROUND((D28+E28)/2,0),D28)))</f>
         <v/>
       </c>
       <c r="G28" s="32">
@@ -5596,11 +5629,11 @@
         <v/>
       </c>
       <c r="R28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(U28&gt;0,"",IFERROR(ROUND((F28*DATA!$T$4+M28*DATA!$T$5+J28*DATA!$T$6+(6-Q28)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(U28&gt;0,"",IFERROR(ROUND((F28*DATA!$AC$4+M28*DATA!$AC$5+J28*DATA!$AC$6+(6-Q28)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S28" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(U28&gt;0,"ข้อมูลไม่ครบ",IF(R28="","",IF(R28&gt;=DATA!$T$10,"สูง",IF(R28&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(U28&gt;0,"ข้อมูลไม่ครบ",IF(R28="","",IF(R28&gt;=DATA!$AC$10,"สูง",IF(R28&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T28" s="33">
@@ -5608,7 +5641,7 @@
         <v/>
       </c>
       <c r="U28" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",COUNTBLANK('1-UseCase ทั้งหมด'!I28)+COUNTBLANK('1-UseCase ทั้งหมด'!L28)+COUNTBLANK('1-UseCase ทั้งหมด'!M28)+COUNTBLANK('1-UseCase ทั้งหมด'!O28)+COUNTBLANK('1-UseCase ทั้งหมด'!P28)+COUNTBLANK('1-UseCase ทั้งหมด'!Q28)+COUNTBLANK('1-UseCase ทั้งหมด'!R28)+COUNTBLANK('1-UseCase ทั้งหมด'!S28)+COUNTBLANK('1-UseCase ทั้งหมด'!T28))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",COUNTBLANK('1-UseCase ทั้งหมด'!I28)+COUNTBLANK('1-UseCase ทั้งหมด'!J28)+COUNTBLANK('1-UseCase ทั้งหมด'!L28)+COUNTBLANK('1-UseCase ทั้งหมด'!M28)+COUNTBLANK('1-UseCase ทั้งหมด'!O28)+COUNTBLANK('1-UseCase ทั้งหมด'!P28)+COUNTBLANK('1-UseCase ทั้งหมด'!Q28)+COUNTBLANK('1-UseCase ทั้งหมด'!R28)+COUNTBLANK('1-UseCase ทั้งหมด'!S28)+COUNTBLANK('1-UseCase ทั้งหมด'!T28))</f>
         <v/>
       </c>
     </row>
@@ -5630,11 +5663,11 @@
         <v/>
       </c>
       <c r="E29" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF('1-UseCase ทั้งหมด'!J29="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J29,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J29,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F29" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(D29="",IF(E29="","",E29),IF(E29="",D29,ROUND((D29+E29)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(D29="",IF(AND(E29&lt;&gt;"",E29&lt;&gt;"-"),E29,""),IF(AND(E29&lt;&gt;"",E29&lt;&gt;"-"),ROUND((D29+E29)/2,0),D29)))</f>
         <v/>
       </c>
       <c r="G29" s="32">
@@ -5682,11 +5715,11 @@
         <v/>
       </c>
       <c r="R29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(U29&gt;0,"",IFERROR(ROUND((F29*DATA!$T$4+M29*DATA!$T$5+J29*DATA!$T$6+(6-Q29)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(U29&gt;0,"",IFERROR(ROUND((F29*DATA!$AC$4+M29*DATA!$AC$5+J29*DATA!$AC$6+(6-Q29)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S29" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(U29&gt;0,"ข้อมูลไม่ครบ",IF(R29="","",IF(R29&gt;=DATA!$T$10,"สูง",IF(R29&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(U29&gt;0,"ข้อมูลไม่ครบ",IF(R29="","",IF(R29&gt;=DATA!$AC$10,"สูง",IF(R29&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T29" s="33">
@@ -5694,7 +5727,7 @@
         <v/>
       </c>
       <c r="U29" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",COUNTBLANK('1-UseCase ทั้งหมด'!I29)+COUNTBLANK('1-UseCase ทั้งหมด'!L29)+COUNTBLANK('1-UseCase ทั้งหมด'!M29)+COUNTBLANK('1-UseCase ทั้งหมด'!O29)+COUNTBLANK('1-UseCase ทั้งหมด'!P29)+COUNTBLANK('1-UseCase ทั้งหมด'!Q29)+COUNTBLANK('1-UseCase ทั้งหมด'!R29)+COUNTBLANK('1-UseCase ทั้งหมด'!S29)+COUNTBLANK('1-UseCase ทั้งหมด'!T29))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",COUNTBLANK('1-UseCase ทั้งหมด'!I29)+COUNTBLANK('1-UseCase ทั้งหมด'!J29)+COUNTBLANK('1-UseCase ทั้งหมด'!L29)+COUNTBLANK('1-UseCase ทั้งหมด'!M29)+COUNTBLANK('1-UseCase ทั้งหมด'!O29)+COUNTBLANK('1-UseCase ทั้งหมด'!P29)+COUNTBLANK('1-UseCase ทั้งหมด'!Q29)+COUNTBLANK('1-UseCase ทั้งหมด'!R29)+COUNTBLANK('1-UseCase ทั้งหมด'!S29)+COUNTBLANK('1-UseCase ทั้งหมด'!T29))</f>
         <v/>
       </c>
     </row>
@@ -5716,11 +5749,11 @@
         <v/>
       </c>
       <c r="E30" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF('1-UseCase ทั้งหมด'!J30="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J30,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J30,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F30" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(D30="",IF(E30="","",E30),IF(E30="",D30,ROUND((D30+E30)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(D30="",IF(AND(E30&lt;&gt;"",E30&lt;&gt;"-"),E30,""),IF(AND(E30&lt;&gt;"",E30&lt;&gt;"-"),ROUND((D30+E30)/2,0),D30)))</f>
         <v/>
       </c>
       <c r="G30" s="32">
@@ -5768,11 +5801,11 @@
         <v/>
       </c>
       <c r="R30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(U30&gt;0,"",IFERROR(ROUND((F30*DATA!$T$4+M30*DATA!$T$5+J30*DATA!$T$6+(6-Q30)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(U30&gt;0,"",IFERROR(ROUND((F30*DATA!$AC$4+M30*DATA!$AC$5+J30*DATA!$AC$6+(6-Q30)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S30" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(U30&gt;0,"ข้อมูลไม่ครบ",IF(R30="","",IF(R30&gt;=DATA!$T$10,"สูง",IF(R30&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(U30&gt;0,"ข้อมูลไม่ครบ",IF(R30="","",IF(R30&gt;=DATA!$AC$10,"สูง",IF(R30&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T30" s="33">
@@ -5780,7 +5813,7 @@
         <v/>
       </c>
       <c r="U30" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",COUNTBLANK('1-UseCase ทั้งหมด'!I30)+COUNTBLANK('1-UseCase ทั้งหมด'!L30)+COUNTBLANK('1-UseCase ทั้งหมด'!M30)+COUNTBLANK('1-UseCase ทั้งหมด'!O30)+COUNTBLANK('1-UseCase ทั้งหมด'!P30)+COUNTBLANK('1-UseCase ทั้งหมด'!Q30)+COUNTBLANK('1-UseCase ทั้งหมด'!R30)+COUNTBLANK('1-UseCase ทั้งหมด'!S30)+COUNTBLANK('1-UseCase ทั้งหมด'!T30))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",COUNTBLANK('1-UseCase ทั้งหมด'!I30)+COUNTBLANK('1-UseCase ทั้งหมด'!J30)+COUNTBLANK('1-UseCase ทั้งหมด'!L30)+COUNTBLANK('1-UseCase ทั้งหมด'!M30)+COUNTBLANK('1-UseCase ทั้งหมด'!O30)+COUNTBLANK('1-UseCase ทั้งหมด'!P30)+COUNTBLANK('1-UseCase ทั้งหมด'!Q30)+COUNTBLANK('1-UseCase ทั้งหมด'!R30)+COUNTBLANK('1-UseCase ทั้งหมด'!S30)+COUNTBLANK('1-UseCase ทั้งหมด'!T30))</f>
         <v/>
       </c>
     </row>
@@ -5802,11 +5835,11 @@
         <v/>
       </c>
       <c r="E31" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF('1-UseCase ทั้งหมด'!J31="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J31,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J31,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F31" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(D31="",IF(E31="","",E31),IF(E31="",D31,ROUND((D31+E31)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(D31="",IF(AND(E31&lt;&gt;"",E31&lt;&gt;"-"),E31,""),IF(AND(E31&lt;&gt;"",E31&lt;&gt;"-"),ROUND((D31+E31)/2,0),D31)))</f>
         <v/>
       </c>
       <c r="G31" s="32">
@@ -5854,11 +5887,11 @@
         <v/>
       </c>
       <c r="R31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(U31&gt;0,"",IFERROR(ROUND((F31*DATA!$T$4+M31*DATA!$T$5+J31*DATA!$T$6+(6-Q31)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(U31&gt;0,"",IFERROR(ROUND((F31*DATA!$AC$4+M31*DATA!$AC$5+J31*DATA!$AC$6+(6-Q31)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S31" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(U31&gt;0,"ข้อมูลไม่ครบ",IF(R31="","",IF(R31&gt;=DATA!$T$10,"สูง",IF(R31&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(U31&gt;0,"ข้อมูลไม่ครบ",IF(R31="","",IF(R31&gt;=DATA!$AC$10,"สูง",IF(R31&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T31" s="33">
@@ -5866,7 +5899,7 @@
         <v/>
       </c>
       <c r="U31" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",COUNTBLANK('1-UseCase ทั้งหมด'!I31)+COUNTBLANK('1-UseCase ทั้งหมด'!L31)+COUNTBLANK('1-UseCase ทั้งหมด'!M31)+COUNTBLANK('1-UseCase ทั้งหมด'!O31)+COUNTBLANK('1-UseCase ทั้งหมด'!P31)+COUNTBLANK('1-UseCase ทั้งหมด'!Q31)+COUNTBLANK('1-UseCase ทั้งหมด'!R31)+COUNTBLANK('1-UseCase ทั้งหมด'!S31)+COUNTBLANK('1-UseCase ทั้งหมด'!T31))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",COUNTBLANK('1-UseCase ทั้งหมด'!I31)+COUNTBLANK('1-UseCase ทั้งหมด'!J31)+COUNTBLANK('1-UseCase ทั้งหมด'!L31)+COUNTBLANK('1-UseCase ทั้งหมด'!M31)+COUNTBLANK('1-UseCase ทั้งหมด'!O31)+COUNTBLANK('1-UseCase ทั้งหมด'!P31)+COUNTBLANK('1-UseCase ทั้งหมด'!Q31)+COUNTBLANK('1-UseCase ทั้งหมด'!R31)+COUNTBLANK('1-UseCase ทั้งหมด'!S31)+COUNTBLANK('1-UseCase ทั้งหมด'!T31))</f>
         <v/>
       </c>
     </row>
@@ -5888,11 +5921,11 @@
         <v/>
       </c>
       <c r="E32" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF('1-UseCase ทั้งหมด'!J32="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J32,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J32,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F32" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(D32="",IF(E32="","",E32),IF(E32="",D32,ROUND((D32+E32)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(D32="",IF(AND(E32&lt;&gt;"",E32&lt;&gt;"-"),E32,""),IF(AND(E32&lt;&gt;"",E32&lt;&gt;"-"),ROUND((D32+E32)/2,0),D32)))</f>
         <v/>
       </c>
       <c r="G32" s="32">
@@ -5940,11 +5973,11 @@
         <v/>
       </c>
       <c r="R32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(U32&gt;0,"",IFERROR(ROUND((F32*DATA!$T$4+M32*DATA!$T$5+J32*DATA!$T$6+(6-Q32)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(U32&gt;0,"",IFERROR(ROUND((F32*DATA!$AC$4+M32*DATA!$AC$5+J32*DATA!$AC$6+(6-Q32)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S32" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(U32&gt;0,"ข้อมูลไม่ครบ",IF(R32="","",IF(R32&gt;=DATA!$T$10,"สูง",IF(R32&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(U32&gt;0,"ข้อมูลไม่ครบ",IF(R32="","",IF(R32&gt;=DATA!$AC$10,"สูง",IF(R32&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T32" s="33">
@@ -5952,7 +5985,7 @@
         <v/>
       </c>
       <c r="U32" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",COUNTBLANK('1-UseCase ทั้งหมด'!I32)+COUNTBLANK('1-UseCase ทั้งหมด'!L32)+COUNTBLANK('1-UseCase ทั้งหมด'!M32)+COUNTBLANK('1-UseCase ทั้งหมด'!O32)+COUNTBLANK('1-UseCase ทั้งหมด'!P32)+COUNTBLANK('1-UseCase ทั้งหมด'!Q32)+COUNTBLANK('1-UseCase ทั้งหมด'!R32)+COUNTBLANK('1-UseCase ทั้งหมด'!S32)+COUNTBLANK('1-UseCase ทั้งหมด'!T32))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",COUNTBLANK('1-UseCase ทั้งหมด'!I32)+COUNTBLANK('1-UseCase ทั้งหมด'!J32)+COUNTBLANK('1-UseCase ทั้งหมด'!L32)+COUNTBLANK('1-UseCase ทั้งหมด'!M32)+COUNTBLANK('1-UseCase ทั้งหมด'!O32)+COUNTBLANK('1-UseCase ทั้งหมด'!P32)+COUNTBLANK('1-UseCase ทั้งหมด'!Q32)+COUNTBLANK('1-UseCase ทั้งหมด'!R32)+COUNTBLANK('1-UseCase ทั้งหมด'!S32)+COUNTBLANK('1-UseCase ทั้งหมด'!T32))</f>
         <v/>
       </c>
     </row>
@@ -5974,11 +6007,11 @@
         <v/>
       </c>
       <c r="E33" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF('1-UseCase ทั้งหมด'!J33="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J33,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J33,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F33" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(D33="",IF(E33="","",E33),IF(E33="",D33,ROUND((D33+E33)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(D33="",IF(AND(E33&lt;&gt;"",E33&lt;&gt;"-"),E33,""),IF(AND(E33&lt;&gt;"",E33&lt;&gt;"-"),ROUND((D33+E33)/2,0),D33)))</f>
         <v/>
       </c>
       <c r="G33" s="32">
@@ -6026,11 +6059,11 @@
         <v/>
       </c>
       <c r="R33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(U33&gt;0,"",IFERROR(ROUND((F33*DATA!$T$4+M33*DATA!$T$5+J33*DATA!$T$6+(6-Q33)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(U33&gt;0,"",IFERROR(ROUND((F33*DATA!$AC$4+M33*DATA!$AC$5+J33*DATA!$AC$6+(6-Q33)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S33" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(U33&gt;0,"ข้อมูลไม่ครบ",IF(R33="","",IF(R33&gt;=DATA!$T$10,"สูง",IF(R33&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(U33&gt;0,"ข้อมูลไม่ครบ",IF(R33="","",IF(R33&gt;=DATA!$AC$10,"สูง",IF(R33&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T33" s="33">
@@ -6038,7 +6071,7 @@
         <v/>
       </c>
       <c r="U33" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",COUNTBLANK('1-UseCase ทั้งหมด'!I33)+COUNTBLANK('1-UseCase ทั้งหมด'!L33)+COUNTBLANK('1-UseCase ทั้งหมด'!M33)+COUNTBLANK('1-UseCase ทั้งหมด'!O33)+COUNTBLANK('1-UseCase ทั้งหมด'!P33)+COUNTBLANK('1-UseCase ทั้งหมด'!Q33)+COUNTBLANK('1-UseCase ทั้งหมด'!R33)+COUNTBLANK('1-UseCase ทั้งหมด'!S33)+COUNTBLANK('1-UseCase ทั้งหมด'!T33))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",COUNTBLANK('1-UseCase ทั้งหมด'!I33)+COUNTBLANK('1-UseCase ทั้งหมด'!J33)+COUNTBLANK('1-UseCase ทั้งหมด'!L33)+COUNTBLANK('1-UseCase ทั้งหมด'!M33)+COUNTBLANK('1-UseCase ทั้งหมด'!O33)+COUNTBLANK('1-UseCase ทั้งหมด'!P33)+COUNTBLANK('1-UseCase ทั้งหมด'!Q33)+COUNTBLANK('1-UseCase ทั้งหมด'!R33)+COUNTBLANK('1-UseCase ทั้งหมด'!S33)+COUNTBLANK('1-UseCase ทั้งหมด'!T33))</f>
         <v/>
       </c>
     </row>
@@ -6060,11 +6093,11 @@
         <v/>
       </c>
       <c r="E34" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF('1-UseCase ทั้งหมด'!J34="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J34,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J34,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F34" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(D34="",IF(E34="","",E34),IF(E34="",D34,ROUND((D34+E34)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(D34="",IF(AND(E34&lt;&gt;"",E34&lt;&gt;"-"),E34,""),IF(AND(E34&lt;&gt;"",E34&lt;&gt;"-"),ROUND((D34+E34)/2,0),D34)))</f>
         <v/>
       </c>
       <c r="G34" s="32">
@@ -6112,11 +6145,11 @@
         <v/>
       </c>
       <c r="R34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(U34&gt;0,"",IFERROR(ROUND((F34*DATA!$T$4+M34*DATA!$T$5+J34*DATA!$T$6+(6-Q34)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(U34&gt;0,"",IFERROR(ROUND((F34*DATA!$AC$4+M34*DATA!$AC$5+J34*DATA!$AC$6+(6-Q34)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S34" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(U34&gt;0,"ข้อมูลไม่ครบ",IF(R34="","",IF(R34&gt;=DATA!$T$10,"สูง",IF(R34&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(U34&gt;0,"ข้อมูลไม่ครบ",IF(R34="","",IF(R34&gt;=DATA!$AC$10,"สูง",IF(R34&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T34" s="33">
@@ -6124,7 +6157,7 @@
         <v/>
       </c>
       <c r="U34" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",COUNTBLANK('1-UseCase ทั้งหมด'!I34)+COUNTBLANK('1-UseCase ทั้งหมด'!L34)+COUNTBLANK('1-UseCase ทั้งหมด'!M34)+COUNTBLANK('1-UseCase ทั้งหมด'!O34)+COUNTBLANK('1-UseCase ทั้งหมด'!P34)+COUNTBLANK('1-UseCase ทั้งหมด'!Q34)+COUNTBLANK('1-UseCase ทั้งหมด'!R34)+COUNTBLANK('1-UseCase ทั้งหมด'!S34)+COUNTBLANK('1-UseCase ทั้งหมด'!T34))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",COUNTBLANK('1-UseCase ทั้งหมด'!I34)+COUNTBLANK('1-UseCase ทั้งหมด'!J34)+COUNTBLANK('1-UseCase ทั้งหมด'!L34)+COUNTBLANK('1-UseCase ทั้งหมด'!M34)+COUNTBLANK('1-UseCase ทั้งหมด'!O34)+COUNTBLANK('1-UseCase ทั้งหมด'!P34)+COUNTBLANK('1-UseCase ทั้งหมด'!Q34)+COUNTBLANK('1-UseCase ทั้งหมด'!R34)+COUNTBLANK('1-UseCase ทั้งหมด'!S34)+COUNTBLANK('1-UseCase ทั้งหมด'!T34))</f>
         <v/>
       </c>
     </row>
@@ -6146,11 +6179,11 @@
         <v/>
       </c>
       <c r="E35" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF('1-UseCase ทั้งหมด'!J35="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J35,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J35,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F35" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(D35="",IF(E35="","",E35),IF(E35="",D35,ROUND((D35+E35)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(D35="",IF(AND(E35&lt;&gt;"",E35&lt;&gt;"-"),E35,""),IF(AND(E35&lt;&gt;"",E35&lt;&gt;"-"),ROUND((D35+E35)/2,0),D35)))</f>
         <v/>
       </c>
       <c r="G35" s="32">
@@ -6198,11 +6231,11 @@
         <v/>
       </c>
       <c r="R35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(U35&gt;0,"",IFERROR(ROUND((F35*DATA!$T$4+M35*DATA!$T$5+J35*DATA!$T$6+(6-Q35)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(U35&gt;0,"",IFERROR(ROUND((F35*DATA!$AC$4+M35*DATA!$AC$5+J35*DATA!$AC$6+(6-Q35)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S35" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(U35&gt;0,"ข้อมูลไม่ครบ",IF(R35="","",IF(R35&gt;=DATA!$T$10,"สูง",IF(R35&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(U35&gt;0,"ข้อมูลไม่ครบ",IF(R35="","",IF(R35&gt;=DATA!$AC$10,"สูง",IF(R35&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T35" s="33">
@@ -6210,7 +6243,7 @@
         <v/>
       </c>
       <c r="U35" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",COUNTBLANK('1-UseCase ทั้งหมด'!I35)+COUNTBLANK('1-UseCase ทั้งหมด'!L35)+COUNTBLANK('1-UseCase ทั้งหมด'!M35)+COUNTBLANK('1-UseCase ทั้งหมด'!O35)+COUNTBLANK('1-UseCase ทั้งหมด'!P35)+COUNTBLANK('1-UseCase ทั้งหมด'!Q35)+COUNTBLANK('1-UseCase ทั้งหมด'!R35)+COUNTBLANK('1-UseCase ทั้งหมด'!S35)+COUNTBLANK('1-UseCase ทั้งหมด'!T35))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",COUNTBLANK('1-UseCase ทั้งหมด'!I35)+COUNTBLANK('1-UseCase ทั้งหมด'!J35)+COUNTBLANK('1-UseCase ทั้งหมด'!L35)+COUNTBLANK('1-UseCase ทั้งหมด'!M35)+COUNTBLANK('1-UseCase ทั้งหมด'!O35)+COUNTBLANK('1-UseCase ทั้งหมด'!P35)+COUNTBLANK('1-UseCase ทั้งหมด'!Q35)+COUNTBLANK('1-UseCase ทั้งหมด'!R35)+COUNTBLANK('1-UseCase ทั้งหมด'!S35)+COUNTBLANK('1-UseCase ทั้งหมด'!T35))</f>
         <v/>
       </c>
     </row>
@@ -6232,11 +6265,11 @@
         <v/>
       </c>
       <c r="E36" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF('1-UseCase ทั้งหมด'!J36="","",IFERROR(MATCH('1-UseCase ทั้งหมด'!J36,DATA!$S$25:$S$29,1),1)))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J36,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F36" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(D36="",IF(E36="","",E36),IF(E36="",D36,ROUND((D36+E36)/2,0))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(D36="",IF(AND(E36&lt;&gt;"",E36&lt;&gt;"-"),E36,""),IF(AND(E36&lt;&gt;"",E36&lt;&gt;"-"),ROUND((D36+E36)/2,0),D36)))</f>
         <v/>
       </c>
       <c r="G36" s="32">
@@ -6284,11 +6317,11 @@
         <v/>
       </c>
       <c r="R36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(U36&gt;0,"",IFERROR(ROUND((F36*DATA!$T$4+M36*DATA!$T$5+J36*DATA!$T$6+(6-Q36)*DATA!$T$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(U36&gt;0,"",IFERROR(ROUND((F36*DATA!$AC$4+M36*DATA!$AC$5+J36*DATA!$AC$6+(6-Q36)*DATA!$AC$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S36" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(U36&gt;0,"ข้อมูลไม่ครบ",IF(R36="","",IF(R36&gt;=DATA!$T$10,"สูง",IF(R36&gt;=DATA!$T$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(U36&gt;0,"ข้อมูลไม่ครบ",IF(R36="","",IF(R36&gt;=DATA!$AC$10,"สูง",IF(R36&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T36" s="33">
@@ -6296,7 +6329,7 @@
         <v/>
       </c>
       <c r="U36" s="32">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",COUNTBLANK('1-UseCase ทั้งหมด'!I36)+COUNTBLANK('1-UseCase ทั้งหมด'!L36)+COUNTBLANK('1-UseCase ทั้งหมด'!M36)+COUNTBLANK('1-UseCase ทั้งหมด'!O36)+COUNTBLANK('1-UseCase ทั้งหมด'!P36)+COUNTBLANK('1-UseCase ทั้งหมด'!Q36)+COUNTBLANK('1-UseCase ทั้งหมด'!R36)+COUNTBLANK('1-UseCase ทั้งหมด'!S36)+COUNTBLANK('1-UseCase ทั้งหมด'!T36))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",COUNTBLANK('1-UseCase ทั้งหมด'!I36)+COUNTBLANK('1-UseCase ทั้งหมด'!J36)+COUNTBLANK('1-UseCase ทั้งหมด'!L36)+COUNTBLANK('1-UseCase ทั้งหมด'!M36)+COUNTBLANK('1-UseCase ทั้งหมด'!O36)+COUNTBLANK('1-UseCase ทั้งหมด'!P36)+COUNTBLANK('1-UseCase ทั้งหมด'!Q36)+COUNTBLANK('1-UseCase ทั้งหมด'!R36)+COUNTBLANK('1-UseCase ทั้งหมด'!S36)+COUNTBLANK('1-UseCase ทั้งหมด'!T36))</f>
         <v/>
       </c>
     </row>
@@ -6338,26 +6371,33 @@
     <row r="43">
       <c r="A43" s="36" t="inlineStr">
         <is>
-          <t>•  ช่องบังคับ 9 ช่อง = เวลาที่ใช้ / รูปแบบข้อมูล / ข้อมูลย้อนหลัง / สิทธิ์ใช้ข้อมูล / ระบบเดิม / คนดูแลต่อ / ผลกระทบถ้า AI ผิด / การตรวจซ้ำ / ระดับความลับ   (มูลค่าความเสียหายไม่บังคับ)</t>
+          <t>•  ช่องบังคับ 10 ช่อง = เวลาที่ใช้ / มูลค่าความเสียหาย / รูปแบบข้อมูล / ข้อมูลย้อนหลัง / สิทธิ์ใช้ข้อมูล / ระบบเดิม / คนดูแลต่อ / ผลกระทบถ้า AI ผิด / การตรวจซ้ำ / ระดับความลับ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="36" t="inlineStr">
         <is>
-          <t>•  คะแนนนี้เป็นตัวช่วยกรองเบื้องต้น ไม่ใช่คำตอบสุดท้าย — ผู้บริหารควรพิจารณา Use Case อันดับต้นๆ ด้วยตนเองอีกครั้ง</t>
+          <t>•  ถ้าตีมูลค่าความเสียหายเป็นเงินไม่ได้ ให้เลือก 'ประเมินเป็นเงินไม่ได้' — ระบบจะใช้เฉพาะชั่วโมงคิด Impact ไม่ได้หักคะแนน (ในตารางจะขึ้นเป็น '-')</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="36" t="inlineStr">
         <is>
+          <t>•  คะแนนนี้เป็นตัวช่วยกรองเบื้องต้น ไม่ใช่คำตอบสุดท้าย — ผู้บริหารควรพิจารณา Use Case อันดับต้นๆ ด้วยตนเองอีกครั้ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="36" t="inlineStr">
+        <is>
           <t>•  ค่าเกณฑ์ชั่วโมง/มูลค่า และน้ำหนักทุกตัว แก้ได้ที่ sheet DATA คอลัมน์ S-T (ตัวเลขสีน้ำเงิน)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A39:U39"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A38:U38"/>
@@ -6371,6 +6411,7 @@
     <mergeCell ref="N4:Q4"/>
     <mergeCell ref="A42:U42"/>
     <mergeCell ref="A45:U45"/>
+    <mergeCell ref="A46:U46"/>
     <mergeCell ref="A44:U44"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A40:U40"/>
@@ -6407,7 +6448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6428,8 +6469,15 @@
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="32" customWidth="1" min="17" max="17"/>
     <col width="44" customWidth="1" min="18" max="18"/>
-    <col width="30" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="19" max="19"/>
+    <col width="32" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="32" customWidth="1" min="22" max="22"/>
+    <col width="32" customWidth="1" min="23" max="23"/>
+    <col width="32" customWidth="1" min="24" max="24"/>
+    <col width="32" customWidth="1" min="25" max="25"/>
+    <col width="34" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6438,7 +6486,7 @@
           <t>รายการตัวเลือก (Dropdown) — เพิ่ม/แก้ตัวเลือกได้ที่นี่ แล้วทุก sheet จะเปลี่ยนตาม</t>
         </is>
       </c>
-      <c r="S1" s="37" t="inlineStr">
+      <c r="AB1" s="37" t="inlineStr">
         <is>
           <t>ค่าตั้งต้นของการคำนวณคะแนน (แก้ได้ ทุกสูตรจะเปลี่ยนตาม)</t>
         </is>
@@ -6535,7 +6583,42 @@
           <t>เวลาที่ใช้กับงานนี้ตอนนี้</t>
         </is>
       </c>
-      <c r="S3" s="39" t="inlineStr">
+      <c r="S3" s="38" t="inlineStr">
+        <is>
+          <t>มูลค่าความเสียหาย/ของเสียต่อปี</t>
+        </is>
+      </c>
+      <c r="T3" s="38" t="inlineStr">
+        <is>
+          <t>จำนวน Users/วัน</t>
+        </is>
+      </c>
+      <c r="U3" s="38" t="inlineStr">
+        <is>
+          <t>Peak concurrent (คนใช้พร้อมกันสูงสุด)</t>
+        </is>
+      </c>
+      <c r="V3" s="38" t="inlineStr">
+        <is>
+          <t>Requests/วัน</t>
+        </is>
+      </c>
+      <c r="W3" s="38" t="inlineStr">
+        <is>
+          <t>ขนาดข้อมูล Input/วัน</t>
+        </is>
+      </c>
+      <c r="X3" s="38" t="inlineStr">
+        <is>
+          <t>ขนาดคลังเอกสารทั้งหมด (RAG)</t>
+        </is>
+      </c>
+      <c r="Y3" s="38" t="inlineStr">
+        <is>
+          <t>จำนวนรูป/วัน</t>
+        </is>
+      </c>
+      <c r="AB3" s="39" t="inlineStr">
         <is>
           <t>น้ำหนักแต่ละปัจจัย</t>
         </is>
@@ -6634,10 +6717,45 @@
       </c>
       <c r="S4" s="40" t="inlineStr">
         <is>
+          <t>ประเมินเป็นเงินไม่ได้ / ไม่มีความเสียหายโดยตรง</t>
+        </is>
+      </c>
+      <c r="T4" s="40" t="inlineStr">
+        <is>
+          <t>1 - 10 คน</t>
+        </is>
+      </c>
+      <c r="U4" s="40" t="inlineStr">
+        <is>
+          <t>1 - 2 คน</t>
+        </is>
+      </c>
+      <c r="V4" s="40" t="inlineStr">
+        <is>
+          <t>น้อยกว่า 100 ครั้ง</t>
+        </is>
+      </c>
+      <c r="W4" s="40" t="inlineStr">
+        <is>
+          <t>น้อยกว่า 1 GB</t>
+        </is>
+      </c>
+      <c r="X4" s="40" t="inlineStr">
+        <is>
+          <t>ไม่เกี่ยวข้อง - ไม่ใช่งานค้นหาเอกสาร</t>
+        </is>
+      </c>
+      <c r="Y4" s="40" t="inlineStr">
+        <is>
+          <t>ไม่เกี่ยวข้อง - ไม่ใช่งานภาพ</t>
+        </is>
+      </c>
+      <c r="AB4" s="40" t="inlineStr">
+        <is>
           <t>Impact (ผลกระทบ)</t>
         </is>
       </c>
-      <c r="T4" s="41" t="n">
+      <c r="AC4" s="41" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -6734,10 +6852,45 @@
       </c>
       <c r="S5" s="40" t="inlineStr">
         <is>
+          <t>น้อยกว่า 1 แสนบาท/ปี</t>
+        </is>
+      </c>
+      <c r="T5" s="40" t="inlineStr">
+        <is>
+          <t>11 - 50 คน</t>
+        </is>
+      </c>
+      <c r="U5" s="40" t="inlineStr">
+        <is>
+          <t>3 - 5 คน</t>
+        </is>
+      </c>
+      <c r="V5" s="40" t="inlineStr">
+        <is>
+          <t>100 - 1,000 ครั้ง</t>
+        </is>
+      </c>
+      <c r="W5" s="40" t="inlineStr">
+        <is>
+          <t>1 - 10 GB</t>
+        </is>
+      </c>
+      <c r="X5" s="40" t="inlineStr">
+        <is>
+          <t>น้อยกว่า 1 GB</t>
+        </is>
+      </c>
+      <c r="Y5" s="40" t="inlineStr">
+        <is>
+          <t>น้อยกว่า 100 รูป</t>
+        </is>
+      </c>
+      <c r="AB5" s="40" t="inlineStr">
+        <is>
           <t>Feasibility (ความเป็นไปได้)</t>
         </is>
       </c>
-      <c r="T5" s="41" t="n">
+      <c r="AC5" s="41" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -6834,10 +6987,45 @@
       </c>
       <c r="S6" s="40" t="inlineStr">
         <is>
+          <t>1 - 5 แสนบาท/ปี</t>
+        </is>
+      </c>
+      <c r="T6" s="40" t="inlineStr">
+        <is>
+          <t>51 - 200 คน</t>
+        </is>
+      </c>
+      <c r="U6" s="40" t="inlineStr">
+        <is>
+          <t>6 - 20 คน</t>
+        </is>
+      </c>
+      <c r="V6" s="40" t="inlineStr">
+        <is>
+          <t>1,000 - 10,000 ครั้ง</t>
+        </is>
+      </c>
+      <c r="W6" s="40" t="inlineStr">
+        <is>
+          <t>10 - 100 GB</t>
+        </is>
+      </c>
+      <c r="X6" s="40" t="inlineStr">
+        <is>
+          <t>1 - 10 GB</t>
+        </is>
+      </c>
+      <c r="Y6" s="40" t="inlineStr">
+        <is>
+          <t>100 - 1,000 รูป</t>
+        </is>
+      </c>
+      <c r="AB6" s="40" t="inlineStr">
+        <is>
           <t>Data (ความพร้อมข้อมูล)</t>
         </is>
       </c>
-      <c r="T6" s="41" t="n">
+      <c r="AC6" s="41" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -6889,10 +7077,45 @@
       </c>
       <c r="S7" s="40" t="inlineStr">
         <is>
+          <t>5 แสน - 2 ล้านบาท/ปี</t>
+        </is>
+      </c>
+      <c r="T7" s="40" t="inlineStr">
+        <is>
+          <t>201 - 1,000 คน</t>
+        </is>
+      </c>
+      <c r="U7" s="40" t="inlineStr">
+        <is>
+          <t>21 - 50 คน</t>
+        </is>
+      </c>
+      <c r="V7" s="40" t="inlineStr">
+        <is>
+          <t>มากกว่า 10,000 ครั้ง</t>
+        </is>
+      </c>
+      <c r="W7" s="40" t="inlineStr">
+        <is>
+          <t>มากกว่า 100 GB</t>
+        </is>
+      </c>
+      <c r="X7" s="40" t="inlineStr">
+        <is>
+          <t>10 - 100 GB</t>
+        </is>
+      </c>
+      <c r="Y7" s="40" t="inlineStr">
+        <is>
+          <t>1,000 - 10,000 รูป</t>
+        </is>
+      </c>
+      <c r="AB7" s="40" t="inlineStr">
+        <is>
           <t>Risk (ความเสี่ยง)</t>
         </is>
       </c>
-      <c r="T7" s="41" t="n">
+      <c r="AC7" s="41" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -6922,6 +7145,31 @@
           <t>มากกว่า 40 ชม./สัปดาห์  (มากกว่า 1 คนเต็มเวลา)</t>
         </is>
       </c>
+      <c r="S8" s="40" t="inlineStr">
+        <is>
+          <t>มากกว่า 2 ล้านบาท/ปี</t>
+        </is>
+      </c>
+      <c r="T8" s="40" t="inlineStr">
+        <is>
+          <t>มากกว่า 1,000 คน</t>
+        </is>
+      </c>
+      <c r="U8" s="40" t="inlineStr">
+        <is>
+          <t>มากกว่า 50 คน</t>
+        </is>
+      </c>
+      <c r="X8" s="40" t="inlineStr">
+        <is>
+          <t>มากกว่า 100 GB</t>
+        </is>
+      </c>
+      <c r="Y8" s="40" t="inlineStr">
+        <is>
+          <t>มากกว่า 10,000 รูป</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="40" t="inlineStr">
@@ -6934,94 +7182,58 @@
           <t>ผสมหลายแบบ</t>
         </is>
       </c>
-      <c r="S9" s="39" t="inlineStr">
+      <c r="AB9" s="39" t="inlineStr">
         <is>
           <t>เกณฑ์แบ่งระดับ</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="S10" s="40" t="inlineStr">
+      <c r="AB10" s="40" t="inlineStr">
         <is>
           <t>คะแนน &gt;= นี้ = สูง</t>
         </is>
       </c>
-      <c r="T10" s="42" t="n">
+      <c r="AC10" s="42" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="11">
-      <c r="S11" s="40" t="inlineStr">
+      <c r="AB11" s="40" t="inlineStr">
         <is>
           <t>คะแนน &gt;= นี้ = กลาง</t>
         </is>
       </c>
-      <c r="T11" s="42" t="n">
+      <c r="AC11" s="42" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="14">
-      <c r="S14" s="39" t="inlineStr">
+      <c r="AB14" s="39" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="S15" s="40" t="inlineStr">
-        <is>
-          <t>ช่วงชั่วโมง/สัปดาห์ เปลี่ยนเป็น dropdown แล้ว</t>
+      <c r="AB15" s="40" t="inlineStr">
+        <is>
+          <t>ช่วงชั่วโมงและช่วงมูลค่าเป็น dropdown แล้ว</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="S16" s="40" t="inlineStr">
-        <is>
-          <t>แก้ตัวเลือกและคะแนนได้ที่คอลัมน์ R</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="S23" s="39" t="inlineStr">
-        <is>
-          <t>ช่วงมูลค่าความเสียหาย/ปี -&gt; คะแนน</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="S24" s="39" t="inlineStr">
-        <is>
-          <t>ตั้งแต่ (บาท)</t>
-        </is>
-      </c>
-      <c r="T24" s="39" t="inlineStr">
-        <is>
-          <t>คะแนน</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="S25" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="S26" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" s="40" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="S27" s="43" t="n">
-        <v>100000</v>
-      </c>
-      <c r="T27" s="40" t="n">
-        <v>3</v>
+      <c r="AB16" s="40" t="inlineStr">
+        <is>
+          <t>แก้ตัวเลือกและคะแนนได้ที่คอลัมน์ R และ S</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="AB17" s="40" t="inlineStr">
+        <is>
+          <t>คะแนน "-" แปลว่าไม่นำมาคิดคะแนน ไม่ใช่ได้ 0</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -7030,12 +7242,6 @@
           <t>ตารางแปลงตัวเลือกเป็นคะแนน 1-5 (เรียงตรงกับรายการด้านบนบรรทัดต่อบรรทัด) — ปรับได้</t>
         </is>
       </c>
-      <c r="S28" s="43" t="n">
-        <v>500000</v>
-      </c>
-      <c r="T28" s="40" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="38" t="inlineStr">
@@ -7128,300 +7334,486 @@
           <t>เวลาที่ใช้กับงานนี้ตอนนี้</t>
         </is>
       </c>
-      <c r="S29" s="43" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="T29" s="40" t="n">
+      <c r="S29" s="38" t="inlineStr">
+        <is>
+          <t>มูลค่าความเสียหาย/ของเสียต่อปี</t>
+        </is>
+      </c>
+      <c r="T29" s="38" t="inlineStr">
+        <is>
+          <t>จำนวน Users/วัน</t>
+        </is>
+      </c>
+      <c r="U29" s="38" t="inlineStr">
+        <is>
+          <t>Peak concurrent (คนใช้พร้อมกันสูงสุด)</t>
+        </is>
+      </c>
+      <c r="V29" s="38" t="inlineStr">
+        <is>
+          <t>Requests/วัน</t>
+        </is>
+      </c>
+      <c r="W29" s="38" t="inlineStr">
+        <is>
+          <t>ขนาดข้อมูล Input/วัน</t>
+        </is>
+      </c>
+      <c r="X29" s="38" t="inlineStr">
+        <is>
+          <t>ขนาดคลังเอกสารทั้งหมด (RAG)</t>
+        </is>
+      </c>
+      <c r="Y29" s="38" t="inlineStr">
+        <is>
+          <t>จำนวนรูป/วัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B30" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="44" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="44" t="inlineStr">
+      <c r="E30" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B30" s="45" t="n">
+      <c r="K30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="45" t="n">
+      <c r="S30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B31" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B32" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="45" t="n">
+      <c r="E32" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="45" t="n">
+      <c r="H32" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="S32" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B33" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="F30" s="45" t="n">
+      <c r="E33" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="G30" s="45" t="n">
+      <c r="K33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="S33" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B34" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O34" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U34" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X34" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y34" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M30" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P30" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q30" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R30" s="45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B31" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M31" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O31" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P31" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q31" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R31" s="45" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B32" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="I32" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M32" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N32" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O32" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P32" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q32" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R32" s="45" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B33" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="E33" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O33" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R33" s="45" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B34" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O34" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R34" s="45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" s="44" t="inlineStr">
+      <c r="K35" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -1100,16 +1100,16 @@
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
     <col width="38" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
   </cols>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>รูปแบบข้อมูล</t>
+          <t>ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน</t>
         </is>
       </c>
       <c r="M5" s="19" t="inlineStr">
         <is>
-          <t>ข้อมูลย้อนหลัง</t>
+          <t>มีข้อมูลย้อนหลังนานแค่ไหน</t>
         </is>
       </c>
       <c r="N5" s="19" t="inlineStr">
@@ -1267,32 +1267,34 @@
       </c>
       <c r="P5" s="19" t="inlineStr">
         <is>
-          <t>มีระบบเดิมที่ต้องเชื่อมต่อ</t>
+          <t>ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย
+(ERP / MES / ระบบที่ใช้อยู่)</t>
         </is>
       </c>
       <c r="Q5" s="19" t="inlineStr">
         <is>
-          <t>มีคนในแผนกดูแลต่อได้มั้ย</t>
+          <t>มีคนดูแลระบบต่อหลังส่งมอบมั้ย</t>
         </is>
       </c>
       <c r="R5" s="19" t="inlineStr">
         <is>
-          <t>ผลกระทบถ้า AI ทำผิด</t>
+          <t>ถ้า AI ตอบผิด จะเกิดอะไรขึ้น</t>
         </is>
       </c>
       <c r="S5" s="19" t="inlineStr">
         <is>
-          <t>ต้องมีคนตรวจซ้ำมั้ย</t>
+          <t>ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย</t>
         </is>
       </c>
       <c r="T5" s="19" t="inlineStr">
         <is>
-          <t>ระดับความลับของข้อมูล</t>
+          <t>ข้อมูลชุดนี้ลับแค่ไหน</t>
         </is>
       </c>
       <c r="U5" s="19" t="inlineStr">
         <is>
-          <t>ความสำคัญที่แผนกอยากได้</t>
+          <t>ความสำคัญที่แผนกอยากได้
+(ความเห็นแผนก ไม่นำไปคิดคะแนน)</t>
         </is>
       </c>
       <c r="V5" s="19" t="inlineStr">
@@ -1368,7 +1370,7 @@
       </c>
       <c r="M6" s="20" t="inlineStr">
         <is>
-          <t>1 - 3 ปี</t>
+          <t>1 - 3 ปี - พอใช้ได้</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -1383,22 +1385,22 @@
       </c>
       <c r="P6" s="20" t="inlineStr">
         <is>
-          <t>ไม่มี - ทำระบบใหม่แยกได้เลย</t>
+          <t>ไม่มี - AI ทำงานแยกเดี่ยวได้เลย ไม่ต้องยุ่งกับระบบไหน</t>
         </is>
       </c>
       <c r="Q6" s="20" t="inlineStr">
         <is>
-          <t>มี - ระบุชื่อในหมายเหตุ</t>
+          <t>มี - มีคนในแผนกรับดูแลต่อได้ (ระบุชื่อในหมายเหตุ)</t>
         </is>
       </c>
       <c r="R6" s="20" t="inlineStr">
         <is>
-          <t>สูง - กระทบลูกค้า/ความปลอดภัย/กฎหมาย</t>
+          <t>สูง - ของเสียหลุดถึงลูกค้า / อันตราย / ผิดกฎหมาย</t>
         </is>
       </c>
       <c r="S6" s="20" t="inlineStr">
         <is>
-          <t>สุ่มตรวจบางส่วน</t>
+          <t>สุ่มตรวจบางส่วน - ตรวจเฉพาะที่ AI ไม่มั่นใจ</t>
         </is>
       </c>
       <c r="T6" s="20" t="inlineStr">
@@ -2193,28 +2195,28 @@
     <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มูลค่าความเสียหาย/ของเสียต่อปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$S$4:$S$8</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="รูปแบบข้อมูลที่มี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$B$4:$B$9</formula1>
     </dataValidation>
-    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ข้อมูลย้อนหลัง" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีข้อมูลย้อนหลังนานแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$C$4:$C$7</formula1>
     </dataValidation>
     <dataValidation sqref="O7:O36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="สิทธิ์นำข้อมูลมาใช้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$D$4:$D$6</formula1>
     </dataValidation>
-    <dataValidation sqref="P7:P36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีระบบเดิมที่ต้องเชื่อมต่อ" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="P7:P36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$E$4:$E$7</formula1>
     </dataValidation>
-    <dataValidation sqref="Q7:Q36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีคนดูแลต่อ" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="Q7:Q36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีคนดูแลระบบต่อหลังส่งมอบมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$F$4:$F$6</formula1>
     </dataValidation>
-    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ผลกระทบถ้า AI ผิด" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ถ้า AI ตอบผิด จะเกิดอะไรขึ้น" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$G$4:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องมีคนตรวจซ้ำ" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$H$4:$H$6</formula1>
     </dataValidation>
-    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ระดับความลับข้อมูล" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ข้อมูลชุดนี้ลับแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$I$4:$I$7</formula1>
     </dataValidation>
     <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความสำคัญที่แผนกอยากได้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
@@ -6500,12 +6502,12 @@
       </c>
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>รูปแบบข้อมูลที่มี</t>
+          <t>ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน</t>
         </is>
       </c>
       <c r="C3" s="38" t="inlineStr">
         <is>
-          <t>ข้อมูลย้อนหลัง</t>
+          <t>มีข้อมูลย้อนหลังนานแค่ไหน</t>
         </is>
       </c>
       <c r="D3" s="38" t="inlineStr">
@@ -6515,27 +6517,27 @@
       </c>
       <c r="E3" s="38" t="inlineStr">
         <is>
-          <t>มีระบบเดิมที่ต้องเชื่อมต่อ</t>
+          <t>ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย</t>
         </is>
       </c>
       <c r="F3" s="38" t="inlineStr">
         <is>
-          <t>มีคนดูแลต่อ</t>
+          <t>มีคนดูแลระบบต่อหลังส่งมอบมั้ย</t>
         </is>
       </c>
       <c r="G3" s="38" t="inlineStr">
         <is>
-          <t>ผลกระทบถ้า AI ผิด</t>
+          <t>ถ้า AI ตอบผิด จะเกิดอะไรขึ้น</t>
         </is>
       </c>
       <c r="H3" s="38" t="inlineStr">
         <is>
-          <t>ต้องมีคนตรวจซ้ำ</t>
+          <t>ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย</t>
         </is>
       </c>
       <c r="I3" s="38" t="inlineStr">
         <is>
-          <t>ระดับความลับข้อมูล</t>
+          <t>ข้อมูลชุดนี้ลับแค่ไหน</t>
         </is>
       </c>
       <c r="J3" s="38" t="inlineStr">
@@ -6632,12 +6634,12 @@
       </c>
       <c r="B4" s="40" t="inlineStr">
         <is>
-          <t>กระดาษ / เอกสารเขียนมือ</t>
+          <t>กระดาษ / เอกสารเขียนมือ - ต้องพิมพ์เข้าคอมก่อน</t>
         </is>
       </c>
       <c r="C4" s="40" t="inlineStr">
         <is>
-          <t>ยังไม่มี</t>
+          <t>ยังไม่มี - ต้องเริ่มเก็บใหม่</t>
         </is>
       </c>
       <c r="D4" s="40" t="inlineStr">
@@ -6647,27 +6649,27 @@
       </c>
       <c r="E4" s="40" t="inlineStr">
         <is>
-          <t>ไม่มี - ทำระบบใหม่แยกได้เลย</t>
+          <t>ไม่มี - AI ทำงานแยกเดี่ยวได้เลย ไม่ต้องยุ่งกับระบบไหน</t>
         </is>
       </c>
       <c r="F4" s="40" t="inlineStr">
         <is>
-          <t>มี - ระบุชื่อในหมายเหตุ</t>
+          <t>มี - มีคนในแผนกรับดูแลต่อได้ (ระบุชื่อในหมายเหตุ)</t>
         </is>
       </c>
       <c r="G4" s="40" t="inlineStr">
         <is>
-          <t>ต่ำ - แก้ไขได้ทันที ไม่กระทบใคร</t>
+          <t>ต่ำ - คนเห็นแล้วแก้ได้ทันที ไม่มีใครเดือดร้อน</t>
         </is>
       </c>
       <c r="H4" s="40" t="inlineStr">
         <is>
-          <t>ไม่ต้อง - เชื่อผล AI ได้เลย</t>
+          <t>ไม่ต้อง - ใช้ผล AI ได้เลย</t>
         </is>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
-          <t>สาธารณะ - ไม่มีข้อมูลลับ</t>
+          <t>สาธารณะ - หลุดออกไปก็ไม่เป็นไร</t>
         </is>
       </c>
       <c r="J4" s="40" t="inlineStr">
@@ -6767,12 +6769,12 @@
       </c>
       <c r="B5" s="40" t="inlineStr">
         <is>
-          <t>ไฟล์ Excel / CSV</t>
+          <t>ไฟล์ Excel / CSV - เปิดใช้ได้เลย</t>
         </is>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
-          <t>น้อยกว่า 1 ปี</t>
+          <t>น้อยกว่า 1 ปี - อาจยังไม่พอเทรน</t>
         </is>
       </c>
       <c r="D5" s="40" t="inlineStr">
@@ -6782,22 +6784,22 @@
       </c>
       <c r="E5" s="40" t="inlineStr">
         <is>
-          <t>มี - เชื่อมแบบส่งไฟล์/Export ได้</t>
+          <t>มี - แค่ export ไฟล์ออกมาให้ AI แล้วเอาผลกลับเข้าไปทีหลังก็พอ</t>
         </is>
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>ยังไม่แน่ใจ</t>
+          <t>ยังไม่แน่ใจ - ต้องหาคนก่อน</t>
         </is>
       </c>
       <c r="G5" s="40" t="inlineStr">
         <is>
-          <t>กลาง - เสียเวลา/ต้นทุนบางส่วน</t>
+          <t>กลาง - เสียเวลาทำใหม่ หรือเสียต้นทุนบางส่วน</t>
         </is>
       </c>
       <c r="H5" s="40" t="inlineStr">
         <is>
-          <t>สุ่มตรวจบางส่วน</t>
+          <t>สุ่มตรวจบางส่วน - ตรวจเฉพาะที่ AI ไม่มั่นใจ</t>
         </is>
       </c>
       <c r="I5" s="40" t="inlineStr">
@@ -6902,12 +6904,12 @@
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>ฐานข้อมูลในระบบ (ERP/MES/SQL)</t>
+          <t>ฐานข้อมูลในระบบ (ERP/MES/SQL) - ดึงอัตโนมัติได้</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>1 - 3 ปี</t>
+          <t>1 - 3 ปี - พอใช้ได้</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
@@ -6917,27 +6919,27 @@
       </c>
       <c r="E6" s="40" t="inlineStr">
         <is>
-          <t>มี - ต้องเชื่อมตรงกับระบบหลัก</t>
+          <t>มี - AI ต้องอ่าน/เขียนข้อมูลในระบบโดยตรงแบบทันที</t>
         </is>
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>ไม่มี</t>
+          <t>ไม่มี - ต้องพึ่งคนนอกแผนกตลอด</t>
         </is>
       </c>
       <c r="G6" s="40" t="inlineStr">
         <is>
-          <t>สูง - กระทบลูกค้า/ความปลอดภัย/กฎหมาย</t>
+          <t>สูง - ของเสียหลุดถึงลูกค้า / อันตราย / ผิดกฎหมาย</t>
         </is>
       </c>
       <c r="H6" s="40" t="inlineStr">
         <is>
-          <t>ตรวจซ้ำทุกครั้ง</t>
+          <t>ตรวจซ้ำทุกครั้ง - คนต้องดูทุกชิ้น/ทุกรายการ</t>
         </is>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
-          <t>ลับ - ต้องมี Access Control</t>
+          <t>ลับ - ต้องจำกัดสิทธิ์ว่าใครเปิดดูได้บ้าง</t>
         </is>
       </c>
       <c r="J6" s="40" t="inlineStr">
@@ -7042,17 +7044,17 @@
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
-          <t>มากกว่า 3 ปี</t>
+          <t>มากกว่า 3 ปี - เพียงพอแน่นอน</t>
         </is>
       </c>
       <c r="E7" s="40" t="inlineStr">
         <is>
-          <t>ยังไม่แน่ใจ</t>
+          <t>ยังไม่แน่ใจ - ต้องถาม IT ก่อน</t>
         </is>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
-          <t>ลับมาก - Regulatory / PDPA</t>
+          <t>ลับมาก - มีข้อมูลส่วนบุคคล / ผูกกับกฎหมาย PDPA</t>
         </is>
       </c>
       <c r="K7" s="40" t="inlineStr">
@@ -7174,7 +7176,7 @@
     <row r="9">
       <c r="B9" s="40" t="inlineStr">
         <is>
-          <t>ยังไม่มีข้อมูลเก็บไว้</t>
+          <t>ยังไม่มีข้อมูลเก็บไว้ - ต้องเริ่มเก็บใหม่</t>
         </is>
       </c>
       <c r="K9" s="40" t="inlineStr">
@@ -7251,12 +7253,12 @@
       </c>
       <c r="B29" s="38" t="inlineStr">
         <is>
-          <t>รูปแบบข้อมูลที่มี</t>
+          <t>ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน</t>
         </is>
       </c>
       <c r="C29" s="38" t="inlineStr">
         <is>
-          <t>ข้อมูลย้อนหลัง</t>
+          <t>มีข้อมูลย้อนหลังนานแค่ไหน</t>
         </is>
       </c>
       <c r="D29" s="38" t="inlineStr">
@@ -7266,27 +7268,27 @@
       </c>
       <c r="E29" s="38" t="inlineStr">
         <is>
-          <t>มีระบบเดิมที่ต้องเชื่อมต่อ</t>
+          <t>ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย</t>
         </is>
       </c>
       <c r="F29" s="38" t="inlineStr">
         <is>
-          <t>มีคนดูแลต่อ</t>
+          <t>มีคนดูแลระบบต่อหลังส่งมอบมั้ย</t>
         </is>
       </c>
       <c r="G29" s="38" t="inlineStr">
         <is>
-          <t>ผลกระทบถ้า AI ผิด</t>
+          <t>ถ้า AI ตอบผิด จะเกิดอะไรขึ้น</t>
         </is>
       </c>
       <c r="H29" s="38" t="inlineStr">
         <is>
-          <t>ต้องมีคนตรวจซ้ำ</t>
+          <t>ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย</t>
         </is>
       </c>
       <c r="I29" s="38" t="inlineStr">
         <is>
-          <t>ระดับความลับข้อมูล</t>
+          <t>ข้อมูลชุดนี้ลับแค่ไหน</t>
         </is>
       </c>
       <c r="J29" s="38" t="inlineStr">

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -1102,7 +1102,7 @@
     <col width="38" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="16"/>
     <col width="34" customWidth="1" min="17" max="17"/>
@@ -1256,7 +1256,8 @@
       <c r="N5" s="19" t="inlineStr">
         <is>
           <t>ปริมาณข้อมูลโดยประมาณ
-(เช่น 5,000 รูป / 2 ปี)</t>
+นับเป็นรายการ : รูป / ใบ / ไฟล์ / ครั้ง / ล็อต แล้วแต่งาน
+(เอาเฉพาะที่รู้คำตอบแล้ว)</t>
         </is>
       </c>
       <c r="O5" s="19" t="inlineStr">
@@ -2185,7 +2186,7 @@
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="K4:O4"/>
   </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="17">
     <dataValidation sqref="C7:C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="บริษัท" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$A$4:$A$8</formula1>
     </dataValidation>
@@ -2222,6 +2223,11 @@
     <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความสำคัญที่แผนกอยากได้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$J$4:$J$6</formula1>
     </dataValidation>
+    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปัญหาที่ต้องการแก้" prompt="ตอนนี้เจอปัญหาอะไร ทำไมถึงอยากได้ AI มาช่วย&#10;เช่น ตรวจด้วยตาเปล่าทำให้ของเสียหลุดถึงลูกค้าเดือนละ 2-3 ครั้ง"/>
+    <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="วิธีการทำงานปัจจุบัน (Existing Work)" prompt="ตอนนี้ทำงานนี้ยังไง ใครเป็นคนทำ ใช้เครื่องมืออะไร บันทึกผลไว้ที่ไหน&#10;เขียนแบบที่คนนอกแผนกอ่านแล้วเห็นภาพ"/>
+    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="แนวทางหลังนำ AI มาใช้ (Description for Redesign)" prompt="อยากให้ AI ทำอะไรให้ และผลลัพธ์ที่อยากได้หน้าตาเป็นยังไง&#10;เช่น ติดกล้องที่สายพาน ให้ AI แยกดี/เสียอัตโนมัติ&#10;ชิ้นที่ AI ไม่มั่นใจค่อยส่งให้คนตรวจ"/>
+    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ข้อมูลที่มีอยู่ตอนนี้ (Data Available)" prompt="มีข้อมูลอะไรบ้าง เก็บไว้ที่ไหน ใครเป็นคนเก็บ&#10;ถ้ามีสัดส่วนที่น่าสนใจให้เขียนด้วย เช่น รูปดี 3,000 / รูปเสีย 1,000"/>
+    <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปริมาณข้อมูลโดยประมาณ" prompt="นับเป็น 'รายการ' โดยหน่วยขึ้นกับประเภทงาน :&#10;   งานตรวจภาพ         =  กี่รูป&#10;   หาสาเหตุปัญหา/NC   =  กี่เคส กี่ใบ&#10;   ค้นหา-สรุปเอกสาร   =  กี่ไฟล์ กี่ฉบับ&#10;   ทำนายเครื่องเสีย   =  เคยเสียมากี่ครั้ง&#10;   วิเคราะห์การผลิต   =  กี่ล็อต กี่แถวข้อมูล&#10;   จัดคน / แนะนำ      =  เคยจัดจริงมากี่ครั้ง&#10;&#10;นับเฉพาะข้อมูลที่รู้คำตอบแล้ว เช่น รูปที่มาร์คแล้วว่าดี/เสีย&#10;ข้อมูลดิบที่ยังไม่ได้แยกใช้เทรนไม่ได้"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -2224,10 +2224,10 @@
       <formula1>DATA!$J$4:$J$6</formula1>
     </dataValidation>
     <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปัญหาที่ต้องการแก้" prompt="ตอนนี้เจอปัญหาอะไร ทำไมถึงอยากได้ AI มาช่วย&#10;เช่น ตรวจด้วยตาเปล่าทำให้ของเสียหลุดถึงลูกค้าเดือนละ 2-3 ครั้ง"/>
-    <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="วิธีการทำงานปัจจุบัน (Existing Work)" prompt="ตอนนี้ทำงานนี้ยังไง ใครเป็นคนทำ ใช้เครื่องมืออะไร บันทึกผลไว้ที่ไหน&#10;เขียนแบบที่คนนอกแผนกอ่านแล้วเห็นภาพ"/>
-    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="แนวทางหลังนำ AI มาใช้ (Description for Redesign)" prompt="อยากให้ AI ทำอะไรให้ และผลลัพธ์ที่อยากได้หน้าตาเป็นยังไง&#10;เช่น ติดกล้องที่สายพาน ให้ AI แยกดี/เสียอัตโนมัติ&#10;ชิ้นที่ AI ไม่มั่นใจค่อยส่งให้คนตรวจ"/>
-    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ข้อมูลที่มีอยู่ตอนนี้ (Data Available)" prompt="มีข้อมูลอะไรบ้าง เก็บไว้ที่ไหน ใครเป็นคนเก็บ&#10;ถ้ามีสัดส่วนที่น่าสนใจให้เขียนด้วย เช่น รูปดี 3,000 / รูปเสีย 1,000"/>
-    <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปริมาณข้อมูลโดยประมาณ" prompt="นับเป็น 'รายการ' โดยหน่วยขึ้นกับประเภทงาน :&#10;   งานตรวจภาพ         =  กี่รูป&#10;   หาสาเหตุปัญหา/NC   =  กี่เคส กี่ใบ&#10;   ค้นหา-สรุปเอกสาร   =  กี่ไฟล์ กี่ฉบับ&#10;   ทำนายเครื่องเสีย   =  เคยเสียมากี่ครั้ง&#10;   วิเคราะห์การผลิต   =  กี่ล็อต กี่แถวข้อมูล&#10;   จัดคน / แนะนำ      =  เคยจัดจริงมากี่ครั้ง&#10;&#10;นับเฉพาะข้อมูลที่รู้คำตอบแล้ว เช่น รูปที่มาร์คแล้วว่าดี/เสีย&#10;ข้อมูลดิบที่ยังไม่ได้แยกใช้เทรนไม่ได้"/>
+    <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="วิธีการทำงานปัจจุบัน" prompt="ตอนนี้ทำงานนี้ยังไง ใครเป็นคนทำ ใช้เครื่องมืออะไร บันทึกผลไว้ที่ไหน&#10;เขียนแบบที่คนนอกแผนกอ่านแล้วเห็นภาพ"/>
+    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="แนวทางหลังนำ AI มาใช้" prompt="อยากให้ AI ทำอะไรให้ และผลลัพธ์ที่อยากได้หน้าตาเป็นยังไง&#10;เช่น ติดกล้องที่สายพาน ให้ AI แยกดี/เสียอัตโนมัติ&#10;ชิ้นที่ AI ไม่มั่นใจค่อยส่งให้คนตรวจ"/>
+    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ข้อมูลที่มีอยู่ตอนนี้" prompt="มีข้อมูลอะไรบ้าง เก็บไว้ที่ไหน ใครเป็นคนเก็บ&#10;ถ้ามีสัดส่วนที่น่าสนใจให้เขียนด้วย เช่น รูปดี 3,000 / รูปเสีย 1,000"/>
+    <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปริมาณข้อมูลโดยประมาณ" prompt="นับเป็น 'รายการ' หน่วยขึ้นกับงาน :&#10;  ตรวจภาพ = กี่รูป&#10;  หาสาเหตุ/NC = กี่เคส&#10;  ค้นหาเอกสาร = กี่ไฟล์&#10;  เครื่องเสีย = กี่ครั้ง&#10;  การผลิต = กี่ล็อต&#10;&#10;นับเฉพาะที่รู้คำตอบแล้ว เช่น รูปที่มาร์คว่าดี/เสีย&#10;(รายละเอียดเต็มอยู่ในคู่มือ)"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3424,7 +3424,7 @@
     <dataValidation sqref="E7:E36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวน Users/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$T$4:$T$8</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนใช้พร้อมกันสูงสุด)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนพร้อมกัน)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$U$4:$U$8</formula1>
     </dataValidation>
     <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Requests/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="U3" s="38" t="inlineStr">
         <is>
-          <t>Peak concurrent (คนใช้พร้อมกันสูงสุด)</t>
+          <t>Peak concurrent (คนพร้อมกัน)</t>
         </is>
       </c>
       <c r="V3" s="38" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="U29" s="38" t="inlineStr">
         <is>
-          <t>Peak concurrent (คนใช้พร้อมกันสูงสุด)</t>
+          <t>Peak concurrent (คนพร้อมกัน)</t>
         </is>
       </c>
       <c r="V29" s="38" t="inlineStr">

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -2239,7 +2239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2256,17 +2256,21 @@
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ชั้นที่ 2 : รายละเอียดเทคนิค   (กรอกทุก Use Case — ใช้กำหนด Spec Hardware และประเมินราคา Server)</t>
+          <t>ชั้นที่ 2 : รายละเอียดเทคนิค   (กรอกทุก Use Case — ใช้กำหนด Spec Server ที่จะตั้งในบริษัท)</t>
         </is>
       </c>
     </row>
@@ -2305,14 +2309,22 @@
       <c r="M4" s="23" t="n"/>
       <c r="N4" s="23" t="n"/>
       <c r="O4" s="23" t="n"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
+        <is>
+          <t>การติดตั้งและใช้เครื่องร่วมกัน</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="17" t="inlineStr">
         <is>
           <t>ข้อจำกัด / งบประมาณ</t>
         </is>
       </c>
-      <c r="Q4" s="18" t="n"/>
-      <c r="R4" s="18" t="n"/>
-      <c r="S4" s="18" t="n"/>
+      <c r="U4" s="18" t="n"/>
+      <c r="V4" s="18" t="n"/>
+      <c r="W4" s="18" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -2365,8 +2377,8 @@
       </c>
       <c r="J5" s="19" t="inlineStr">
         <is>
-          <t>จำนวนรูป/วัน
-(งานภาพเท่านั้น)</t>
+          <t>จำนวนกล้อง/จุดตรวจ
+ที่ทำงานพร้อมกัน (งานภาพ)</t>
         </is>
       </c>
       <c r="K5" s="19" t="inlineStr">
@@ -2391,7 +2403,8 @@
       </c>
       <c r="O5" s="19" t="inlineStr">
         <is>
-          <t>ต้องติดตั้งที่ไหน</t>
+          <t>ติดตั้งแบบไหน
+(server ตั้งที่เดียว ไม่ใช้ Cloud)</t>
         </is>
       </c>
       <c r="P5" s="19" t="inlineStr">
@@ -2400,17 +2413,37 @@
         </is>
       </c>
       <c r="Q5" s="19" t="inlineStr">
+        <is>
+          <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
+        </is>
+      </c>
+      <c r="R5" s="19" t="inlineStr">
+        <is>
+          <t>มีเครื่อง/GPU เดิมใช้ได้มั้ย</t>
+        </is>
+      </c>
+      <c r="S5" s="19" t="inlineStr">
+        <is>
+          <t>แชร์เครื่องกับ use case อื่นได้มั้ย</t>
+        </is>
+      </c>
+      <c r="T5" s="19" t="inlineStr">
+        <is>
+          <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
+        </is>
+      </c>
+      <c r="U5" s="19" t="inlineStr">
         <is>
           <t>งบประมาณที่ตั้งไว้ (บาท)
 - ถ้ามี</t>
         </is>
       </c>
-      <c r="R5" s="19" t="inlineStr">
+      <c r="V5" s="19" t="inlineStr">
         <is>
           <t>ข้อจำกัดอื่นๆ / หมายเหตุ</t>
         </is>
       </c>
-      <c r="S5" s="19" t="inlineStr">
+      <c r="W5" s="19" t="inlineStr">
         <is>
           <t>ผู้ให้ข้อมูลเทคนิค</t>
         </is>
@@ -2461,7 +2494,7 @@
       </c>
       <c r="J6" s="20" t="inlineStr">
         <is>
-          <t>100 - 1,000 รูป</t>
+          <t>2 - 3 จุด</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -2486,7 +2519,7 @@
       </c>
       <c r="O6" s="20" t="inlineStr">
         <is>
-          <t>On-premise เท่านั้น (ห้ามออกนอก)</t>
+          <t>ต้องมีเครื่องที่หน้างาน - ติดข้างเครื่องจักร/สายพาน</t>
         </is>
       </c>
       <c r="P6" s="20" t="inlineStr">
@@ -2494,15 +2527,35 @@
           <t>ต้อง Fine-tune ด้วยข้อมูลบริษัท</t>
         </is>
       </c>
-      <c r="Q6" s="20" t="n">
+      <c r="Q6" s="20" t="inlineStr">
+        <is>
+          <t>ทุกไตรมาส</t>
+        </is>
+      </c>
+      <c r="R6" s="20" t="inlineStr">
+        <is>
+          <t>ไม่มีเลย - ต้องซื้อใหม่ทั้งหมด</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr">
+        <is>
+          <t>แชร์ไม่ได้ - ต้องมีเครื่องของตัวเอง</t>
+        </is>
+      </c>
+      <c r="T6" s="20" t="inlineStr">
+        <is>
+          <t>2 - 3 ปี</t>
+        </is>
+      </c>
+      <c r="U6" s="20" t="n">
         <v>500000</v>
       </c>
-      <c r="R6" s="20" t="inlineStr">
+      <c r="V6" s="20" t="inlineStr">
         <is>
           <t>ต้องติดกล้องที่สายพานเดิม มีพื้นที่จำกัด</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr">
+      <c r="W6" s="20" t="inlineStr">
         <is>
           <t>คุณสมชาย</t>
         </is>
@@ -2537,6 +2590,10 @@
       <c r="Q7" s="21" t="n"/>
       <c r="R7" s="21" t="n"/>
       <c r="S7" s="21" t="n"/>
+      <c r="T7" s="21" t="n"/>
+      <c r="U7" s="21" t="n"/>
+      <c r="V7" s="21" t="n"/>
+      <c r="W7" s="21" t="n"/>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="25">
@@ -2567,6 +2624,10 @@
       <c r="Q8" s="21" t="n"/>
       <c r="R8" s="21" t="n"/>
       <c r="S8" s="21" t="n"/>
+      <c r="T8" s="21" t="n"/>
+      <c r="U8" s="21" t="n"/>
+      <c r="V8" s="21" t="n"/>
+      <c r="W8" s="21" t="n"/>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="25">
@@ -2597,6 +2658,10 @@
       <c r="Q9" s="21" t="n"/>
       <c r="R9" s="21" t="n"/>
       <c r="S9" s="21" t="n"/>
+      <c r="T9" s="21" t="n"/>
+      <c r="U9" s="21" t="n"/>
+      <c r="V9" s="21" t="n"/>
+      <c r="W9" s="21" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="25">
@@ -2627,6 +2692,10 @@
       <c r="Q10" s="21" t="n"/>
       <c r="R10" s="21" t="n"/>
       <c r="S10" s="21" t="n"/>
+      <c r="T10" s="21" t="n"/>
+      <c r="U10" s="21" t="n"/>
+      <c r="V10" s="21" t="n"/>
+      <c r="W10" s="21" t="n"/>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="25">
@@ -2657,6 +2726,10 @@
       <c r="Q11" s="21" t="n"/>
       <c r="R11" s="21" t="n"/>
       <c r="S11" s="21" t="n"/>
+      <c r="T11" s="21" t="n"/>
+      <c r="U11" s="21" t="n"/>
+      <c r="V11" s="21" t="n"/>
+      <c r="W11" s="21" t="n"/>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="25">
@@ -2687,6 +2760,10 @@
       <c r="Q12" s="21" t="n"/>
       <c r="R12" s="21" t="n"/>
       <c r="S12" s="21" t="n"/>
+      <c r="T12" s="21" t="n"/>
+      <c r="U12" s="21" t="n"/>
+      <c r="V12" s="21" t="n"/>
+      <c r="W12" s="21" t="n"/>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="25">
@@ -2717,6 +2794,10 @@
       <c r="Q13" s="21" t="n"/>
       <c r="R13" s="21" t="n"/>
       <c r="S13" s="21" t="n"/>
+      <c r="T13" s="21" t="n"/>
+      <c r="U13" s="21" t="n"/>
+      <c r="V13" s="21" t="n"/>
+      <c r="W13" s="21" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="25">
@@ -2747,6 +2828,10 @@
       <c r="Q14" s="21" t="n"/>
       <c r="R14" s="21" t="n"/>
       <c r="S14" s="21" t="n"/>
+      <c r="T14" s="21" t="n"/>
+      <c r="U14" s="21" t="n"/>
+      <c r="V14" s="21" t="n"/>
+      <c r="W14" s="21" t="n"/>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="25">
@@ -2777,6 +2862,10 @@
       <c r="Q15" s="21" t="n"/>
       <c r="R15" s="21" t="n"/>
       <c r="S15" s="21" t="n"/>
+      <c r="T15" s="21" t="n"/>
+      <c r="U15" s="21" t="n"/>
+      <c r="V15" s="21" t="n"/>
+      <c r="W15" s="21" t="n"/>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="25">
@@ -2807,6 +2896,10 @@
       <c r="Q16" s="21" t="n"/>
       <c r="R16" s="21" t="n"/>
       <c r="S16" s="21" t="n"/>
+      <c r="T16" s="21" t="n"/>
+      <c r="U16" s="21" t="n"/>
+      <c r="V16" s="21" t="n"/>
+      <c r="W16" s="21" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="25">
@@ -2837,6 +2930,10 @@
       <c r="Q17" s="21" t="n"/>
       <c r="R17" s="21" t="n"/>
       <c r="S17" s="21" t="n"/>
+      <c r="T17" s="21" t="n"/>
+      <c r="U17" s="21" t="n"/>
+      <c r="V17" s="21" t="n"/>
+      <c r="W17" s="21" t="n"/>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="25">
@@ -2867,6 +2964,10 @@
       <c r="Q18" s="21" t="n"/>
       <c r="R18" s="21" t="n"/>
       <c r="S18" s="21" t="n"/>
+      <c r="T18" s="21" t="n"/>
+      <c r="U18" s="21" t="n"/>
+      <c r="V18" s="21" t="n"/>
+      <c r="W18" s="21" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="25">
@@ -2897,6 +2998,10 @@
       <c r="Q19" s="21" t="n"/>
       <c r="R19" s="21" t="n"/>
       <c r="S19" s="21" t="n"/>
+      <c r="T19" s="21" t="n"/>
+      <c r="U19" s="21" t="n"/>
+      <c r="V19" s="21" t="n"/>
+      <c r="W19" s="21" t="n"/>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="25">
@@ -2927,6 +3032,10 @@
       <c r="Q20" s="21" t="n"/>
       <c r="R20" s="21" t="n"/>
       <c r="S20" s="21" t="n"/>
+      <c r="T20" s="21" t="n"/>
+      <c r="U20" s="21" t="n"/>
+      <c r="V20" s="21" t="n"/>
+      <c r="W20" s="21" t="n"/>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="25">
@@ -2957,6 +3066,10 @@
       <c r="Q21" s="21" t="n"/>
       <c r="R21" s="21" t="n"/>
       <c r="S21" s="21" t="n"/>
+      <c r="T21" s="21" t="n"/>
+      <c r="U21" s="21" t="n"/>
+      <c r="V21" s="21" t="n"/>
+      <c r="W21" s="21" t="n"/>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="25">
@@ -2987,6 +3100,10 @@
       <c r="Q22" s="21" t="n"/>
       <c r="R22" s="21" t="n"/>
       <c r="S22" s="21" t="n"/>
+      <c r="T22" s="21" t="n"/>
+      <c r="U22" s="21" t="n"/>
+      <c r="V22" s="21" t="n"/>
+      <c r="W22" s="21" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="25">
@@ -3017,6 +3134,10 @@
       <c r="Q23" s="21" t="n"/>
       <c r="R23" s="21" t="n"/>
       <c r="S23" s="21" t="n"/>
+      <c r="T23" s="21" t="n"/>
+      <c r="U23" s="21" t="n"/>
+      <c r="V23" s="21" t="n"/>
+      <c r="W23" s="21" t="n"/>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="25">
@@ -3047,6 +3168,10 @@
       <c r="Q24" s="21" t="n"/>
       <c r="R24" s="21" t="n"/>
       <c r="S24" s="21" t="n"/>
+      <c r="T24" s="21" t="n"/>
+      <c r="U24" s="21" t="n"/>
+      <c r="V24" s="21" t="n"/>
+      <c r="W24" s="21" t="n"/>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="25">
@@ -3077,6 +3202,10 @@
       <c r="Q25" s="21" t="n"/>
       <c r="R25" s="21" t="n"/>
       <c r="S25" s="21" t="n"/>
+      <c r="T25" s="21" t="n"/>
+      <c r="U25" s="21" t="n"/>
+      <c r="V25" s="21" t="n"/>
+      <c r="W25" s="21" t="n"/>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="25">
@@ -3107,6 +3236,10 @@
       <c r="Q26" s="21" t="n"/>
       <c r="R26" s="21" t="n"/>
       <c r="S26" s="21" t="n"/>
+      <c r="T26" s="21" t="n"/>
+      <c r="U26" s="21" t="n"/>
+      <c r="V26" s="21" t="n"/>
+      <c r="W26" s="21" t="n"/>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="25">
@@ -3137,6 +3270,10 @@
       <c r="Q27" s="21" t="n"/>
       <c r="R27" s="21" t="n"/>
       <c r="S27" s="21" t="n"/>
+      <c r="T27" s="21" t="n"/>
+      <c r="U27" s="21" t="n"/>
+      <c r="V27" s="21" t="n"/>
+      <c r="W27" s="21" t="n"/>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="25">
@@ -3167,6 +3304,10 @@
       <c r="Q28" s="21" t="n"/>
       <c r="R28" s="21" t="n"/>
       <c r="S28" s="21" t="n"/>
+      <c r="T28" s="21" t="n"/>
+      <c r="U28" s="21" t="n"/>
+      <c r="V28" s="21" t="n"/>
+      <c r="W28" s="21" t="n"/>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="25">
@@ -3197,6 +3338,10 @@
       <c r="Q29" s="21" t="n"/>
       <c r="R29" s="21" t="n"/>
       <c r="S29" s="21" t="n"/>
+      <c r="T29" s="21" t="n"/>
+      <c r="U29" s="21" t="n"/>
+      <c r="V29" s="21" t="n"/>
+      <c r="W29" s="21" t="n"/>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="25">
@@ -3227,6 +3372,10 @@
       <c r="Q30" s="21" t="n"/>
       <c r="R30" s="21" t="n"/>
       <c r="S30" s="21" t="n"/>
+      <c r="T30" s="21" t="n"/>
+      <c r="U30" s="21" t="n"/>
+      <c r="V30" s="21" t="n"/>
+      <c r="W30" s="21" t="n"/>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="25">
@@ -3257,6 +3406,10 @@
       <c r="Q31" s="21" t="n"/>
       <c r="R31" s="21" t="n"/>
       <c r="S31" s="21" t="n"/>
+      <c r="T31" s="21" t="n"/>
+      <c r="U31" s="21" t="n"/>
+      <c r="V31" s="21" t="n"/>
+      <c r="W31" s="21" t="n"/>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="25">
@@ -3287,6 +3440,10 @@
       <c r="Q32" s="21" t="n"/>
       <c r="R32" s="21" t="n"/>
       <c r="S32" s="21" t="n"/>
+      <c r="T32" s="21" t="n"/>
+      <c r="U32" s="21" t="n"/>
+      <c r="V32" s="21" t="n"/>
+      <c r="W32" s="21" t="n"/>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="25">
@@ -3317,6 +3474,10 @@
       <c r="Q33" s="21" t="n"/>
       <c r="R33" s="21" t="n"/>
       <c r="S33" s="21" t="n"/>
+      <c r="T33" s="21" t="n"/>
+      <c r="U33" s="21" t="n"/>
+      <c r="V33" s="21" t="n"/>
+      <c r="W33" s="21" t="n"/>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="25">
@@ -3347,6 +3508,10 @@
       <c r="Q34" s="21" t="n"/>
       <c r="R34" s="21" t="n"/>
       <c r="S34" s="21" t="n"/>
+      <c r="T34" s="21" t="n"/>
+      <c r="U34" s="21" t="n"/>
+      <c r="V34" s="21" t="n"/>
+      <c r="W34" s="21" t="n"/>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="25">
@@ -3377,6 +3542,10 @@
       <c r="Q35" s="21" t="n"/>
       <c r="R35" s="21" t="n"/>
       <c r="S35" s="21" t="n"/>
+      <c r="T35" s="21" t="n"/>
+      <c r="U35" s="21" t="n"/>
+      <c r="V35" s="21" t="n"/>
+      <c r="W35" s="21" t="n"/>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="25">
@@ -3407,17 +3576,22 @@
       <c r="Q36" s="21" t="n"/>
       <c r="R36" s="21" t="n"/>
       <c r="S36" s="21" t="n"/>
+      <c r="T36" s="21" t="n"/>
+      <c r="U36" s="21" t="n"/>
+      <c r="V36" s="21" t="n"/>
+      <c r="W36" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="J4:O4"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:W1"/>
     <mergeCell ref="D4:I4"/>
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="T4:W4"/>
     <mergeCell ref="P4:S4"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A2:W2"/>
   </mergeCells>
-  <dataValidations count="13">
+  <dataValidations count="17">
     <dataValidation sqref="D7:D36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ประเภทข้อมูล Input" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$K$4:$K$9</formula1>
     </dataValidation>
@@ -3436,7 +3610,7 @@
     <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดคลังเอกสารทั้งหมด (RAG)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$X$4:$X$8</formula1>
     </dataValidation>
-    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวนรูป/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวนกล้อง/จุดตรวจพร้อมกัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$Y$4:$Y$8</formula1>
     </dataValidation>
     <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความละเอียดรูป" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
@@ -3451,11 +3625,23 @@
     <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Availability" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$N$4:$N$6</formula1>
     </dataValidation>
-    <dataValidation sqref="O7:O36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ที่ตั้งระบบ" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$P$4:$P$6</formula1>
+    <dataValidation sqref="O7:O36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ติดตั้งแบบไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$Z$4:$Z$6</formula1>
     </dataValidation>
     <dataValidation sqref="P7:P36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความต้องการโมเดล" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$Q$4:$Q$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q7:Q36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเทรนโมเดลใหม่บ่อยแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$AC$4:$AC$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีเครื่อง/GPU เดิมใช้ได้มั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$AA$4:$AA$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="แชร์เครื่องกับงานอื่นได้มั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$AD$4:$AD$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเก็บข้อมูลย้อนหลังกี่ปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$AB$4:$AB$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3744,11 +3930,11 @@
         <v/>
       </c>
       <c r="R6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(U6&gt;0,"",IFERROR(ROUND((F6*DATA!$AC$4+M6*DATA!$AC$5+J6*DATA!$AC$6+(6-Q6)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(U6&gt;0,"",IFERROR(ROUND((F6*DATA!$AI$4+M6*DATA!$AI$5+J6*DATA!$AI$6+(6-Q6)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S6" s="30">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(U6&gt;0,"ข้อมูลไม่ครบ",IF(R6="","",IF(R6&gt;=DATA!$AC$10,"สูง",IF(R6&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(U6&gt;0,"ข้อมูลไม่ครบ",IF(R6="","",IF(R6&gt;=DATA!$AI$10,"สูง",IF(R6&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T6" s="29" t="inlineStr">
@@ -3831,11 +4017,11 @@
         <v/>
       </c>
       <c r="R7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(U7&gt;0,"",IFERROR(ROUND((F7*DATA!$AC$4+M7*DATA!$AC$5+J7*DATA!$AC$6+(6-Q7)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(U7&gt;0,"",IFERROR(ROUND((F7*DATA!$AI$4+M7*DATA!$AI$5+J7*DATA!$AI$6+(6-Q7)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S7" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(U7&gt;0,"ข้อมูลไม่ครบ",IF(R7="","",IF(R7&gt;=DATA!$AC$10,"สูง",IF(R7&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(U7&gt;0,"ข้อมูลไม่ครบ",IF(R7="","",IF(R7&gt;=DATA!$AI$10,"สูง",IF(R7&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T7" s="33">
@@ -3917,11 +4103,11 @@
         <v/>
       </c>
       <c r="R8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(U8&gt;0,"",IFERROR(ROUND((F8*DATA!$AC$4+M8*DATA!$AC$5+J8*DATA!$AC$6+(6-Q8)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(U8&gt;0,"",IFERROR(ROUND((F8*DATA!$AI$4+M8*DATA!$AI$5+J8*DATA!$AI$6+(6-Q8)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S8" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(U8&gt;0,"ข้อมูลไม่ครบ",IF(R8="","",IF(R8&gt;=DATA!$AC$10,"สูง",IF(R8&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(U8&gt;0,"ข้อมูลไม่ครบ",IF(R8="","",IF(R8&gt;=DATA!$AI$10,"สูง",IF(R8&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T8" s="33">
@@ -4003,11 +4189,11 @@
         <v/>
       </c>
       <c r="R9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(U9&gt;0,"",IFERROR(ROUND((F9*DATA!$AC$4+M9*DATA!$AC$5+J9*DATA!$AC$6+(6-Q9)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(U9&gt;0,"",IFERROR(ROUND((F9*DATA!$AI$4+M9*DATA!$AI$5+J9*DATA!$AI$6+(6-Q9)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S9" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(U9&gt;0,"ข้อมูลไม่ครบ",IF(R9="","",IF(R9&gt;=DATA!$AC$10,"สูง",IF(R9&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(U9&gt;0,"ข้อมูลไม่ครบ",IF(R9="","",IF(R9&gt;=DATA!$AI$10,"สูง",IF(R9&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T9" s="33">
@@ -4089,11 +4275,11 @@
         <v/>
       </c>
       <c r="R10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(U10&gt;0,"",IFERROR(ROUND((F10*DATA!$AC$4+M10*DATA!$AC$5+J10*DATA!$AC$6+(6-Q10)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(U10&gt;0,"",IFERROR(ROUND((F10*DATA!$AI$4+M10*DATA!$AI$5+J10*DATA!$AI$6+(6-Q10)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S10" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(U10&gt;0,"ข้อมูลไม่ครบ",IF(R10="","",IF(R10&gt;=DATA!$AC$10,"สูง",IF(R10&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(U10&gt;0,"ข้อมูลไม่ครบ",IF(R10="","",IF(R10&gt;=DATA!$AI$10,"สูง",IF(R10&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T10" s="33">
@@ -4175,11 +4361,11 @@
         <v/>
       </c>
       <c r="R11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(U11&gt;0,"",IFERROR(ROUND((F11*DATA!$AC$4+M11*DATA!$AC$5+J11*DATA!$AC$6+(6-Q11)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(U11&gt;0,"",IFERROR(ROUND((F11*DATA!$AI$4+M11*DATA!$AI$5+J11*DATA!$AI$6+(6-Q11)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S11" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(U11&gt;0,"ข้อมูลไม่ครบ",IF(R11="","",IF(R11&gt;=DATA!$AC$10,"สูง",IF(R11&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(U11&gt;0,"ข้อมูลไม่ครบ",IF(R11="","",IF(R11&gt;=DATA!$AI$10,"สูง",IF(R11&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T11" s="33">
@@ -4261,11 +4447,11 @@
         <v/>
       </c>
       <c r="R12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(U12&gt;0,"",IFERROR(ROUND((F12*DATA!$AC$4+M12*DATA!$AC$5+J12*DATA!$AC$6+(6-Q12)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(U12&gt;0,"",IFERROR(ROUND((F12*DATA!$AI$4+M12*DATA!$AI$5+J12*DATA!$AI$6+(6-Q12)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S12" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(U12&gt;0,"ข้อมูลไม่ครบ",IF(R12="","",IF(R12&gt;=DATA!$AC$10,"สูง",IF(R12&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(U12&gt;0,"ข้อมูลไม่ครบ",IF(R12="","",IF(R12&gt;=DATA!$AI$10,"สูง",IF(R12&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T12" s="33">
@@ -4347,11 +4533,11 @@
         <v/>
       </c>
       <c r="R13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(U13&gt;0,"",IFERROR(ROUND((F13*DATA!$AC$4+M13*DATA!$AC$5+J13*DATA!$AC$6+(6-Q13)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(U13&gt;0,"",IFERROR(ROUND((F13*DATA!$AI$4+M13*DATA!$AI$5+J13*DATA!$AI$6+(6-Q13)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S13" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(U13&gt;0,"ข้อมูลไม่ครบ",IF(R13="","",IF(R13&gt;=DATA!$AC$10,"สูง",IF(R13&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(U13&gt;0,"ข้อมูลไม่ครบ",IF(R13="","",IF(R13&gt;=DATA!$AI$10,"สูง",IF(R13&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T13" s="33">
@@ -4433,11 +4619,11 @@
         <v/>
       </c>
       <c r="R14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(U14&gt;0,"",IFERROR(ROUND((F14*DATA!$AC$4+M14*DATA!$AC$5+J14*DATA!$AC$6+(6-Q14)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(U14&gt;0,"",IFERROR(ROUND((F14*DATA!$AI$4+M14*DATA!$AI$5+J14*DATA!$AI$6+(6-Q14)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S14" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(U14&gt;0,"ข้อมูลไม่ครบ",IF(R14="","",IF(R14&gt;=DATA!$AC$10,"สูง",IF(R14&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(U14&gt;0,"ข้อมูลไม่ครบ",IF(R14="","",IF(R14&gt;=DATA!$AI$10,"สูง",IF(R14&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T14" s="33">
@@ -4519,11 +4705,11 @@
         <v/>
       </c>
       <c r="R15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(U15&gt;0,"",IFERROR(ROUND((F15*DATA!$AC$4+M15*DATA!$AC$5+J15*DATA!$AC$6+(6-Q15)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(U15&gt;0,"",IFERROR(ROUND((F15*DATA!$AI$4+M15*DATA!$AI$5+J15*DATA!$AI$6+(6-Q15)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S15" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(U15&gt;0,"ข้อมูลไม่ครบ",IF(R15="","",IF(R15&gt;=DATA!$AC$10,"สูง",IF(R15&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(U15&gt;0,"ข้อมูลไม่ครบ",IF(R15="","",IF(R15&gt;=DATA!$AI$10,"สูง",IF(R15&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T15" s="33">
@@ -4605,11 +4791,11 @@
         <v/>
       </c>
       <c r="R16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(U16&gt;0,"",IFERROR(ROUND((F16*DATA!$AC$4+M16*DATA!$AC$5+J16*DATA!$AC$6+(6-Q16)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(U16&gt;0,"",IFERROR(ROUND((F16*DATA!$AI$4+M16*DATA!$AI$5+J16*DATA!$AI$6+(6-Q16)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S16" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(U16&gt;0,"ข้อมูลไม่ครบ",IF(R16="","",IF(R16&gt;=DATA!$AC$10,"สูง",IF(R16&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(U16&gt;0,"ข้อมูลไม่ครบ",IF(R16="","",IF(R16&gt;=DATA!$AI$10,"สูง",IF(R16&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T16" s="33">
@@ -4691,11 +4877,11 @@
         <v/>
       </c>
       <c r="R17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(U17&gt;0,"",IFERROR(ROUND((F17*DATA!$AC$4+M17*DATA!$AC$5+J17*DATA!$AC$6+(6-Q17)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(U17&gt;0,"",IFERROR(ROUND((F17*DATA!$AI$4+M17*DATA!$AI$5+J17*DATA!$AI$6+(6-Q17)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S17" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(U17&gt;0,"ข้อมูลไม่ครบ",IF(R17="","",IF(R17&gt;=DATA!$AC$10,"สูง",IF(R17&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(U17&gt;0,"ข้อมูลไม่ครบ",IF(R17="","",IF(R17&gt;=DATA!$AI$10,"สูง",IF(R17&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T17" s="33">
@@ -4777,11 +4963,11 @@
         <v/>
       </c>
       <c r="R18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(U18&gt;0,"",IFERROR(ROUND((F18*DATA!$AC$4+M18*DATA!$AC$5+J18*DATA!$AC$6+(6-Q18)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(U18&gt;0,"",IFERROR(ROUND((F18*DATA!$AI$4+M18*DATA!$AI$5+J18*DATA!$AI$6+(6-Q18)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S18" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(U18&gt;0,"ข้อมูลไม่ครบ",IF(R18="","",IF(R18&gt;=DATA!$AC$10,"สูง",IF(R18&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(U18&gt;0,"ข้อมูลไม่ครบ",IF(R18="","",IF(R18&gt;=DATA!$AI$10,"สูง",IF(R18&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T18" s="33">
@@ -4863,11 +5049,11 @@
         <v/>
       </c>
       <c r="R19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(U19&gt;0,"",IFERROR(ROUND((F19*DATA!$AC$4+M19*DATA!$AC$5+J19*DATA!$AC$6+(6-Q19)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(U19&gt;0,"",IFERROR(ROUND((F19*DATA!$AI$4+M19*DATA!$AI$5+J19*DATA!$AI$6+(6-Q19)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S19" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(U19&gt;0,"ข้อมูลไม่ครบ",IF(R19="","",IF(R19&gt;=DATA!$AC$10,"สูง",IF(R19&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(U19&gt;0,"ข้อมูลไม่ครบ",IF(R19="","",IF(R19&gt;=DATA!$AI$10,"สูง",IF(R19&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T19" s="33">
@@ -4949,11 +5135,11 @@
         <v/>
       </c>
       <c r="R20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(U20&gt;0,"",IFERROR(ROUND((F20*DATA!$AC$4+M20*DATA!$AC$5+J20*DATA!$AC$6+(6-Q20)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(U20&gt;0,"",IFERROR(ROUND((F20*DATA!$AI$4+M20*DATA!$AI$5+J20*DATA!$AI$6+(6-Q20)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S20" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(U20&gt;0,"ข้อมูลไม่ครบ",IF(R20="","",IF(R20&gt;=DATA!$AC$10,"สูง",IF(R20&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(U20&gt;0,"ข้อมูลไม่ครบ",IF(R20="","",IF(R20&gt;=DATA!$AI$10,"สูง",IF(R20&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T20" s="33">
@@ -5035,11 +5221,11 @@
         <v/>
       </c>
       <c r="R21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(U21&gt;0,"",IFERROR(ROUND((F21*DATA!$AC$4+M21*DATA!$AC$5+J21*DATA!$AC$6+(6-Q21)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(U21&gt;0,"",IFERROR(ROUND((F21*DATA!$AI$4+M21*DATA!$AI$5+J21*DATA!$AI$6+(6-Q21)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S21" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(U21&gt;0,"ข้อมูลไม่ครบ",IF(R21="","",IF(R21&gt;=DATA!$AC$10,"สูง",IF(R21&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(U21&gt;0,"ข้อมูลไม่ครบ",IF(R21="","",IF(R21&gt;=DATA!$AI$10,"สูง",IF(R21&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T21" s="33">
@@ -5121,11 +5307,11 @@
         <v/>
       </c>
       <c r="R22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(U22&gt;0,"",IFERROR(ROUND((F22*DATA!$AC$4+M22*DATA!$AC$5+J22*DATA!$AC$6+(6-Q22)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(U22&gt;0,"",IFERROR(ROUND((F22*DATA!$AI$4+M22*DATA!$AI$5+J22*DATA!$AI$6+(6-Q22)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S22" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(U22&gt;0,"ข้อมูลไม่ครบ",IF(R22="","",IF(R22&gt;=DATA!$AC$10,"สูง",IF(R22&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(U22&gt;0,"ข้อมูลไม่ครบ",IF(R22="","",IF(R22&gt;=DATA!$AI$10,"สูง",IF(R22&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T22" s="33">
@@ -5207,11 +5393,11 @@
         <v/>
       </c>
       <c r="R23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(U23&gt;0,"",IFERROR(ROUND((F23*DATA!$AC$4+M23*DATA!$AC$5+J23*DATA!$AC$6+(6-Q23)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(U23&gt;0,"",IFERROR(ROUND((F23*DATA!$AI$4+M23*DATA!$AI$5+J23*DATA!$AI$6+(6-Q23)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S23" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(U23&gt;0,"ข้อมูลไม่ครบ",IF(R23="","",IF(R23&gt;=DATA!$AC$10,"สูง",IF(R23&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(U23&gt;0,"ข้อมูลไม่ครบ",IF(R23="","",IF(R23&gt;=DATA!$AI$10,"สูง",IF(R23&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T23" s="33">
@@ -5293,11 +5479,11 @@
         <v/>
       </c>
       <c r="R24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(U24&gt;0,"",IFERROR(ROUND((F24*DATA!$AC$4+M24*DATA!$AC$5+J24*DATA!$AC$6+(6-Q24)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(U24&gt;0,"",IFERROR(ROUND((F24*DATA!$AI$4+M24*DATA!$AI$5+J24*DATA!$AI$6+(6-Q24)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S24" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(U24&gt;0,"ข้อมูลไม่ครบ",IF(R24="","",IF(R24&gt;=DATA!$AC$10,"สูง",IF(R24&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(U24&gt;0,"ข้อมูลไม่ครบ",IF(R24="","",IF(R24&gt;=DATA!$AI$10,"สูง",IF(R24&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T24" s="33">
@@ -5379,11 +5565,11 @@
         <v/>
       </c>
       <c r="R25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(U25&gt;0,"",IFERROR(ROUND((F25*DATA!$AC$4+M25*DATA!$AC$5+J25*DATA!$AC$6+(6-Q25)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(U25&gt;0,"",IFERROR(ROUND((F25*DATA!$AI$4+M25*DATA!$AI$5+J25*DATA!$AI$6+(6-Q25)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S25" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(U25&gt;0,"ข้อมูลไม่ครบ",IF(R25="","",IF(R25&gt;=DATA!$AC$10,"สูง",IF(R25&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(U25&gt;0,"ข้อมูลไม่ครบ",IF(R25="","",IF(R25&gt;=DATA!$AI$10,"สูง",IF(R25&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T25" s="33">
@@ -5465,11 +5651,11 @@
         <v/>
       </c>
       <c r="R26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(U26&gt;0,"",IFERROR(ROUND((F26*DATA!$AC$4+M26*DATA!$AC$5+J26*DATA!$AC$6+(6-Q26)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(U26&gt;0,"",IFERROR(ROUND((F26*DATA!$AI$4+M26*DATA!$AI$5+J26*DATA!$AI$6+(6-Q26)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S26" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(U26&gt;0,"ข้อมูลไม่ครบ",IF(R26="","",IF(R26&gt;=DATA!$AC$10,"สูง",IF(R26&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(U26&gt;0,"ข้อมูลไม่ครบ",IF(R26="","",IF(R26&gt;=DATA!$AI$10,"สูง",IF(R26&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T26" s="33">
@@ -5551,11 +5737,11 @@
         <v/>
       </c>
       <c r="R27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(U27&gt;0,"",IFERROR(ROUND((F27*DATA!$AC$4+M27*DATA!$AC$5+J27*DATA!$AC$6+(6-Q27)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(U27&gt;0,"",IFERROR(ROUND((F27*DATA!$AI$4+M27*DATA!$AI$5+J27*DATA!$AI$6+(6-Q27)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S27" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(U27&gt;0,"ข้อมูลไม่ครบ",IF(R27="","",IF(R27&gt;=DATA!$AC$10,"สูง",IF(R27&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(U27&gt;0,"ข้อมูลไม่ครบ",IF(R27="","",IF(R27&gt;=DATA!$AI$10,"สูง",IF(R27&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T27" s="33">
@@ -5637,11 +5823,11 @@
         <v/>
       </c>
       <c r="R28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(U28&gt;0,"",IFERROR(ROUND((F28*DATA!$AC$4+M28*DATA!$AC$5+J28*DATA!$AC$6+(6-Q28)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(U28&gt;0,"",IFERROR(ROUND((F28*DATA!$AI$4+M28*DATA!$AI$5+J28*DATA!$AI$6+(6-Q28)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S28" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(U28&gt;0,"ข้อมูลไม่ครบ",IF(R28="","",IF(R28&gt;=DATA!$AC$10,"สูง",IF(R28&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(U28&gt;0,"ข้อมูลไม่ครบ",IF(R28="","",IF(R28&gt;=DATA!$AI$10,"สูง",IF(R28&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T28" s="33">
@@ -5723,11 +5909,11 @@
         <v/>
       </c>
       <c r="R29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(U29&gt;0,"",IFERROR(ROUND((F29*DATA!$AC$4+M29*DATA!$AC$5+J29*DATA!$AC$6+(6-Q29)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(U29&gt;0,"",IFERROR(ROUND((F29*DATA!$AI$4+M29*DATA!$AI$5+J29*DATA!$AI$6+(6-Q29)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S29" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(U29&gt;0,"ข้อมูลไม่ครบ",IF(R29="","",IF(R29&gt;=DATA!$AC$10,"สูง",IF(R29&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(U29&gt;0,"ข้อมูลไม่ครบ",IF(R29="","",IF(R29&gt;=DATA!$AI$10,"สูง",IF(R29&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T29" s="33">
@@ -5809,11 +5995,11 @@
         <v/>
       </c>
       <c r="R30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(U30&gt;0,"",IFERROR(ROUND((F30*DATA!$AC$4+M30*DATA!$AC$5+J30*DATA!$AC$6+(6-Q30)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(U30&gt;0,"",IFERROR(ROUND((F30*DATA!$AI$4+M30*DATA!$AI$5+J30*DATA!$AI$6+(6-Q30)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S30" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(U30&gt;0,"ข้อมูลไม่ครบ",IF(R30="","",IF(R30&gt;=DATA!$AC$10,"สูง",IF(R30&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(U30&gt;0,"ข้อมูลไม่ครบ",IF(R30="","",IF(R30&gt;=DATA!$AI$10,"สูง",IF(R30&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T30" s="33">
@@ -5895,11 +6081,11 @@
         <v/>
       </c>
       <c r="R31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(U31&gt;0,"",IFERROR(ROUND((F31*DATA!$AC$4+M31*DATA!$AC$5+J31*DATA!$AC$6+(6-Q31)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(U31&gt;0,"",IFERROR(ROUND((F31*DATA!$AI$4+M31*DATA!$AI$5+J31*DATA!$AI$6+(6-Q31)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S31" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(U31&gt;0,"ข้อมูลไม่ครบ",IF(R31="","",IF(R31&gt;=DATA!$AC$10,"สูง",IF(R31&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(U31&gt;0,"ข้อมูลไม่ครบ",IF(R31="","",IF(R31&gt;=DATA!$AI$10,"สูง",IF(R31&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T31" s="33">
@@ -5981,11 +6167,11 @@
         <v/>
       </c>
       <c r="R32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(U32&gt;0,"",IFERROR(ROUND((F32*DATA!$AC$4+M32*DATA!$AC$5+J32*DATA!$AC$6+(6-Q32)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(U32&gt;0,"",IFERROR(ROUND((F32*DATA!$AI$4+M32*DATA!$AI$5+J32*DATA!$AI$6+(6-Q32)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S32" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(U32&gt;0,"ข้อมูลไม่ครบ",IF(R32="","",IF(R32&gt;=DATA!$AC$10,"สูง",IF(R32&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(U32&gt;0,"ข้อมูลไม่ครบ",IF(R32="","",IF(R32&gt;=DATA!$AI$10,"สูง",IF(R32&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T32" s="33">
@@ -6067,11 +6253,11 @@
         <v/>
       </c>
       <c r="R33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(U33&gt;0,"",IFERROR(ROUND((F33*DATA!$AC$4+M33*DATA!$AC$5+J33*DATA!$AC$6+(6-Q33)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(U33&gt;0,"",IFERROR(ROUND((F33*DATA!$AI$4+M33*DATA!$AI$5+J33*DATA!$AI$6+(6-Q33)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S33" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(U33&gt;0,"ข้อมูลไม่ครบ",IF(R33="","",IF(R33&gt;=DATA!$AC$10,"สูง",IF(R33&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(U33&gt;0,"ข้อมูลไม่ครบ",IF(R33="","",IF(R33&gt;=DATA!$AI$10,"สูง",IF(R33&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T33" s="33">
@@ -6153,11 +6339,11 @@
         <v/>
       </c>
       <c r="R34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(U34&gt;0,"",IFERROR(ROUND((F34*DATA!$AC$4+M34*DATA!$AC$5+J34*DATA!$AC$6+(6-Q34)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(U34&gt;0,"",IFERROR(ROUND((F34*DATA!$AI$4+M34*DATA!$AI$5+J34*DATA!$AI$6+(6-Q34)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S34" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(U34&gt;0,"ข้อมูลไม่ครบ",IF(R34="","",IF(R34&gt;=DATA!$AC$10,"สูง",IF(R34&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(U34&gt;0,"ข้อมูลไม่ครบ",IF(R34="","",IF(R34&gt;=DATA!$AI$10,"สูง",IF(R34&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T34" s="33">
@@ -6239,11 +6425,11 @@
         <v/>
       </c>
       <c r="R35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(U35&gt;0,"",IFERROR(ROUND((F35*DATA!$AC$4+M35*DATA!$AC$5+J35*DATA!$AC$6+(6-Q35)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(U35&gt;0,"",IFERROR(ROUND((F35*DATA!$AI$4+M35*DATA!$AI$5+J35*DATA!$AI$6+(6-Q35)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S35" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(U35&gt;0,"ข้อมูลไม่ครบ",IF(R35="","",IF(R35&gt;=DATA!$AC$10,"สูง",IF(R35&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(U35&gt;0,"ข้อมูลไม่ครบ",IF(R35="","",IF(R35&gt;=DATA!$AI$10,"สูง",IF(R35&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T35" s="33">
@@ -6325,11 +6511,11 @@
         <v/>
       </c>
       <c r="R36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(U36&gt;0,"",IFERROR(ROUND((F36*DATA!$AC$4+M36*DATA!$AC$5+J36*DATA!$AC$6+(6-Q36)*DATA!$AC$7)*20,1),"")))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(U36&gt;0,"",IFERROR(ROUND((F36*DATA!$AI$4+M36*DATA!$AI$5+J36*DATA!$AI$6+(6-Q36)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
       <c r="S36" s="33">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(U36&gt;0,"ข้อมูลไม่ครบ",IF(R36="","",IF(R36&gt;=DATA!$AC$10,"สูง",IF(R36&gt;=DATA!$AC$11,"กลาง","ต่ำ")))))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(U36&gt;0,"ข้อมูลไม่ครบ",IF(R36="","",IF(R36&gt;=DATA!$AI$10,"สูง",IF(R36&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
       <c r="T36" s="33">
@@ -6456,7 +6642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AI35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6484,8 +6670,13 @@
     <col width="32" customWidth="1" min="23" max="23"/>
     <col width="32" customWidth="1" min="24" max="24"/>
     <col width="32" customWidth="1" min="25" max="25"/>
-    <col width="34" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="28" max="28"/>
+    <col width="32" customWidth="1" min="29" max="29"/>
+    <col width="32" customWidth="1" min="30" max="30"/>
+    <col width="34" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6494,7 +6685,7 @@
           <t>รายการตัวเลือก (Dropdown) — เพิ่ม/แก้ตัวเลือกได้ที่นี่ แล้วทุก sheet จะเปลี่ยนตาม</t>
         </is>
       </c>
-      <c r="AB1" s="37" t="inlineStr">
+      <c r="AH1" s="37" t="inlineStr">
         <is>
           <t>ค่าตั้งต้นของการคำนวณคะแนน (แก้ได้ ทุกสูตรจะเปลี่ยนตาม)</t>
         </is>
@@ -6623,10 +6814,35 @@
       </c>
       <c r="Y3" s="38" t="inlineStr">
         <is>
-          <t>จำนวนรูป/วัน</t>
-        </is>
-      </c>
-      <c r="AB3" s="39" t="inlineStr">
+          <t>จำนวนกล้อง/จุดตรวจพร้อมกัน</t>
+        </is>
+      </c>
+      <c r="Z3" s="38" t="inlineStr">
+        <is>
+          <t>ติดตั้งแบบไหน</t>
+        </is>
+      </c>
+      <c r="AA3" s="38" t="inlineStr">
+        <is>
+          <t>มีเครื่อง/GPU เดิมใช้ได้มั้ย</t>
+        </is>
+      </c>
+      <c r="AB3" s="38" t="inlineStr">
+        <is>
+          <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
+        </is>
+      </c>
+      <c r="AC3" s="38" t="inlineStr">
+        <is>
+          <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
+        </is>
+      </c>
+      <c r="AD3" s="38" t="inlineStr">
+        <is>
+          <t>แชร์เครื่องกับงานอื่นได้มั้ย</t>
+        </is>
+      </c>
+      <c r="AH3" s="39" t="inlineStr">
         <is>
           <t>น้ำหนักแต่ละปัจจัย</t>
         </is>
@@ -6758,12 +6974,37 @@
           <t>ไม่เกี่ยวข้อง - ไม่ใช่งานภาพ</t>
         </is>
       </c>
+      <c r="Z4" s="40" t="inlineStr">
+        <is>
+          <t>รันบน server กลางได้ - ส่งข้อมูลผ่านเครือข่ายมาได้</t>
+        </is>
+      </c>
+      <c r="AA4" s="40" t="inlineStr">
+        <is>
+          <t>มี GPU ว่างอยู่ - ใช้ได้เลย</t>
+        </is>
+      </c>
       <c r="AB4" s="40" t="inlineStr">
         <is>
+          <t>1 ปี</t>
+        </is>
+      </c>
+      <c r="AC4" s="40" t="inlineStr">
+        <is>
+          <t>ครั้งเดียวจบ - เทรนเสร็จใช้ยาว</t>
+        </is>
+      </c>
+      <c r="AD4" s="40" t="inlineStr">
+        <is>
+          <t>แชร์ได้ - ไม่ซีเรียสเรื่องความเร็ว</t>
+        </is>
+      </c>
+      <c r="AH4" s="40" t="inlineStr">
+        <is>
           <t>Impact (ผลกระทบ)</t>
         </is>
       </c>
-      <c r="AC4" s="41" t="n">
+      <c r="AI4" s="41" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -6890,15 +7131,40 @@
       </c>
       <c r="Y5" s="40" t="inlineStr">
         <is>
-          <t>น้อยกว่า 100 รูป</t>
+          <t>1 จุด</t>
+        </is>
+      </c>
+      <c r="Z5" s="40" t="inlineStr">
+        <is>
+          <t>ต้องมีเครื่องที่หน้างาน - ติดข้างเครื่องจักร/สายพาน</t>
+        </is>
+      </c>
+      <c r="AA5" s="40" t="inlineStr">
+        <is>
+          <t>มี server แต่ไม่มี GPU</t>
         </is>
       </c>
       <c r="AB5" s="40" t="inlineStr">
         <is>
+          <t>2 - 3 ปี</t>
+        </is>
+      </c>
+      <c r="AC5" s="40" t="inlineStr">
+        <is>
+          <t>ปีละครั้ง</t>
+        </is>
+      </c>
+      <c r="AD5" s="40" t="inlineStr">
+        <is>
+          <t>แชร์ได้บางส่วน - ช่วงพีคต้องได้ก่อน</t>
+        </is>
+      </c>
+      <c r="AH5" s="40" t="inlineStr">
+        <is>
           <t>Feasibility (ความเป็นไปได้)</t>
         </is>
       </c>
-      <c r="AC5" s="41" t="n">
+      <c r="AI5" s="41" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -7025,15 +7291,40 @@
       </c>
       <c r="Y6" s="40" t="inlineStr">
         <is>
-          <t>100 - 1,000 รูป</t>
+          <t>2 - 3 จุด</t>
+        </is>
+      </c>
+      <c r="Z6" s="40" t="inlineStr">
+        <is>
+          <t>ยังไม่แน่ใจ</t>
+        </is>
+      </c>
+      <c r="AA6" s="40" t="inlineStr">
+        <is>
+          <t>ไม่มีเลย - ต้องซื้อใหม่ทั้งหมด</t>
         </is>
       </c>
       <c r="AB6" s="40" t="inlineStr">
         <is>
+          <t>5 ปี</t>
+        </is>
+      </c>
+      <c r="AC6" s="40" t="inlineStr">
+        <is>
+          <t>ทุกไตรมาส</t>
+        </is>
+      </c>
+      <c r="AD6" s="40" t="inlineStr">
+        <is>
+          <t>แชร์ไม่ได้ - ต้องมีเครื่องของตัวเอง</t>
+        </is>
+      </c>
+      <c r="AH6" s="40" t="inlineStr">
+        <is>
           <t>Data (ความพร้อมข้อมูล)</t>
         </is>
       </c>
-      <c r="AC6" s="41" t="n">
+      <c r="AI6" s="41" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -7115,15 +7406,35 @@
       </c>
       <c r="Y7" s="40" t="inlineStr">
         <is>
-          <t>1,000 - 10,000 รูป</t>
+          <t>4 - 8 จุด</t>
+        </is>
+      </c>
+      <c r="AA7" s="40" t="inlineStr">
+        <is>
+          <t>ยังไม่แน่ใจ - ต้องถาม IT</t>
         </is>
       </c>
       <c r="AB7" s="40" t="inlineStr">
         <is>
+          <t>เก็บถาวร - ห้ามลบ (ข้อกำหนดลูกค้า/กฎหมาย)</t>
+        </is>
+      </c>
+      <c r="AC7" s="40" t="inlineStr">
+        <is>
+          <t>ทุกเดือนหรือถี่กว่า</t>
+        </is>
+      </c>
+      <c r="AD7" s="40" t="inlineStr">
+        <is>
+          <t>ยังไม่แน่ใจ</t>
+        </is>
+      </c>
+      <c r="AH7" s="40" t="inlineStr">
+        <is>
           <t>Risk (ความเสี่ยง)</t>
         </is>
       </c>
-      <c r="AC7" s="41" t="n">
+      <c r="AI7" s="41" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -7175,7 +7486,12 @@
       </c>
       <c r="Y8" s="40" t="inlineStr">
         <is>
-          <t>มากกว่า 10,000 รูป</t>
+          <t>มากกว่า 8 จุด</t>
+        </is>
+      </c>
+      <c r="AC8" s="40" t="inlineStr">
+        <is>
+          <t>ยังไม่แน่ใจ</t>
         </is>
       </c>
     </row>
@@ -7190,55 +7506,55 @@
           <t>ผสมหลายแบบ</t>
         </is>
       </c>
-      <c r="AB9" s="39" t="inlineStr">
+      <c r="AH9" s="39" t="inlineStr">
         <is>
           <t>เกณฑ์แบ่งระดับ</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="AB10" s="40" t="inlineStr">
+      <c r="AH10" s="40" t="inlineStr">
         <is>
           <t>คะแนน &gt;= นี้ = สูง</t>
         </is>
       </c>
-      <c r="AC10" s="42" t="n">
+      <c r="AI10" s="42" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="11">
-      <c r="AB11" s="40" t="inlineStr">
+      <c r="AH11" s="40" t="inlineStr">
         <is>
           <t>คะแนน &gt;= นี้ = กลาง</t>
         </is>
       </c>
-      <c r="AC11" s="42" t="n">
+      <c r="AI11" s="42" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="14">
-      <c r="AB14" s="39" t="inlineStr">
+      <c r="AH14" s="39" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="AB15" s="40" t="inlineStr">
+      <c r="AH15" s="40" t="inlineStr">
         <is>
           <t>ช่วงชั่วโมงและช่วงมูลค่าเป็น dropdown แล้ว</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="AB16" s="40" t="inlineStr">
+      <c r="AH16" s="40" t="inlineStr">
         <is>
           <t>แก้ตัวเลือกและคะแนนได้ที่คอลัมน์ R และ S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="AB17" s="40" t="inlineStr">
+      <c r="AH17" s="40" t="inlineStr">
         <is>
           <t>คะแนน "-" แปลว่าไม่นำมาคิดคะแนน ไม่ใช่ได้ 0</t>
         </is>
@@ -7374,7 +7690,32 @@
       </c>
       <c r="Y29" s="38" t="inlineStr">
         <is>
-          <t>จำนวนรูป/วัน</t>
+          <t>จำนวนกล้อง/จุดตรวจพร้อมกัน</t>
+        </is>
+      </c>
+      <c r="Z29" s="38" t="inlineStr">
+        <is>
+          <t>ติดตั้งแบบไหน</t>
+        </is>
+      </c>
+      <c r="AA29" s="38" t="inlineStr">
+        <is>
+          <t>มีเครื่อง/GPU เดิมใช้ได้มั้ย</t>
+        </is>
+      </c>
+      <c r="AB29" s="38" t="inlineStr">
+        <is>
+          <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
+        </is>
+      </c>
+      <c r="AC29" s="38" t="inlineStr">
+        <is>
+          <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
+        </is>
+      </c>
+      <c r="AD29" s="38" t="inlineStr">
+        <is>
+          <t>แชร์เครื่องกับงานอื่นได้มั้ย</t>
         </is>
       </c>
     </row>
@@ -7486,6 +7827,31 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD30" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="43" t="inlineStr">
@@ -7593,6 +7959,31 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="43" t="inlineStr">
@@ -7700,6 +8091,31 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD32" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="43" t="inlineStr">
@@ -7770,6 +8186,26 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
@@ -7812,6 +8248,11 @@
         </is>
       </c>
       <c r="Y34" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC34" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -100,7 +100,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -172,6 +172,16 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF4FB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -199,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -259,7 +269,13 @@
     <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2239,32 +2255,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="34" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2277,7 +2292,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>ช่องสีเขียวอ่อน (No. / ชื่อ / แผนก) ระบบดึงมาจากชั้นที่ 1 ให้อัตโนมัติ ห้ามพิมพ์ทับ — ถ้าอยากแก้ชื่อให้ไปแก้ที่ sheet '1-UseCase ทั้งหมด'  |  ถ้าช่องไหนไม่เกี่ยวข้องให้ใส่ 0</t>
+          <t>Server เป็นเครื่องซื้อใหม่ ตั้งในบริษัทที่เดียว ไม่ใช้ Cloud  |  เขียว = ระบบดึงมาให้  |  เหลือง = แผนกกรอก  |  ฟ้า = ทีม AI/IT เติมให้ทีหลัง แผนกข้ามไปได้เลย</t>
         </is>
       </c>
     </row>
@@ -2291,40 +2306,39 @@
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>ปริมาณงาน (Workload)</t>
+          <t>โซน A : ปริมาณงาน  (แผนกกรอก)</t>
         </is>
       </c>
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="10" t="n"/>
       <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="22" t="inlineStr">
-        <is>
-          <t>ความต้องการเชิงเทคนิค</t>
-        </is>
-      </c>
-      <c r="K4" s="23" t="n"/>
-      <c r="L4" s="23" t="n"/>
-      <c r="M4" s="23" t="n"/>
-      <c r="N4" s="23" t="n"/>
-      <c r="O4" s="23" t="n"/>
-      <c r="P4" s="13" t="inlineStr">
-        <is>
-          <t>การติดตั้งและใช้เครื่องร่วมกัน</t>
-        </is>
-      </c>
-      <c r="Q4" s="14" t="n"/>
-      <c r="R4" s="14" t="n"/>
-      <c r="S4" s="14" t="n"/>
-      <c r="T4" s="17" t="inlineStr">
-        <is>
-          <t>ข้อจำกัด / งบประมาณ</t>
-        </is>
-      </c>
-      <c r="U4" s="18" t="n"/>
-      <c r="V4" s="18" t="n"/>
-      <c r="W4" s="18" t="n"/>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>โซน A : ความต้องการใช้งาน  (แผนกกรอก)</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>โซน A : ข้อกำหนดและงบ  (แผนกกรอก)</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="n"/>
+      <c r="O4" s="18" t="n"/>
+      <c r="P4" s="18" t="n"/>
+      <c r="Q4" s="22" t="inlineStr">
+        <is>
+          <t>โซน B : ทีม AI / IT เติมให้ทีหลัง — แผนกไม่ต้องกรอก</t>
+        </is>
+      </c>
+      <c r="R4" s="23" t="n"/>
+      <c r="S4" s="23" t="n"/>
+      <c r="T4" s="23" t="n"/>
+      <c r="U4" s="23" t="n"/>
+      <c r="V4" s="23" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -2344,108 +2358,102 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>ประเภทข้อมูล Input</t>
+          <t>ข้อมูลที่ AI ต้องอ่าน/ดู เป็นแบบไหน</t>
         </is>
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>จำนวน Users/วัน</t>
+          <t>จำนวนคนที่ใช้งาน/วัน</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>Peak concurrent
-(คนใช้พร้อมกันสูงสุด)</t>
+          <t>ช่วงพีค มีคนใช้พร้อมกันมากสุดกี่คน</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>Requests/วัน
-(ประมาณ)</t>
+          <t>ใช้งานกี่ครั้ง/วัน</t>
         </is>
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
+          <t>จำนวนกล้อง/จุดตรวจ
+ที่ทำงานพร้อมกัน (งานภาพ)</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>ภาษาที่ต้องการ</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="inlineStr">
+        <is>
+          <t>รอผลได้นานแค่ไหน</t>
+        </is>
+      </c>
+      <c r="K5" s="19" t="inlineStr">
+        <is>
+          <t>ต้องใช้งานช่วงเวลาไหน</t>
+        </is>
+      </c>
+      <c r="L5" s="19" t="inlineStr">
+        <is>
+          <t>ถ้าช่วงไหนคนใช้เยอะ แล้วงานนี้ช้าลง
+จะเป็นปัญหามั้ย</t>
+        </is>
+      </c>
+      <c r="M5" s="19" t="inlineStr">
+        <is>
+          <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
+        </is>
+      </c>
+      <c r="N5" s="19" t="inlineStr">
+        <is>
+          <t>งบประมาณที่ตั้งไว้ (บาท)
+- ถ้ามี</t>
+        </is>
+      </c>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>ข้อจำกัดอื่นๆ / หมายเหตุ</t>
+        </is>
+      </c>
+      <c r="P5" s="19" t="inlineStr">
+        <is>
+          <t>ผู้ให้ข้อมูล (แผนก)</t>
+        </is>
+      </c>
+      <c r="Q5" s="19" t="inlineStr">
+        <is>
           <t>ขนาดข้อมูล Input/วัน</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="R5" s="19" t="inlineStr">
         <is>
           <t>ขนาดคลังเอกสารทั้งหมด
 (สำหรับงานค้นหา/RAG)</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
-        <is>
-          <t>จำนวนกล้อง/จุดตรวจ
-ที่ทำงานพร้อมกัน (งานภาพ)</t>
-        </is>
-      </c>
-      <c r="K5" s="19" t="inlineStr">
+      <c r="S5" s="19" t="inlineStr">
         <is>
           <t>ความละเอียดรูป</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>ภาษาที่ต้องการ</t>
-        </is>
-      </c>
-      <c r="M5" s="19" t="inlineStr">
-        <is>
-          <t>Latency ที่รับได้</t>
-        </is>
-      </c>
-      <c r="N5" s="19" t="inlineStr">
-        <is>
-          <t>Availability ที่ต้องการ</t>
-        </is>
-      </c>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="T5" s="19" t="inlineStr">
         <is>
           <t>ติดตั้งแบบไหน
 (server ตั้งที่เดียว ไม่ใช้ Cloud)</t>
         </is>
       </c>
-      <c r="P5" s="19" t="inlineStr">
-        <is>
-          <t>ความต้องการโมเดล</t>
-        </is>
-      </c>
-      <c r="Q5" s="19" t="inlineStr">
+      <c r="U5" s="19" t="inlineStr">
+        <is>
+          <t>ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย</t>
+        </is>
+      </c>
+      <c r="V5" s="19" t="inlineStr">
         <is>
           <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
-        </is>
-      </c>
-      <c r="R5" s="19" t="inlineStr">
-        <is>
-          <t>มีเครื่อง/GPU เดิมใช้ได้มั้ย</t>
-        </is>
-      </c>
-      <c r="S5" s="19" t="inlineStr">
-        <is>
-          <t>แชร์เครื่องกับ use case อื่นได้มั้ย</t>
-        </is>
-      </c>
-      <c r="T5" s="19" t="inlineStr">
-        <is>
-          <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
-        </is>
-      </c>
-      <c r="U5" s="19" t="inlineStr">
-        <is>
-          <t>งบประมาณที่ตั้งไว้ (บาท)
-- ถ้ามี</t>
-        </is>
-      </c>
-      <c r="V5" s="19" t="inlineStr">
-        <is>
-          <t>ข้อจำกัดอื่นๆ / หมายเหตุ</t>
-        </is>
-      </c>
-      <c r="W5" s="19" t="inlineStr">
-        <is>
-          <t>ผู้ให้ข้อมูลเทคนิค</t>
         </is>
       </c>
     </row>
@@ -2484,93 +2492,88 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
+          <t>2 - 3 จุด</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>ไม่เกี่ยวกับภาษา</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>Real-time (0 - 2 วินาที)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>Business Hour (8:00 - 18:00)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>เป็นปัญหา - งานนี้ช้าหรือหยุดไม่ได้เลย (อยู่ในสายการผลิต)</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="inlineStr">
+        <is>
+          <t>2 - 3 ปี</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="n">
+        <v>500000</v>
+      </c>
+      <c r="O6" s="20" t="inlineStr">
+        <is>
+          <t>ต้องติดกล้องที่สายพานเดิม มีพื้นที่จำกัด</t>
+        </is>
+      </c>
+      <c r="P6" s="20" t="inlineStr">
+        <is>
+          <t>คุณสมชาย</t>
+        </is>
+      </c>
+      <c r="Q6" s="25" t="inlineStr">
+        <is>
           <t>1 - 10 GB</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="R6" s="25" t="inlineStr">
         <is>
           <t>ไม่เกี่ยวข้อง - ไม่ใช่งานค้นหาเอกสาร</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
-        <is>
-          <t>2 - 3 จุด</t>
-        </is>
-      </c>
-      <c r="K6" s="20" t="inlineStr">
+      <c r="S6" s="25" t="inlineStr">
         <is>
           <t>1 - 5 MP</t>
         </is>
       </c>
-      <c r="L6" s="20" t="inlineStr">
-        <is>
-          <t>ไม่เกี่ยวกับภาษา</t>
-        </is>
-      </c>
-      <c r="M6" s="20" t="inlineStr">
-        <is>
-          <t>Real-time (0 - 2 วินาที)</t>
-        </is>
-      </c>
-      <c r="N6" s="20" t="inlineStr">
-        <is>
-          <t>Business Hour (8:00 - 18:00)</t>
-        </is>
-      </c>
-      <c r="O6" s="20" t="inlineStr">
+      <c r="T6" s="25" t="inlineStr">
         <is>
           <t>ต้องมีเครื่องที่หน้างาน - ติดข้างเครื่องจักร/สายพาน</t>
         </is>
       </c>
-      <c r="P6" s="20" t="inlineStr">
-        <is>
-          <t>ต้อง Fine-tune ด้วยข้อมูลบริษัท</t>
-        </is>
-      </c>
-      <c r="Q6" s="20" t="inlineStr">
+      <c r="U6" s="25" t="inlineStr">
+        <is>
+          <t>ต้อง Fine-tune - สอนด้วยข้อมูล/รูปของบริษัทเอง</t>
+        </is>
+      </c>
+      <c r="V6" s="25" t="inlineStr">
         <is>
           <t>ทุกไตรมาส</t>
         </is>
       </c>
-      <c r="R6" s="20" t="inlineStr">
-        <is>
-          <t>ไม่มีเลย - ต้องซื้อใหม่ทั้งหมด</t>
-        </is>
-      </c>
-      <c r="S6" s="20" t="inlineStr">
-        <is>
-          <t>แชร์ไม่ได้ - ต้องมีเครื่องของตัวเอง</t>
-        </is>
-      </c>
-      <c r="T6" s="20" t="inlineStr">
-        <is>
-          <t>2 - 3 ปี</t>
-        </is>
-      </c>
-      <c r="U6" s="20" t="n">
-        <v>500000</v>
-      </c>
-      <c r="V6" s="20" t="inlineStr">
-        <is>
-          <t>ต้องติดกล้องที่สายพานเดิม มีพื้นที่จำกัด</t>
-        </is>
-      </c>
-      <c r="W6" s="20" t="inlineStr">
-        <is>
-          <t>คุณสมชาย</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="25">
+      <c r="A7" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",'1-UseCase ทั้งหมด'!A7)</f>
         <v/>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",'1-UseCase ทั้งหมด'!B7)</f>
         <v/>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",'1-UseCase ทั้งหมด'!D7)</f>
         <v/>
       </c>
@@ -2587,24 +2590,23 @@
       <c r="N7" s="21" t="n"/>
       <c r="O7" s="21" t="n"/>
       <c r="P7" s="21" t="n"/>
-      <c r="Q7" s="21" t="n"/>
-      <c r="R7" s="21" t="n"/>
-      <c r="S7" s="21" t="n"/>
-      <c r="T7" s="21" t="n"/>
-      <c r="U7" s="21" t="n"/>
-      <c r="V7" s="21" t="n"/>
-      <c r="W7" s="21" t="n"/>
+      <c r="Q7" s="27" t="n"/>
+      <c r="R7" s="27" t="n"/>
+      <c r="S7" s="27" t="n"/>
+      <c r="T7" s="27" t="n"/>
+      <c r="U7" s="27" t="n"/>
+      <c r="V7" s="27" t="n"/>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="25">
+      <c r="A8" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",'1-UseCase ทั้งหมด'!A8)</f>
         <v/>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",'1-UseCase ทั้งหมด'!B8)</f>
         <v/>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",'1-UseCase ทั้งหมด'!D8)</f>
         <v/>
       </c>
@@ -2621,24 +2623,23 @@
       <c r="N8" s="21" t="n"/>
       <c r="O8" s="21" t="n"/>
       <c r="P8" s="21" t="n"/>
-      <c r="Q8" s="21" t="n"/>
-      <c r="R8" s="21" t="n"/>
-      <c r="S8" s="21" t="n"/>
-      <c r="T8" s="21" t="n"/>
-      <c r="U8" s="21" t="n"/>
-      <c r="V8" s="21" t="n"/>
-      <c r="W8" s="21" t="n"/>
+      <c r="Q8" s="27" t="n"/>
+      <c r="R8" s="27" t="n"/>
+      <c r="S8" s="27" t="n"/>
+      <c r="T8" s="27" t="n"/>
+      <c r="U8" s="27" t="n"/>
+      <c r="V8" s="27" t="n"/>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="25">
+      <c r="A9" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",'1-UseCase ทั้งหมด'!A9)</f>
         <v/>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",'1-UseCase ทั้งหมด'!B9)</f>
         <v/>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",'1-UseCase ทั้งหมด'!D9)</f>
         <v/>
       </c>
@@ -2655,24 +2656,23 @@
       <c r="N9" s="21" t="n"/>
       <c r="O9" s="21" t="n"/>
       <c r="P9" s="21" t="n"/>
-      <c r="Q9" s="21" t="n"/>
-      <c r="R9" s="21" t="n"/>
-      <c r="S9" s="21" t="n"/>
-      <c r="T9" s="21" t="n"/>
-      <c r="U9" s="21" t="n"/>
-      <c r="V9" s="21" t="n"/>
-      <c r="W9" s="21" t="n"/>
+      <c r="Q9" s="27" t="n"/>
+      <c r="R9" s="27" t="n"/>
+      <c r="S9" s="27" t="n"/>
+      <c r="T9" s="27" t="n"/>
+      <c r="U9" s="27" t="n"/>
+      <c r="V9" s="27" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="25">
+      <c r="A10" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",'1-UseCase ทั้งหมด'!A10)</f>
         <v/>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",'1-UseCase ทั้งหมด'!B10)</f>
         <v/>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",'1-UseCase ทั้งหมด'!D10)</f>
         <v/>
       </c>
@@ -2689,24 +2689,23 @@
       <c r="N10" s="21" t="n"/>
       <c r="O10" s="21" t="n"/>
       <c r="P10" s="21" t="n"/>
-      <c r="Q10" s="21" t="n"/>
-      <c r="R10" s="21" t="n"/>
-      <c r="S10" s="21" t="n"/>
-      <c r="T10" s="21" t="n"/>
-      <c r="U10" s="21" t="n"/>
-      <c r="V10" s="21" t="n"/>
-      <c r="W10" s="21" t="n"/>
+      <c r="Q10" s="27" t="n"/>
+      <c r="R10" s="27" t="n"/>
+      <c r="S10" s="27" t="n"/>
+      <c r="T10" s="27" t="n"/>
+      <c r="U10" s="27" t="n"/>
+      <c r="V10" s="27" t="n"/>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="25">
+      <c r="A11" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",'1-UseCase ทั้งหมด'!A11)</f>
         <v/>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",'1-UseCase ทั้งหมด'!B11)</f>
         <v/>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",'1-UseCase ทั้งหมด'!D11)</f>
         <v/>
       </c>
@@ -2723,24 +2722,23 @@
       <c r="N11" s="21" t="n"/>
       <c r="O11" s="21" t="n"/>
       <c r="P11" s="21" t="n"/>
-      <c r="Q11" s="21" t="n"/>
-      <c r="R11" s="21" t="n"/>
-      <c r="S11" s="21" t="n"/>
-      <c r="T11" s="21" t="n"/>
-      <c r="U11" s="21" t="n"/>
-      <c r="V11" s="21" t="n"/>
-      <c r="W11" s="21" t="n"/>
+      <c r="Q11" s="27" t="n"/>
+      <c r="R11" s="27" t="n"/>
+      <c r="S11" s="27" t="n"/>
+      <c r="T11" s="27" t="n"/>
+      <c r="U11" s="27" t="n"/>
+      <c r="V11" s="27" t="n"/>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="25">
+      <c r="A12" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",'1-UseCase ทั้งหมด'!A12)</f>
         <v/>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",'1-UseCase ทั้งหมด'!B12)</f>
         <v/>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",'1-UseCase ทั้งหมด'!D12)</f>
         <v/>
       </c>
@@ -2757,24 +2755,23 @@
       <c r="N12" s="21" t="n"/>
       <c r="O12" s="21" t="n"/>
       <c r="P12" s="21" t="n"/>
-      <c r="Q12" s="21" t="n"/>
-      <c r="R12" s="21" t="n"/>
-      <c r="S12" s="21" t="n"/>
-      <c r="T12" s="21" t="n"/>
-      <c r="U12" s="21" t="n"/>
-      <c r="V12" s="21" t="n"/>
-      <c r="W12" s="21" t="n"/>
+      <c r="Q12" s="27" t="n"/>
+      <c r="R12" s="27" t="n"/>
+      <c r="S12" s="27" t="n"/>
+      <c r="T12" s="27" t="n"/>
+      <c r="U12" s="27" t="n"/>
+      <c r="V12" s="27" t="n"/>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="25">
+      <c r="A13" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",'1-UseCase ทั้งหมด'!A13)</f>
         <v/>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",'1-UseCase ทั้งหมด'!B13)</f>
         <v/>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",'1-UseCase ทั้งหมด'!D13)</f>
         <v/>
       </c>
@@ -2791,24 +2788,23 @@
       <c r="N13" s="21" t="n"/>
       <c r="O13" s="21" t="n"/>
       <c r="P13" s="21" t="n"/>
-      <c r="Q13" s="21" t="n"/>
-      <c r="R13" s="21" t="n"/>
-      <c r="S13" s="21" t="n"/>
-      <c r="T13" s="21" t="n"/>
-      <c r="U13" s="21" t="n"/>
-      <c r="V13" s="21" t="n"/>
-      <c r="W13" s="21" t="n"/>
+      <c r="Q13" s="27" t="n"/>
+      <c r="R13" s="27" t="n"/>
+      <c r="S13" s="27" t="n"/>
+      <c r="T13" s="27" t="n"/>
+      <c r="U13" s="27" t="n"/>
+      <c r="V13" s="27" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="25">
+      <c r="A14" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",'1-UseCase ทั้งหมด'!A14)</f>
         <v/>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",'1-UseCase ทั้งหมด'!B14)</f>
         <v/>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",'1-UseCase ทั้งหมด'!D14)</f>
         <v/>
       </c>
@@ -2825,24 +2821,23 @@
       <c r="N14" s="21" t="n"/>
       <c r="O14" s="21" t="n"/>
       <c r="P14" s="21" t="n"/>
-      <c r="Q14" s="21" t="n"/>
-      <c r="R14" s="21" t="n"/>
-      <c r="S14" s="21" t="n"/>
-      <c r="T14" s="21" t="n"/>
-      <c r="U14" s="21" t="n"/>
-      <c r="V14" s="21" t="n"/>
-      <c r="W14" s="21" t="n"/>
+      <c r="Q14" s="27" t="n"/>
+      <c r="R14" s="27" t="n"/>
+      <c r="S14" s="27" t="n"/>
+      <c r="T14" s="27" t="n"/>
+      <c r="U14" s="27" t="n"/>
+      <c r="V14" s="27" t="n"/>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="25">
+      <c r="A15" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",'1-UseCase ทั้งหมด'!A15)</f>
         <v/>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",'1-UseCase ทั้งหมด'!B15)</f>
         <v/>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",'1-UseCase ทั้งหมด'!D15)</f>
         <v/>
       </c>
@@ -2859,24 +2854,23 @@
       <c r="N15" s="21" t="n"/>
       <c r="O15" s="21" t="n"/>
       <c r="P15" s="21" t="n"/>
-      <c r="Q15" s="21" t="n"/>
-      <c r="R15" s="21" t="n"/>
-      <c r="S15" s="21" t="n"/>
-      <c r="T15" s="21" t="n"/>
-      <c r="U15" s="21" t="n"/>
-      <c r="V15" s="21" t="n"/>
-      <c r="W15" s="21" t="n"/>
+      <c r="Q15" s="27" t="n"/>
+      <c r="R15" s="27" t="n"/>
+      <c r="S15" s="27" t="n"/>
+      <c r="T15" s="27" t="n"/>
+      <c r="U15" s="27" t="n"/>
+      <c r="V15" s="27" t="n"/>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="25">
+      <c r="A16" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",'1-UseCase ทั้งหมด'!A16)</f>
         <v/>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",'1-UseCase ทั้งหมด'!B16)</f>
         <v/>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",'1-UseCase ทั้งหมด'!D16)</f>
         <v/>
       </c>
@@ -2893,24 +2887,23 @@
       <c r="N16" s="21" t="n"/>
       <c r="O16" s="21" t="n"/>
       <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
-      <c r="S16" s="21" t="n"/>
-      <c r="T16" s="21" t="n"/>
-      <c r="U16" s="21" t="n"/>
-      <c r="V16" s="21" t="n"/>
-      <c r="W16" s="21" t="n"/>
+      <c r="Q16" s="27" t="n"/>
+      <c r="R16" s="27" t="n"/>
+      <c r="S16" s="27" t="n"/>
+      <c r="T16" s="27" t="n"/>
+      <c r="U16" s="27" t="n"/>
+      <c r="V16" s="27" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="25">
+      <c r="A17" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",'1-UseCase ทั้งหมด'!A17)</f>
         <v/>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",'1-UseCase ทั้งหมด'!B17)</f>
         <v/>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",'1-UseCase ทั้งหมด'!D17)</f>
         <v/>
       </c>
@@ -2927,24 +2920,23 @@
       <c r="N17" s="21" t="n"/>
       <c r="O17" s="21" t="n"/>
       <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="21" t="n"/>
-      <c r="S17" s="21" t="n"/>
-      <c r="T17" s="21" t="n"/>
-      <c r="U17" s="21" t="n"/>
-      <c r="V17" s="21" t="n"/>
-      <c r="W17" s="21" t="n"/>
+      <c r="Q17" s="27" t="n"/>
+      <c r="R17" s="27" t="n"/>
+      <c r="S17" s="27" t="n"/>
+      <c r="T17" s="27" t="n"/>
+      <c r="U17" s="27" t="n"/>
+      <c r="V17" s="27" t="n"/>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="25">
+      <c r="A18" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",'1-UseCase ทั้งหมด'!A18)</f>
         <v/>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",'1-UseCase ทั้งหมด'!B18)</f>
         <v/>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",'1-UseCase ทั้งหมด'!D18)</f>
         <v/>
       </c>
@@ -2961,24 +2953,23 @@
       <c r="N18" s="21" t="n"/>
       <c r="O18" s="21" t="n"/>
       <c r="P18" s="21" t="n"/>
-      <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="21" t="n"/>
-      <c r="S18" s="21" t="n"/>
-      <c r="T18" s="21" t="n"/>
-      <c r="U18" s="21" t="n"/>
-      <c r="V18" s="21" t="n"/>
-      <c r="W18" s="21" t="n"/>
+      <c r="Q18" s="27" t="n"/>
+      <c r="R18" s="27" t="n"/>
+      <c r="S18" s="27" t="n"/>
+      <c r="T18" s="27" t="n"/>
+      <c r="U18" s="27" t="n"/>
+      <c r="V18" s="27" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="25">
+      <c r="A19" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",'1-UseCase ทั้งหมด'!A19)</f>
         <v/>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",'1-UseCase ทั้งหมด'!B19)</f>
         <v/>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",'1-UseCase ทั้งหมด'!D19)</f>
         <v/>
       </c>
@@ -2995,24 +2986,23 @@
       <c r="N19" s="21" t="n"/>
       <c r="O19" s="21" t="n"/>
       <c r="P19" s="21" t="n"/>
-      <c r="Q19" s="21" t="n"/>
-      <c r="R19" s="21" t="n"/>
-      <c r="S19" s="21" t="n"/>
-      <c r="T19" s="21" t="n"/>
-      <c r="U19" s="21" t="n"/>
-      <c r="V19" s="21" t="n"/>
-      <c r="W19" s="21" t="n"/>
+      <c r="Q19" s="27" t="n"/>
+      <c r="R19" s="27" t="n"/>
+      <c r="S19" s="27" t="n"/>
+      <c r="T19" s="27" t="n"/>
+      <c r="U19" s="27" t="n"/>
+      <c r="V19" s="27" t="n"/>
     </row>
     <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="25">
+      <c r="A20" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",'1-UseCase ทั้งหมด'!A20)</f>
         <v/>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",'1-UseCase ทั้งหมด'!B20)</f>
         <v/>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",'1-UseCase ทั้งหมด'!D20)</f>
         <v/>
       </c>
@@ -3029,24 +3019,23 @@
       <c r="N20" s="21" t="n"/>
       <c r="O20" s="21" t="n"/>
       <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="21" t="n"/>
-      <c r="S20" s="21" t="n"/>
-      <c r="T20" s="21" t="n"/>
-      <c r="U20" s="21" t="n"/>
-      <c r="V20" s="21" t="n"/>
-      <c r="W20" s="21" t="n"/>
+      <c r="Q20" s="27" t="n"/>
+      <c r="R20" s="27" t="n"/>
+      <c r="S20" s="27" t="n"/>
+      <c r="T20" s="27" t="n"/>
+      <c r="U20" s="27" t="n"/>
+      <c r="V20" s="27" t="n"/>
     </row>
     <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="25">
+      <c r="A21" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",'1-UseCase ทั้งหมด'!A21)</f>
         <v/>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",'1-UseCase ทั้งหมด'!B21)</f>
         <v/>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",'1-UseCase ทั้งหมด'!D21)</f>
         <v/>
       </c>
@@ -3063,24 +3052,23 @@
       <c r="N21" s="21" t="n"/>
       <c r="O21" s="21" t="n"/>
       <c r="P21" s="21" t="n"/>
-      <c r="Q21" s="21" t="n"/>
-      <c r="R21" s="21" t="n"/>
-      <c r="S21" s="21" t="n"/>
-      <c r="T21" s="21" t="n"/>
-      <c r="U21" s="21" t="n"/>
-      <c r="V21" s="21" t="n"/>
-      <c r="W21" s="21" t="n"/>
+      <c r="Q21" s="27" t="n"/>
+      <c r="R21" s="27" t="n"/>
+      <c r="S21" s="27" t="n"/>
+      <c r="T21" s="27" t="n"/>
+      <c r="U21" s="27" t="n"/>
+      <c r="V21" s="27" t="n"/>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="25">
+      <c r="A22" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",'1-UseCase ทั้งหมด'!A22)</f>
         <v/>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",'1-UseCase ทั้งหมด'!B22)</f>
         <v/>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",'1-UseCase ทั้งหมด'!D22)</f>
         <v/>
       </c>
@@ -3097,24 +3085,23 @@
       <c r="N22" s="21" t="n"/>
       <c r="O22" s="21" t="n"/>
       <c r="P22" s="21" t="n"/>
-      <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="21" t="n"/>
-      <c r="S22" s="21" t="n"/>
-      <c r="T22" s="21" t="n"/>
-      <c r="U22" s="21" t="n"/>
-      <c r="V22" s="21" t="n"/>
-      <c r="W22" s="21" t="n"/>
+      <c r="Q22" s="27" t="n"/>
+      <c r="R22" s="27" t="n"/>
+      <c r="S22" s="27" t="n"/>
+      <c r="T22" s="27" t="n"/>
+      <c r="U22" s="27" t="n"/>
+      <c r="V22" s="27" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="25">
+      <c r="A23" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",'1-UseCase ทั้งหมด'!A23)</f>
         <v/>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",'1-UseCase ทั้งหมด'!B23)</f>
         <v/>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",'1-UseCase ทั้งหมด'!D23)</f>
         <v/>
       </c>
@@ -3131,24 +3118,23 @@
       <c r="N23" s="21" t="n"/>
       <c r="O23" s="21" t="n"/>
       <c r="P23" s="21" t="n"/>
-      <c r="Q23" s="21" t="n"/>
-      <c r="R23" s="21" t="n"/>
-      <c r="S23" s="21" t="n"/>
-      <c r="T23" s="21" t="n"/>
-      <c r="U23" s="21" t="n"/>
-      <c r="V23" s="21" t="n"/>
-      <c r="W23" s="21" t="n"/>
+      <c r="Q23" s="27" t="n"/>
+      <c r="R23" s="27" t="n"/>
+      <c r="S23" s="27" t="n"/>
+      <c r="T23" s="27" t="n"/>
+      <c r="U23" s="27" t="n"/>
+      <c r="V23" s="27" t="n"/>
     </row>
     <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="25">
+      <c r="A24" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",'1-UseCase ทั้งหมด'!A24)</f>
         <v/>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",'1-UseCase ทั้งหมด'!B24)</f>
         <v/>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",'1-UseCase ทั้งหมด'!D24)</f>
         <v/>
       </c>
@@ -3165,24 +3151,23 @@
       <c r="N24" s="21" t="n"/>
       <c r="O24" s="21" t="n"/>
       <c r="P24" s="21" t="n"/>
-      <c r="Q24" s="21" t="n"/>
-      <c r="R24" s="21" t="n"/>
-      <c r="S24" s="21" t="n"/>
-      <c r="T24" s="21" t="n"/>
-      <c r="U24" s="21" t="n"/>
-      <c r="V24" s="21" t="n"/>
-      <c r="W24" s="21" t="n"/>
+      <c r="Q24" s="27" t="n"/>
+      <c r="R24" s="27" t="n"/>
+      <c r="S24" s="27" t="n"/>
+      <c r="T24" s="27" t="n"/>
+      <c r="U24" s="27" t="n"/>
+      <c r="V24" s="27" t="n"/>
     </row>
     <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="25">
+      <c r="A25" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",'1-UseCase ทั้งหมด'!A25)</f>
         <v/>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",'1-UseCase ทั้งหมด'!B25)</f>
         <v/>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",'1-UseCase ทั้งหมด'!D25)</f>
         <v/>
       </c>
@@ -3199,24 +3184,23 @@
       <c r="N25" s="21" t="n"/>
       <c r="O25" s="21" t="n"/>
       <c r="P25" s="21" t="n"/>
-      <c r="Q25" s="21" t="n"/>
-      <c r="R25" s="21" t="n"/>
-      <c r="S25" s="21" t="n"/>
-      <c r="T25" s="21" t="n"/>
-      <c r="U25" s="21" t="n"/>
-      <c r="V25" s="21" t="n"/>
-      <c r="W25" s="21" t="n"/>
+      <c r="Q25" s="27" t="n"/>
+      <c r="R25" s="27" t="n"/>
+      <c r="S25" s="27" t="n"/>
+      <c r="T25" s="27" t="n"/>
+      <c r="U25" s="27" t="n"/>
+      <c r="V25" s="27" t="n"/>
     </row>
     <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="25">
+      <c r="A26" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",'1-UseCase ทั้งหมด'!A26)</f>
         <v/>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",'1-UseCase ทั้งหมด'!B26)</f>
         <v/>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",'1-UseCase ทั้งหมด'!D26)</f>
         <v/>
       </c>
@@ -3233,24 +3217,23 @@
       <c r="N26" s="21" t="n"/>
       <c r="O26" s="21" t="n"/>
       <c r="P26" s="21" t="n"/>
-      <c r="Q26" s="21" t="n"/>
-      <c r="R26" s="21" t="n"/>
-      <c r="S26" s="21" t="n"/>
-      <c r="T26" s="21" t="n"/>
-      <c r="U26" s="21" t="n"/>
-      <c r="V26" s="21" t="n"/>
-      <c r="W26" s="21" t="n"/>
+      <c r="Q26" s="27" t="n"/>
+      <c r="R26" s="27" t="n"/>
+      <c r="S26" s="27" t="n"/>
+      <c r="T26" s="27" t="n"/>
+      <c r="U26" s="27" t="n"/>
+      <c r="V26" s="27" t="n"/>
     </row>
     <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="25">
+      <c r="A27" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",'1-UseCase ทั้งหมด'!A27)</f>
         <v/>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",'1-UseCase ทั้งหมด'!B27)</f>
         <v/>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",'1-UseCase ทั้งหมด'!D27)</f>
         <v/>
       </c>
@@ -3267,24 +3250,23 @@
       <c r="N27" s="21" t="n"/>
       <c r="O27" s="21" t="n"/>
       <c r="P27" s="21" t="n"/>
-      <c r="Q27" s="21" t="n"/>
-      <c r="R27" s="21" t="n"/>
-      <c r="S27" s="21" t="n"/>
-      <c r="T27" s="21" t="n"/>
-      <c r="U27" s="21" t="n"/>
-      <c r="V27" s="21" t="n"/>
-      <c r="W27" s="21" t="n"/>
+      <c r="Q27" s="27" t="n"/>
+      <c r="R27" s="27" t="n"/>
+      <c r="S27" s="27" t="n"/>
+      <c r="T27" s="27" t="n"/>
+      <c r="U27" s="27" t="n"/>
+      <c r="V27" s="27" t="n"/>
     </row>
     <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="25">
+      <c r="A28" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",'1-UseCase ทั้งหมด'!A28)</f>
         <v/>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",'1-UseCase ทั้งหมด'!B28)</f>
         <v/>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",'1-UseCase ทั้งหมด'!D28)</f>
         <v/>
       </c>
@@ -3301,24 +3283,23 @@
       <c r="N28" s="21" t="n"/>
       <c r="O28" s="21" t="n"/>
       <c r="P28" s="21" t="n"/>
-      <c r="Q28" s="21" t="n"/>
-      <c r="R28" s="21" t="n"/>
-      <c r="S28" s="21" t="n"/>
-      <c r="T28" s="21" t="n"/>
-      <c r="U28" s="21" t="n"/>
-      <c r="V28" s="21" t="n"/>
-      <c r="W28" s="21" t="n"/>
+      <c r="Q28" s="27" t="n"/>
+      <c r="R28" s="27" t="n"/>
+      <c r="S28" s="27" t="n"/>
+      <c r="T28" s="27" t="n"/>
+      <c r="U28" s="27" t="n"/>
+      <c r="V28" s="27" t="n"/>
     </row>
     <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="25">
+      <c r="A29" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",'1-UseCase ทั้งหมด'!A29)</f>
         <v/>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",'1-UseCase ทั้งหมด'!B29)</f>
         <v/>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",'1-UseCase ทั้งหมด'!D29)</f>
         <v/>
       </c>
@@ -3335,24 +3316,23 @@
       <c r="N29" s="21" t="n"/>
       <c r="O29" s="21" t="n"/>
       <c r="P29" s="21" t="n"/>
-      <c r="Q29" s="21" t="n"/>
-      <c r="R29" s="21" t="n"/>
-      <c r="S29" s="21" t="n"/>
-      <c r="T29" s="21" t="n"/>
-      <c r="U29" s="21" t="n"/>
-      <c r="V29" s="21" t="n"/>
-      <c r="W29" s="21" t="n"/>
+      <c r="Q29" s="27" t="n"/>
+      <c r="R29" s="27" t="n"/>
+      <c r="S29" s="27" t="n"/>
+      <c r="T29" s="27" t="n"/>
+      <c r="U29" s="27" t="n"/>
+      <c r="V29" s="27" t="n"/>
     </row>
     <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="25">
+      <c r="A30" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",'1-UseCase ทั้งหมด'!A30)</f>
         <v/>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",'1-UseCase ทั้งหมด'!B30)</f>
         <v/>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",'1-UseCase ทั้งหมด'!D30)</f>
         <v/>
       </c>
@@ -3369,24 +3349,23 @@
       <c r="N30" s="21" t="n"/>
       <c r="O30" s="21" t="n"/>
       <c r="P30" s="21" t="n"/>
-      <c r="Q30" s="21" t="n"/>
-      <c r="R30" s="21" t="n"/>
-      <c r="S30" s="21" t="n"/>
-      <c r="T30" s="21" t="n"/>
-      <c r="U30" s="21" t="n"/>
-      <c r="V30" s="21" t="n"/>
-      <c r="W30" s="21" t="n"/>
+      <c r="Q30" s="27" t="n"/>
+      <c r="R30" s="27" t="n"/>
+      <c r="S30" s="27" t="n"/>
+      <c r="T30" s="27" t="n"/>
+      <c r="U30" s="27" t="n"/>
+      <c r="V30" s="27" t="n"/>
     </row>
     <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="25">
+      <c r="A31" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",'1-UseCase ทั้งหมด'!A31)</f>
         <v/>
       </c>
-      <c r="B31" s="25">
+      <c r="B31" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",'1-UseCase ทั้งหมด'!B31)</f>
         <v/>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",'1-UseCase ทั้งหมด'!D31)</f>
         <v/>
       </c>
@@ -3403,24 +3382,23 @@
       <c r="N31" s="21" t="n"/>
       <c r="O31" s="21" t="n"/>
       <c r="P31" s="21" t="n"/>
-      <c r="Q31" s="21" t="n"/>
-      <c r="R31" s="21" t="n"/>
-      <c r="S31" s="21" t="n"/>
-      <c r="T31" s="21" t="n"/>
-      <c r="U31" s="21" t="n"/>
-      <c r="V31" s="21" t="n"/>
-      <c r="W31" s="21" t="n"/>
+      <c r="Q31" s="27" t="n"/>
+      <c r="R31" s="27" t="n"/>
+      <c r="S31" s="27" t="n"/>
+      <c r="T31" s="27" t="n"/>
+      <c r="U31" s="27" t="n"/>
+      <c r="V31" s="27" t="n"/>
     </row>
     <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="25">
+      <c r="A32" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",'1-UseCase ทั้งหมด'!A32)</f>
         <v/>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",'1-UseCase ทั้งหมด'!B32)</f>
         <v/>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",'1-UseCase ทั้งหมด'!D32)</f>
         <v/>
       </c>
@@ -3437,24 +3415,23 @@
       <c r="N32" s="21" t="n"/>
       <c r="O32" s="21" t="n"/>
       <c r="P32" s="21" t="n"/>
-      <c r="Q32" s="21" t="n"/>
-      <c r="R32" s="21" t="n"/>
-      <c r="S32" s="21" t="n"/>
-      <c r="T32" s="21" t="n"/>
-      <c r="U32" s="21" t="n"/>
-      <c r="V32" s="21" t="n"/>
-      <c r="W32" s="21" t="n"/>
+      <c r="Q32" s="27" t="n"/>
+      <c r="R32" s="27" t="n"/>
+      <c r="S32" s="27" t="n"/>
+      <c r="T32" s="27" t="n"/>
+      <c r="U32" s="27" t="n"/>
+      <c r="V32" s="27" t="n"/>
     </row>
     <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="25">
+      <c r="A33" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",'1-UseCase ทั้งหมด'!A33)</f>
         <v/>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",'1-UseCase ทั้งหมด'!B33)</f>
         <v/>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",'1-UseCase ทั้งหมด'!D33)</f>
         <v/>
       </c>
@@ -3471,24 +3448,23 @@
       <c r="N33" s="21" t="n"/>
       <c r="O33" s="21" t="n"/>
       <c r="P33" s="21" t="n"/>
-      <c r="Q33" s="21" t="n"/>
-      <c r="R33" s="21" t="n"/>
-      <c r="S33" s="21" t="n"/>
-      <c r="T33" s="21" t="n"/>
-      <c r="U33" s="21" t="n"/>
-      <c r="V33" s="21" t="n"/>
-      <c r="W33" s="21" t="n"/>
+      <c r="Q33" s="27" t="n"/>
+      <c r="R33" s="27" t="n"/>
+      <c r="S33" s="27" t="n"/>
+      <c r="T33" s="27" t="n"/>
+      <c r="U33" s="27" t="n"/>
+      <c r="V33" s="27" t="n"/>
     </row>
     <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="25">
+      <c r="A34" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",'1-UseCase ทั้งหมด'!A34)</f>
         <v/>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",'1-UseCase ทั้งหมด'!B34)</f>
         <v/>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",'1-UseCase ทั้งหมด'!D34)</f>
         <v/>
       </c>
@@ -3505,24 +3481,23 @@
       <c r="N34" s="21" t="n"/>
       <c r="O34" s="21" t="n"/>
       <c r="P34" s="21" t="n"/>
-      <c r="Q34" s="21" t="n"/>
-      <c r="R34" s="21" t="n"/>
-      <c r="S34" s="21" t="n"/>
-      <c r="T34" s="21" t="n"/>
-      <c r="U34" s="21" t="n"/>
-      <c r="V34" s="21" t="n"/>
-      <c r="W34" s="21" t="n"/>
+      <c r="Q34" s="27" t="n"/>
+      <c r="R34" s="27" t="n"/>
+      <c r="S34" s="27" t="n"/>
+      <c r="T34" s="27" t="n"/>
+      <c r="U34" s="27" t="n"/>
+      <c r="V34" s="27" t="n"/>
     </row>
     <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="25">
+      <c r="A35" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",'1-UseCase ทั้งหมด'!A35)</f>
         <v/>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",'1-UseCase ทั้งหมด'!B35)</f>
         <v/>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",'1-UseCase ทั้งหมด'!D35)</f>
         <v/>
       </c>
@@ -3539,24 +3514,23 @@
       <c r="N35" s="21" t="n"/>
       <c r="O35" s="21" t="n"/>
       <c r="P35" s="21" t="n"/>
-      <c r="Q35" s="21" t="n"/>
-      <c r="R35" s="21" t="n"/>
-      <c r="S35" s="21" t="n"/>
-      <c r="T35" s="21" t="n"/>
-      <c r="U35" s="21" t="n"/>
-      <c r="V35" s="21" t="n"/>
-      <c r="W35" s="21" t="n"/>
+      <c r="Q35" s="27" t="n"/>
+      <c r="R35" s="27" t="n"/>
+      <c r="S35" s="27" t="n"/>
+      <c r="T35" s="27" t="n"/>
+      <c r="U35" s="27" t="n"/>
+      <c r="V35" s="27" t="n"/>
     </row>
     <row r="36" ht="40" customHeight="1">
-      <c r="A36" s="25">
+      <c r="A36" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",'1-UseCase ทั้งหมด'!A36)</f>
         <v/>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",'1-UseCase ทั้งหมด'!B36)</f>
         <v/>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",'1-UseCase ทั้งหมด'!D36)</f>
         <v/>
       </c>
@@ -3573,25 +3547,24 @@
       <c r="N36" s="21" t="n"/>
       <c r="O36" s="21" t="n"/>
       <c r="P36" s="21" t="n"/>
-      <c r="Q36" s="21" t="n"/>
-      <c r="R36" s="21" t="n"/>
-      <c r="S36" s="21" t="n"/>
-      <c r="T36" s="21" t="n"/>
-      <c r="U36" s="21" t="n"/>
-      <c r="V36" s="21" t="n"/>
-      <c r="W36" s="21" t="n"/>
+      <c r="Q36" s="27" t="n"/>
+      <c r="R36" s="27" t="n"/>
+      <c r="S36" s="27" t="n"/>
+      <c r="T36" s="27" t="n"/>
+      <c r="U36" s="27" t="n"/>
+      <c r="V36" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="Q4:V4"/>
+    <mergeCell ref="D4:H4"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="P4:S4"/>
-    <mergeCell ref="A2:W2"/>
   </mergeCells>
-  <dataValidations count="17">
+  <dataValidations count="16">
     <dataValidation sqref="D7:D36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ประเภทข้อมูล Input" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$K$4:$K$9</formula1>
     </dataValidation>
@@ -3604,44 +3577,41 @@
     <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Requests/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$V$4:$V$7</formula1>
     </dataValidation>
-    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดข้อมูล Input/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวนกล้อง/จุดตรวจพร้อมกัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$Y$4:$Y$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ภาษาที่ต้องการ" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$L$4:$L$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Latency ที่รับได้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$M$4:$M$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Availability" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$N$4:$N$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ถ้างานนี้ช้าลงจะเป็นปัญหามั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$AD$4:$AD$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเก็บข้อมูลย้อนหลังกี่ปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$AB$4:$AB$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q7:Q36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดข้อมูล Input/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$W$4:$W$7</formula1>
     </dataValidation>
-    <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดคลังเอกสารทั้งหมด (RAG)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดคลังเอกสารทั้งหมด (RAG)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$X$4:$X$8</formula1>
     </dataValidation>
-    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวนกล้อง/จุดตรวจพร้อมกัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$Y$4:$Y$8</formula1>
-    </dataValidation>
-    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความละเอียดรูป" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความละเอียดรูป" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$O$4:$O$8</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ภาษาที่ต้องการ" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$L$4:$L$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Latency ที่รับได้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$M$4:$M$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Availability" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$N$4:$N$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="O7:O36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ติดตั้งแบบไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ติดตั้งแบบไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$Z$4:$Z$6</formula1>
     </dataValidation>
-    <dataValidation sqref="P7:P36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความต้องการโมเดล" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$Q$4:$Q$6</formula1>
+    <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$Q$4:$Q$7</formula1>
     </dataValidation>
-    <dataValidation sqref="Q7:Q36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเทรนโมเดลใหม่บ่อยแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$AC$4:$AC$8</formula1>
-    </dataValidation>
-    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีเครื่อง/GPU เดิมใช้ได้มั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$AA$4:$AA$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="แชร์เครื่องกับงานอื่นได้มั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$AD$4:$AD$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเก็บข้อมูลย้อนหลังกี่ปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$AB$4:$AB$7</formula1>
+    <dataValidation sqref="V7:V36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเทรนโมเดลใหม่บ่อยแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+      <formula1>DATA!$AC$4:$AC$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3732,14 +3702,14 @@
       <c r="O4" s="16" t="n"/>
       <c r="P4" s="16" t="n"/>
       <c r="Q4" s="16" t="n"/>
-      <c r="R4" s="26" t="inlineStr">
+      <c r="R4" s="28" t="inlineStr">
         <is>
           <t>ผลลัพธ์</t>
         </is>
       </c>
-      <c r="S4" s="27" t="n"/>
-      <c r="T4" s="27" t="n"/>
-      <c r="U4" s="27" t="n"/>
+      <c r="S4" s="29" t="n"/>
+      <c r="T4" s="29" t="n"/>
+      <c r="U4" s="29" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -3861,2730 +3831,2730 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28">
+      <c r="A6" s="30">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",'1-UseCase ทั้งหมด'!A6)</f>
         <v/>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="30">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",'1-UseCase ทั้งหมด'!B6)</f>
         <v/>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="30">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",'1-UseCase ทั้งหมด'!D6)</f>
         <v/>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I6,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J6,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="32">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(D6="",IF(AND(E6&lt;&gt;"",E6&lt;&gt;"-"),E6,""),IF(AND(E6&lt;&gt;"",E6&lt;&gt;"-"),ROUND((D6+E6)/2,0),D6)))</f>
         <v/>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L6,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M6,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O6,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J6" s="30">
+      <c r="J6" s="32">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(ROUND(AVERAGE(G6:I6),0),""))</f>
         <v/>
       </c>
-      <c r="K6" s="29">
+      <c r="K6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P6,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L6" s="29">
+      <c r="L6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q6,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="32">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(ROUND(AVERAGE(K6:L6),0),""))</f>
         <v/>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R6,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S6,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T6,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q6" s="30">
+      <c r="Q6" s="32">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(ROUND(AVERAGE(N6:P6),0),""))</f>
         <v/>
       </c>
-      <c r="R6" s="31">
+      <c r="R6" s="33">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(U6&gt;0,"",IFERROR(ROUND((F6*DATA!$AI$4+M6*DATA!$AI$5+J6*DATA!$AI$6+(6-Q6)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S6" s="30">
+      <c r="S6" s="32">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",IF(U6&gt;0,"ข้อมูลไม่ครบ",IF(R6="","",IF(R6&gt;=DATA!$AI$10,"สูง",IF(R6&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T6" s="29" t="inlineStr">
+      <c r="T6" s="31" t="inlineStr">
         <is>
           <t>ตัวอย่าง</t>
         </is>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="31">
         <f>IF('1-UseCase ทั้งหมด'!B6="","",COUNTBLANK('1-UseCase ทั้งหมด'!I6)+COUNTBLANK('1-UseCase ทั้งหมด'!J6)+COUNTBLANK('1-UseCase ทั้งหมด'!L6)+COUNTBLANK('1-UseCase ทั้งหมด'!M6)+COUNTBLANK('1-UseCase ทั้งหมด'!O6)+COUNTBLANK('1-UseCase ทั้งหมด'!P6)+COUNTBLANK('1-UseCase ทั้งหมด'!Q6)+COUNTBLANK('1-UseCase ทั้งหมด'!R6)+COUNTBLANK('1-UseCase ทั้งหมด'!S6)+COUNTBLANK('1-UseCase ทั้งหมด'!T6))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="25">
+      <c r="A7" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",'1-UseCase ทั้งหมด'!A7)</f>
         <v/>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",'1-UseCase ทั้งหมด'!B7)</f>
         <v/>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",'1-UseCase ทั้งหมด'!D7)</f>
         <v/>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I7,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J7,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(D7="",IF(AND(E7&lt;&gt;"",E7&lt;&gt;"-"),E7,""),IF(AND(E7&lt;&gt;"",E7&lt;&gt;"-"),ROUND((D7+E7)/2,0),D7)))</f>
         <v/>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L7,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M7,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O7,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(ROUND(AVERAGE(G7:I7),0),""))</f>
         <v/>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P7,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L7" s="32">
+      <c r="L7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q7,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M7" s="33">
+      <c r="M7" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(ROUND(AVERAGE(K7:L7),0),""))</f>
         <v/>
       </c>
-      <c r="N7" s="32">
+      <c r="N7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R7,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O7" s="32">
+      <c r="O7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S7,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P7" s="32">
+      <c r="P7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T7,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q7" s="33">
+      <c r="Q7" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(ROUND(AVERAGE(N7:P7),0),""))</f>
         <v/>
       </c>
-      <c r="R7" s="34">
+      <c r="R7" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(U7&gt;0,"",IFERROR(ROUND((F7*DATA!$AI$4+M7*DATA!$AI$5+J7*DATA!$AI$6+(6-Q7)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S7" s="33">
+      <c r="S7" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(U7&gt;0,"ข้อมูลไม่ครบ",IF(R7="","",IF(R7&gt;=DATA!$AI$10,"สูง",IF(R7&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T7" s="33">
+      <c r="T7" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",IF(R7="","",RANK(R7,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U7" s="32">
+      <c r="U7" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B7="","",COUNTBLANK('1-UseCase ทั้งหมด'!I7)+COUNTBLANK('1-UseCase ทั้งหมด'!J7)+COUNTBLANK('1-UseCase ทั้งหมด'!L7)+COUNTBLANK('1-UseCase ทั้งหมด'!M7)+COUNTBLANK('1-UseCase ทั้งหมด'!O7)+COUNTBLANK('1-UseCase ทั้งหมด'!P7)+COUNTBLANK('1-UseCase ทั้งหมด'!Q7)+COUNTBLANK('1-UseCase ทั้งหมด'!R7)+COUNTBLANK('1-UseCase ทั้งหมด'!S7)+COUNTBLANK('1-UseCase ทั้งหมด'!T7))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="25">
+      <c r="A8" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",'1-UseCase ทั้งหมด'!A8)</f>
         <v/>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",'1-UseCase ทั้งหมด'!B8)</f>
         <v/>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",'1-UseCase ทั้งหมด'!D8)</f>
         <v/>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I8,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J8,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(D8="",IF(AND(E8&lt;&gt;"",E8&lt;&gt;"-"),E8,""),IF(AND(E8&lt;&gt;"",E8&lt;&gt;"-"),ROUND((D8+E8)/2,0),D8)))</f>
         <v/>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L8,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M8,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O8,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(ROUND(AVERAGE(G8:I8),0),""))</f>
         <v/>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P8,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L8" s="32">
+      <c r="L8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q8,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M8" s="33">
+      <c r="M8" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(ROUND(AVERAGE(K8:L8),0),""))</f>
         <v/>
       </c>
-      <c r="N8" s="32">
+      <c r="N8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R8,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O8" s="32">
+      <c r="O8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S8,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P8" s="32">
+      <c r="P8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T8,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q8" s="33">
+      <c r="Q8" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(ROUND(AVERAGE(N8:P8),0),""))</f>
         <v/>
       </c>
-      <c r="R8" s="34">
+      <c r="R8" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(U8&gt;0,"",IFERROR(ROUND((F8*DATA!$AI$4+M8*DATA!$AI$5+J8*DATA!$AI$6+(6-Q8)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S8" s="33">
+      <c r="S8" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(U8&gt;0,"ข้อมูลไม่ครบ",IF(R8="","",IF(R8&gt;=DATA!$AI$10,"สูง",IF(R8&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T8" s="33">
+      <c r="T8" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",IF(R8="","",RANK(R8,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U8" s="32">
+      <c r="U8" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B8="","",COUNTBLANK('1-UseCase ทั้งหมด'!I8)+COUNTBLANK('1-UseCase ทั้งหมด'!J8)+COUNTBLANK('1-UseCase ทั้งหมด'!L8)+COUNTBLANK('1-UseCase ทั้งหมด'!M8)+COUNTBLANK('1-UseCase ทั้งหมด'!O8)+COUNTBLANK('1-UseCase ทั้งหมด'!P8)+COUNTBLANK('1-UseCase ทั้งหมด'!Q8)+COUNTBLANK('1-UseCase ทั้งหมด'!R8)+COUNTBLANK('1-UseCase ทั้งหมด'!S8)+COUNTBLANK('1-UseCase ทั้งหมด'!T8))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="25">
+      <c r="A9" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",'1-UseCase ทั้งหมด'!A9)</f>
         <v/>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",'1-UseCase ทั้งหมด'!B9)</f>
         <v/>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",'1-UseCase ทั้งหมด'!D9)</f>
         <v/>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I9,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J9,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(D9="",IF(AND(E9&lt;&gt;"",E9&lt;&gt;"-"),E9,""),IF(AND(E9&lt;&gt;"",E9&lt;&gt;"-"),ROUND((D9+E9)/2,0),D9)))</f>
         <v/>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L9,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M9,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O9,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(ROUND(AVERAGE(G9:I9),0),""))</f>
         <v/>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P9,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L9" s="32">
+      <c r="L9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q9,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M9" s="33">
+      <c r="M9" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(ROUND(AVERAGE(K9:L9),0),""))</f>
         <v/>
       </c>
-      <c r="N9" s="32">
+      <c r="N9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R9,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O9" s="32">
+      <c r="O9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S9,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P9" s="32">
+      <c r="P9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T9,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q9" s="33">
+      <c r="Q9" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(ROUND(AVERAGE(N9:P9),0),""))</f>
         <v/>
       </c>
-      <c r="R9" s="34">
+      <c r="R9" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(U9&gt;0,"",IFERROR(ROUND((F9*DATA!$AI$4+M9*DATA!$AI$5+J9*DATA!$AI$6+(6-Q9)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S9" s="33">
+      <c r="S9" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(U9&gt;0,"ข้อมูลไม่ครบ",IF(R9="","",IF(R9&gt;=DATA!$AI$10,"สูง",IF(R9&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T9" s="33">
+      <c r="T9" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",IF(R9="","",RANK(R9,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U9" s="32">
+      <c r="U9" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B9="","",COUNTBLANK('1-UseCase ทั้งหมด'!I9)+COUNTBLANK('1-UseCase ทั้งหมด'!J9)+COUNTBLANK('1-UseCase ทั้งหมด'!L9)+COUNTBLANK('1-UseCase ทั้งหมด'!M9)+COUNTBLANK('1-UseCase ทั้งหมด'!O9)+COUNTBLANK('1-UseCase ทั้งหมด'!P9)+COUNTBLANK('1-UseCase ทั้งหมด'!Q9)+COUNTBLANK('1-UseCase ทั้งหมด'!R9)+COUNTBLANK('1-UseCase ทั้งหมด'!S9)+COUNTBLANK('1-UseCase ทั้งหมด'!T9))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="25">
+      <c r="A10" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",'1-UseCase ทั้งหมด'!A10)</f>
         <v/>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",'1-UseCase ทั้งหมด'!B10)</f>
         <v/>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",'1-UseCase ทั้งหมด'!D10)</f>
         <v/>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I10,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J10,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(D10="",IF(AND(E10&lt;&gt;"",E10&lt;&gt;"-"),E10,""),IF(AND(E10&lt;&gt;"",E10&lt;&gt;"-"),ROUND((D10+E10)/2,0),D10)))</f>
         <v/>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L10,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M10,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O10,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J10" s="33">
+      <c r="J10" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(ROUND(AVERAGE(G10:I10),0),""))</f>
         <v/>
       </c>
-      <c r="K10" s="32">
+      <c r="K10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P10,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L10" s="32">
+      <c r="L10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q10,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M10" s="33">
+      <c r="M10" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(ROUND(AVERAGE(K10:L10),0),""))</f>
         <v/>
       </c>
-      <c r="N10" s="32">
+      <c r="N10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R10,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O10" s="32">
+      <c r="O10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S10,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P10" s="32">
+      <c r="P10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T10,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q10" s="33">
+      <c r="Q10" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(ROUND(AVERAGE(N10:P10),0),""))</f>
         <v/>
       </c>
-      <c r="R10" s="34">
+      <c r="R10" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(U10&gt;0,"",IFERROR(ROUND((F10*DATA!$AI$4+M10*DATA!$AI$5+J10*DATA!$AI$6+(6-Q10)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S10" s="33">
+      <c r="S10" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(U10&gt;0,"ข้อมูลไม่ครบ",IF(R10="","",IF(R10&gt;=DATA!$AI$10,"สูง",IF(R10&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T10" s="33">
+      <c r="T10" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",IF(R10="","",RANK(R10,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U10" s="32">
+      <c r="U10" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B10="","",COUNTBLANK('1-UseCase ทั้งหมด'!I10)+COUNTBLANK('1-UseCase ทั้งหมด'!J10)+COUNTBLANK('1-UseCase ทั้งหมด'!L10)+COUNTBLANK('1-UseCase ทั้งหมด'!M10)+COUNTBLANK('1-UseCase ทั้งหมด'!O10)+COUNTBLANK('1-UseCase ทั้งหมด'!P10)+COUNTBLANK('1-UseCase ทั้งหมด'!Q10)+COUNTBLANK('1-UseCase ทั้งหมด'!R10)+COUNTBLANK('1-UseCase ทั้งหมด'!S10)+COUNTBLANK('1-UseCase ทั้งหมด'!T10))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="25">
+      <c r="A11" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",'1-UseCase ทั้งหมด'!A11)</f>
         <v/>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",'1-UseCase ทั้งหมด'!B11)</f>
         <v/>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",'1-UseCase ทั้งหมด'!D11)</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I11,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J11,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(D11="",IF(AND(E11&lt;&gt;"",E11&lt;&gt;"-"),E11,""),IF(AND(E11&lt;&gt;"",E11&lt;&gt;"-"),ROUND((D11+E11)/2,0),D11)))</f>
         <v/>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L11,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M11,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O11,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(ROUND(AVERAGE(G11:I11),0),""))</f>
         <v/>
       </c>
-      <c r="K11" s="32">
+      <c r="K11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P11,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L11" s="32">
+      <c r="L11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q11,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M11" s="33">
+      <c r="M11" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(ROUND(AVERAGE(K11:L11),0),""))</f>
         <v/>
       </c>
-      <c r="N11" s="32">
+      <c r="N11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R11,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O11" s="32">
+      <c r="O11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S11,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P11" s="32">
+      <c r="P11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T11,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q11" s="33">
+      <c r="Q11" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(ROUND(AVERAGE(N11:P11),0),""))</f>
         <v/>
       </c>
-      <c r="R11" s="34">
+      <c r="R11" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(U11&gt;0,"",IFERROR(ROUND((F11*DATA!$AI$4+M11*DATA!$AI$5+J11*DATA!$AI$6+(6-Q11)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S11" s="33">
+      <c r="S11" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(U11&gt;0,"ข้อมูลไม่ครบ",IF(R11="","",IF(R11&gt;=DATA!$AI$10,"สูง",IF(R11&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T11" s="33">
+      <c r="T11" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",IF(R11="","",RANK(R11,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U11" s="32">
+      <c r="U11" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B11="","",COUNTBLANK('1-UseCase ทั้งหมด'!I11)+COUNTBLANK('1-UseCase ทั้งหมด'!J11)+COUNTBLANK('1-UseCase ทั้งหมด'!L11)+COUNTBLANK('1-UseCase ทั้งหมด'!M11)+COUNTBLANK('1-UseCase ทั้งหมด'!O11)+COUNTBLANK('1-UseCase ทั้งหมด'!P11)+COUNTBLANK('1-UseCase ทั้งหมด'!Q11)+COUNTBLANK('1-UseCase ทั้งหมด'!R11)+COUNTBLANK('1-UseCase ทั้งหมด'!S11)+COUNTBLANK('1-UseCase ทั้งหมด'!T11))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="25">
+      <c r="A12" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",'1-UseCase ทั้งหมด'!A12)</f>
         <v/>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",'1-UseCase ทั้งหมด'!B12)</f>
         <v/>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",'1-UseCase ทั้งหมด'!D12)</f>
         <v/>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I12,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J12,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(D12="",IF(AND(E12&lt;&gt;"",E12&lt;&gt;"-"),E12,""),IF(AND(E12&lt;&gt;"",E12&lt;&gt;"-"),ROUND((D12+E12)/2,0),D12)))</f>
         <v/>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L12,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M12,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O12,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(ROUND(AVERAGE(G12:I12),0),""))</f>
         <v/>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P12,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L12" s="32">
+      <c r="L12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q12,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M12" s="33">
+      <c r="M12" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(ROUND(AVERAGE(K12:L12),0),""))</f>
         <v/>
       </c>
-      <c r="N12" s="32">
+      <c r="N12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R12,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O12" s="32">
+      <c r="O12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S12,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P12" s="32">
+      <c r="P12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T12,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q12" s="33">
+      <c r="Q12" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(ROUND(AVERAGE(N12:P12),0),""))</f>
         <v/>
       </c>
-      <c r="R12" s="34">
+      <c r="R12" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(U12&gt;0,"",IFERROR(ROUND((F12*DATA!$AI$4+M12*DATA!$AI$5+J12*DATA!$AI$6+(6-Q12)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S12" s="33">
+      <c r="S12" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(U12&gt;0,"ข้อมูลไม่ครบ",IF(R12="","",IF(R12&gt;=DATA!$AI$10,"สูง",IF(R12&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T12" s="33">
+      <c r="T12" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",IF(R12="","",RANK(R12,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U12" s="32">
+      <c r="U12" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B12="","",COUNTBLANK('1-UseCase ทั้งหมด'!I12)+COUNTBLANK('1-UseCase ทั้งหมด'!J12)+COUNTBLANK('1-UseCase ทั้งหมด'!L12)+COUNTBLANK('1-UseCase ทั้งหมด'!M12)+COUNTBLANK('1-UseCase ทั้งหมด'!O12)+COUNTBLANK('1-UseCase ทั้งหมด'!P12)+COUNTBLANK('1-UseCase ทั้งหมด'!Q12)+COUNTBLANK('1-UseCase ทั้งหมด'!R12)+COUNTBLANK('1-UseCase ทั้งหมด'!S12)+COUNTBLANK('1-UseCase ทั้งหมด'!T12))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="25">
+      <c r="A13" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",'1-UseCase ทั้งหมด'!A13)</f>
         <v/>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",'1-UseCase ทั้งหมด'!B13)</f>
         <v/>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",'1-UseCase ทั้งหมด'!D13)</f>
         <v/>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I13,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J13,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(D13="",IF(AND(E13&lt;&gt;"",E13&lt;&gt;"-"),E13,""),IF(AND(E13&lt;&gt;"",E13&lt;&gt;"-"),ROUND((D13+E13)/2,0),D13)))</f>
         <v/>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L13,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M13,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O13,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(ROUND(AVERAGE(G13:I13),0),""))</f>
         <v/>
       </c>
-      <c r="K13" s="32">
+      <c r="K13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P13,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L13" s="32">
+      <c r="L13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q13,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M13" s="33">
+      <c r="M13" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(ROUND(AVERAGE(K13:L13),0),""))</f>
         <v/>
       </c>
-      <c r="N13" s="32">
+      <c r="N13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R13,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O13" s="32">
+      <c r="O13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S13,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P13" s="32">
+      <c r="P13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T13,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q13" s="33">
+      <c r="Q13" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(ROUND(AVERAGE(N13:P13),0),""))</f>
         <v/>
       </c>
-      <c r="R13" s="34">
+      <c r="R13" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(U13&gt;0,"",IFERROR(ROUND((F13*DATA!$AI$4+M13*DATA!$AI$5+J13*DATA!$AI$6+(6-Q13)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S13" s="33">
+      <c r="S13" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(U13&gt;0,"ข้อมูลไม่ครบ",IF(R13="","",IF(R13&gt;=DATA!$AI$10,"สูง",IF(R13&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T13" s="33">
+      <c r="T13" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",IF(R13="","",RANK(R13,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U13" s="32">
+      <c r="U13" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B13="","",COUNTBLANK('1-UseCase ทั้งหมด'!I13)+COUNTBLANK('1-UseCase ทั้งหมด'!J13)+COUNTBLANK('1-UseCase ทั้งหมด'!L13)+COUNTBLANK('1-UseCase ทั้งหมด'!M13)+COUNTBLANK('1-UseCase ทั้งหมด'!O13)+COUNTBLANK('1-UseCase ทั้งหมด'!P13)+COUNTBLANK('1-UseCase ทั้งหมด'!Q13)+COUNTBLANK('1-UseCase ทั้งหมด'!R13)+COUNTBLANK('1-UseCase ทั้งหมด'!S13)+COUNTBLANK('1-UseCase ทั้งหมด'!T13))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="25">
+      <c r="A14" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",'1-UseCase ทั้งหมด'!A14)</f>
         <v/>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",'1-UseCase ทั้งหมด'!B14)</f>
         <v/>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",'1-UseCase ทั้งหมด'!D14)</f>
         <v/>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I14,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J14,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(D14="",IF(AND(E14&lt;&gt;"",E14&lt;&gt;"-"),E14,""),IF(AND(E14&lt;&gt;"",E14&lt;&gt;"-"),ROUND((D14+E14)/2,0),D14)))</f>
         <v/>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L14,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M14,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O14,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(ROUND(AVERAGE(G14:I14),0),""))</f>
         <v/>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P14,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q14,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M14" s="33">
+      <c r="M14" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(ROUND(AVERAGE(K14:L14),0),""))</f>
         <v/>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R14,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O14" s="32">
+      <c r="O14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S14,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P14" s="32">
+      <c r="P14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T14,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q14" s="33">
+      <c r="Q14" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(ROUND(AVERAGE(N14:P14),0),""))</f>
         <v/>
       </c>
-      <c r="R14" s="34">
+      <c r="R14" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(U14&gt;0,"",IFERROR(ROUND((F14*DATA!$AI$4+M14*DATA!$AI$5+J14*DATA!$AI$6+(6-Q14)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S14" s="33">
+      <c r="S14" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(U14&gt;0,"ข้อมูลไม่ครบ",IF(R14="","",IF(R14&gt;=DATA!$AI$10,"สูง",IF(R14&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T14" s="33">
+      <c r="T14" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",IF(R14="","",RANK(R14,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U14" s="32">
+      <c r="U14" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B14="","",COUNTBLANK('1-UseCase ทั้งหมด'!I14)+COUNTBLANK('1-UseCase ทั้งหมด'!J14)+COUNTBLANK('1-UseCase ทั้งหมด'!L14)+COUNTBLANK('1-UseCase ทั้งหมด'!M14)+COUNTBLANK('1-UseCase ทั้งหมด'!O14)+COUNTBLANK('1-UseCase ทั้งหมด'!P14)+COUNTBLANK('1-UseCase ทั้งหมด'!Q14)+COUNTBLANK('1-UseCase ทั้งหมด'!R14)+COUNTBLANK('1-UseCase ทั้งหมด'!S14)+COUNTBLANK('1-UseCase ทั้งหมด'!T14))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="25">
+      <c r="A15" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",'1-UseCase ทั้งหมด'!A15)</f>
         <v/>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",'1-UseCase ทั้งหมด'!B15)</f>
         <v/>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",'1-UseCase ทั้งหมด'!D15)</f>
         <v/>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I15,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J15,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(D15="",IF(AND(E15&lt;&gt;"",E15&lt;&gt;"-"),E15,""),IF(AND(E15&lt;&gt;"",E15&lt;&gt;"-"),ROUND((D15+E15)/2,0),D15)))</f>
         <v/>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L15,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M15,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O15,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J15" s="33">
+      <c r="J15" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(ROUND(AVERAGE(G15:I15),0),""))</f>
         <v/>
       </c>
-      <c r="K15" s="32">
+      <c r="K15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P15,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L15" s="32">
+      <c r="L15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q15,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M15" s="33">
+      <c r="M15" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(ROUND(AVERAGE(K15:L15),0),""))</f>
         <v/>
       </c>
-      <c r="N15" s="32">
+      <c r="N15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R15,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O15" s="32">
+      <c r="O15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S15,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P15" s="32">
+      <c r="P15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T15,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q15" s="33">
+      <c r="Q15" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(ROUND(AVERAGE(N15:P15),0),""))</f>
         <v/>
       </c>
-      <c r="R15" s="34">
+      <c r="R15" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(U15&gt;0,"",IFERROR(ROUND((F15*DATA!$AI$4+M15*DATA!$AI$5+J15*DATA!$AI$6+(6-Q15)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S15" s="33">
+      <c r="S15" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(U15&gt;0,"ข้อมูลไม่ครบ",IF(R15="","",IF(R15&gt;=DATA!$AI$10,"สูง",IF(R15&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T15" s="33">
+      <c r="T15" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",IF(R15="","",RANK(R15,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U15" s="32">
+      <c r="U15" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B15="","",COUNTBLANK('1-UseCase ทั้งหมด'!I15)+COUNTBLANK('1-UseCase ทั้งหมด'!J15)+COUNTBLANK('1-UseCase ทั้งหมด'!L15)+COUNTBLANK('1-UseCase ทั้งหมด'!M15)+COUNTBLANK('1-UseCase ทั้งหมด'!O15)+COUNTBLANK('1-UseCase ทั้งหมด'!P15)+COUNTBLANK('1-UseCase ทั้งหมด'!Q15)+COUNTBLANK('1-UseCase ทั้งหมด'!R15)+COUNTBLANK('1-UseCase ทั้งหมด'!S15)+COUNTBLANK('1-UseCase ทั้งหมด'!T15))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="25">
+      <c r="A16" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",'1-UseCase ทั้งหมด'!A16)</f>
         <v/>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",'1-UseCase ทั้งหมด'!B16)</f>
         <v/>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",'1-UseCase ทั้งหมด'!D16)</f>
         <v/>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I16,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J16,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(D16="",IF(AND(E16&lt;&gt;"",E16&lt;&gt;"-"),E16,""),IF(AND(E16&lt;&gt;"",E16&lt;&gt;"-"),ROUND((D16+E16)/2,0),D16)))</f>
         <v/>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L16,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M16,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O16,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J16" s="33">
+      <c r="J16" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(ROUND(AVERAGE(G16:I16),0),""))</f>
         <v/>
       </c>
-      <c r="K16" s="32">
+      <c r="K16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P16,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L16" s="32">
+      <c r="L16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q16,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M16" s="33">
+      <c r="M16" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(ROUND(AVERAGE(K16:L16),0),""))</f>
         <v/>
       </c>
-      <c r="N16" s="32">
+      <c r="N16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R16,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O16" s="32">
+      <c r="O16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S16,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P16" s="32">
+      <c r="P16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T16,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q16" s="33">
+      <c r="Q16" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(ROUND(AVERAGE(N16:P16),0),""))</f>
         <v/>
       </c>
-      <c r="R16" s="34">
+      <c r="R16" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(U16&gt;0,"",IFERROR(ROUND((F16*DATA!$AI$4+M16*DATA!$AI$5+J16*DATA!$AI$6+(6-Q16)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S16" s="33">
+      <c r="S16" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(U16&gt;0,"ข้อมูลไม่ครบ",IF(R16="","",IF(R16&gt;=DATA!$AI$10,"สูง",IF(R16&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T16" s="33">
+      <c r="T16" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",IF(R16="","",RANK(R16,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U16" s="32">
+      <c r="U16" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B16="","",COUNTBLANK('1-UseCase ทั้งหมด'!I16)+COUNTBLANK('1-UseCase ทั้งหมด'!J16)+COUNTBLANK('1-UseCase ทั้งหมด'!L16)+COUNTBLANK('1-UseCase ทั้งหมด'!M16)+COUNTBLANK('1-UseCase ทั้งหมด'!O16)+COUNTBLANK('1-UseCase ทั้งหมด'!P16)+COUNTBLANK('1-UseCase ทั้งหมด'!Q16)+COUNTBLANK('1-UseCase ทั้งหมด'!R16)+COUNTBLANK('1-UseCase ทั้งหมด'!S16)+COUNTBLANK('1-UseCase ทั้งหมด'!T16))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="25">
+      <c r="A17" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",'1-UseCase ทั้งหมด'!A17)</f>
         <v/>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",'1-UseCase ทั้งหมด'!B17)</f>
         <v/>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",'1-UseCase ทั้งหมด'!D17)</f>
         <v/>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I17,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J17,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(D17="",IF(AND(E17&lt;&gt;"",E17&lt;&gt;"-"),E17,""),IF(AND(E17&lt;&gt;"",E17&lt;&gt;"-"),ROUND((D17+E17)/2,0),D17)))</f>
         <v/>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L17,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M17,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I17" s="32">
+      <c r="I17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O17,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J17" s="33">
+      <c r="J17" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(ROUND(AVERAGE(G17:I17),0),""))</f>
         <v/>
       </c>
-      <c r="K17" s="32">
+      <c r="K17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P17,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L17" s="32">
+      <c r="L17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q17,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M17" s="33">
+      <c r="M17" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(ROUND(AVERAGE(K17:L17),0),""))</f>
         <v/>
       </c>
-      <c r="N17" s="32">
+      <c r="N17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R17,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O17" s="32">
+      <c r="O17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S17,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P17" s="32">
+      <c r="P17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T17,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q17" s="33">
+      <c r="Q17" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(ROUND(AVERAGE(N17:P17),0),""))</f>
         <v/>
       </c>
-      <c r="R17" s="34">
+      <c r="R17" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(U17&gt;0,"",IFERROR(ROUND((F17*DATA!$AI$4+M17*DATA!$AI$5+J17*DATA!$AI$6+(6-Q17)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S17" s="33">
+      <c r="S17" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(U17&gt;0,"ข้อมูลไม่ครบ",IF(R17="","",IF(R17&gt;=DATA!$AI$10,"สูง",IF(R17&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T17" s="33">
+      <c r="T17" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",IF(R17="","",RANK(R17,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U17" s="32">
+      <c r="U17" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B17="","",COUNTBLANK('1-UseCase ทั้งหมด'!I17)+COUNTBLANK('1-UseCase ทั้งหมด'!J17)+COUNTBLANK('1-UseCase ทั้งหมด'!L17)+COUNTBLANK('1-UseCase ทั้งหมด'!M17)+COUNTBLANK('1-UseCase ทั้งหมด'!O17)+COUNTBLANK('1-UseCase ทั้งหมด'!P17)+COUNTBLANK('1-UseCase ทั้งหมด'!Q17)+COUNTBLANK('1-UseCase ทั้งหมด'!R17)+COUNTBLANK('1-UseCase ทั้งหมด'!S17)+COUNTBLANK('1-UseCase ทั้งหมด'!T17))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="25">
+      <c r="A18" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",'1-UseCase ทั้งหมด'!A18)</f>
         <v/>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",'1-UseCase ทั้งหมด'!B18)</f>
         <v/>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",'1-UseCase ทั้งหมด'!D18)</f>
         <v/>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I18,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J18,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(D18="",IF(AND(E18&lt;&gt;"",E18&lt;&gt;"-"),E18,""),IF(AND(E18&lt;&gt;"",E18&lt;&gt;"-"),ROUND((D18+E18)/2,0),D18)))</f>
         <v/>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L18,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M18,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O18,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J18" s="33">
+      <c r="J18" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(ROUND(AVERAGE(G18:I18),0),""))</f>
         <v/>
       </c>
-      <c r="K18" s="32">
+      <c r="K18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P18,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L18" s="32">
+      <c r="L18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q18,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M18" s="33">
+      <c r="M18" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(ROUND(AVERAGE(K18:L18),0),""))</f>
         <v/>
       </c>
-      <c r="N18" s="32">
+      <c r="N18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R18,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O18" s="32">
+      <c r="O18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S18,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P18" s="32">
+      <c r="P18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T18,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q18" s="33">
+      <c r="Q18" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(ROUND(AVERAGE(N18:P18),0),""))</f>
         <v/>
       </c>
-      <c r="R18" s="34">
+      <c r="R18" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(U18&gt;0,"",IFERROR(ROUND((F18*DATA!$AI$4+M18*DATA!$AI$5+J18*DATA!$AI$6+(6-Q18)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S18" s="33">
+      <c r="S18" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(U18&gt;0,"ข้อมูลไม่ครบ",IF(R18="","",IF(R18&gt;=DATA!$AI$10,"สูง",IF(R18&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T18" s="33">
+      <c r="T18" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",IF(R18="","",RANK(R18,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U18" s="32">
+      <c r="U18" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B18="","",COUNTBLANK('1-UseCase ทั้งหมด'!I18)+COUNTBLANK('1-UseCase ทั้งหมด'!J18)+COUNTBLANK('1-UseCase ทั้งหมด'!L18)+COUNTBLANK('1-UseCase ทั้งหมด'!M18)+COUNTBLANK('1-UseCase ทั้งหมด'!O18)+COUNTBLANK('1-UseCase ทั้งหมด'!P18)+COUNTBLANK('1-UseCase ทั้งหมด'!Q18)+COUNTBLANK('1-UseCase ทั้งหมด'!R18)+COUNTBLANK('1-UseCase ทั้งหมด'!S18)+COUNTBLANK('1-UseCase ทั้งหมด'!T18))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="25">
+      <c r="A19" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",'1-UseCase ทั้งหมด'!A19)</f>
         <v/>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",'1-UseCase ทั้งหมด'!B19)</f>
         <v/>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",'1-UseCase ทั้งหมด'!D19)</f>
         <v/>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I19,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J19,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(D19="",IF(AND(E19&lt;&gt;"",E19&lt;&gt;"-"),E19,""),IF(AND(E19&lt;&gt;"",E19&lt;&gt;"-"),ROUND((D19+E19)/2,0),D19)))</f>
         <v/>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L19,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M19,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O19,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J19" s="33">
+      <c r="J19" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(ROUND(AVERAGE(G19:I19),0),""))</f>
         <v/>
       </c>
-      <c r="K19" s="32">
+      <c r="K19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P19,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L19" s="32">
+      <c r="L19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q19,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M19" s="33">
+      <c r="M19" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(ROUND(AVERAGE(K19:L19),0),""))</f>
         <v/>
       </c>
-      <c r="N19" s="32">
+      <c r="N19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R19,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O19" s="32">
+      <c r="O19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S19,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P19" s="32">
+      <c r="P19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T19,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q19" s="33">
+      <c r="Q19" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(ROUND(AVERAGE(N19:P19),0),""))</f>
         <v/>
       </c>
-      <c r="R19" s="34">
+      <c r="R19" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(U19&gt;0,"",IFERROR(ROUND((F19*DATA!$AI$4+M19*DATA!$AI$5+J19*DATA!$AI$6+(6-Q19)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S19" s="33">
+      <c r="S19" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(U19&gt;0,"ข้อมูลไม่ครบ",IF(R19="","",IF(R19&gt;=DATA!$AI$10,"สูง",IF(R19&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T19" s="33">
+      <c r="T19" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",IF(R19="","",RANK(R19,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U19" s="32">
+      <c r="U19" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B19="","",COUNTBLANK('1-UseCase ทั้งหมด'!I19)+COUNTBLANK('1-UseCase ทั้งหมด'!J19)+COUNTBLANK('1-UseCase ทั้งหมด'!L19)+COUNTBLANK('1-UseCase ทั้งหมด'!M19)+COUNTBLANK('1-UseCase ทั้งหมด'!O19)+COUNTBLANK('1-UseCase ทั้งหมด'!P19)+COUNTBLANK('1-UseCase ทั้งหมด'!Q19)+COUNTBLANK('1-UseCase ทั้งหมด'!R19)+COUNTBLANK('1-UseCase ทั้งหมด'!S19)+COUNTBLANK('1-UseCase ทั้งหมด'!T19))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="25">
+      <c r="A20" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",'1-UseCase ทั้งหมด'!A20)</f>
         <v/>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",'1-UseCase ทั้งหมด'!B20)</f>
         <v/>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",'1-UseCase ทั้งหมด'!D20)</f>
         <v/>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I20,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J20,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(D20="",IF(AND(E20&lt;&gt;"",E20&lt;&gt;"-"),E20,""),IF(AND(E20&lt;&gt;"",E20&lt;&gt;"-"),ROUND((D20+E20)/2,0),D20)))</f>
         <v/>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L20,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M20,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I20" s="32">
+      <c r="I20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O20,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J20" s="33">
+      <c r="J20" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(ROUND(AVERAGE(G20:I20),0),""))</f>
         <v/>
       </c>
-      <c r="K20" s="32">
+      <c r="K20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P20,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L20" s="32">
+      <c r="L20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q20,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M20" s="33">
+      <c r="M20" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(ROUND(AVERAGE(K20:L20),0),""))</f>
         <v/>
       </c>
-      <c r="N20" s="32">
+      <c r="N20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R20,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O20" s="32">
+      <c r="O20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S20,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P20" s="32">
+      <c r="P20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T20,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q20" s="33">
+      <c r="Q20" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(ROUND(AVERAGE(N20:P20),0),""))</f>
         <v/>
       </c>
-      <c r="R20" s="34">
+      <c r="R20" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(U20&gt;0,"",IFERROR(ROUND((F20*DATA!$AI$4+M20*DATA!$AI$5+J20*DATA!$AI$6+(6-Q20)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S20" s="33">
+      <c r="S20" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(U20&gt;0,"ข้อมูลไม่ครบ",IF(R20="","",IF(R20&gt;=DATA!$AI$10,"สูง",IF(R20&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T20" s="33">
+      <c r="T20" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",IF(R20="","",RANK(R20,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U20" s="32">
+      <c r="U20" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B20="","",COUNTBLANK('1-UseCase ทั้งหมด'!I20)+COUNTBLANK('1-UseCase ทั้งหมด'!J20)+COUNTBLANK('1-UseCase ทั้งหมด'!L20)+COUNTBLANK('1-UseCase ทั้งหมด'!M20)+COUNTBLANK('1-UseCase ทั้งหมด'!O20)+COUNTBLANK('1-UseCase ทั้งหมด'!P20)+COUNTBLANK('1-UseCase ทั้งหมด'!Q20)+COUNTBLANK('1-UseCase ทั้งหมด'!R20)+COUNTBLANK('1-UseCase ทั้งหมด'!S20)+COUNTBLANK('1-UseCase ทั้งหมด'!T20))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="25">
+      <c r="A21" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",'1-UseCase ทั้งหมด'!A21)</f>
         <v/>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",'1-UseCase ทั้งหมด'!B21)</f>
         <v/>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",'1-UseCase ทั้งหมด'!D21)</f>
         <v/>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I21,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J21,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(D21="",IF(AND(E21&lt;&gt;"",E21&lt;&gt;"-"),E21,""),IF(AND(E21&lt;&gt;"",E21&lt;&gt;"-"),ROUND((D21+E21)/2,0),D21)))</f>
         <v/>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L21,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M21,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O21,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J21" s="33">
+      <c r="J21" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(ROUND(AVERAGE(G21:I21),0),""))</f>
         <v/>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P21,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q21,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(ROUND(AVERAGE(K21:L21),0),""))</f>
         <v/>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R21,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S21,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T21,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q21" s="33">
+      <c r="Q21" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(ROUND(AVERAGE(N21:P21),0),""))</f>
         <v/>
       </c>
-      <c r="R21" s="34">
+      <c r="R21" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(U21&gt;0,"",IFERROR(ROUND((F21*DATA!$AI$4+M21*DATA!$AI$5+J21*DATA!$AI$6+(6-Q21)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S21" s="33">
+      <c r="S21" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(U21&gt;0,"ข้อมูลไม่ครบ",IF(R21="","",IF(R21&gt;=DATA!$AI$10,"สูง",IF(R21&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",IF(R21="","",RANK(R21,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U21" s="32">
+      <c r="U21" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B21="","",COUNTBLANK('1-UseCase ทั้งหมด'!I21)+COUNTBLANK('1-UseCase ทั้งหมด'!J21)+COUNTBLANK('1-UseCase ทั้งหมด'!L21)+COUNTBLANK('1-UseCase ทั้งหมด'!M21)+COUNTBLANK('1-UseCase ทั้งหมด'!O21)+COUNTBLANK('1-UseCase ทั้งหมด'!P21)+COUNTBLANK('1-UseCase ทั้งหมด'!Q21)+COUNTBLANK('1-UseCase ทั้งหมด'!R21)+COUNTBLANK('1-UseCase ทั้งหมด'!S21)+COUNTBLANK('1-UseCase ทั้งหมด'!T21))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="25">
+      <c r="A22" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",'1-UseCase ทั้งหมด'!A22)</f>
         <v/>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",'1-UseCase ทั้งหมด'!B22)</f>
         <v/>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",'1-UseCase ทั้งหมด'!D22)</f>
         <v/>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I22,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J22,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(D22="",IF(AND(E22&lt;&gt;"",E22&lt;&gt;"-"),E22,""),IF(AND(E22&lt;&gt;"",E22&lt;&gt;"-"),ROUND((D22+E22)/2,0),D22)))</f>
         <v/>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L22,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M22,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O22,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J22" s="33">
+      <c r="J22" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(ROUND(AVERAGE(G22:I22),0),""))</f>
         <v/>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P22,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q22,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M22" s="33">
+      <c r="M22" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(ROUND(AVERAGE(K22:L22),0),""))</f>
         <v/>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R22,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S22,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T22,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q22" s="33">
+      <c r="Q22" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(ROUND(AVERAGE(N22:P22),0),""))</f>
         <v/>
       </c>
-      <c r="R22" s="34">
+      <c r="R22" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(U22&gt;0,"",IFERROR(ROUND((F22*DATA!$AI$4+M22*DATA!$AI$5+J22*DATA!$AI$6+(6-Q22)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S22" s="33">
+      <c r="S22" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(U22&gt;0,"ข้อมูลไม่ครบ",IF(R22="","",IF(R22&gt;=DATA!$AI$10,"สูง",IF(R22&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T22" s="33">
+      <c r="T22" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",IF(R22="","",RANK(R22,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U22" s="32">
+      <c r="U22" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B22="","",COUNTBLANK('1-UseCase ทั้งหมด'!I22)+COUNTBLANK('1-UseCase ทั้งหมด'!J22)+COUNTBLANK('1-UseCase ทั้งหมด'!L22)+COUNTBLANK('1-UseCase ทั้งหมด'!M22)+COUNTBLANK('1-UseCase ทั้งหมด'!O22)+COUNTBLANK('1-UseCase ทั้งหมด'!P22)+COUNTBLANK('1-UseCase ทั้งหมด'!Q22)+COUNTBLANK('1-UseCase ทั้งหมด'!R22)+COUNTBLANK('1-UseCase ทั้งหมด'!S22)+COUNTBLANK('1-UseCase ทั้งหมด'!T22))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="25">
+      <c r="A23" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",'1-UseCase ทั้งหมด'!A23)</f>
         <v/>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",'1-UseCase ทั้งหมด'!B23)</f>
         <v/>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",'1-UseCase ทั้งหมด'!D23)</f>
         <v/>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I23,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J23,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(D23="",IF(AND(E23&lt;&gt;"",E23&lt;&gt;"-"),E23,""),IF(AND(E23&lt;&gt;"",E23&lt;&gt;"-"),ROUND((D23+E23)/2,0),D23)))</f>
         <v/>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L23,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H23" s="32">
+      <c r="H23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M23,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I23" s="32">
+      <c r="I23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O23,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J23" s="33">
+      <c r="J23" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(ROUND(AVERAGE(G23:I23),0),""))</f>
         <v/>
       </c>
-      <c r="K23" s="32">
+      <c r="K23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P23,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L23" s="32">
+      <c r="L23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q23,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M23" s="33">
+      <c r="M23" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(ROUND(AVERAGE(K23:L23),0),""))</f>
         <v/>
       </c>
-      <c r="N23" s="32">
+      <c r="N23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R23,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O23" s="32">
+      <c r="O23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S23,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P23" s="32">
+      <c r="P23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T23,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q23" s="33">
+      <c r="Q23" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(ROUND(AVERAGE(N23:P23),0),""))</f>
         <v/>
       </c>
-      <c r="R23" s="34">
+      <c r="R23" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(U23&gt;0,"",IFERROR(ROUND((F23*DATA!$AI$4+M23*DATA!$AI$5+J23*DATA!$AI$6+(6-Q23)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S23" s="33">
+      <c r="S23" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(U23&gt;0,"ข้อมูลไม่ครบ",IF(R23="","",IF(R23&gt;=DATA!$AI$10,"สูง",IF(R23&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T23" s="33">
+      <c r="T23" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",IF(R23="","",RANK(R23,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U23" s="32">
+      <c r="U23" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B23="","",COUNTBLANK('1-UseCase ทั้งหมด'!I23)+COUNTBLANK('1-UseCase ทั้งหมด'!J23)+COUNTBLANK('1-UseCase ทั้งหมด'!L23)+COUNTBLANK('1-UseCase ทั้งหมด'!M23)+COUNTBLANK('1-UseCase ทั้งหมด'!O23)+COUNTBLANK('1-UseCase ทั้งหมด'!P23)+COUNTBLANK('1-UseCase ทั้งหมด'!Q23)+COUNTBLANK('1-UseCase ทั้งหมด'!R23)+COUNTBLANK('1-UseCase ทั้งหมด'!S23)+COUNTBLANK('1-UseCase ทั้งหมด'!T23))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="25">
+      <c r="A24" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",'1-UseCase ทั้งหมด'!A24)</f>
         <v/>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",'1-UseCase ทั้งหมด'!B24)</f>
         <v/>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",'1-UseCase ทั้งหมด'!D24)</f>
         <v/>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I24,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J24,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(D24="",IF(AND(E24&lt;&gt;"",E24&lt;&gt;"-"),E24,""),IF(AND(E24&lt;&gt;"",E24&lt;&gt;"-"),ROUND((D24+E24)/2,0),D24)))</f>
         <v/>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L24,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M24,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O24,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J24" s="33">
+      <c r="J24" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(ROUND(AVERAGE(G24:I24),0),""))</f>
         <v/>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P24,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q24,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M24" s="33">
+      <c r="M24" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(ROUND(AVERAGE(K24:L24),0),""))</f>
         <v/>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R24,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S24,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T24,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(ROUND(AVERAGE(N24:P24),0),""))</f>
         <v/>
       </c>
-      <c r="R24" s="34">
+      <c r="R24" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(U24&gt;0,"",IFERROR(ROUND((F24*DATA!$AI$4+M24*DATA!$AI$5+J24*DATA!$AI$6+(6-Q24)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S24" s="33">
+      <c r="S24" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(U24&gt;0,"ข้อมูลไม่ครบ",IF(R24="","",IF(R24&gt;=DATA!$AI$10,"สูง",IF(R24&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T24" s="33">
+      <c r="T24" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",IF(R24="","",RANK(R24,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U24" s="32">
+      <c r="U24" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B24="","",COUNTBLANK('1-UseCase ทั้งหมด'!I24)+COUNTBLANK('1-UseCase ทั้งหมด'!J24)+COUNTBLANK('1-UseCase ทั้งหมด'!L24)+COUNTBLANK('1-UseCase ทั้งหมด'!M24)+COUNTBLANK('1-UseCase ทั้งหมด'!O24)+COUNTBLANK('1-UseCase ทั้งหมด'!P24)+COUNTBLANK('1-UseCase ทั้งหมด'!Q24)+COUNTBLANK('1-UseCase ทั้งหมด'!R24)+COUNTBLANK('1-UseCase ทั้งหมด'!S24)+COUNTBLANK('1-UseCase ทั้งหมด'!T24))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="25">
+      <c r="A25" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",'1-UseCase ทั้งหมด'!A25)</f>
         <v/>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",'1-UseCase ทั้งหมด'!B25)</f>
         <v/>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",'1-UseCase ทั้งหมด'!D25)</f>
         <v/>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I25,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J25,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(D25="",IF(AND(E25&lt;&gt;"",E25&lt;&gt;"-"),E25,""),IF(AND(E25&lt;&gt;"",E25&lt;&gt;"-"),ROUND((D25+E25)/2,0),D25)))</f>
         <v/>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L25,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M25,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O25,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J25" s="33">
+      <c r="J25" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(ROUND(AVERAGE(G25:I25),0),""))</f>
         <v/>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P25,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q25,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(ROUND(AVERAGE(K25:L25),0),""))</f>
         <v/>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R25,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S25,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T25,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q25" s="33">
+      <c r="Q25" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(ROUND(AVERAGE(N25:P25),0),""))</f>
         <v/>
       </c>
-      <c r="R25" s="34">
+      <c r="R25" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(U25&gt;0,"",IFERROR(ROUND((F25*DATA!$AI$4+M25*DATA!$AI$5+J25*DATA!$AI$6+(6-Q25)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S25" s="33">
+      <c r="S25" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(U25&gt;0,"ข้อมูลไม่ครบ",IF(R25="","",IF(R25&gt;=DATA!$AI$10,"สูง",IF(R25&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T25" s="33">
+      <c r="T25" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",IF(R25="","",RANK(R25,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U25" s="32">
+      <c r="U25" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B25="","",COUNTBLANK('1-UseCase ทั้งหมด'!I25)+COUNTBLANK('1-UseCase ทั้งหมด'!J25)+COUNTBLANK('1-UseCase ทั้งหมด'!L25)+COUNTBLANK('1-UseCase ทั้งหมด'!M25)+COUNTBLANK('1-UseCase ทั้งหมด'!O25)+COUNTBLANK('1-UseCase ทั้งหมด'!P25)+COUNTBLANK('1-UseCase ทั้งหมด'!Q25)+COUNTBLANK('1-UseCase ทั้งหมด'!R25)+COUNTBLANK('1-UseCase ทั้งหมด'!S25)+COUNTBLANK('1-UseCase ทั้งหมด'!T25))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="25">
+      <c r="A26" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",'1-UseCase ทั้งหมด'!A26)</f>
         <v/>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",'1-UseCase ทั้งหมด'!B26)</f>
         <v/>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",'1-UseCase ทั้งหมด'!D26)</f>
         <v/>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I26,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E26" s="32">
+      <c r="E26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J26,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F26" s="33">
+      <c r="F26" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(D26="",IF(AND(E26&lt;&gt;"",E26&lt;&gt;"-"),E26,""),IF(AND(E26&lt;&gt;"",E26&lt;&gt;"-"),ROUND((D26+E26)/2,0),D26)))</f>
         <v/>
       </c>
-      <c r="G26" s="32">
+      <c r="G26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L26,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M26,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I26" s="32">
+      <c r="I26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O26,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J26" s="33">
+      <c r="J26" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(ROUND(AVERAGE(G26:I26),0),""))</f>
         <v/>
       </c>
-      <c r="K26" s="32">
+      <c r="K26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P26,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L26" s="32">
+      <c r="L26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q26,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M26" s="33">
+      <c r="M26" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(ROUND(AVERAGE(K26:L26),0),""))</f>
         <v/>
       </c>
-      <c r="N26" s="32">
+      <c r="N26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R26,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O26" s="32">
+      <c r="O26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S26,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P26" s="32">
+      <c r="P26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T26,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q26" s="33">
+      <c r="Q26" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(ROUND(AVERAGE(N26:P26),0),""))</f>
         <v/>
       </c>
-      <c r="R26" s="34">
+      <c r="R26" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(U26&gt;0,"",IFERROR(ROUND((F26*DATA!$AI$4+M26*DATA!$AI$5+J26*DATA!$AI$6+(6-Q26)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S26" s="33">
+      <c r="S26" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(U26&gt;0,"ข้อมูลไม่ครบ",IF(R26="","",IF(R26&gt;=DATA!$AI$10,"สูง",IF(R26&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T26" s="33">
+      <c r="T26" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",IF(R26="","",RANK(R26,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U26" s="32">
+      <c r="U26" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B26="","",COUNTBLANK('1-UseCase ทั้งหมด'!I26)+COUNTBLANK('1-UseCase ทั้งหมด'!J26)+COUNTBLANK('1-UseCase ทั้งหมด'!L26)+COUNTBLANK('1-UseCase ทั้งหมด'!M26)+COUNTBLANK('1-UseCase ทั้งหมด'!O26)+COUNTBLANK('1-UseCase ทั้งหมด'!P26)+COUNTBLANK('1-UseCase ทั้งหมด'!Q26)+COUNTBLANK('1-UseCase ทั้งหมด'!R26)+COUNTBLANK('1-UseCase ทั้งหมด'!S26)+COUNTBLANK('1-UseCase ทั้งหมด'!T26))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="25">
+      <c r="A27" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",'1-UseCase ทั้งหมด'!A27)</f>
         <v/>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",'1-UseCase ทั้งหมด'!B27)</f>
         <v/>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",'1-UseCase ทั้งหมด'!D27)</f>
         <v/>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I27,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J27,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(D27="",IF(AND(E27&lt;&gt;"",E27&lt;&gt;"-"),E27,""),IF(AND(E27&lt;&gt;"",E27&lt;&gt;"-"),ROUND((D27+E27)/2,0),D27)))</f>
         <v/>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L27,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M27,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O27,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(ROUND(AVERAGE(G27:I27),0),""))</f>
         <v/>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P27,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q27,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(ROUND(AVERAGE(K27:L27),0),""))</f>
         <v/>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R27,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S27,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T27,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(ROUND(AVERAGE(N27:P27),0),""))</f>
         <v/>
       </c>
-      <c r="R27" s="34">
+      <c r="R27" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(U27&gt;0,"",IFERROR(ROUND((F27*DATA!$AI$4+M27*DATA!$AI$5+J27*DATA!$AI$6+(6-Q27)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(U27&gt;0,"ข้อมูลไม่ครบ",IF(R27="","",IF(R27&gt;=DATA!$AI$10,"สูง",IF(R27&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",IF(R27="","",RANK(R27,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U27" s="32">
+      <c r="U27" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B27="","",COUNTBLANK('1-UseCase ทั้งหมด'!I27)+COUNTBLANK('1-UseCase ทั้งหมด'!J27)+COUNTBLANK('1-UseCase ทั้งหมด'!L27)+COUNTBLANK('1-UseCase ทั้งหมด'!M27)+COUNTBLANK('1-UseCase ทั้งหมด'!O27)+COUNTBLANK('1-UseCase ทั้งหมด'!P27)+COUNTBLANK('1-UseCase ทั้งหมด'!Q27)+COUNTBLANK('1-UseCase ทั้งหมด'!R27)+COUNTBLANK('1-UseCase ทั้งหมด'!S27)+COUNTBLANK('1-UseCase ทั้งหมด'!T27))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="25">
+      <c r="A28" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",'1-UseCase ทั้งหมด'!A28)</f>
         <v/>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",'1-UseCase ทั้งหมด'!B28)</f>
         <v/>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",'1-UseCase ทั้งหมด'!D28)</f>
         <v/>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I28,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J28,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(D28="",IF(AND(E28&lt;&gt;"",E28&lt;&gt;"-"),E28,""),IF(AND(E28&lt;&gt;"",E28&lt;&gt;"-"),ROUND((D28+E28)/2,0),D28)))</f>
         <v/>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L28,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M28,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O28,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(ROUND(AVERAGE(G28:I28),0),""))</f>
         <v/>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P28,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q28,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(ROUND(AVERAGE(K28:L28),0),""))</f>
         <v/>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R28,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S28,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T28,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q28" s="33">
+      <c r="Q28" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(ROUND(AVERAGE(N28:P28),0),""))</f>
         <v/>
       </c>
-      <c r="R28" s="34">
+      <c r="R28" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(U28&gt;0,"",IFERROR(ROUND((F28*DATA!$AI$4+M28*DATA!$AI$5+J28*DATA!$AI$6+(6-Q28)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(U28&gt;0,"ข้อมูลไม่ครบ",IF(R28="","",IF(R28&gt;=DATA!$AI$10,"สูง",IF(R28&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T28" s="33">
+      <c r="T28" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",IF(R28="","",RANK(R28,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U28" s="32">
+      <c r="U28" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B28="","",COUNTBLANK('1-UseCase ทั้งหมด'!I28)+COUNTBLANK('1-UseCase ทั้งหมด'!J28)+COUNTBLANK('1-UseCase ทั้งหมด'!L28)+COUNTBLANK('1-UseCase ทั้งหมด'!M28)+COUNTBLANK('1-UseCase ทั้งหมด'!O28)+COUNTBLANK('1-UseCase ทั้งหมด'!P28)+COUNTBLANK('1-UseCase ทั้งหมด'!Q28)+COUNTBLANK('1-UseCase ทั้งหมด'!R28)+COUNTBLANK('1-UseCase ทั้งหมด'!S28)+COUNTBLANK('1-UseCase ทั้งหมด'!T28))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="25">
+      <c r="A29" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",'1-UseCase ทั้งหมด'!A29)</f>
         <v/>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",'1-UseCase ทั้งหมด'!B29)</f>
         <v/>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",'1-UseCase ทั้งหมด'!D29)</f>
         <v/>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I29,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J29,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(D29="",IF(AND(E29&lt;&gt;"",E29&lt;&gt;"-"),E29,""),IF(AND(E29&lt;&gt;"",E29&lt;&gt;"-"),ROUND((D29+E29)/2,0),D29)))</f>
         <v/>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L29,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M29,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O29,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J29" s="33">
+      <c r="J29" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(ROUND(AVERAGE(G29:I29),0),""))</f>
         <v/>
       </c>
-      <c r="K29" s="32">
+      <c r="K29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P29,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L29" s="32">
+      <c r="L29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q29,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M29" s="33">
+      <c r="M29" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(ROUND(AVERAGE(K29:L29),0),""))</f>
         <v/>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R29,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O29" s="32">
+      <c r="O29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S29,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P29" s="32">
+      <c r="P29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T29,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q29" s="33">
+      <c r="Q29" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(ROUND(AVERAGE(N29:P29),0),""))</f>
         <v/>
       </c>
-      <c r="R29" s="34">
+      <c r="R29" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(U29&gt;0,"",IFERROR(ROUND((F29*DATA!$AI$4+M29*DATA!$AI$5+J29*DATA!$AI$6+(6-Q29)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S29" s="33">
+      <c r="S29" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(U29&gt;0,"ข้อมูลไม่ครบ",IF(R29="","",IF(R29&gt;=DATA!$AI$10,"สูง",IF(R29&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T29" s="33">
+      <c r="T29" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",IF(R29="","",RANK(R29,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U29" s="32">
+      <c r="U29" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B29="","",COUNTBLANK('1-UseCase ทั้งหมด'!I29)+COUNTBLANK('1-UseCase ทั้งหมด'!J29)+COUNTBLANK('1-UseCase ทั้งหมด'!L29)+COUNTBLANK('1-UseCase ทั้งหมด'!M29)+COUNTBLANK('1-UseCase ทั้งหมด'!O29)+COUNTBLANK('1-UseCase ทั้งหมด'!P29)+COUNTBLANK('1-UseCase ทั้งหมด'!Q29)+COUNTBLANK('1-UseCase ทั้งหมด'!R29)+COUNTBLANK('1-UseCase ทั้งหมด'!S29)+COUNTBLANK('1-UseCase ทั้งหมด'!T29))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="25">
+      <c r="A30" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",'1-UseCase ทั้งหมด'!A30)</f>
         <v/>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",'1-UseCase ทั้งหมด'!B30)</f>
         <v/>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",'1-UseCase ทั้งหมด'!D30)</f>
         <v/>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I30,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J30,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(D30="",IF(AND(E30&lt;&gt;"",E30&lt;&gt;"-"),E30,""),IF(AND(E30&lt;&gt;"",E30&lt;&gt;"-"),ROUND((D30+E30)/2,0),D30)))</f>
         <v/>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L30,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M30,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O30,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(ROUND(AVERAGE(G30:I30),0),""))</f>
         <v/>
       </c>
-      <c r="K30" s="32">
+      <c r="K30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P30,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L30" s="32">
+      <c r="L30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q30,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(ROUND(AVERAGE(K30:L30),0),""))</f>
         <v/>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R30,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O30" s="32">
+      <c r="O30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S30,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T30,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q30" s="33">
+      <c r="Q30" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(ROUND(AVERAGE(N30:P30),0),""))</f>
         <v/>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(U30&gt;0,"",IFERROR(ROUND((F30*DATA!$AI$4+M30*DATA!$AI$5+J30*DATA!$AI$6+(6-Q30)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(U30&gt;0,"ข้อมูลไม่ครบ",IF(R30="","",IF(R30&gt;=DATA!$AI$10,"สูง",IF(R30&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T30" s="33">
+      <c r="T30" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",IF(R30="","",RANK(R30,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U30" s="32">
+      <c r="U30" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B30="","",COUNTBLANK('1-UseCase ทั้งหมด'!I30)+COUNTBLANK('1-UseCase ทั้งหมด'!J30)+COUNTBLANK('1-UseCase ทั้งหมด'!L30)+COUNTBLANK('1-UseCase ทั้งหมด'!M30)+COUNTBLANK('1-UseCase ทั้งหมด'!O30)+COUNTBLANK('1-UseCase ทั้งหมด'!P30)+COUNTBLANK('1-UseCase ทั้งหมด'!Q30)+COUNTBLANK('1-UseCase ทั้งหมด'!R30)+COUNTBLANK('1-UseCase ทั้งหมด'!S30)+COUNTBLANK('1-UseCase ทั้งหมด'!T30))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="25">
+      <c r="A31" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",'1-UseCase ทั้งหมด'!A31)</f>
         <v/>
       </c>
-      <c r="B31" s="25">
+      <c r="B31" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",'1-UseCase ทั้งหมด'!B31)</f>
         <v/>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",'1-UseCase ทั้งหมด'!D31)</f>
         <v/>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I31,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E31" s="32">
+      <c r="E31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J31,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(D31="",IF(AND(E31&lt;&gt;"",E31&lt;&gt;"-"),E31,""),IF(AND(E31&lt;&gt;"",E31&lt;&gt;"-"),ROUND((D31+E31)/2,0),D31)))</f>
         <v/>
       </c>
-      <c r="G31" s="32">
+      <c r="G31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L31,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H31" s="32">
+      <c r="H31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M31,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I31" s="32">
+      <c r="I31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O31,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J31" s="33">
+      <c r="J31" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(ROUND(AVERAGE(G31:I31),0),""))</f>
         <v/>
       </c>
-      <c r="K31" s="32">
+      <c r="K31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P31,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L31" s="32">
+      <c r="L31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q31,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M31" s="33">
+      <c r="M31" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(ROUND(AVERAGE(K31:L31),0),""))</f>
         <v/>
       </c>
-      <c r="N31" s="32">
+      <c r="N31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R31,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O31" s="32">
+      <c r="O31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S31,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P31" s="32">
+      <c r="P31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T31,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q31" s="33">
+      <c r="Q31" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(ROUND(AVERAGE(N31:P31),0),""))</f>
         <v/>
       </c>
-      <c r="R31" s="34">
+      <c r="R31" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(U31&gt;0,"",IFERROR(ROUND((F31*DATA!$AI$4+M31*DATA!$AI$5+J31*DATA!$AI$6+(6-Q31)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S31" s="33">
+      <c r="S31" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(U31&gt;0,"ข้อมูลไม่ครบ",IF(R31="","",IF(R31&gt;=DATA!$AI$10,"สูง",IF(R31&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T31" s="33">
+      <c r="T31" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",IF(R31="","",RANK(R31,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U31" s="32">
+      <c r="U31" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B31="","",COUNTBLANK('1-UseCase ทั้งหมด'!I31)+COUNTBLANK('1-UseCase ทั้งหมด'!J31)+COUNTBLANK('1-UseCase ทั้งหมด'!L31)+COUNTBLANK('1-UseCase ทั้งหมด'!M31)+COUNTBLANK('1-UseCase ทั้งหมด'!O31)+COUNTBLANK('1-UseCase ทั้งหมด'!P31)+COUNTBLANK('1-UseCase ทั้งหมด'!Q31)+COUNTBLANK('1-UseCase ทั้งหมด'!R31)+COUNTBLANK('1-UseCase ทั้งหมด'!S31)+COUNTBLANK('1-UseCase ทั้งหมด'!T31))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="25">
+      <c r="A32" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",'1-UseCase ทั้งหมด'!A32)</f>
         <v/>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",'1-UseCase ทั้งหมด'!B32)</f>
         <v/>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",'1-UseCase ทั้งหมด'!D32)</f>
         <v/>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I32,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E32" s="32">
+      <c r="E32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J32,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F32" s="33">
+      <c r="F32" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(D32="",IF(AND(E32&lt;&gt;"",E32&lt;&gt;"-"),E32,""),IF(AND(E32&lt;&gt;"",E32&lt;&gt;"-"),ROUND((D32+E32)/2,0),D32)))</f>
         <v/>
       </c>
-      <c r="G32" s="32">
+      <c r="G32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L32,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H32" s="32">
+      <c r="H32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M32,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I32" s="32">
+      <c r="I32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O32,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J32" s="33">
+      <c r="J32" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(ROUND(AVERAGE(G32:I32),0),""))</f>
         <v/>
       </c>
-      <c r="K32" s="32">
+      <c r="K32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P32,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L32" s="32">
+      <c r="L32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q32,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M32" s="33">
+      <c r="M32" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(ROUND(AVERAGE(K32:L32),0),""))</f>
         <v/>
       </c>
-      <c r="N32" s="32">
+      <c r="N32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R32,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O32" s="32">
+      <c r="O32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S32,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P32" s="32">
+      <c r="P32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T32,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q32" s="33">
+      <c r="Q32" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(ROUND(AVERAGE(N32:P32),0),""))</f>
         <v/>
       </c>
-      <c r="R32" s="34">
+      <c r="R32" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(U32&gt;0,"",IFERROR(ROUND((F32*DATA!$AI$4+M32*DATA!$AI$5+J32*DATA!$AI$6+(6-Q32)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S32" s="33">
+      <c r="S32" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(U32&gt;0,"ข้อมูลไม่ครบ",IF(R32="","",IF(R32&gt;=DATA!$AI$10,"สูง",IF(R32&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T32" s="33">
+      <c r="T32" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",IF(R32="","",RANK(R32,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U32" s="32">
+      <c r="U32" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B32="","",COUNTBLANK('1-UseCase ทั้งหมด'!I32)+COUNTBLANK('1-UseCase ทั้งหมด'!J32)+COUNTBLANK('1-UseCase ทั้งหมด'!L32)+COUNTBLANK('1-UseCase ทั้งหมด'!M32)+COUNTBLANK('1-UseCase ทั้งหมด'!O32)+COUNTBLANK('1-UseCase ทั้งหมด'!P32)+COUNTBLANK('1-UseCase ทั้งหมด'!Q32)+COUNTBLANK('1-UseCase ทั้งหมด'!R32)+COUNTBLANK('1-UseCase ทั้งหมด'!S32)+COUNTBLANK('1-UseCase ทั้งหมด'!T32))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="25">
+      <c r="A33" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",'1-UseCase ทั้งหมด'!A33)</f>
         <v/>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",'1-UseCase ทั้งหมด'!B33)</f>
         <v/>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",'1-UseCase ทั้งหมด'!D33)</f>
         <v/>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I33,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J33,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(D33="",IF(AND(E33&lt;&gt;"",E33&lt;&gt;"-"),E33,""),IF(AND(E33&lt;&gt;"",E33&lt;&gt;"-"),ROUND((D33+E33)/2,0),D33)))</f>
         <v/>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L33,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M33,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O33,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J33" s="33">
+      <c r="J33" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(ROUND(AVERAGE(G33:I33),0),""))</f>
         <v/>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P33,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L33" s="32">
+      <c r="L33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q33,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M33" s="33">
+      <c r="M33" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(ROUND(AVERAGE(K33:L33),0),""))</f>
         <v/>
       </c>
-      <c r="N33" s="32">
+      <c r="N33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R33,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O33" s="32">
+      <c r="O33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S33,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P33" s="32">
+      <c r="P33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T33,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q33" s="33">
+      <c r="Q33" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(ROUND(AVERAGE(N33:P33),0),""))</f>
         <v/>
       </c>
-      <c r="R33" s="34">
+      <c r="R33" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(U33&gt;0,"",IFERROR(ROUND((F33*DATA!$AI$4+M33*DATA!$AI$5+J33*DATA!$AI$6+(6-Q33)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(U33&gt;0,"ข้อมูลไม่ครบ",IF(R33="","",IF(R33&gt;=DATA!$AI$10,"สูง",IF(R33&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T33" s="33">
+      <c r="T33" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",IF(R33="","",RANK(R33,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U33" s="32">
+      <c r="U33" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B33="","",COUNTBLANK('1-UseCase ทั้งหมด'!I33)+COUNTBLANK('1-UseCase ทั้งหมด'!J33)+COUNTBLANK('1-UseCase ทั้งหมด'!L33)+COUNTBLANK('1-UseCase ทั้งหมด'!M33)+COUNTBLANK('1-UseCase ทั้งหมด'!O33)+COUNTBLANK('1-UseCase ทั้งหมด'!P33)+COUNTBLANK('1-UseCase ทั้งหมด'!Q33)+COUNTBLANK('1-UseCase ทั้งหมด'!R33)+COUNTBLANK('1-UseCase ทั้งหมด'!S33)+COUNTBLANK('1-UseCase ทั้งหมด'!T33))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="25">
+      <c r="A34" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",'1-UseCase ทั้งหมด'!A34)</f>
         <v/>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",'1-UseCase ทั้งหมด'!B34)</f>
         <v/>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",'1-UseCase ทั้งหมด'!D34)</f>
         <v/>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I34,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E34" s="32">
+      <c r="E34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J34,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(D34="",IF(AND(E34&lt;&gt;"",E34&lt;&gt;"-"),E34,""),IF(AND(E34&lt;&gt;"",E34&lt;&gt;"-"),ROUND((D34+E34)/2,0),D34)))</f>
         <v/>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L34,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M34,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I34" s="32">
+      <c r="I34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O34,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J34" s="33">
+      <c r="J34" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(ROUND(AVERAGE(G34:I34),0),""))</f>
         <v/>
       </c>
-      <c r="K34" s="32">
+      <c r="K34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P34,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L34" s="32">
+      <c r="L34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q34,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M34" s="33">
+      <c r="M34" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(ROUND(AVERAGE(K34:L34),0),""))</f>
         <v/>
       </c>
-      <c r="N34" s="32">
+      <c r="N34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R34,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O34" s="32">
+      <c r="O34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S34,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P34" s="32">
+      <c r="P34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T34,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q34" s="33">
+      <c r="Q34" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(ROUND(AVERAGE(N34:P34),0),""))</f>
         <v/>
       </c>
-      <c r="R34" s="34">
+      <c r="R34" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(U34&gt;0,"",IFERROR(ROUND((F34*DATA!$AI$4+M34*DATA!$AI$5+J34*DATA!$AI$6+(6-Q34)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S34" s="33">
+      <c r="S34" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(U34&gt;0,"ข้อมูลไม่ครบ",IF(R34="","",IF(R34&gt;=DATA!$AI$10,"สูง",IF(R34&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T34" s="33">
+      <c r="T34" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",IF(R34="","",RANK(R34,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U34" s="32">
+      <c r="U34" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B34="","",COUNTBLANK('1-UseCase ทั้งหมด'!I34)+COUNTBLANK('1-UseCase ทั้งหมด'!J34)+COUNTBLANK('1-UseCase ทั้งหมด'!L34)+COUNTBLANK('1-UseCase ทั้งหมด'!M34)+COUNTBLANK('1-UseCase ทั้งหมด'!O34)+COUNTBLANK('1-UseCase ทั้งหมด'!P34)+COUNTBLANK('1-UseCase ทั้งหมด'!Q34)+COUNTBLANK('1-UseCase ทั้งหมด'!R34)+COUNTBLANK('1-UseCase ทั้งหมด'!S34)+COUNTBLANK('1-UseCase ทั้งหมด'!T34))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="25">
+      <c r="A35" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",'1-UseCase ทั้งหมด'!A35)</f>
         <v/>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",'1-UseCase ทั้งหมด'!B35)</f>
         <v/>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",'1-UseCase ทั้งหมด'!D35)</f>
         <v/>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I35,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E35" s="32">
+      <c r="E35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J35,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(D35="",IF(AND(E35&lt;&gt;"",E35&lt;&gt;"-"),E35,""),IF(AND(E35&lt;&gt;"",E35&lt;&gt;"-"),ROUND((D35+E35)/2,0),D35)))</f>
         <v/>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L35,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H35" s="32">
+      <c r="H35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M35,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I35" s="32">
+      <c r="I35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O35,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J35" s="33">
+      <c r="J35" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(ROUND(AVERAGE(G35:I35),0),""))</f>
         <v/>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P35,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L35" s="32">
+      <c r="L35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q35,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M35" s="33">
+      <c r="M35" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(ROUND(AVERAGE(K35:L35),0),""))</f>
         <v/>
       </c>
-      <c r="N35" s="32">
+      <c r="N35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R35,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O35" s="32">
+      <c r="O35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S35,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P35" s="32">
+      <c r="P35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T35,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q35" s="33">
+      <c r="Q35" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(ROUND(AVERAGE(N35:P35),0),""))</f>
         <v/>
       </c>
-      <c r="R35" s="34">
+      <c r="R35" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(U35&gt;0,"",IFERROR(ROUND((F35*DATA!$AI$4+M35*DATA!$AI$5+J35*DATA!$AI$6+(6-Q35)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S35" s="33">
+      <c r="S35" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(U35&gt;0,"ข้อมูลไม่ครบ",IF(R35="","",IF(R35&gt;=DATA!$AI$10,"สูง",IF(R35&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T35" s="33">
+      <c r="T35" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",IF(R35="","",RANK(R35,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U35" s="32">
+      <c r="U35" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B35="","",COUNTBLANK('1-UseCase ทั้งหมด'!I35)+COUNTBLANK('1-UseCase ทั้งหมด'!J35)+COUNTBLANK('1-UseCase ทั้งหมด'!L35)+COUNTBLANK('1-UseCase ทั้งหมด'!M35)+COUNTBLANK('1-UseCase ทั้งหมด'!O35)+COUNTBLANK('1-UseCase ทั้งหมด'!P35)+COUNTBLANK('1-UseCase ทั้งหมด'!Q35)+COUNTBLANK('1-UseCase ทั้งหมด'!R35)+COUNTBLANK('1-UseCase ทั้งหมด'!S35)+COUNTBLANK('1-UseCase ทั้งหมด'!T35))</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="25">
+      <c r="A36" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",'1-UseCase ทั้งหมด'!A36)</f>
         <v/>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",'1-UseCase ทั้งหมด'!B36)</f>
         <v/>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="26">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",'1-UseCase ทั้งหมด'!D36)</f>
         <v/>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I36,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
-      <c r="E36" s="32">
+      <c r="E36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J36,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(D36="",IF(AND(E36&lt;&gt;"",E36&lt;&gt;"-"),E36,""),IF(AND(E36&lt;&gt;"",E36&lt;&gt;"-"),ROUND((D36+E36)/2,0),D36)))</f>
         <v/>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L36,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
-      <c r="H36" s="32">
+      <c r="H36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M36,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
-      <c r="I36" s="32">
+      <c r="I36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O36,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
-      <c r="J36" s="33">
+      <c r="J36" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(ROUND(AVERAGE(G36:I36),0),""))</f>
         <v/>
       </c>
-      <c r="K36" s="32">
+      <c r="K36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P36,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
-      <c r="L36" s="32">
+      <c r="L36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q36,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
-      <c r="M36" s="33">
+      <c r="M36" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(ROUND(AVERAGE(K36:L36),0),""))</f>
         <v/>
       </c>
-      <c r="N36" s="32">
+      <c r="N36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R36,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
-      <c r="O36" s="32">
+      <c r="O36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S36,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
-      <c r="P36" s="32">
+      <c r="P36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T36,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
-      <c r="Q36" s="33">
+      <c r="Q36" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(ROUND(AVERAGE(N36:P36),0),""))</f>
         <v/>
       </c>
-      <c r="R36" s="34">
+      <c r="R36" s="36">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(U36&gt;0,"",IFERROR(ROUND((F36*DATA!$AI$4+M36*DATA!$AI$5+J36*DATA!$AI$6+(6-Q36)*DATA!$AI$7)*20,1),"")))</f>
         <v/>
       </c>
-      <c r="S36" s="33">
+      <c r="S36" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(U36&gt;0,"ข้อมูลไม่ครบ",IF(R36="","",IF(R36&gt;=DATA!$AI$10,"สูง",IF(R36&gt;=DATA!$AI$11,"กลาง","ต่ำ")))))</f>
         <v/>
       </c>
-      <c r="T36" s="33">
+      <c r="T36" s="35">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",IF(R36="","",RANK(R36,$R$7:$R$36,0)))</f>
         <v/>
       </c>
-      <c r="U36" s="32">
+      <c r="U36" s="34">
         <f>IF('1-UseCase ทั้งหมด'!B36="","",COUNTBLANK('1-UseCase ทั้งหมด'!I36)+COUNTBLANK('1-UseCase ทั้งหมด'!J36)+COUNTBLANK('1-UseCase ทั้งหมด'!L36)+COUNTBLANK('1-UseCase ทั้งหมด'!M36)+COUNTBLANK('1-UseCase ทั้งหมด'!O36)+COUNTBLANK('1-UseCase ทั้งหมด'!P36)+COUNTBLANK('1-UseCase ทั้งหมด'!Q36)+COUNTBLANK('1-UseCase ทั้งหมด'!R36)+COUNTBLANK('1-UseCase ทั้งหมด'!S36)+COUNTBLANK('1-UseCase ทั้งหมด'!T36))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="37" t="inlineStr">
         <is>
           <t>เกณฑ์การแบ่งระดับ และสูตรที่ใช้</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="36" t="inlineStr">
+      <c r="A39" s="38" t="inlineStr">
         <is>
           <t>•  สูตร :  คะแนนรวม = ( Impact x 35%  +  Feasibility x 25%  +  Data x 25%  +  (6 - Risk) x 15% )  x 20</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="38" t="inlineStr">
         <is>
           <t>•  Risk ถูกกลับด้านด้วย (6 - Risk) เพราะความเสี่ยงสูง = คะแนนควรต่ำ</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>•  ระดับ สูง = 75 คะแนนขึ้นไป  |  กลาง = 50 - 74  |  ต่ำ = ต่ำกว่า 50  (คะแนนต่ำสุดที่เป็นไปได้คือ 20 ไม่ใช่ 0)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="38" t="inlineStr">
         <is>
           <t>•  ถ้าช่องบังคับในชั้นที่ 1 ยังกรอกไม่ครบ ระบบจะไม่แสดงคะแนนรวม แต่ขึ้นว่า 'ข้อมูลไม่ครบ' และบอกจำนวนช่องที่ยังขาดในคอลัมน์สุดท้าย — กลับไปกรอกให้ครบแล้วคะแนนจะขึ้นเอง</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>•  ช่องบังคับ 10 ช่อง = เวลาที่ใช้ / มูลค่าความเสียหาย / รูปแบบข้อมูล / ข้อมูลย้อนหลัง / สิทธิ์ใช้ข้อมูล / ระบบเดิม / คนดูแลต่อ / ผลกระทบถ้า AI ผิด / การตรวจซ้ำ / ระดับความลับ</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="38" t="inlineStr">
         <is>
           <t>•  ถ้าตีมูลค่าความเสียหายเป็นเงินไม่ได้ ให้เลือก 'ประเมินเป็นเงินไม่ได้' — ระบบจะใช้เฉพาะชั่วโมงคิด Impact ไม่ได้หักคะแนน (ในตารางจะขึ้นเป็น '-')</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t>•  คะแนนนี้เป็นตัวช่วยกรองเบื้องต้น ไม่ใช่คำตอบสุดท้าย — ผู้บริหารควรพิจารณา Use Case อันดับต้นๆ ด้วยตนเองอีกครั้ง</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t>•  ค่าเกณฑ์ชั่วโมง/มูลค่า และน้ำหนักทุกตัว แก้ได้ที่ sheet DATA คอลัมน์ S-T (ตัวเลขสีน้ำเงิน)</t>
         </is>
@@ -6671,7 +6641,6 @@
     <col width="32" customWidth="1" min="24" max="24"/>
     <col width="32" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="32" customWidth="1" min="27" max="27"/>
     <col width="32" customWidth="1" min="28" max="28"/>
     <col width="32" customWidth="1" min="29" max="29"/>
     <col width="32" customWidth="1" min="30" max="30"/>
@@ -6680,1589 +6649,1559 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>รายการตัวเลือก (Dropdown) — เพิ่ม/แก้ตัวเลือกได้ที่นี่ แล้วทุก sheet จะเปลี่ยนตาม</t>
         </is>
       </c>
-      <c r="AH1" s="37" t="inlineStr">
+      <c r="AH1" s="39" t="inlineStr">
         <is>
           <t>ค่าตั้งต้นของการคำนวณคะแนน (แก้ได้ ทุกสูตรจะเปลี่ยนตาม)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="40" t="inlineStr">
         <is>
           <t>บริษัท</t>
         </is>
       </c>
-      <c r="B3" s="38" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน</t>
         </is>
       </c>
-      <c r="C3" s="38" t="inlineStr">
+      <c r="C3" s="40" t="inlineStr">
         <is>
           <t>มีข้อมูลย้อนหลังนานแค่ไหน</t>
         </is>
       </c>
-      <c r="D3" s="38" t="inlineStr">
+      <c r="D3" s="40" t="inlineStr">
         <is>
           <t>สิทธิ์นำข้อมูลมาใช้</t>
         </is>
       </c>
-      <c r="E3" s="38" t="inlineStr">
+      <c r="E3" s="40" t="inlineStr">
         <is>
           <t>ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย</t>
         </is>
       </c>
-      <c r="F3" s="38" t="inlineStr">
+      <c r="F3" s="40" t="inlineStr">
         <is>
           <t>มีคนดูแลระบบต่อหลังส่งมอบมั้ย</t>
         </is>
       </c>
-      <c r="G3" s="38" t="inlineStr">
+      <c r="G3" s="40" t="inlineStr">
         <is>
           <t>ถ้า AI ตอบผิด จะเกิดอะไรขึ้น</t>
         </is>
       </c>
-      <c r="H3" s="38" t="inlineStr">
+      <c r="H3" s="40" t="inlineStr">
         <is>
           <t>ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย</t>
         </is>
       </c>
-      <c r="I3" s="38" t="inlineStr">
+      <c r="I3" s="40" t="inlineStr">
         <is>
           <t>ข้อมูลชุดนี้ลับแค่ไหน</t>
         </is>
       </c>
-      <c r="J3" s="38" t="inlineStr">
+      <c r="J3" s="40" t="inlineStr">
         <is>
           <t>ความสำคัญที่แผนกอยากได้</t>
         </is>
       </c>
-      <c r="K3" s="38" t="inlineStr">
+      <c r="K3" s="40" t="inlineStr">
         <is>
           <t>ประเภทข้อมูล Input</t>
         </is>
       </c>
-      <c r="L3" s="38" t="inlineStr">
+      <c r="L3" s="40" t="inlineStr">
         <is>
           <t>ภาษาที่ต้องการ</t>
         </is>
       </c>
-      <c r="M3" s="38" t="inlineStr">
+      <c r="M3" s="40" t="inlineStr">
         <is>
           <t>Latency ที่รับได้</t>
         </is>
       </c>
-      <c r="N3" s="38" t="inlineStr">
+      <c r="N3" s="40" t="inlineStr">
         <is>
           <t>Availability</t>
         </is>
       </c>
-      <c r="O3" s="38" t="inlineStr">
+      <c r="O3" s="40" t="inlineStr">
         <is>
           <t>ความละเอียดรูป</t>
         </is>
       </c>
-      <c r="P3" s="38" t="inlineStr">
+      <c r="P3" s="40" t="inlineStr">
         <is>
           <t>ที่ตั้งระบบ</t>
         </is>
       </c>
-      <c r="Q3" s="38" t="inlineStr">
-        <is>
-          <t>ความต้องการโมเดล</t>
-        </is>
-      </c>
-      <c r="R3" s="38" t="inlineStr">
+      <c r="Q3" s="40" t="inlineStr">
+        <is>
+          <t>ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย</t>
+        </is>
+      </c>
+      <c r="R3" s="40" t="inlineStr">
         <is>
           <t>เวลาที่ใช้กับงานนี้ตอนนี้</t>
         </is>
       </c>
-      <c r="S3" s="38" t="inlineStr">
+      <c r="S3" s="40" t="inlineStr">
         <is>
           <t>มูลค่าความเสียหาย/ของเสียต่อปี</t>
         </is>
       </c>
-      <c r="T3" s="38" t="inlineStr">
+      <c r="T3" s="40" t="inlineStr">
         <is>
           <t>จำนวน Users/วัน</t>
         </is>
       </c>
-      <c r="U3" s="38" t="inlineStr">
+      <c r="U3" s="40" t="inlineStr">
         <is>
           <t>Peak concurrent (คนพร้อมกัน)</t>
         </is>
       </c>
-      <c r="V3" s="38" t="inlineStr">
+      <c r="V3" s="40" t="inlineStr">
         <is>
           <t>Requests/วัน</t>
         </is>
       </c>
-      <c r="W3" s="38" t="inlineStr">
+      <c r="W3" s="40" t="inlineStr">
         <is>
           <t>ขนาดข้อมูล Input/วัน</t>
         </is>
       </c>
-      <c r="X3" s="38" t="inlineStr">
+      <c r="X3" s="40" t="inlineStr">
         <is>
           <t>ขนาดคลังเอกสารทั้งหมด (RAG)</t>
         </is>
       </c>
-      <c r="Y3" s="38" t="inlineStr">
+      <c r="Y3" s="40" t="inlineStr">
         <is>
           <t>จำนวนกล้อง/จุดตรวจพร้อมกัน</t>
         </is>
       </c>
-      <c r="Z3" s="38" t="inlineStr">
+      <c r="Z3" s="40" t="inlineStr">
         <is>
           <t>ติดตั้งแบบไหน</t>
         </is>
       </c>
-      <c r="AA3" s="38" t="inlineStr">
-        <is>
-          <t>มีเครื่อง/GPU เดิมใช้ได้มั้ย</t>
-        </is>
-      </c>
-      <c r="AB3" s="38" t="inlineStr">
+      <c r="AB3" s="40" t="inlineStr">
         <is>
           <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
         </is>
       </c>
-      <c r="AC3" s="38" t="inlineStr">
+      <c r="AC3" s="40" t="inlineStr">
         <is>
           <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
         </is>
       </c>
-      <c r="AD3" s="38" t="inlineStr">
-        <is>
-          <t>แชร์เครื่องกับงานอื่นได้มั้ย</t>
-        </is>
-      </c>
-      <c r="AH3" s="39" t="inlineStr">
+      <c r="AD3" s="40" t="inlineStr">
+        <is>
+          <t>ถ้างานนี้ช้าลงจะเป็นปัญหามั้ย</t>
+        </is>
+      </c>
+      <c r="AH3" s="41" t="inlineStr">
         <is>
           <t>น้ำหนักแต่ละปัจจัย</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>S.K.Polymer</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>กระดาษ / เอกสารเขียนมือ - ต้องพิมพ์เข้าคอมก่อน</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>ยังไม่มี - ต้องเริ่มเก็บใหม่</t>
         </is>
       </c>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>ได้ทันที - ข้อมูลอยู่ในมือแผนกเราเอง</t>
         </is>
       </c>
-      <c r="E4" s="40" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>ไม่มี - AI ทำงานแยกเดี่ยวได้เลย ไม่ต้องยุ่งกับระบบไหน</t>
         </is>
       </c>
-      <c r="F4" s="40" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>มี - มีคนในแผนกรับดูแลต่อได้ (ระบุชื่อในหมายเหตุ)</t>
         </is>
       </c>
-      <c r="G4" s="40" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>ต่ำ - คนเห็นแล้วแก้ได้ทันที ไม่มีใครเดือดร้อน</t>
         </is>
       </c>
-      <c r="H4" s="40" t="inlineStr">
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>ไม่ต้อง - ใช้ผล AI ได้เลย</t>
         </is>
       </c>
-      <c r="I4" s="40" t="inlineStr">
+      <c r="I4" s="42" t="inlineStr">
         <is>
           <t>สาธารณะ - หลุดออกไปก็ไม่เป็นไร</t>
         </is>
       </c>
-      <c r="J4" s="40" t="inlineStr">
+      <c r="J4" s="42" t="inlineStr">
         <is>
           <t>สูง - ต้องการด่วน</t>
         </is>
       </c>
-      <c r="K4" s="40" t="inlineStr">
+      <c r="K4" s="42" t="inlineStr">
         <is>
           <t>ข้อความ / เอกสาร</t>
         </is>
       </c>
-      <c r="L4" s="40" t="inlineStr">
+      <c r="L4" s="42" t="inlineStr">
         <is>
           <t>ไทย</t>
         </is>
       </c>
-      <c r="M4" s="40" t="inlineStr">
+      <c r="M4" s="42" t="inlineStr">
         <is>
           <t>Real-time (0 - 2 วินาที)</t>
         </is>
       </c>
-      <c r="N4" s="40" t="inlineStr">
+      <c r="N4" s="42" t="inlineStr">
         <is>
           <t>Business Hour (8:00 - 18:00)</t>
         </is>
       </c>
-      <c r="O4" s="40" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>ไม่เกี่ยวข้อง</t>
         </is>
       </c>
-      <c r="P4" s="40" t="inlineStr">
+      <c r="P4" s="42" t="inlineStr">
         <is>
           <t>On-premise เท่านั้น (ห้ามออกนอก)</t>
         </is>
       </c>
-      <c r="Q4" s="40" t="inlineStr">
-        <is>
-          <t>ใช้โมเดลสำเร็จรูปได้</t>
-        </is>
-      </c>
-      <c r="R4" s="40" t="inlineStr">
+      <c r="Q4" s="42" t="inlineStr">
+        <is>
+          <t>ไม่ต้อง - ใช้โมเดลสำเร็จรูปได้เลย (งานความรู้ทั่วไป)</t>
+        </is>
+      </c>
+      <c r="R4" s="42" t="inlineStr">
         <is>
           <t>น้อยกว่า 4 ชม./สัปดาห์  (ไม่ถึงครึ่งวันทำงาน)</t>
         </is>
       </c>
-      <c r="S4" s="40" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr">
         <is>
           <t>ประเมินเป็นเงินไม่ได้ / ไม่มีความเสียหายโดยตรง</t>
         </is>
       </c>
-      <c r="T4" s="40" t="inlineStr">
+      <c r="T4" s="42" t="inlineStr">
         <is>
           <t>1 - 10 คน</t>
         </is>
       </c>
-      <c r="U4" s="40" t="inlineStr">
+      <c r="U4" s="42" t="inlineStr">
         <is>
           <t>1 - 2 คน</t>
         </is>
       </c>
-      <c r="V4" s="40" t="inlineStr">
+      <c r="V4" s="42" t="inlineStr">
         <is>
           <t>น้อยกว่า 100 ครั้ง</t>
         </is>
       </c>
-      <c r="W4" s="40" t="inlineStr">
+      <c r="W4" s="42" t="inlineStr">
         <is>
           <t>น้อยกว่า 1 GB</t>
         </is>
       </c>
-      <c r="X4" s="40" t="inlineStr">
+      <c r="X4" s="42" t="inlineStr">
         <is>
           <t>ไม่เกี่ยวข้อง - ไม่ใช่งานค้นหาเอกสาร</t>
         </is>
       </c>
-      <c r="Y4" s="40" t="inlineStr">
+      <c r="Y4" s="42" t="inlineStr">
         <is>
           <t>ไม่เกี่ยวข้อง - ไม่ใช่งานภาพ</t>
         </is>
       </c>
-      <c r="Z4" s="40" t="inlineStr">
+      <c r="Z4" s="42" t="inlineStr">
         <is>
           <t>รันบน server กลางได้ - ส่งข้อมูลผ่านเครือข่ายมาได้</t>
         </is>
       </c>
-      <c r="AA4" s="40" t="inlineStr">
-        <is>
-          <t>มี GPU ว่างอยู่ - ใช้ได้เลย</t>
-        </is>
-      </c>
-      <c r="AB4" s="40" t="inlineStr">
+      <c r="AB4" s="42" t="inlineStr">
         <is>
           <t>1 ปี</t>
         </is>
       </c>
-      <c r="AC4" s="40" t="inlineStr">
+      <c r="AC4" s="42" t="inlineStr">
+        <is>
+          <t>ไม่ต้องเทรนเลย - ใช้โมเดลสำเร็จรูป</t>
+        </is>
+      </c>
+      <c r="AD4" s="42" t="inlineStr">
+        <is>
+          <t>ไม่เป็นไร - รอได้ ช้าหน่อยก็ยังใช้งานได้</t>
+        </is>
+      </c>
+      <c r="AH4" s="42" t="inlineStr">
+        <is>
+          <t>Impact (ผลกระทบ)</t>
+        </is>
+      </c>
+      <c r="AI4" s="43" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>Thairubbtech</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>ไฟล์ Excel / CSV - เปิดใช้ได้เลย</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>น้อยกว่า 1 ปี - อาจยังไม่พอเทรน</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>ต้องขออนุมัติก่อน - เป็นของแผนกอื่น / IT</t>
+        </is>
+      </c>
+      <c r="E5" s="42" t="inlineStr">
+        <is>
+          <t>มี - แค่ export ไฟล์ออกมาให้ AI แล้วเอาผลกลับเข้าไปทีหลังก็พอ</t>
+        </is>
+      </c>
+      <c r="F5" s="42" t="inlineStr">
+        <is>
+          <t>ยังไม่แน่ใจ - ต้องหาคนก่อน</t>
+        </is>
+      </c>
+      <c r="G5" s="42" t="inlineStr">
+        <is>
+          <t>กลาง - เสียเวลาทำใหม่ หรือเสียต้นทุนบางส่วน</t>
+        </is>
+      </c>
+      <c r="H5" s="42" t="inlineStr">
+        <is>
+          <t>สุ่มตรวจบางส่วน - ตรวจเฉพาะที่ AI ไม่มั่นใจ</t>
+        </is>
+      </c>
+      <c r="I5" s="42" t="inlineStr">
+        <is>
+          <t>ข้อมูลภายใน - ห้ามออกนอกบริษัท</t>
+        </is>
+      </c>
+      <c r="J5" s="42" t="inlineStr">
+        <is>
+          <t>กลาง - (Q2 - Q3)</t>
+        </is>
+      </c>
+      <c r="K5" s="42" t="inlineStr">
+        <is>
+          <t>รูปภาพ</t>
+        </is>
+      </c>
+      <c r="L5" s="42" t="inlineStr">
+        <is>
+          <t>อังกฤษ</t>
+        </is>
+      </c>
+      <c r="M5" s="42" t="inlineStr">
+        <is>
+          <t>Interactive (2 - 10 วินาที)</t>
+        </is>
+      </c>
+      <c r="N5" s="42" t="inlineStr">
+        <is>
+          <t>Extended (6:00 - 22:00)</t>
+        </is>
+      </c>
+      <c r="O5" s="42" t="inlineStr">
+        <is>
+          <t>ต่ำกว่า 1 MP</t>
+        </is>
+      </c>
+      <c r="P5" s="42" t="inlineStr">
+        <is>
+          <t>ใช้ Cloud / API ภายนอกได้</t>
+        </is>
+      </c>
+      <c r="Q5" s="42" t="inlineStr">
+        <is>
+          <t>ไม่ต้องเทรน แต่ให้อ่านเอกสารบริษัท (RAG)</t>
+        </is>
+      </c>
+      <c r="R5" s="42" t="inlineStr">
+        <is>
+          <t>4 - 10 ชม./สัปดาห์  (ประมาณ 1 วันทำงาน)</t>
+        </is>
+      </c>
+      <c r="S5" s="42" t="inlineStr">
+        <is>
+          <t>น้อยกว่า 1 แสนบาท/ปี</t>
+        </is>
+      </c>
+      <c r="T5" s="42" t="inlineStr">
+        <is>
+          <t>11 - 50 คน</t>
+        </is>
+      </c>
+      <c r="U5" s="42" t="inlineStr">
+        <is>
+          <t>3 - 5 คน</t>
+        </is>
+      </c>
+      <c r="V5" s="42" t="inlineStr">
+        <is>
+          <t>100 - 1,000 ครั้ง</t>
+        </is>
+      </c>
+      <c r="W5" s="42" t="inlineStr">
+        <is>
+          <t>1 - 10 GB</t>
+        </is>
+      </c>
+      <c r="X5" s="42" t="inlineStr">
+        <is>
+          <t>น้อยกว่า 1 GB</t>
+        </is>
+      </c>
+      <c r="Y5" s="42" t="inlineStr">
+        <is>
+          <t>1 จุด</t>
+        </is>
+      </c>
+      <c r="Z5" s="42" t="inlineStr">
+        <is>
+          <t>ต้องมีเครื่องที่หน้างาน - ติดข้างเครื่องจักร/สายพาน</t>
+        </is>
+      </c>
+      <c r="AB5" s="42" t="inlineStr">
+        <is>
+          <t>2 - 3 ปี</t>
+        </is>
+      </c>
+      <c r="AC5" s="42" t="inlineStr">
         <is>
           <t>ครั้งเดียวจบ - เทรนเสร็จใช้ยาว</t>
         </is>
       </c>
-      <c r="AD4" s="40" t="inlineStr">
-        <is>
-          <t>แชร์ได้ - ไม่ซีเรียสเรื่องความเร็ว</t>
-        </is>
-      </c>
-      <c r="AH4" s="40" t="inlineStr">
-        <is>
-          <t>Impact (ผลกระทบ)</t>
-        </is>
-      </c>
-      <c r="AI4" s="41" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="40" t="inlineStr">
-        <is>
-          <t>Thairubbtech</t>
-        </is>
-      </c>
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t>ไฟล์ Excel / CSV - เปิดใช้ได้เลย</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>น้อยกว่า 1 ปี - อาจยังไม่พอเทรน</t>
-        </is>
-      </c>
-      <c r="D5" s="40" t="inlineStr">
-        <is>
-          <t>ต้องขออนุมัติก่อน - เป็นของแผนกอื่น / IT</t>
-        </is>
-      </c>
-      <c r="E5" s="40" t="inlineStr">
-        <is>
-          <t>มี - แค่ export ไฟล์ออกมาให้ AI แล้วเอาผลกลับเข้าไปทีหลังก็พอ</t>
-        </is>
-      </c>
-      <c r="F5" s="40" t="inlineStr">
-        <is>
-          <t>ยังไม่แน่ใจ - ต้องหาคนก่อน</t>
-        </is>
-      </c>
-      <c r="G5" s="40" t="inlineStr">
-        <is>
-          <t>กลาง - เสียเวลาทำใหม่ หรือเสียต้นทุนบางส่วน</t>
-        </is>
-      </c>
-      <c r="H5" s="40" t="inlineStr">
-        <is>
-          <t>สุ่มตรวจบางส่วน - ตรวจเฉพาะที่ AI ไม่มั่นใจ</t>
-        </is>
-      </c>
-      <c r="I5" s="40" t="inlineStr">
-        <is>
-          <t>ข้อมูลภายใน - ห้ามออกนอกบริษัท</t>
-        </is>
-      </c>
-      <c r="J5" s="40" t="inlineStr">
-        <is>
-          <t>กลาง - (Q2 - Q3)</t>
-        </is>
-      </c>
-      <c r="K5" s="40" t="inlineStr">
-        <is>
-          <t>รูปภาพ</t>
-        </is>
-      </c>
-      <c r="L5" s="40" t="inlineStr">
-        <is>
-          <t>อังกฤษ</t>
-        </is>
-      </c>
-      <c r="M5" s="40" t="inlineStr">
-        <is>
-          <t>Interactive (2 - 10 วินาที)</t>
-        </is>
-      </c>
-      <c r="N5" s="40" t="inlineStr">
-        <is>
-          <t>Extended (6:00 - 22:00)</t>
-        </is>
-      </c>
-      <c r="O5" s="40" t="inlineStr">
-        <is>
-          <t>ต่ำกว่า 1 MP</t>
-        </is>
-      </c>
-      <c r="P5" s="40" t="inlineStr">
-        <is>
-          <t>ใช้ Cloud / API ภายนอกได้</t>
-        </is>
-      </c>
-      <c r="Q5" s="40" t="inlineStr">
-        <is>
-          <t>ต้อง Fine-tune ด้วยข้อมูลบริษัท</t>
-        </is>
-      </c>
-      <c r="R5" s="40" t="inlineStr">
-        <is>
-          <t>4 - 10 ชม./สัปดาห์  (ประมาณ 1 วันทำงาน)</t>
-        </is>
-      </c>
-      <c r="S5" s="40" t="inlineStr">
-        <is>
-          <t>น้อยกว่า 1 แสนบาท/ปี</t>
-        </is>
-      </c>
-      <c r="T5" s="40" t="inlineStr">
-        <is>
-          <t>11 - 50 คน</t>
-        </is>
-      </c>
-      <c r="U5" s="40" t="inlineStr">
-        <is>
-          <t>3 - 5 คน</t>
-        </is>
-      </c>
-      <c r="V5" s="40" t="inlineStr">
-        <is>
-          <t>100 - 1,000 ครั้ง</t>
-        </is>
-      </c>
-      <c r="W5" s="40" t="inlineStr">
+      <c r="AD5" s="42" t="inlineStr">
+        <is>
+          <t>พอรับได้ - แต่ช่วงเร่งด่วนต้องได้ใช้ก่อน</t>
+        </is>
+      </c>
+      <c r="AH5" s="42" t="inlineStr">
+        <is>
+          <t>Feasibility (ความเป็นไปได้)</t>
+        </is>
+      </c>
+      <c r="AI5" s="43" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>Polymate</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>ฐานข้อมูลในระบบ (ERP/MES/SQL) - ดึงอัตโนมัติได้</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>1 - 3 ปี - พอใช้ได้</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>ขอไม่ได้ / ยังไม่แน่ใจ - เป็นของลูกค้าหรือ vendor</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr">
+        <is>
+          <t>มี - AI ต้องอ่าน/เขียนข้อมูลในระบบโดยตรงแบบทันที</t>
+        </is>
+      </c>
+      <c r="F6" s="42" t="inlineStr">
+        <is>
+          <t>ไม่มี - ต้องพึ่งคนนอกแผนกตลอด</t>
+        </is>
+      </c>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>สูง - ของเสียหลุดถึงลูกค้า / อันตราย / ผิดกฎหมาย</t>
+        </is>
+      </c>
+      <c r="H6" s="42" t="inlineStr">
+        <is>
+          <t>ตรวจซ้ำทุกครั้ง - คนต้องดูทุกชิ้น/ทุกรายการ</t>
+        </is>
+      </c>
+      <c r="I6" s="42" t="inlineStr">
+        <is>
+          <t>ลับ - ต้องจำกัดสิทธิ์ว่าใครเปิดดูได้บ้าง</t>
+        </is>
+      </c>
+      <c r="J6" s="42" t="inlineStr">
+        <is>
+          <t>ต่ำ - Nice to have</t>
+        </is>
+      </c>
+      <c r="K6" s="42" t="inlineStr">
+        <is>
+          <t>เสียง</t>
+        </is>
+      </c>
+      <c r="L6" s="42" t="inlineStr">
+        <is>
+          <t>ไทย + อังกฤษ</t>
+        </is>
+      </c>
+      <c r="M6" s="42" t="inlineStr">
+        <is>
+          <t>Batch (นาที - ชั่วโมง)</t>
+        </is>
+      </c>
+      <c r="N6" s="42" t="inlineStr">
+        <is>
+          <t>24 ชม. x 7 วัน</t>
+        </is>
+      </c>
+      <c r="O6" s="42" t="inlineStr">
+        <is>
+          <t>1 - 5 MP</t>
+        </is>
+      </c>
+      <c r="P6" s="42" t="inlineStr">
+        <is>
+          <t>ผสม (ข้อมูลลับอยู่ใน, ที่เหลือออกได้)</t>
+        </is>
+      </c>
+      <c r="Q6" s="42" t="inlineStr">
+        <is>
+          <t>ต้อง Fine-tune - สอนด้วยข้อมูล/รูปของบริษัทเอง</t>
+        </is>
+      </c>
+      <c r="R6" s="42" t="inlineStr">
+        <is>
+          <t>10 - 20 ชม./สัปดาห์  (ประมาณ 2 วันทำงาน)</t>
+        </is>
+      </c>
+      <c r="S6" s="42" t="inlineStr">
+        <is>
+          <t>1 - 5 แสนบาท/ปี</t>
+        </is>
+      </c>
+      <c r="T6" s="42" t="inlineStr">
+        <is>
+          <t>51 - 200 คน</t>
+        </is>
+      </c>
+      <c r="U6" s="42" t="inlineStr">
+        <is>
+          <t>6 - 20 คน</t>
+        </is>
+      </c>
+      <c r="V6" s="42" t="inlineStr">
+        <is>
+          <t>1,000 - 10,000 ครั้ง</t>
+        </is>
+      </c>
+      <c r="W6" s="42" t="inlineStr">
+        <is>
+          <t>10 - 100 GB</t>
+        </is>
+      </c>
+      <c r="X6" s="42" t="inlineStr">
         <is>
           <t>1 - 10 GB</t>
         </is>
       </c>
-      <c r="X5" s="40" t="inlineStr">
-        <is>
-          <t>น้อยกว่า 1 GB</t>
-        </is>
-      </c>
-      <c r="Y5" s="40" t="inlineStr">
-        <is>
-          <t>1 จุด</t>
-        </is>
-      </c>
-      <c r="Z5" s="40" t="inlineStr">
-        <is>
-          <t>ต้องมีเครื่องที่หน้างาน - ติดข้างเครื่องจักร/สายพาน</t>
-        </is>
-      </c>
-      <c r="AA5" s="40" t="inlineStr">
-        <is>
-          <t>มี server แต่ไม่มี GPU</t>
-        </is>
-      </c>
-      <c r="AB5" s="40" t="inlineStr">
-        <is>
-          <t>2 - 3 ปี</t>
-        </is>
-      </c>
-      <c r="AC5" s="40" t="inlineStr">
+      <c r="Y6" s="42" t="inlineStr">
+        <is>
+          <t>2 - 3 จุด</t>
+        </is>
+      </c>
+      <c r="Z6" s="42" t="inlineStr">
+        <is>
+          <t>ยังไม่แน่ใจ</t>
+        </is>
+      </c>
+      <c r="AB6" s="42" t="inlineStr">
+        <is>
+          <t>5 ปี</t>
+        </is>
+      </c>
+      <c r="AC6" s="42" t="inlineStr">
         <is>
           <t>ปีละครั้ง</t>
         </is>
       </c>
-      <c r="AD5" s="40" t="inlineStr">
-        <is>
-          <t>แชร์ได้บางส่วน - ช่วงพีคต้องได้ก่อน</t>
-        </is>
-      </c>
-      <c r="AH5" s="40" t="inlineStr">
-        <is>
-          <t>Feasibility (ความเป็นไปได้)</t>
-        </is>
-      </c>
-      <c r="AI5" s="41" t="n">
+      <c r="AD6" s="42" t="inlineStr">
+        <is>
+          <t>เป็นปัญหา - งานนี้ช้าหรือหยุดไม่ได้เลย (อยู่ในสายการผลิต)</t>
+        </is>
+      </c>
+      <c r="AH6" s="42" t="inlineStr">
+        <is>
+          <t>Data (ความพร้อมข้อมูล)</t>
+        </is>
+      </c>
+      <c r="AI6" s="43" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="40" t="inlineStr">
-        <is>
-          <t>Polymate</t>
-        </is>
-      </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>ฐานข้อมูลในระบบ (ERP/MES/SQL) - ดึงอัตโนมัติได้</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="inlineStr">
-        <is>
-          <t>1 - 3 ปี - พอใช้ได้</t>
-        </is>
-      </c>
-      <c r="D6" s="40" t="inlineStr">
-        <is>
-          <t>ขอไม่ได้ / ยังไม่แน่ใจ - เป็นของลูกค้าหรือ vendor</t>
-        </is>
-      </c>
-      <c r="E6" s="40" t="inlineStr">
-        <is>
-          <t>มี - AI ต้องอ่าน/เขียนข้อมูลในระบบโดยตรงแบบทันที</t>
-        </is>
-      </c>
-      <c r="F6" s="40" t="inlineStr">
-        <is>
-          <t>ไม่มี - ต้องพึ่งคนนอกแผนกตลอด</t>
-        </is>
-      </c>
-      <c r="G6" s="40" t="inlineStr">
-        <is>
-          <t>สูง - ของเสียหลุดถึงลูกค้า / อันตราย / ผิดกฎหมาย</t>
-        </is>
-      </c>
-      <c r="H6" s="40" t="inlineStr">
-        <is>
-          <t>ตรวจซ้ำทุกครั้ง - คนต้องดูทุกชิ้น/ทุกรายการ</t>
-        </is>
-      </c>
-      <c r="I6" s="40" t="inlineStr">
-        <is>
-          <t>ลับ - ต้องจำกัดสิทธิ์ว่าใครเปิดดูได้บ้าง</t>
-        </is>
-      </c>
-      <c r="J6" s="40" t="inlineStr">
-        <is>
-          <t>ต่ำ - Nice to have</t>
-        </is>
-      </c>
-      <c r="K6" s="40" t="inlineStr">
-        <is>
-          <t>เสียง</t>
-        </is>
-      </c>
-      <c r="L6" s="40" t="inlineStr">
-        <is>
-          <t>ไทย + อังกฤษ</t>
-        </is>
-      </c>
-      <c r="M6" s="40" t="inlineStr">
-        <is>
-          <t>Batch (นาที - ชั่วโมง)</t>
-        </is>
-      </c>
-      <c r="N6" s="40" t="inlineStr">
-        <is>
-          <t>24 ชม. x 7 วัน</t>
-        </is>
-      </c>
-      <c r="O6" s="40" t="inlineStr">
-        <is>
-          <t>1 - 5 MP</t>
-        </is>
-      </c>
-      <c r="P6" s="40" t="inlineStr">
-        <is>
-          <t>ผสม (ข้อมูลลับอยู่ใน, ที่เหลือออกได้)</t>
-        </is>
-      </c>
-      <c r="Q6" s="40" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>GTK</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>รูปภาพ / ภาพถ่าย</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 3 ปี - เพียงพอแน่นอน</t>
+        </is>
+      </c>
+      <c r="E7" s="42" t="inlineStr">
+        <is>
+          <t>ยังไม่แน่ใจ - ต้องถาม IT ก่อน</t>
+        </is>
+      </c>
+      <c r="I7" s="42" t="inlineStr">
+        <is>
+          <t>ลับมาก - มีข้อมูลส่วนบุคคล / ผูกกับกฎหมาย PDPA</t>
+        </is>
+      </c>
+      <c r="K7" s="42" t="inlineStr">
+        <is>
+          <t>วิดีโอ</t>
+        </is>
+      </c>
+      <c r="L7" s="42" t="inlineStr">
+        <is>
+          <t>ไม่เกี่ยวกับภาษา</t>
+        </is>
+      </c>
+      <c r="O7" s="42" t="inlineStr">
+        <is>
+          <t>5 - 12 MP</t>
+        </is>
+      </c>
+      <c r="Q7" s="42" t="inlineStr">
         <is>
           <t>ยังไม่แน่ใจ</t>
         </is>
       </c>
-      <c r="R6" s="40" t="inlineStr">
-        <is>
-          <t>10 - 20 ชม./สัปดาห์  (ประมาณ 2 วันทำงาน)</t>
-        </is>
-      </c>
-      <c r="S6" s="40" t="inlineStr">
-        <is>
-          <t>1 - 5 แสนบาท/ปี</t>
-        </is>
-      </c>
-      <c r="T6" s="40" t="inlineStr">
-        <is>
-          <t>51 - 200 คน</t>
-        </is>
-      </c>
-      <c r="U6" s="40" t="inlineStr">
-        <is>
-          <t>6 - 20 คน</t>
-        </is>
-      </c>
-      <c r="V6" s="40" t="inlineStr">
-        <is>
-          <t>1,000 - 10,000 ครั้ง</t>
-        </is>
-      </c>
-      <c r="W6" s="40" t="inlineStr">
+      <c r="R7" s="42" t="inlineStr">
+        <is>
+          <t>20 - 40 ชม./สัปดาห์  (เท่ากับใช้คน 1 คนเต็มเวลา)</t>
+        </is>
+      </c>
+      <c r="S7" s="42" t="inlineStr">
+        <is>
+          <t>5 แสน - 2 ล้านบาท/ปี</t>
+        </is>
+      </c>
+      <c r="T7" s="42" t="inlineStr">
+        <is>
+          <t>201 - 1,000 คน</t>
+        </is>
+      </c>
+      <c r="U7" s="42" t="inlineStr">
+        <is>
+          <t>21 - 50 คน</t>
+        </is>
+      </c>
+      <c r="V7" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 10,000 ครั้ง</t>
+        </is>
+      </c>
+      <c r="W7" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 100 GB</t>
+        </is>
+      </c>
+      <c r="X7" s="42" t="inlineStr">
         <is>
           <t>10 - 100 GB</t>
         </is>
       </c>
-      <c r="X6" s="40" t="inlineStr">
-        <is>
-          <t>1 - 10 GB</t>
-        </is>
-      </c>
-      <c r="Y6" s="40" t="inlineStr">
-        <is>
-          <t>2 - 3 จุด</t>
-        </is>
-      </c>
-      <c r="Z6" s="40" t="inlineStr">
+      <c r="Y7" s="42" t="inlineStr">
+        <is>
+          <t>4 - 8 จุด</t>
+        </is>
+      </c>
+      <c r="AB7" s="42" t="inlineStr">
+        <is>
+          <t>เก็บถาวร - ห้ามลบ (ข้อกำหนดลูกค้า/กฎหมาย)</t>
+        </is>
+      </c>
+      <c r="AC7" s="42" t="inlineStr">
+        <is>
+          <t>ทุกไตรมาส</t>
+        </is>
+      </c>
+      <c r="AD7" s="42" t="inlineStr">
         <is>
           <t>ยังไม่แน่ใจ</t>
         </is>
       </c>
-      <c r="AA6" s="40" t="inlineStr">
-        <is>
-          <t>ไม่มีเลย - ต้องซื้อใหม่ทั้งหมด</t>
-        </is>
-      </c>
-      <c r="AB6" s="40" t="inlineStr">
-        <is>
-          <t>5 ปี</t>
-        </is>
-      </c>
-      <c r="AC6" s="40" t="inlineStr">
-        <is>
-          <t>ทุกไตรมาส</t>
-        </is>
-      </c>
-      <c r="AD6" s="40" t="inlineStr">
-        <is>
-          <t>แชร์ไม่ได้ - ต้องมีเครื่องของตัวเอง</t>
-        </is>
-      </c>
-      <c r="AH6" s="40" t="inlineStr">
-        <is>
-          <t>Data (ความพร้อมข้อมูล)</t>
-        </is>
-      </c>
-      <c r="AI6" s="41" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="40" t="inlineStr">
-        <is>
-          <t>GTK</t>
-        </is>
-      </c>
-      <c r="B7" s="40" t="inlineStr">
-        <is>
-          <t>รูปภาพ / ภาพถ่าย</t>
-        </is>
-      </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>มากกว่า 3 ปี - เพียงพอแน่นอน</t>
-        </is>
-      </c>
-      <c r="E7" s="40" t="inlineStr">
-        <is>
-          <t>ยังไม่แน่ใจ - ต้องถาม IT ก่อน</t>
-        </is>
-      </c>
-      <c r="I7" s="40" t="inlineStr">
-        <is>
-          <t>ลับมาก - มีข้อมูลส่วนบุคคล / ผูกกับกฎหมาย PDPA</t>
-        </is>
-      </c>
-      <c r="K7" s="40" t="inlineStr">
-        <is>
-          <t>วิดีโอ</t>
-        </is>
-      </c>
-      <c r="L7" s="40" t="inlineStr">
-        <is>
-          <t>ไม่เกี่ยวกับภาษา</t>
-        </is>
-      </c>
-      <c r="O7" s="40" t="inlineStr">
-        <is>
-          <t>5 - 12 MP</t>
-        </is>
-      </c>
-      <c r="R7" s="40" t="inlineStr">
-        <is>
-          <t>20 - 40 ชม./สัปดาห์  (เท่ากับใช้คน 1 คนเต็มเวลา)</t>
-        </is>
-      </c>
-      <c r="S7" s="40" t="inlineStr">
-        <is>
-          <t>5 แสน - 2 ล้านบาท/ปี</t>
-        </is>
-      </c>
-      <c r="T7" s="40" t="inlineStr">
-        <is>
-          <t>201 - 1,000 คน</t>
-        </is>
-      </c>
-      <c r="U7" s="40" t="inlineStr">
-        <is>
-          <t>21 - 50 คน</t>
-        </is>
-      </c>
-      <c r="V7" s="40" t="inlineStr">
-        <is>
-          <t>มากกว่า 10,000 ครั้ง</t>
-        </is>
-      </c>
-      <c r="W7" s="40" t="inlineStr">
+      <c r="AH7" s="42" t="inlineStr">
+        <is>
+          <t>Risk (ความเสี่ยง)</t>
+        </is>
+      </c>
+      <c r="AI7" s="43" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>อื่นๆ</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t>เสียง / วิดีโอ</t>
+        </is>
+      </c>
+      <c r="K8" s="42" t="inlineStr">
+        <is>
+          <t>ตัวเลข / ตาราง</t>
+        </is>
+      </c>
+      <c r="O8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 12 MP</t>
+        </is>
+      </c>
+      <c r="R8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 40 ชม./สัปดาห์  (มากกว่า 1 คนเต็มเวลา)</t>
+        </is>
+      </c>
+      <c r="S8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 2 ล้านบาท/ปี</t>
+        </is>
+      </c>
+      <c r="T8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 1,000 คน</t>
+        </is>
+      </c>
+      <c r="U8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 50 คน</t>
+        </is>
+      </c>
+      <c r="X8" s="42" t="inlineStr">
         <is>
           <t>มากกว่า 100 GB</t>
         </is>
       </c>
-      <c r="X7" s="40" t="inlineStr">
-        <is>
-          <t>10 - 100 GB</t>
-        </is>
-      </c>
-      <c r="Y7" s="40" t="inlineStr">
-        <is>
-          <t>4 - 8 จุด</t>
-        </is>
-      </c>
-      <c r="AA7" s="40" t="inlineStr">
-        <is>
-          <t>ยังไม่แน่ใจ - ต้องถาม IT</t>
-        </is>
-      </c>
-      <c r="AB7" s="40" t="inlineStr">
-        <is>
-          <t>เก็บถาวร - ห้ามลบ (ข้อกำหนดลูกค้า/กฎหมาย)</t>
-        </is>
-      </c>
-      <c r="AC7" s="40" t="inlineStr">
+      <c r="Y8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 8 จุด</t>
+        </is>
+      </c>
+      <c r="AC8" s="42" t="inlineStr">
         <is>
           <t>ทุกเดือนหรือถี่กว่า</t>
         </is>
       </c>
-      <c r="AD7" s="40" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>ยังไม่มีข้อมูลเก็บไว้ - ต้องเริ่มเก็บใหม่</t>
+        </is>
+      </c>
+      <c r="K9" s="42" t="inlineStr">
+        <is>
+          <t>ผสมหลายแบบ</t>
+        </is>
+      </c>
+      <c r="AC9" s="42" t="inlineStr">
         <is>
           <t>ยังไม่แน่ใจ</t>
         </is>
       </c>
-      <c r="AH7" s="40" t="inlineStr">
-        <is>
-          <t>Risk (ความเสี่ยง)</t>
-        </is>
-      </c>
-      <c r="AI7" s="41" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="40" t="inlineStr">
-        <is>
-          <t>อื่นๆ</t>
-        </is>
-      </c>
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>เสียง / วิดีโอ</t>
-        </is>
-      </c>
-      <c r="K8" s="40" t="inlineStr">
-        <is>
-          <t>ตัวเลข / ตาราง</t>
-        </is>
-      </c>
-      <c r="O8" s="40" t="inlineStr">
-        <is>
-          <t>มากกว่า 12 MP</t>
-        </is>
-      </c>
-      <c r="R8" s="40" t="inlineStr">
-        <is>
-          <t>มากกว่า 40 ชม./สัปดาห์  (มากกว่า 1 คนเต็มเวลา)</t>
-        </is>
-      </c>
-      <c r="S8" s="40" t="inlineStr">
-        <is>
-          <t>มากกว่า 2 ล้านบาท/ปี</t>
-        </is>
-      </c>
-      <c r="T8" s="40" t="inlineStr">
-        <is>
-          <t>มากกว่า 1,000 คน</t>
-        </is>
-      </c>
-      <c r="U8" s="40" t="inlineStr">
-        <is>
-          <t>มากกว่า 50 คน</t>
-        </is>
-      </c>
-      <c r="X8" s="40" t="inlineStr">
-        <is>
-          <t>มากกว่า 100 GB</t>
-        </is>
-      </c>
-      <c r="Y8" s="40" t="inlineStr">
-        <is>
-          <t>มากกว่า 8 จุด</t>
-        </is>
-      </c>
-      <c r="AC8" s="40" t="inlineStr">
-        <is>
-          <t>ยังไม่แน่ใจ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>ยังไม่มีข้อมูลเก็บไว้ - ต้องเริ่มเก็บใหม่</t>
-        </is>
-      </c>
-      <c r="K9" s="40" t="inlineStr">
-        <is>
-          <t>ผสมหลายแบบ</t>
-        </is>
-      </c>
-      <c r="AH9" s="39" t="inlineStr">
+      <c r="AH9" s="41" t="inlineStr">
         <is>
           <t>เกณฑ์แบ่งระดับ</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="AH10" s="40" t="inlineStr">
+      <c r="AH10" s="42" t="inlineStr">
         <is>
           <t>คะแนน &gt;= นี้ = สูง</t>
         </is>
       </c>
-      <c r="AI10" s="42" t="n">
+      <c r="AI10" s="44" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="11">
-      <c r="AH11" s="40" t="inlineStr">
+      <c r="AH11" s="42" t="inlineStr">
         <is>
           <t>คะแนน &gt;= นี้ = กลาง</t>
         </is>
       </c>
-      <c r="AI11" s="42" t="n">
+      <c r="AI11" s="44" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="14">
-      <c r="AH14" s="39" t="inlineStr">
+      <c r="AH14" s="41" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="AH15" s="40" t="inlineStr">
+      <c r="AH15" s="42" t="inlineStr">
         <is>
           <t>ช่วงชั่วโมงและช่วงมูลค่าเป็น dropdown แล้ว</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="AH16" s="40" t="inlineStr">
+      <c r="AH16" s="42" t="inlineStr">
         <is>
           <t>แก้ตัวเลือกและคะแนนได้ที่คอลัมน์ R และ S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="AH17" s="40" t="inlineStr">
+      <c r="AH17" s="42" t="inlineStr">
         <is>
           <t>คะแนน "-" แปลว่าไม่นำมาคิดคะแนน ไม่ใช่ได้ 0</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="inlineStr">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>ตารางแปลงตัวเลือกเป็นคะแนน 1-5 (เรียงตรงกับรายการด้านบนบรรทัดต่อบรรทัด) — ปรับได้</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>บริษัท</t>
         </is>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน</t>
         </is>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C29" s="40" t="inlineStr">
         <is>
           <t>มีข้อมูลย้อนหลังนานแค่ไหน</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr">
+      <c r="D29" s="40" t="inlineStr">
         <is>
           <t>สิทธิ์นำข้อมูลมาใช้</t>
         </is>
       </c>
-      <c r="E29" s="38" t="inlineStr">
+      <c r="E29" s="40" t="inlineStr">
         <is>
           <t>ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย</t>
         </is>
       </c>
-      <c r="F29" s="38" t="inlineStr">
+      <c r="F29" s="40" t="inlineStr">
         <is>
           <t>มีคนดูแลระบบต่อหลังส่งมอบมั้ย</t>
         </is>
       </c>
-      <c r="G29" s="38" t="inlineStr">
+      <c r="G29" s="40" t="inlineStr">
         <is>
           <t>ถ้า AI ตอบผิด จะเกิดอะไรขึ้น</t>
         </is>
       </c>
-      <c r="H29" s="38" t="inlineStr">
+      <c r="H29" s="40" t="inlineStr">
         <is>
           <t>ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย</t>
         </is>
       </c>
-      <c r="I29" s="38" t="inlineStr">
+      <c r="I29" s="40" t="inlineStr">
         <is>
           <t>ข้อมูลชุดนี้ลับแค่ไหน</t>
         </is>
       </c>
-      <c r="J29" s="38" t="inlineStr">
+      <c r="J29" s="40" t="inlineStr">
         <is>
           <t>ความสำคัญที่แผนกอยากได้</t>
         </is>
       </c>
-      <c r="K29" s="38" t="inlineStr">
+      <c r="K29" s="40" t="inlineStr">
         <is>
           <t>ประเภทข้อมูล Input</t>
         </is>
       </c>
-      <c r="L29" s="38" t="inlineStr">
+      <c r="L29" s="40" t="inlineStr">
         <is>
           <t>ภาษาที่ต้องการ</t>
         </is>
       </c>
-      <c r="M29" s="38" t="inlineStr">
+      <c r="M29" s="40" t="inlineStr">
         <is>
           <t>Latency ที่รับได้</t>
         </is>
       </c>
-      <c r="N29" s="38" t="inlineStr">
+      <c r="N29" s="40" t="inlineStr">
         <is>
           <t>Availability</t>
         </is>
       </c>
-      <c r="O29" s="38" t="inlineStr">
+      <c r="O29" s="40" t="inlineStr">
         <is>
           <t>ความละเอียดรูป</t>
         </is>
       </c>
-      <c r="P29" s="38" t="inlineStr">
+      <c r="P29" s="40" t="inlineStr">
         <is>
           <t>ที่ตั้งระบบ</t>
         </is>
       </c>
-      <c r="Q29" s="38" t="inlineStr">
-        <is>
-          <t>ความต้องการโมเดล</t>
-        </is>
-      </c>
-      <c r="R29" s="38" t="inlineStr">
+      <c r="Q29" s="40" t="inlineStr">
+        <is>
+          <t>ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย</t>
+        </is>
+      </c>
+      <c r="R29" s="40" t="inlineStr">
         <is>
           <t>เวลาที่ใช้กับงานนี้ตอนนี้</t>
         </is>
       </c>
-      <c r="S29" s="38" t="inlineStr">
+      <c r="S29" s="40" t="inlineStr">
         <is>
           <t>มูลค่าความเสียหาย/ของเสียต่อปี</t>
         </is>
       </c>
-      <c r="T29" s="38" t="inlineStr">
+      <c r="T29" s="40" t="inlineStr">
         <is>
           <t>จำนวน Users/วัน</t>
         </is>
       </c>
-      <c r="U29" s="38" t="inlineStr">
+      <c r="U29" s="40" t="inlineStr">
         <is>
           <t>Peak concurrent (คนพร้อมกัน)</t>
         </is>
       </c>
-      <c r="V29" s="38" t="inlineStr">
+      <c r="V29" s="40" t="inlineStr">
         <is>
           <t>Requests/วัน</t>
         </is>
       </c>
-      <c r="W29" s="38" t="inlineStr">
+      <c r="W29" s="40" t="inlineStr">
         <is>
           <t>ขนาดข้อมูล Input/วัน</t>
         </is>
       </c>
-      <c r="X29" s="38" t="inlineStr">
+      <c r="X29" s="40" t="inlineStr">
         <is>
           <t>ขนาดคลังเอกสารทั้งหมด (RAG)</t>
         </is>
       </c>
-      <c r="Y29" s="38" t="inlineStr">
+      <c r="Y29" s="40" t="inlineStr">
         <is>
           <t>จำนวนกล้อง/จุดตรวจพร้อมกัน</t>
         </is>
       </c>
-      <c r="Z29" s="38" t="inlineStr">
+      <c r="Z29" s="40" t="inlineStr">
         <is>
           <t>ติดตั้งแบบไหน</t>
         </is>
       </c>
-      <c r="AA29" s="38" t="inlineStr">
-        <is>
-          <t>มีเครื่อง/GPU เดิมใช้ได้มั้ย</t>
-        </is>
-      </c>
-      <c r="AB29" s="38" t="inlineStr">
+      <c r="AB29" s="40" t="inlineStr">
         <is>
           <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
         </is>
       </c>
-      <c r="AC29" s="38" t="inlineStr">
+      <c r="AC29" s="40" t="inlineStr">
         <is>
           <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
         </is>
       </c>
-      <c r="AD29" s="38" t="inlineStr">
-        <is>
-          <t>แชร์เครื่องกับงานอื่นได้มั้ย</t>
+      <c r="AD29" s="40" t="inlineStr">
+        <is>
+          <t>ถ้างานนี้ช้าลงจะเป็นปัญหามั้ย</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B30" s="44" t="n">
+      <c r="B30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="44" t="n">
+      <c r="C30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="44" t="n">
+      <c r="D30" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="44" t="n">
+      <c r="E30" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="F30" s="44" t="n">
+      <c r="F30" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G30" s="44" t="n">
+      <c r="G30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="44" t="n">
+      <c r="H30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="44" t="n">
+      <c r="I30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="43" t="inlineStr">
+      <c r="J30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K30" s="43" t="inlineStr">
+      <c r="K30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L30" s="43" t="inlineStr">
+      <c r="L30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="43" t="inlineStr">
+      <c r="M30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N30" s="43" t="inlineStr">
+      <c r="N30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O30" s="43" t="inlineStr">
+      <c r="O30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P30" s="43" t="inlineStr">
+      <c r="P30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q30" s="43" t="inlineStr">
+      <c r="Q30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R30" s="44" t="n">
+      <c r="R30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="S30" s="43" t="inlineStr">
+      <c r="S30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T30" s="43" t="inlineStr">
+      <c r="T30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U30" s="43" t="inlineStr">
+      <c r="U30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V30" s="43" t="inlineStr">
+      <c r="V30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W30" s="43" t="inlineStr">
+      <c r="W30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="X30" s="43" t="inlineStr">
+      <c r="X30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y30" s="43" t="inlineStr">
+      <c r="Y30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z30" s="43" t="inlineStr">
+      <c r="Z30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA30" s="43" t="inlineStr">
+      <c r="AB30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB30" s="43" t="inlineStr">
+      <c r="AC30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC30" s="43" t="inlineStr">
+      <c r="AD30" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AD30" s="43" t="inlineStr">
+    </row>
+    <row r="31">
+      <c r="A31" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="B31" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B31" s="44" t="n">
+      <c r="K31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="C31" s="44" t="n">
+      <c r="D32" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="S32" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B33" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="44" t="n">
+      <c r="I33" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="S33" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="43" t="inlineStr">
+      <c r="K34" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K31" s="43" t="inlineStr">
+      <c r="O34" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L31" s="43" t="inlineStr">
+      <c r="R34" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M31" s="43" t="inlineStr">
+      <c r="U34" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N31" s="43" t="inlineStr">
+      <c r="X34" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O31" s="43" t="inlineStr">
+      <c r="Y34" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P31" s="43" t="inlineStr">
+      <c r="AC34" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q31" s="43" t="inlineStr">
+    </row>
+    <row r="35">
+      <c r="B35" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R31" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B32" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="I32" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R32" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="S32" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="T32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD32" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B33" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="E33" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R33" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="S33" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD33" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B34" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O34" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R34" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="S34" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T34" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U34" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X34" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y34" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC34" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" s="43" t="inlineStr">
+      <c r="AC35" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -328,12 +328,12 @@
       <font>
         <name val="Tahoma"/>
         <b val="1"/>
-        <color rgb="00006100"/>
+        <color rgb="FF9C0006"/>
         <sz val="9"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6EFCE"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -341,24 +341,12 @@
       <font>
         <name val="Tahoma"/>
         <b val="1"/>
-        <color rgb="009C5700"/>
+        <color rgb="FF006100"/>
         <sz val="9"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Tahoma"/>
-        <color rgb="00808080"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F2F2F2"/>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -366,12 +354,24 @@
       <font>
         <name val="Tahoma"/>
         <b val="1"/>
-        <color rgb="009C0006"/>
+        <color rgb="FF9C5700"/>
         <sz val="9"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Tahoma"/>
+        <color rgb="FF808080"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3564,14 +3564,19 @@
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
+  <conditionalFormatting sqref="F7:F36">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>OR(AND($E7="1 - 10 คน",OR($F7="21 - 50 คน",$F7="มากกว่า 50 คน")),AND($E7="11 - 50 คน",OR($F7="มากกว่า 50 คน")))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="16">
     <dataValidation sqref="D7:D36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ประเภทข้อมูล Input" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$K$4:$K$9</formula1>
     </dataValidation>
-    <dataValidation sqref="E7:E36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวน Users/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="E7:E36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวน Users/วัน" prompt="นับคนทั้งหมดที่เข้ามาใช้ตลอดทั้งวัน ไม่ใช่พร้อมกัน&#10;เช่น ทยอยเข้ามาตั้งแต่เช้าถึงเย็น รวม 10 คน = เลือก 1 - 10 คน" type="list">
       <formula1>DATA!$T$4:$T$8</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนพร้อมกัน)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนพร้อมกัน)" prompt="ช่วงที่คนใช้เยอะที่สุดของวัน มีกี่คนกดพร้อมกัน&#10;&#10;ต้องไม่เกินจำนวนคนที่ใช้งาน/วัน&#10;เช่น ทั้งวันมี 10 คน ช่วงพีคมักอยู่แค่ 1 - 2 คน&#10;&#10;ช่องนี้คือตัวกำหนดขนาดเครื่อง ไม่ใช่จำนวนคนต่อวัน" type="list">
       <formula1>DATA!$U$4:$U$8</formula1>
     </dataValidation>
     <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Requests/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
@@ -6581,24 +6586,24 @@
     <mergeCell ref="A40:U40"/>
   </mergeCells>
   <conditionalFormatting sqref="R6:R36">
-    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="1">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="between" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="2">
       <formula>50</formula>
       <formula>74.99</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="3">
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S36">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
       <formula>"ข้อมูลไม่ครบ"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6:U36">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -328,12 +328,12 @@
       <font>
         <name val="Tahoma"/>
         <b val="1"/>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C5700"/>
         <sz val="9"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -353,25 +353,25 @@
     <dxf>
       <font>
         <name val="Tahoma"/>
-        <b val="1"/>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF808080"/>
         <sz val="9"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <name val="Tahoma"/>
-        <color rgb="FF808080"/>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
         <sz val="9"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3566,7 +3566,7 @@
   </mergeCells>
   <conditionalFormatting sqref="F7:F36">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(AND($E7="1 - 10 คน",OR($F7="21 - 50 คน",$F7="มากกว่า 50 คน")),AND($E7="11 - 50 คน",OR($F7="มากกว่า 50 คน")))</formula>
+      <formula>OR(AND($E7="1 - 10 คน",OR($F7="6 - 20 คน",$F7="21 - 50 คน",$F7="มากกว่า 50 คน")),AND($E7="11 - 50 คน",OR($F7="มากกว่า 50 คน")))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="16">
@@ -3576,7 +3576,7 @@
     <dataValidation sqref="E7:E36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวน Users/วัน" prompt="นับคนทั้งหมดที่เข้ามาใช้ตลอดทั้งวัน ไม่ใช่พร้อมกัน&#10;เช่น ทยอยเข้ามาตั้งแต่เช้าถึงเย็น รวม 10 คน = เลือก 1 - 10 คน" type="list">
       <formula1>DATA!$T$4:$T$8</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนพร้อมกัน)" prompt="ช่วงที่คนใช้เยอะที่สุดของวัน มีกี่คนกดพร้อมกัน&#10;&#10;ต้องไม่เกินจำนวนคนที่ใช้งาน/วัน&#10;เช่น ทั้งวันมี 10 คน ช่วงพีคมักอยู่แค่ 1 - 2 คน&#10;&#10;ช่องนี้คือตัวกำหนดขนาดเครื่อง ไม่ใช่จำนวนคนต่อวัน" type="list">
+    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนพร้อมกัน)" prompt="ช่วงที่คนใช้เยอะที่สุดของวัน มีกี่คนกดพร้อมกัน&#10;&#10;ต้องไม่เกินจำนวนคนที่ใช้งาน/วัน&#10;เช่น ทั้งวันมี 10 คน ช่วงพีคมักอยู่แค่ 1 - 2 คน&#10;&#10;ช่องนี้คือตัวกำหนดขนาดเครื่อง&#10;&#10;ถ้าขึ้นพื้นสีส้ม = ตัวเลขดูสูงผิดปกติ ลองทบทวนอีกครั้ง" type="list">
       <formula1>DATA!$U$4:$U$8</formula1>
     </dataValidation>
     <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Requests/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
@@ -6589,21 +6589,21 @@
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="1">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="between" dxfId="2">
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="0">
       <formula>50</formula>
       <formula>74.99</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="3">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S36">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"ข้อมูลไม่ครบ"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6:U36">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -328,12 +328,12 @@
       <font>
         <name val="Tahoma"/>
         <b val="1"/>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF9C0006"/>
         <sz val="9"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -353,25 +353,25 @@
     <dxf>
       <font>
         <name val="Tahoma"/>
+        <b val="1"/>
+        <color rgb="FF9C5700"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Tahoma"/>
         <color rgb="FF808080"/>
         <sz val="9"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Tahoma"/>
-        <b val="1"/>
-        <color rgb="FF9C0006"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3576,7 +3576,7 @@
     <dataValidation sqref="E7:E36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวน Users/วัน" prompt="นับคนทั้งหมดที่เข้ามาใช้ตลอดทั้งวัน ไม่ใช่พร้อมกัน&#10;เช่น ทยอยเข้ามาตั้งแต่เช้าถึงเย็น รวม 10 คน = เลือก 1 - 10 คน" type="list">
       <formula1>DATA!$T$4:$T$8</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนพร้อมกัน)" prompt="ช่วงที่คนใช้เยอะที่สุดของวัน มีกี่คนกดพร้อมกัน&#10;&#10;ต้องไม่เกินจำนวนคนที่ใช้งาน/วัน&#10;เช่น ทั้งวันมี 10 คน ช่วงพีคมักอยู่แค่ 1 - 2 คน&#10;&#10;ช่องนี้คือตัวกำหนดขนาดเครื่อง&#10;&#10;ถ้าขึ้นพื้นสีส้ม = ตัวเลขดูสูงผิดปกติ ลองทบทวนอีกครั้ง" type="list">
+    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนพร้อมกัน)" prompt="ช่วงที่คนใช้เยอะที่สุดของวัน มีกี่คนกดพร้อมกัน&#10;&#10;ต้องไม่เกินจำนวนคนที่ใช้งาน/วัน&#10;เช่น ทั้งวันมี 10 คน ช่วงพีคมักอยู่แค่ 1 - 2 คน&#10;&#10;ช่องนี้คือตัวกำหนดขนาดเครื่อง&#10;&#10;ถ้าขึ้นพื้นสีแดง = ตัวเลขดูสูงผิดปกติ ลองทบทวนอีกครั้ง" type="list">
       <formula1>DATA!$U$4:$U$8</formula1>
     </dataValidation>
     <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Requests/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
@@ -6589,21 +6589,21 @@
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="1">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="between" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="2">
       <formula>50</formula>
       <formula>74.99</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="3">
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S36">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
       <formula>"ข้อมูลไม่ครบ"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6:U36">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -2255,31 +2255,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
     <col width="42" customWidth="1" min="21" max="21"/>
-    <col width="34" customWidth="1" min="22" max="22"/>
+    <col width="42" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2313,32 +2314,33 @@
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="10" t="n"/>
       <c r="H4" s="10" t="n"/>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>โซน A : ความต้องการใช้งาน  (แผนกกรอก)</t>
         </is>
       </c>
-      <c r="J4" s="14" t="n"/>
       <c r="K4" s="14" t="n"/>
       <c r="L4" s="14" t="n"/>
-      <c r="M4" s="17" t="inlineStr">
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="17" t="inlineStr">
         <is>
           <t>โซน A : ข้อกำหนดและงบ  (แผนกกรอก)</t>
         </is>
       </c>
-      <c r="N4" s="18" t="n"/>
       <c r="O4" s="18" t="n"/>
       <c r="P4" s="18" t="n"/>
-      <c r="Q4" s="22" t="inlineStr">
+      <c r="Q4" s="18" t="n"/>
+      <c r="R4" s="22" t="inlineStr">
         <is>
           <t>โซน B : ทีม AI / IT เติมให้ทีหลัง — แผนกไม่ต้องกรอก</t>
         </is>
       </c>
-      <c r="R4" s="23" t="n"/>
       <c r="S4" s="23" t="n"/>
       <c r="T4" s="23" t="n"/>
       <c r="U4" s="23" t="n"/>
       <c r="V4" s="23" t="n"/>
+      <c r="W4" s="23" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -2358,100 +2360,106 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
+          <t>งานนี้เริ่มทำงานยังไง</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
           <t>ข้อมูลที่ AI ต้องอ่าน/ดู เป็นแบบไหน</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>จำนวนคนที่ใช้งาน/วัน</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>ช่วงพีค มีคนใช้พร้อมกันมากสุดกี่คน</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>ใช้งานกี่ครั้ง/วัน</t>
-        </is>
-      </c>
       <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>AI ต้องประมวลผลกี่รายการ/วัน
+(ไม่ใช่จำนวนครั้งที่สั่งงาน)</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>จำนวนกล้อง/จุดตรวจ
 ที่ทำงานพร้อมกัน (งานภาพ)</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>ภาษาที่ต้องการ</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="K5" s="19" t="inlineStr">
         <is>
           <t>รอผลได้นานแค่ไหน</t>
         </is>
       </c>
-      <c r="K5" s="19" t="inlineStr">
+      <c r="L5" s="19" t="inlineStr">
         <is>
           <t>ต้องใช้งานช่วงเวลาไหน</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
+      <c r="M5" s="19" t="inlineStr">
         <is>
           <t>ถ้าช่วงไหนคนใช้เยอะ แล้วงานนี้ช้าลง
 จะเป็นปัญหามั้ย</t>
         </is>
       </c>
-      <c r="M5" s="19" t="inlineStr">
+      <c r="N5" s="19" t="inlineStr">
         <is>
           <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
         </is>
       </c>
-      <c r="N5" s="19" t="inlineStr">
+      <c r="O5" s="19" t="inlineStr">
         <is>
           <t>งบประมาณที่ตั้งไว้ (บาท)
 - ถ้ามี</t>
         </is>
       </c>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="P5" s="19" t="inlineStr">
         <is>
           <t>ข้อจำกัดอื่นๆ / หมายเหตุ</t>
         </is>
       </c>
-      <c r="P5" s="19" t="inlineStr">
+      <c r="Q5" s="19" t="inlineStr">
         <is>
           <t>ผู้ให้ข้อมูล (แผนก)</t>
         </is>
       </c>
-      <c r="Q5" s="19" t="inlineStr">
+      <c r="R5" s="19" t="inlineStr">
         <is>
           <t>ขนาดข้อมูล Input/วัน</t>
         </is>
       </c>
-      <c r="R5" s="19" t="inlineStr">
+      <c r="S5" s="19" t="inlineStr">
         <is>
           <t>ขนาดคลังเอกสารทั้งหมด
 (สำหรับงานค้นหา/RAG)</t>
         </is>
       </c>
-      <c r="S5" s="19" t="inlineStr">
+      <c r="T5" s="19" t="inlineStr">
         <is>
           <t>ความละเอียดรูป</t>
         </is>
       </c>
-      <c r="T5" s="19" t="inlineStr">
+      <c r="U5" s="19" t="inlineStr">
         <is>
           <t>ติดตั้งแบบไหน
 (server ตั้งที่เดียว ไม่ใช้ Cloud)</t>
         </is>
       </c>
-      <c r="U5" s="19" t="inlineStr">
+      <c r="V5" s="19" t="inlineStr">
         <is>
           <t>ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย</t>
         </is>
       </c>
-      <c r="V5" s="19" t="inlineStr">
+      <c r="W5" s="19" t="inlineStr">
         <is>
           <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
         </is>
@@ -2472,93 +2480,98 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
+          <t>ทำงานอัตโนมัติต่อเนื่อง - ระบบสั่งเอง ไม่มีคนกด</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
           <t>รูปภาพ</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>1 - 10 คน</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>1 - 2 คน</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>100 - 1,000 ครั้ง</t>
-        </is>
-      </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
+          <t>1,000 - 10,000 รายการ</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
           <t>2 - 3 จุด</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>ไม่เกี่ยวกับภาษา</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>Real-time (0 - 2 วินาที)</t>
         </is>
       </c>
-      <c r="K6" s="20" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>Business Hour (8:00 - 18:00)</t>
         </is>
       </c>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>เป็นปัญหา - งานนี้ช้าหรือหยุดไม่ได้เลย (อยู่ในสายการผลิต)</t>
         </is>
       </c>
-      <c r="M6" s="20" t="inlineStr">
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>2 - 3 ปี</t>
         </is>
       </c>
-      <c r="N6" s="20" t="n">
+      <c r="O6" s="20" t="n">
         <v>500000</v>
       </c>
-      <c r="O6" s="20" t="inlineStr">
+      <c r="P6" s="20" t="inlineStr">
         <is>
           <t>ต้องติดกล้องที่สายพานเดิม มีพื้นที่จำกัด</t>
         </is>
       </c>
-      <c r="P6" s="20" t="inlineStr">
+      <c r="Q6" s="20" t="inlineStr">
         <is>
           <t>คุณสมชาย</t>
         </is>
       </c>
-      <c r="Q6" s="25" t="inlineStr">
+      <c r="R6" s="25" t="inlineStr">
         <is>
           <t>1 - 10 GB</t>
         </is>
       </c>
-      <c r="R6" s="25" t="inlineStr">
+      <c r="S6" s="25" t="inlineStr">
         <is>
           <t>ไม่เกี่ยวข้อง - ไม่ใช่งานค้นหาเอกสาร</t>
         </is>
       </c>
-      <c r="S6" s="25" t="inlineStr">
+      <c r="T6" s="25" t="inlineStr">
         <is>
           <t>1 - 5 MP</t>
         </is>
       </c>
-      <c r="T6" s="25" t="inlineStr">
+      <c r="U6" s="25" t="inlineStr">
         <is>
           <t>ต้องมีเครื่องที่หน้างาน - ติดข้างเครื่องจักร/สายพาน</t>
         </is>
       </c>
-      <c r="U6" s="25" t="inlineStr">
+      <c r="V6" s="25" t="inlineStr">
         <is>
           <t>ต้อง Fine-tune - สอนด้วยข้อมูล/รูปของบริษัทเอง</t>
         </is>
       </c>
-      <c r="V6" s="25" t="inlineStr">
+      <c r="W6" s="25" t="inlineStr">
         <is>
           <t>ทุกไตรมาส</t>
         </is>
@@ -2590,12 +2603,13 @@
       <c r="N7" s="21" t="n"/>
       <c r="O7" s="21" t="n"/>
       <c r="P7" s="21" t="n"/>
-      <c r="Q7" s="27" t="n"/>
+      <c r="Q7" s="21" t="n"/>
       <c r="R7" s="27" t="n"/>
       <c r="S7" s="27" t="n"/>
       <c r="T7" s="27" t="n"/>
       <c r="U7" s="27" t="n"/>
       <c r="V7" s="27" t="n"/>
+      <c r="W7" s="27" t="n"/>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="26">
@@ -2623,12 +2637,13 @@
       <c r="N8" s="21" t="n"/>
       <c r="O8" s="21" t="n"/>
       <c r="P8" s="21" t="n"/>
-      <c r="Q8" s="27" t="n"/>
+      <c r="Q8" s="21" t="n"/>
       <c r="R8" s="27" t="n"/>
       <c r="S8" s="27" t="n"/>
       <c r="T8" s="27" t="n"/>
       <c r="U8" s="27" t="n"/>
       <c r="V8" s="27" t="n"/>
+      <c r="W8" s="27" t="n"/>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="26">
@@ -2656,12 +2671,13 @@
       <c r="N9" s="21" t="n"/>
       <c r="O9" s="21" t="n"/>
       <c r="P9" s="21" t="n"/>
-      <c r="Q9" s="27" t="n"/>
+      <c r="Q9" s="21" t="n"/>
       <c r="R9" s="27" t="n"/>
       <c r="S9" s="27" t="n"/>
       <c r="T9" s="27" t="n"/>
       <c r="U9" s="27" t="n"/>
       <c r="V9" s="27" t="n"/>
+      <c r="W9" s="27" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="26">
@@ -2689,12 +2705,13 @@
       <c r="N10" s="21" t="n"/>
       <c r="O10" s="21" t="n"/>
       <c r="P10" s="21" t="n"/>
-      <c r="Q10" s="27" t="n"/>
+      <c r="Q10" s="21" t="n"/>
       <c r="R10" s="27" t="n"/>
       <c r="S10" s="27" t="n"/>
       <c r="T10" s="27" t="n"/>
       <c r="U10" s="27" t="n"/>
       <c r="V10" s="27" t="n"/>
+      <c r="W10" s="27" t="n"/>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="26">
@@ -2722,12 +2739,13 @@
       <c r="N11" s="21" t="n"/>
       <c r="O11" s="21" t="n"/>
       <c r="P11" s="21" t="n"/>
-      <c r="Q11" s="27" t="n"/>
+      <c r="Q11" s="21" t="n"/>
       <c r="R11" s="27" t="n"/>
       <c r="S11" s="27" t="n"/>
       <c r="T11" s="27" t="n"/>
       <c r="U11" s="27" t="n"/>
       <c r="V11" s="27" t="n"/>
+      <c r="W11" s="27" t="n"/>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="26">
@@ -2755,12 +2773,13 @@
       <c r="N12" s="21" t="n"/>
       <c r="O12" s="21" t="n"/>
       <c r="P12" s="21" t="n"/>
-      <c r="Q12" s="27" t="n"/>
+      <c r="Q12" s="21" t="n"/>
       <c r="R12" s="27" t="n"/>
       <c r="S12" s="27" t="n"/>
       <c r="T12" s="27" t="n"/>
       <c r="U12" s="27" t="n"/>
       <c r="V12" s="27" t="n"/>
+      <c r="W12" s="27" t="n"/>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="26">
@@ -2788,12 +2807,13 @@
       <c r="N13" s="21" t="n"/>
       <c r="O13" s="21" t="n"/>
       <c r="P13" s="21" t="n"/>
-      <c r="Q13" s="27" t="n"/>
+      <c r="Q13" s="21" t="n"/>
       <c r="R13" s="27" t="n"/>
       <c r="S13" s="27" t="n"/>
       <c r="T13" s="27" t="n"/>
       <c r="U13" s="27" t="n"/>
       <c r="V13" s="27" t="n"/>
+      <c r="W13" s="27" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="26">
@@ -2821,12 +2841,13 @@
       <c r="N14" s="21" t="n"/>
       <c r="O14" s="21" t="n"/>
       <c r="P14" s="21" t="n"/>
-      <c r="Q14" s="27" t="n"/>
+      <c r="Q14" s="21" t="n"/>
       <c r="R14" s="27" t="n"/>
       <c r="S14" s="27" t="n"/>
       <c r="T14" s="27" t="n"/>
       <c r="U14" s="27" t="n"/>
       <c r="V14" s="27" t="n"/>
+      <c r="W14" s="27" t="n"/>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="26">
@@ -2854,12 +2875,13 @@
       <c r="N15" s="21" t="n"/>
       <c r="O15" s="21" t="n"/>
       <c r="P15" s="21" t="n"/>
-      <c r="Q15" s="27" t="n"/>
+      <c r="Q15" s="21" t="n"/>
       <c r="R15" s="27" t="n"/>
       <c r="S15" s="27" t="n"/>
       <c r="T15" s="27" t="n"/>
       <c r="U15" s="27" t="n"/>
       <c r="V15" s="27" t="n"/>
+      <c r="W15" s="27" t="n"/>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="26">
@@ -2887,12 +2909,13 @@
       <c r="N16" s="21" t="n"/>
       <c r="O16" s="21" t="n"/>
       <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="27" t="n"/>
+      <c r="Q16" s="21" t="n"/>
       <c r="R16" s="27" t="n"/>
       <c r="S16" s="27" t="n"/>
       <c r="T16" s="27" t="n"/>
       <c r="U16" s="27" t="n"/>
       <c r="V16" s="27" t="n"/>
+      <c r="W16" s="27" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="26">
@@ -2920,12 +2943,13 @@
       <c r="N17" s="21" t="n"/>
       <c r="O17" s="21" t="n"/>
       <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="27" t="n"/>
+      <c r="Q17" s="21" t="n"/>
       <c r="R17" s="27" t="n"/>
       <c r="S17" s="27" t="n"/>
       <c r="T17" s="27" t="n"/>
       <c r="U17" s="27" t="n"/>
       <c r="V17" s="27" t="n"/>
+      <c r="W17" s="27" t="n"/>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="26">
@@ -2953,12 +2977,13 @@
       <c r="N18" s="21" t="n"/>
       <c r="O18" s="21" t="n"/>
       <c r="P18" s="21" t="n"/>
-      <c r="Q18" s="27" t="n"/>
+      <c r="Q18" s="21" t="n"/>
       <c r="R18" s="27" t="n"/>
       <c r="S18" s="27" t="n"/>
       <c r="T18" s="27" t="n"/>
       <c r="U18" s="27" t="n"/>
       <c r="V18" s="27" t="n"/>
+      <c r="W18" s="27" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="26">
@@ -2986,12 +3011,13 @@
       <c r="N19" s="21" t="n"/>
       <c r="O19" s="21" t="n"/>
       <c r="P19" s="21" t="n"/>
-      <c r="Q19" s="27" t="n"/>
+      <c r="Q19" s="21" t="n"/>
       <c r="R19" s="27" t="n"/>
       <c r="S19" s="27" t="n"/>
       <c r="T19" s="27" t="n"/>
       <c r="U19" s="27" t="n"/>
       <c r="V19" s="27" t="n"/>
+      <c r="W19" s="27" t="n"/>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="26">
@@ -3019,12 +3045,13 @@
       <c r="N20" s="21" t="n"/>
       <c r="O20" s="21" t="n"/>
       <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="27" t="n"/>
+      <c r="Q20" s="21" t="n"/>
       <c r="R20" s="27" t="n"/>
       <c r="S20" s="27" t="n"/>
       <c r="T20" s="27" t="n"/>
       <c r="U20" s="27" t="n"/>
       <c r="V20" s="27" t="n"/>
+      <c r="W20" s="27" t="n"/>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="26">
@@ -3052,12 +3079,13 @@
       <c r="N21" s="21" t="n"/>
       <c r="O21" s="21" t="n"/>
       <c r="P21" s="21" t="n"/>
-      <c r="Q21" s="27" t="n"/>
+      <c r="Q21" s="21" t="n"/>
       <c r="R21" s="27" t="n"/>
       <c r="S21" s="27" t="n"/>
       <c r="T21" s="27" t="n"/>
       <c r="U21" s="27" t="n"/>
       <c r="V21" s="27" t="n"/>
+      <c r="W21" s="27" t="n"/>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="26">
@@ -3085,12 +3113,13 @@
       <c r="N22" s="21" t="n"/>
       <c r="O22" s="21" t="n"/>
       <c r="P22" s="21" t="n"/>
-      <c r="Q22" s="27" t="n"/>
+      <c r="Q22" s="21" t="n"/>
       <c r="R22" s="27" t="n"/>
       <c r="S22" s="27" t="n"/>
       <c r="T22" s="27" t="n"/>
       <c r="U22" s="27" t="n"/>
       <c r="V22" s="27" t="n"/>
+      <c r="W22" s="27" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="26">
@@ -3118,12 +3147,13 @@
       <c r="N23" s="21" t="n"/>
       <c r="O23" s="21" t="n"/>
       <c r="P23" s="21" t="n"/>
-      <c r="Q23" s="27" t="n"/>
+      <c r="Q23" s="21" t="n"/>
       <c r="R23" s="27" t="n"/>
       <c r="S23" s="27" t="n"/>
       <c r="T23" s="27" t="n"/>
       <c r="U23" s="27" t="n"/>
       <c r="V23" s="27" t="n"/>
+      <c r="W23" s="27" t="n"/>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="26">
@@ -3151,12 +3181,13 @@
       <c r="N24" s="21" t="n"/>
       <c r="O24" s="21" t="n"/>
       <c r="P24" s="21" t="n"/>
-      <c r="Q24" s="27" t="n"/>
+      <c r="Q24" s="21" t="n"/>
       <c r="R24" s="27" t="n"/>
       <c r="S24" s="27" t="n"/>
       <c r="T24" s="27" t="n"/>
       <c r="U24" s="27" t="n"/>
       <c r="V24" s="27" t="n"/>
+      <c r="W24" s="27" t="n"/>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="26">
@@ -3184,12 +3215,13 @@
       <c r="N25" s="21" t="n"/>
       <c r="O25" s="21" t="n"/>
       <c r="P25" s="21" t="n"/>
-      <c r="Q25" s="27" t="n"/>
+      <c r="Q25" s="21" t="n"/>
       <c r="R25" s="27" t="n"/>
       <c r="S25" s="27" t="n"/>
       <c r="T25" s="27" t="n"/>
       <c r="U25" s="27" t="n"/>
       <c r="V25" s="27" t="n"/>
+      <c r="W25" s="27" t="n"/>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="26">
@@ -3217,12 +3249,13 @@
       <c r="N26" s="21" t="n"/>
       <c r="O26" s="21" t="n"/>
       <c r="P26" s="21" t="n"/>
-      <c r="Q26" s="27" t="n"/>
+      <c r="Q26" s="21" t="n"/>
       <c r="R26" s="27" t="n"/>
       <c r="S26" s="27" t="n"/>
       <c r="T26" s="27" t="n"/>
       <c r="U26" s="27" t="n"/>
       <c r="V26" s="27" t="n"/>
+      <c r="W26" s="27" t="n"/>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="26">
@@ -3250,12 +3283,13 @@
       <c r="N27" s="21" t="n"/>
       <c r="O27" s="21" t="n"/>
       <c r="P27" s="21" t="n"/>
-      <c r="Q27" s="27" t="n"/>
+      <c r="Q27" s="21" t="n"/>
       <c r="R27" s="27" t="n"/>
       <c r="S27" s="27" t="n"/>
       <c r="T27" s="27" t="n"/>
       <c r="U27" s="27" t="n"/>
       <c r="V27" s="27" t="n"/>
+      <c r="W27" s="27" t="n"/>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="26">
@@ -3283,12 +3317,13 @@
       <c r="N28" s="21" t="n"/>
       <c r="O28" s="21" t="n"/>
       <c r="P28" s="21" t="n"/>
-      <c r="Q28" s="27" t="n"/>
+      <c r="Q28" s="21" t="n"/>
       <c r="R28" s="27" t="n"/>
       <c r="S28" s="27" t="n"/>
       <c r="T28" s="27" t="n"/>
       <c r="U28" s="27" t="n"/>
       <c r="V28" s="27" t="n"/>
+      <c r="W28" s="27" t="n"/>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="26">
@@ -3316,12 +3351,13 @@
       <c r="N29" s="21" t="n"/>
       <c r="O29" s="21" t="n"/>
       <c r="P29" s="21" t="n"/>
-      <c r="Q29" s="27" t="n"/>
+      <c r="Q29" s="21" t="n"/>
       <c r="R29" s="27" t="n"/>
       <c r="S29" s="27" t="n"/>
       <c r="T29" s="27" t="n"/>
       <c r="U29" s="27" t="n"/>
       <c r="V29" s="27" t="n"/>
+      <c r="W29" s="27" t="n"/>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="26">
@@ -3349,12 +3385,13 @@
       <c r="N30" s="21" t="n"/>
       <c r="O30" s="21" t="n"/>
       <c r="P30" s="21" t="n"/>
-      <c r="Q30" s="27" t="n"/>
+      <c r="Q30" s="21" t="n"/>
       <c r="R30" s="27" t="n"/>
       <c r="S30" s="27" t="n"/>
       <c r="T30" s="27" t="n"/>
       <c r="U30" s="27" t="n"/>
       <c r="V30" s="27" t="n"/>
+      <c r="W30" s="27" t="n"/>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="26">
@@ -3382,12 +3419,13 @@
       <c r="N31" s="21" t="n"/>
       <c r="O31" s="21" t="n"/>
       <c r="P31" s="21" t="n"/>
-      <c r="Q31" s="27" t="n"/>
+      <c r="Q31" s="21" t="n"/>
       <c r="R31" s="27" t="n"/>
       <c r="S31" s="27" t="n"/>
       <c r="T31" s="27" t="n"/>
       <c r="U31" s="27" t="n"/>
       <c r="V31" s="27" t="n"/>
+      <c r="W31" s="27" t="n"/>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="26">
@@ -3415,12 +3453,13 @@
       <c r="N32" s="21" t="n"/>
       <c r="O32" s="21" t="n"/>
       <c r="P32" s="21" t="n"/>
-      <c r="Q32" s="27" t="n"/>
+      <c r="Q32" s="21" t="n"/>
       <c r="R32" s="27" t="n"/>
       <c r="S32" s="27" t="n"/>
       <c r="T32" s="27" t="n"/>
       <c r="U32" s="27" t="n"/>
       <c r="V32" s="27" t="n"/>
+      <c r="W32" s="27" t="n"/>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="26">
@@ -3448,12 +3487,13 @@
       <c r="N33" s="21" t="n"/>
       <c r="O33" s="21" t="n"/>
       <c r="P33" s="21" t="n"/>
-      <c r="Q33" s="27" t="n"/>
+      <c r="Q33" s="21" t="n"/>
       <c r="R33" s="27" t="n"/>
       <c r="S33" s="27" t="n"/>
       <c r="T33" s="27" t="n"/>
       <c r="U33" s="27" t="n"/>
       <c r="V33" s="27" t="n"/>
+      <c r="W33" s="27" t="n"/>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="26">
@@ -3481,12 +3521,13 @@
       <c r="N34" s="21" t="n"/>
       <c r="O34" s="21" t="n"/>
       <c r="P34" s="21" t="n"/>
-      <c r="Q34" s="27" t="n"/>
+      <c r="Q34" s="21" t="n"/>
       <c r="R34" s="27" t="n"/>
       <c r="S34" s="27" t="n"/>
       <c r="T34" s="27" t="n"/>
       <c r="U34" s="27" t="n"/>
       <c r="V34" s="27" t="n"/>
+      <c r="W34" s="27" t="n"/>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="26">
@@ -3514,12 +3555,13 @@
       <c r="N35" s="21" t="n"/>
       <c r="O35" s="21" t="n"/>
       <c r="P35" s="21" t="n"/>
-      <c r="Q35" s="27" t="n"/>
+      <c r="Q35" s="21" t="n"/>
       <c r="R35" s="27" t="n"/>
       <c r="S35" s="27" t="n"/>
       <c r="T35" s="27" t="n"/>
       <c r="U35" s="27" t="n"/>
       <c r="V35" s="27" t="n"/>
+      <c r="W35" s="27" t="n"/>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="26">
@@ -3547,75 +3589,79 @@
       <c r="N36" s="21" t="n"/>
       <c r="O36" s="21" t="n"/>
       <c r="P36" s="21" t="n"/>
-      <c r="Q36" s="27" t="n"/>
+      <c r="Q36" s="21" t="n"/>
       <c r="R36" s="27" t="n"/>
       <c r="S36" s="27" t="n"/>
       <c r="T36" s="27" t="n"/>
       <c r="U36" s="27" t="n"/>
       <c r="V36" s="27" t="n"/>
+      <c r="W36" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="Q4:V4"/>
-    <mergeCell ref="D4:H4"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="R4:W4"/>
+    <mergeCell ref="A2:W2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F7:F36">
+  <conditionalFormatting sqref="G7:G36">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(AND($E7="1 - 10 คน",OR($F7="6 - 20 คน",$F7="21 - 50 คน",$F7="มากกว่า 50 คน")),AND($E7="11 - 50 คน",OR($F7="มากกว่า 50 คน")))</formula>
+      <formula>OR(AND($F7="1 - 10 คน",OR($G7="6 - 20 คน",$G7="21 - 50 คน",$G7="มากกว่า 50 คน")),AND($F7="11 - 50 คน",OR($G7="มากกว่า 50 คน")))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
-    <dataValidation sqref="D7:D36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ประเภทข้อมูล Input" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+  <dataValidations count="17">
+    <dataValidation sqref="D7:D36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="งานนี้เริ่มทำงานยังไง" prompt="ตอบก่อนช่องอื่น เพราะเป็นตัวบอกว่าช่องที่เหลือต้องกรอกยังไง&#10;&#10;งานที่ระบบสั่งเอง จะไม่มี 'คนใช้งาน' — ให้กรอกคนที่เข้ามาดูผลแทน" type="list">
+      <formula1>DATA!$AE$4:$AE$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="E7:E36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ประเภทข้อมูล Input" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$K$4:$K$9</formula1>
     </dataValidation>
-    <dataValidation sqref="E7:E36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวน Users/วัน" prompt="นับคนทั้งหมดที่เข้ามาใช้ตลอดทั้งวัน ไม่ใช่พร้อมกัน&#10;เช่น ทยอยเข้ามาตั้งแต่เช้าถึงเย็น รวม 10 คน = เลือก 1 - 10 คน" type="list">
+    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวน Users/วัน" prompt="นับคนทั้งหมดที่เข้ามาใช้ตลอดทั้งวัน ไม่ใช่พร้อมกัน&#10;&#10;ถ้าเป็นงานอัตโนมัติหรือรันตามรอบ ให้นับคนที่เข้ามาดูผล" type="list">
       <formula1>DATA!$T$4:$T$8</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนพร้อมกัน)" prompt="ช่วงที่คนใช้เยอะที่สุดของวัน มีกี่คนกดพร้อมกัน&#10;&#10;ต้องไม่เกินจำนวนคนที่ใช้งาน/วัน&#10;เช่น ทั้งวันมี 10 คน ช่วงพีคมักอยู่แค่ 1 - 2 คน&#10;&#10;ช่องนี้คือตัวกำหนดขนาดเครื่อง&#10;&#10;ถ้าขึ้นพื้นสีแดง = ตัวเลขดูสูงผิดปกติ ลองทบทวนอีกครั้ง" type="list">
+    <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนพร้อมกัน)" prompt="ช่วงที่คนใช้เยอะที่สุดของวัน มีกี่คนกดพร้อมกัน&#10;&#10;ต้องไม่เกินจำนวนคนที่ใช้งาน/วัน&#10;งานอัตโนมัติ/รันตามรอบ มักเป็น 1 - 2 คน&#10;&#10;ถ้าขึ้นพื้นสีแดง = ตัวเลขดูสูงผิดปกติ ลองทบทวนอีกครั้ง" type="list">
       <formula1>DATA!$U$4:$U$8</formula1>
     </dataValidation>
-    <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Requests/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$V$4:$V$7</formula1>
+    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="AI ประมวลผลกี่รายการ/วัน" prompt="นับรายการที่ AI ต้องประมวลผลจริง ไม่ใช่จำนวนครั้งที่สั่งงาน&#10;&#10;คนกดใช้เอง = กี่คำถาม&#10;อัตโนมัติ = กี่ชิ้น กี่ภาพ&#10;รันตามรอบ = กี่ล็อต กี่แถวในรอบนั้น&#10;เมื่อมีเหตุการณ์ = กี่เคส&#10;&#10;รันคืนละครั้งแต่ประมวลผล 12,000 ล็อต = 12,000 ไม่ใช่ 1" type="list">
+      <formula1>DATA!$V$4:$V$8</formula1>
     </dataValidation>
-    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวนกล้อง/จุดตรวจพร้อมกัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวนกล้อง/จุดตรวจพร้อมกัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$Y$4:$Y$8</formula1>
     </dataValidation>
-    <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ภาษาที่ต้องการ" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ภาษาที่ต้องการ" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$L$4:$L$7</formula1>
     </dataValidation>
-    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Latency ที่รับได้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Latency ที่รับได้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$M$4:$M$6</formula1>
     </dataValidation>
-    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Availability" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Availability" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$N$4:$N$6</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ถ้างานนี้ช้าลงจะเป็นปัญหามั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ถ้างานนี้ช้าลงจะเป็นปัญหามั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$AD$4:$AD$7</formula1>
     </dataValidation>
-    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเก็บข้อมูลย้อนหลังกี่ปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเก็บข้อมูลย้อนหลังกี่ปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$AB$4:$AB$7</formula1>
     </dataValidation>
-    <dataValidation sqref="Q7:Q36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดข้อมูล Input/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดข้อมูล Input/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$W$4:$W$7</formula1>
     </dataValidation>
-    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดคลังเอกสารทั้งหมด (RAG)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดคลังเอกสารทั้งหมด (RAG)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$X$4:$X$8</formula1>
     </dataValidation>
-    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความละเอียดรูป" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความละเอียดรูป" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$O$4:$O$8</formula1>
     </dataValidation>
-    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ติดตั้งแบบไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ติดตั้งแบบไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$Z$4:$Z$6</formula1>
     </dataValidation>
-    <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="V7:V36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$Q$4:$Q$7</formula1>
     </dataValidation>
-    <dataValidation sqref="V7:V36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเทรนโมเดลใหม่บ่อยแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="W7:W36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเทรนโมเดลใหม่บ่อยแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$AC$4:$AC$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -6649,6 +6695,7 @@
     <col width="32" customWidth="1" min="28" max="28"/>
     <col width="32" customWidth="1" min="29" max="29"/>
     <col width="32" customWidth="1" min="30" max="30"/>
+    <col width="32" customWidth="1" min="31" max="31"/>
     <col width="34" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
   </cols>
@@ -6773,7 +6820,7 @@
       </c>
       <c r="V3" s="40" t="inlineStr">
         <is>
-          <t>Requests/วัน</t>
+          <t>AI ประมวลผลกี่รายการ/วัน</t>
         </is>
       </c>
       <c r="W3" s="40" t="inlineStr">
@@ -6809,6 +6856,11 @@
       <c r="AD3" s="40" t="inlineStr">
         <is>
           <t>ถ้างานนี้ช้าลงจะเป็นปัญหามั้ย</t>
+        </is>
+      </c>
+      <c r="AE3" s="40" t="inlineStr">
+        <is>
+          <t>งานนี้เริ่มทำงานยังไง</t>
         </is>
       </c>
       <c r="AH3" s="41" t="inlineStr">
@@ -6925,7 +6977,7 @@
       </c>
       <c r="V4" s="42" t="inlineStr">
         <is>
-          <t>น้อยกว่า 100 ครั้ง</t>
+          <t>น้อยกว่า 100 รายการ</t>
         </is>
       </c>
       <c r="W4" s="42" t="inlineStr">
@@ -6961,6 +7013,11 @@
       <c r="AD4" s="42" t="inlineStr">
         <is>
           <t>ไม่เป็นไร - รอได้ ช้าหน่อยก็ยังใช้งานได้</t>
+        </is>
+      </c>
+      <c r="AE4" s="42" t="inlineStr">
+        <is>
+          <t>คนกดใช้เอง - มีคนเปิดใช้เป็นครั้งๆ</t>
         </is>
       </c>
       <c r="AH4" s="42" t="inlineStr">
@@ -7080,7 +7137,7 @@
       </c>
       <c r="V5" s="42" t="inlineStr">
         <is>
-          <t>100 - 1,000 ครั้ง</t>
+          <t>100 - 1,000 รายการ</t>
         </is>
       </c>
       <c r="W5" s="42" t="inlineStr">
@@ -7116,6 +7173,11 @@
       <c r="AD5" s="42" t="inlineStr">
         <is>
           <t>พอรับได้ - แต่ช่วงเร่งด่วนต้องได้ใช้ก่อน</t>
+        </is>
+      </c>
+      <c r="AE5" s="42" t="inlineStr">
+        <is>
+          <t>ทำงานอัตโนมัติต่อเนื่อง - ระบบสั่งเอง ไม่มีคนกด</t>
         </is>
       </c>
       <c r="AH5" s="42" t="inlineStr">
@@ -7235,7 +7297,7 @@
       </c>
       <c r="V6" s="42" t="inlineStr">
         <is>
-          <t>1,000 - 10,000 ครั้ง</t>
+          <t>1,000 - 10,000 รายการ</t>
         </is>
       </c>
       <c r="W6" s="42" t="inlineStr">
@@ -7271,6 +7333,11 @@
       <c r="AD6" s="42" t="inlineStr">
         <is>
           <t>เป็นปัญหา - งานนี้ช้าหรือหยุดไม่ได้เลย (อยู่ในสายการผลิต)</t>
+        </is>
+      </c>
+      <c r="AE6" s="42" t="inlineStr">
+        <is>
+          <t>รันตามรอบเวลา - เช่น ทุกคืน ทุกเช้าวันจันทร์</t>
         </is>
       </c>
       <c r="AH6" s="42" t="inlineStr">
@@ -7350,7 +7417,7 @@
       </c>
       <c r="V7" s="42" t="inlineStr">
         <is>
-          <t>มากกว่า 10,000 ครั้ง</t>
+          <t>10,000 - 100,000 รายการ</t>
         </is>
       </c>
       <c r="W7" s="42" t="inlineStr">
@@ -7381,6 +7448,11 @@
       <c r="AD7" s="42" t="inlineStr">
         <is>
           <t>ยังไม่แน่ใจ</t>
+        </is>
+      </c>
+      <c r="AE7" s="42" t="inlineStr">
+        <is>
+          <t>ทำงานเมื่อมีเหตุการณ์ - เช่น มีใบ NC เข้ามา</t>
         </is>
       </c>
       <c r="AH7" s="42" t="inlineStr">
@@ -7433,6 +7505,11 @@
           <t>มากกว่า 50 คน</t>
         </is>
       </c>
+      <c r="V8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 100,000 รายการ</t>
+        </is>
+      </c>
       <c r="X8" s="42" t="inlineStr">
         <is>
           <t>มากกว่า 100 GB</t>
@@ -7634,7 +7711,7 @@
       </c>
       <c r="V29" s="40" t="inlineStr">
         <is>
-          <t>Requests/วัน</t>
+          <t>AI ประมวลผลกี่รายการ/วัน</t>
         </is>
       </c>
       <c r="W29" s="40" t="inlineStr">
@@ -7670,6 +7747,11 @@
       <c r="AD29" s="40" t="inlineStr">
         <is>
           <t>ถ้างานนี้ช้าลงจะเป็นปัญหามั้ย</t>
+        </is>
+      </c>
+      <c r="AE29" s="40" t="inlineStr">
+        <is>
+          <t>งานนี้เริ่มทำงานยังไง</t>
         </is>
       </c>
     </row>
@@ -7801,6 +7883,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AE30" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="45" t="inlineStr">
@@ -7928,6 +8015,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AE31" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="45" t="inlineStr">
@@ -8055,6 +8147,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AE32" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="45" t="inlineStr">
@@ -8145,6 +8242,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AE33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="45" t="inlineStr">
@@ -8177,6 +8279,11 @@
         </is>
       </c>
       <c r="U34" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V34" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -124,6 +124,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="000F6E6E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C55A11"/>
       </patternFill>
     </fill>
@@ -160,11 +165,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000F6E6E"/>
       </patternFill>
     </fill>
     <fill>
@@ -214,7 +214,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -253,19 +253,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -282,14 +282,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -301,7 +301,7 @@
     <xf numFmtId="164" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1110,24 +1110,27 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
     <col width="38" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="38" customWidth="1" min="14" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="36" customWidth="1" min="18" max="18"/>
-    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
     <col width="34" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1154,1096 +1157,1226 @@
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>อ้างอิงระบบคุณภาพ (QWP / SQP)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>ผลกระทบ (Impact)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>ความพร้อมข้อมูล (Data)</t>
-        </is>
-      </c>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
       <c r="L4" s="12" t="n"/>
       <c r="M4" s="12" t="n"/>
-      <c r="N4" s="12" t="n"/>
-      <c r="O4" s="12" t="n"/>
-      <c r="P4" s="13" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
+        <is>
+          <t>ความพร้อมข้อมูล (Data)</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="15" t="inlineStr">
         <is>
           <t>ความเป็นไปได้ (Feasibility)</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="n"/>
-      <c r="R4" s="15" t="inlineStr">
-        <is>
-          <t>ความเสี่ยง (Risk)</t>
-        </is>
-      </c>
-      <c r="S4" s="16" t="n"/>
       <c r="T4" s="16" t="n"/>
       <c r="U4" s="17" t="inlineStr">
         <is>
-          <t>แผน</t>
+          <t>ความเสี่ยง (Risk)</t>
         </is>
       </c>
       <c r="V4" s="18" t="n"/>
       <c r="W4" s="18" t="n"/>
+      <c r="X4" s="19" t="inlineStr">
+        <is>
+          <t>แผน</t>
+        </is>
+      </c>
+      <c r="Y4" s="20" t="n"/>
+      <c r="Z4" s="20" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>ชื่อ Use Case</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>บริษัท</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>ฝ่าย / แผนก</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>ผู้รับผิดชอบ
 (Owner)</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>QWP อ้างอิง
+(รหัส / ชื่อเอกสาร)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>kQI / QI ที่เกี่ยวข้อง</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>ขั้นตอนที่เกี่ยวข้อง
+(ขั้นตอนใน SQP ที่ use case นี้แตะ)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>ปัญหาที่ต้องการแก้
 (ทำไมถึงอยากได้ AI)</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>วิธีการทำงานปัจจุบัน
 Existing Work
 (ตอนนี้ทำยังไง ใครทำ)</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>แนวทางหลังนำ AI มาใช้
 Description for Redesign
 (อยากให้ AI ทำอะไร ผลลัพธ์ที่คาดหวัง)</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t>เวลาที่ใช้กับงานนี้ตอนนี้ (ยังไม่ใช้ AI)
 นับรวมทุกคนในแผนก เช่น 3 คน x 6 ชม. = 18 ชม./สัปดาห์</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="M5" s="21" t="inlineStr">
         <is>
           <t>มูลค่าความเสียหาย/ของเสียต่อปี
 (ของเสีย เคลม งานแก้ ค่าปรับ)</t>
         </is>
       </c>
-      <c r="K5" s="19" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t>ข้อมูลที่มีอยู่ตอนนี้
 Data Available
 (มีอะไร เก็บที่ไหน ใครเก็บ)</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
+      <c r="O5" s="21" t="inlineStr">
         <is>
           <t>ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน</t>
         </is>
       </c>
-      <c r="M5" s="19" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t>มีข้อมูลย้อนหลังนานแค่ไหน</t>
         </is>
       </c>
-      <c r="N5" s="19" t="inlineStr">
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>ปริมาณข้อมูลโดยประมาณ
 นับเป็นรายการ : รูป / ใบ / ไฟล์ / ครั้ง / ล็อต แล้วแต่งาน
 (เอาเฉพาะที่รู้คำตอบแล้ว)</t>
         </is>
       </c>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t>สิทธิ์นำข้อมูลมาใช้
 (เจ้าของข้อมูลยอมให้เอามาพัฒนา AI มั้ย)</t>
         </is>
       </c>
-      <c r="P5" s="19" t="inlineStr">
+      <c r="S5" s="21" t="inlineStr">
         <is>
           <t>ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย
 (ERP / MES / ระบบที่ใช้อยู่)</t>
         </is>
       </c>
-      <c r="Q5" s="19" t="inlineStr">
+      <c r="T5" s="21" t="inlineStr">
         <is>
           <t>มีคนดูแลระบบต่อหลังส่งมอบมั้ย</t>
         </is>
       </c>
-      <c r="R5" s="19" t="inlineStr">
+      <c r="U5" s="21" t="inlineStr">
         <is>
           <t>ถ้า AI ตอบผิด จะเกิดอะไรขึ้น</t>
         </is>
       </c>
-      <c r="S5" s="19" t="inlineStr">
+      <c r="V5" s="21" t="inlineStr">
         <is>
           <t>ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย</t>
         </is>
       </c>
-      <c r="T5" s="19" t="inlineStr">
+      <c r="W5" s="21" t="inlineStr">
         <is>
           <t>ข้อมูลชุดนี้ลับแค่ไหน</t>
         </is>
       </c>
-      <c r="U5" s="19" t="inlineStr">
+      <c r="X5" s="21" t="inlineStr">
         <is>
           <t>ความสำคัญที่แผนกอยากได้
 (ความเห็นแผนก ไม่นำไปคิดคะแนน)</t>
         </is>
       </c>
-      <c r="V5" s="19" t="inlineStr">
+      <c r="Y5" s="21" t="inlineStr">
         <is>
           <t>ต้องการใช้งานภายใน
 (ไตรมาส/ปี)</t>
         </is>
       </c>
-      <c r="W5" s="19" t="inlineStr">
+      <c r="Z5" s="21" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Auto Inspection ตรวจคุณภาพชิ้นงานด้วย Machine Learning</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>S.K.Polymer</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>คุณสมชาย</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>QWP-PRD-012 ตรวจสอบคุณภาพชิ้นงานก่อนส่งมอบ</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>kQI-2 อัตราของเสียที่หลุดถึงลูกค้า</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>ขั้นตอนที่ 4 ตรวจสอบชิ้นงานหลังถอดจากแม่พิมพ์</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>พนักงาน QC ตรวจชิ้นงานด้วยตาเปล่า เหนื่อยล้าตอนบ่าย ทำให้ของเสียหลุดไปถึงลูกค้าเดือนละ 2-3 ครั้ง</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>QC 3 คน ผลัดกันตรวจทุกล็อตด้วยตาเปล่า เทียบกับตัวอย่างมาตรฐาน บันทึกผลลงกระดาษ</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>ติดกล้องที่สายพาน ให้ AI แยกชิ้นงานดี/เสียอัตโนมัติแบบ Real-time ชิ้นที่ AI ไม่มั่นใจค่อยส่งให้คนตรวจ และบันทึกผลลงระบบแทนกระดาษ</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>มากกว่า 40 ชม./สัปดาห์  (มากกว่า 1 คนเต็มเวลา)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t>5 แสน - 2 ล้านบาท/ปี</t>
         </is>
       </c>
-      <c r="K6" s="20" t="inlineStr">
+      <c r="N6" s="22" t="inlineStr">
         <is>
           <t>มีรูปถ่ายชิ้นงานดี/เสียเก็บไว้ในมือถือหัวหน้ากะ ประมาณ 2 ปี และใบบันทึกผลตรวจเป็นกระดาษ</t>
         </is>
       </c>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t>รูปภาพ / ภาพถ่าย</t>
         </is>
       </c>
-      <c r="M6" s="20" t="inlineStr">
+      <c r="P6" s="22" t="inlineStr">
         <is>
           <t>1 - 3 ปี - พอใช้ได้</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t>ประมาณ 4,000 รูป (ดี 3,000 / เสีย 1,000)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr">
+      <c r="R6" s="22" t="inlineStr">
         <is>
           <t>ได้ทันที - ข้อมูลอยู่ในมือแผนกเราเอง</t>
         </is>
       </c>
-      <c r="P6" s="20" t="inlineStr">
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t>ไม่มี - AI ทำงานแยกเดี่ยวได้เลย ไม่ต้องยุ่งกับระบบไหน</t>
         </is>
       </c>
-      <c r="Q6" s="20" t="inlineStr">
+      <c r="T6" s="22" t="inlineStr">
         <is>
           <t>มี - มีคนในแผนกรับดูแลต่อได้ (ระบุชื่อในหมายเหตุ)</t>
         </is>
       </c>
-      <c r="R6" s="20" t="inlineStr">
+      <c r="U6" s="22" t="inlineStr">
         <is>
           <t>สูง - ของเสียหลุดถึงลูกค้า / อันตราย / ผิดกฎหมาย</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr">
+      <c r="V6" s="22" t="inlineStr">
         <is>
           <t>สุ่มตรวจบางส่วน - ตรวจเฉพาะที่ AI ไม่มั่นใจ</t>
         </is>
       </c>
-      <c r="T6" s="20" t="inlineStr">
+      <c r="W6" s="22" t="inlineStr">
         <is>
           <t>ข้อมูลภายใน - ห้ามออกนอกบริษัท</t>
         </is>
       </c>
-      <c r="U6" s="20" t="inlineStr">
+      <c r="X6" s="22" t="inlineStr">
         <is>
           <t>สูง - ต้องการด่วน</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr">
+      <c r="Y6" s="22" t="inlineStr">
         <is>
           <t>Q2 2570</t>
         </is>
       </c>
-      <c r="W6" s="20" t="inlineStr">
+      <c r="Z6" s="22" t="inlineStr">
         <is>
           <t>คุณสมชายเคยอบรม Python มาแล้ว</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="21" t="n"/>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="21" t="n"/>
-      <c r="P7" s="21" t="n"/>
-      <c r="Q7" s="21" t="n"/>
-      <c r="R7" s="21" t="n"/>
-      <c r="S7" s="21" t="n"/>
-      <c r="T7" s="21" t="n"/>
-      <c r="U7" s="21" t="n"/>
-      <c r="V7" s="21" t="n"/>
-      <c r="W7" s="21" t="n"/>
+      <c r="A7" s="23" t="n"/>
+      <c r="B7" s="23" t="n"/>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="23" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="23" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+      <c r="R7" s="23" t="n"/>
+      <c r="S7" s="23" t="n"/>
+      <c r="T7" s="23" t="n"/>
+      <c r="U7" s="23" t="n"/>
+      <c r="V7" s="23" t="n"/>
+      <c r="W7" s="23" t="n"/>
+      <c r="X7" s="23" t="n"/>
+      <c r="Y7" s="23" t="n"/>
+      <c r="Z7" s="23" t="n"/>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="21" t="n"/>
-      <c r="B8" s="21" t="n"/>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="21" t="n"/>
-      <c r="G8" s="21" t="n"/>
-      <c r="H8" s="21" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
-      <c r="P8" s="21" t="n"/>
-      <c r="Q8" s="21" t="n"/>
-      <c r="R8" s="21" t="n"/>
-      <c r="S8" s="21" t="n"/>
-      <c r="T8" s="21" t="n"/>
-      <c r="U8" s="21" t="n"/>
-      <c r="V8" s="21" t="n"/>
-      <c r="W8" s="21" t="n"/>
+      <c r="A8" s="23" t="n"/>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="23" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="23" t="n"/>
+      <c r="M8" s="23" t="n"/>
+      <c r="N8" s="23" t="n"/>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="23" t="n"/>
+      <c r="Q8" s="23" t="n"/>
+      <c r="R8" s="23" t="n"/>
+      <c r="S8" s="23" t="n"/>
+      <c r="T8" s="23" t="n"/>
+      <c r="U8" s="23" t="n"/>
+      <c r="V8" s="23" t="n"/>
+      <c r="W8" s="23" t="n"/>
+      <c r="X8" s="23" t="n"/>
+      <c r="Y8" s="23" t="n"/>
+      <c r="Z8" s="23" t="n"/>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="21" t="n"/>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="21" t="n"/>
-      <c r="P9" s="21" t="n"/>
-      <c r="Q9" s="21" t="n"/>
-      <c r="R9" s="21" t="n"/>
-      <c r="S9" s="21" t="n"/>
-      <c r="T9" s="21" t="n"/>
-      <c r="U9" s="21" t="n"/>
-      <c r="V9" s="21" t="n"/>
-      <c r="W9" s="21" t="n"/>
+      <c r="A9" s="23" t="n"/>
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="23" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="23" t="n"/>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="23" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="n"/>
+      <c r="Q9" s="23" t="n"/>
+      <c r="R9" s="23" t="n"/>
+      <c r="S9" s="23" t="n"/>
+      <c r="T9" s="23" t="n"/>
+      <c r="U9" s="23" t="n"/>
+      <c r="V9" s="23" t="n"/>
+      <c r="W9" s="23" t="n"/>
+      <c r="X9" s="23" t="n"/>
+      <c r="Y9" s="23" t="n"/>
+      <c r="Z9" s="23" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="21" t="n"/>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="21" t="n"/>
-      <c r="M10" s="21" t="n"/>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="21" t="n"/>
-      <c r="P10" s="21" t="n"/>
-      <c r="Q10" s="21" t="n"/>
-      <c r="R10" s="21" t="n"/>
-      <c r="S10" s="21" t="n"/>
-      <c r="T10" s="21" t="n"/>
-      <c r="U10" s="21" t="n"/>
-      <c r="V10" s="21" t="n"/>
-      <c r="W10" s="21" t="n"/>
+      <c r="A10" s="23" t="n"/>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="23" t="n"/>
+      <c r="L10" s="23" t="n"/>
+      <c r="M10" s="23" t="n"/>
+      <c r="N10" s="23" t="n"/>
+      <c r="O10" s="23" t="n"/>
+      <c r="P10" s="23" t="n"/>
+      <c r="Q10" s="23" t="n"/>
+      <c r="R10" s="23" t="n"/>
+      <c r="S10" s="23" t="n"/>
+      <c r="T10" s="23" t="n"/>
+      <c r="U10" s="23" t="n"/>
+      <c r="V10" s="23" t="n"/>
+      <c r="W10" s="23" t="n"/>
+      <c r="X10" s="23" t="n"/>
+      <c r="Y10" s="23" t="n"/>
+      <c r="Z10" s="23" t="n"/>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="21" t="n"/>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="21" t="n"/>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="21" t="n"/>
-      <c r="P11" s="21" t="n"/>
-      <c r="Q11" s="21" t="n"/>
-      <c r="R11" s="21" t="n"/>
-      <c r="S11" s="21" t="n"/>
-      <c r="T11" s="21" t="n"/>
-      <c r="U11" s="21" t="n"/>
-      <c r="V11" s="21" t="n"/>
-      <c r="W11" s="21" t="n"/>
+      <c r="A11" s="23" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="23" t="n"/>
+      <c r="M11" s="23" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+      <c r="R11" s="23" t="n"/>
+      <c r="S11" s="23" t="n"/>
+      <c r="T11" s="23" t="n"/>
+      <c r="U11" s="23" t="n"/>
+      <c r="V11" s="23" t="n"/>
+      <c r="W11" s="23" t="n"/>
+      <c r="X11" s="23" t="n"/>
+      <c r="Y11" s="23" t="n"/>
+      <c r="Z11" s="23" t="n"/>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="21" t="n"/>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="21" t="n"/>
-      <c r="P12" s="21" t="n"/>
-      <c r="Q12" s="21" t="n"/>
-      <c r="R12" s="21" t="n"/>
-      <c r="S12" s="21" t="n"/>
-      <c r="T12" s="21" t="n"/>
-      <c r="U12" s="21" t="n"/>
-      <c r="V12" s="21" t="n"/>
-      <c r="W12" s="21" t="n"/>
+      <c r="A12" s="23" t="n"/>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="23" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="23" t="n"/>
+      <c r="L12" s="23" t="n"/>
+      <c r="M12" s="23" t="n"/>
+      <c r="N12" s="23" t="n"/>
+      <c r="O12" s="23" t="n"/>
+      <c r="P12" s="23" t="n"/>
+      <c r="Q12" s="23" t="n"/>
+      <c r="R12" s="23" t="n"/>
+      <c r="S12" s="23" t="n"/>
+      <c r="T12" s="23" t="n"/>
+      <c r="U12" s="23" t="n"/>
+      <c r="V12" s="23" t="n"/>
+      <c r="W12" s="23" t="n"/>
+      <c r="X12" s="23" t="n"/>
+      <c r="Y12" s="23" t="n"/>
+      <c r="Z12" s="23" t="n"/>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="21" t="n"/>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="21" t="n"/>
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="21" t="n"/>
-      <c r="P13" s="21" t="n"/>
-      <c r="Q13" s="21" t="n"/>
-      <c r="R13" s="21" t="n"/>
-      <c r="S13" s="21" t="n"/>
-      <c r="T13" s="21" t="n"/>
-      <c r="U13" s="21" t="n"/>
-      <c r="V13" s="21" t="n"/>
-      <c r="W13" s="21" t="n"/>
+      <c r="A13" s="23" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="23" t="n"/>
+      <c r="I13" s="23" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="23" t="n"/>
+      <c r="L13" s="23" t="n"/>
+      <c r="M13" s="23" t="n"/>
+      <c r="N13" s="23" t="n"/>
+      <c r="O13" s="23" t="n"/>
+      <c r="P13" s="23" t="n"/>
+      <c r="Q13" s="23" t="n"/>
+      <c r="R13" s="23" t="n"/>
+      <c r="S13" s="23" t="n"/>
+      <c r="T13" s="23" t="n"/>
+      <c r="U13" s="23" t="n"/>
+      <c r="V13" s="23" t="n"/>
+      <c r="W13" s="23" t="n"/>
+      <c r="X13" s="23" t="n"/>
+      <c r="Y13" s="23" t="n"/>
+      <c r="Z13" s="23" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="21" t="n"/>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="21" t="n"/>
-      <c r="P14" s="21" t="n"/>
-      <c r="Q14" s="21" t="n"/>
-      <c r="R14" s="21" t="n"/>
-      <c r="S14" s="21" t="n"/>
-      <c r="T14" s="21" t="n"/>
-      <c r="U14" s="21" t="n"/>
-      <c r="V14" s="21" t="n"/>
-      <c r="W14" s="21" t="n"/>
+      <c r="A14" s="23" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="23" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="23" t="n"/>
+      <c r="I14" s="23" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="23" t="n"/>
+      <c r="M14" s="23" t="n"/>
+      <c r="N14" s="23" t="n"/>
+      <c r="O14" s="23" t="n"/>
+      <c r="P14" s="23" t="n"/>
+      <c r="Q14" s="23" t="n"/>
+      <c r="R14" s="23" t="n"/>
+      <c r="S14" s="23" t="n"/>
+      <c r="T14" s="23" t="n"/>
+      <c r="U14" s="23" t="n"/>
+      <c r="V14" s="23" t="n"/>
+      <c r="W14" s="23" t="n"/>
+      <c r="X14" s="23" t="n"/>
+      <c r="Y14" s="23" t="n"/>
+      <c r="Z14" s="23" t="n"/>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="21" t="n"/>
-      <c r="B15" s="21" t="n"/>
-      <c r="C15" s="21" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="21" t="n"/>
-      <c r="P15" s="21" t="n"/>
-      <c r="Q15" s="21" t="n"/>
-      <c r="R15" s="21" t="n"/>
-      <c r="S15" s="21" t="n"/>
-      <c r="T15" s="21" t="n"/>
-      <c r="U15" s="21" t="n"/>
-      <c r="V15" s="21" t="n"/>
-      <c r="W15" s="21" t="n"/>
+      <c r="A15" s="23" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="23" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+      <c r="R15" s="23" t="n"/>
+      <c r="S15" s="23" t="n"/>
+      <c r="T15" s="23" t="n"/>
+      <c r="U15" s="23" t="n"/>
+      <c r="V15" s="23" t="n"/>
+      <c r="W15" s="23" t="n"/>
+      <c r="X15" s="23" t="n"/>
+      <c r="Y15" s="23" t="n"/>
+      <c r="Z15" s="23" t="n"/>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="21" t="n"/>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="21" t="n"/>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="21" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
-      <c r="S16" s="21" t="n"/>
-      <c r="T16" s="21" t="n"/>
-      <c r="U16" s="21" t="n"/>
-      <c r="V16" s="21" t="n"/>
-      <c r="W16" s="21" t="n"/>
+      <c r="A16" s="23" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="n"/>
+      <c r="I16" s="23" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="23" t="n"/>
+      <c r="L16" s="23" t="n"/>
+      <c r="M16" s="23" t="n"/>
+      <c r="N16" s="23" t="n"/>
+      <c r="O16" s="23" t="n"/>
+      <c r="P16" s="23" t="n"/>
+      <c r="Q16" s="23" t="n"/>
+      <c r="R16" s="23" t="n"/>
+      <c r="S16" s="23" t="n"/>
+      <c r="T16" s="23" t="n"/>
+      <c r="U16" s="23" t="n"/>
+      <c r="V16" s="23" t="n"/>
+      <c r="W16" s="23" t="n"/>
+      <c r="X16" s="23" t="n"/>
+      <c r="Y16" s="23" t="n"/>
+      <c r="Z16" s="23" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="21" t="n"/>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="21" t="n"/>
-      <c r="S17" s="21" t="n"/>
-      <c r="T17" s="21" t="n"/>
-      <c r="U17" s="21" t="n"/>
-      <c r="V17" s="21" t="n"/>
-      <c r="W17" s="21" t="n"/>
+      <c r="A17" s="23" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="23" t="n"/>
+      <c r="I17" s="23" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="23" t="n"/>
+      <c r="L17" s="23" t="n"/>
+      <c r="M17" s="23" t="n"/>
+      <c r="N17" s="23" t="n"/>
+      <c r="O17" s="23" t="n"/>
+      <c r="P17" s="23" t="n"/>
+      <c r="Q17" s="23" t="n"/>
+      <c r="R17" s="23" t="n"/>
+      <c r="S17" s="23" t="n"/>
+      <c r="T17" s="23" t="n"/>
+      <c r="U17" s="23" t="n"/>
+      <c r="V17" s="23" t="n"/>
+      <c r="W17" s="23" t="n"/>
+      <c r="X17" s="23" t="n"/>
+      <c r="Y17" s="23" t="n"/>
+      <c r="Z17" s="23" t="n"/>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="21" t="n"/>
-      <c r="B18" s="21" t="n"/>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
-      <c r="P18" s="21" t="n"/>
-      <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="21" t="n"/>
-      <c r="S18" s="21" t="n"/>
-      <c r="T18" s="21" t="n"/>
-      <c r="U18" s="21" t="n"/>
-      <c r="V18" s="21" t="n"/>
-      <c r="W18" s="21" t="n"/>
+      <c r="A18" s="23" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="n"/>
+      <c r="I18" s="23" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="23" t="n"/>
+      <c r="L18" s="23" t="n"/>
+      <c r="M18" s="23" t="n"/>
+      <c r="N18" s="23" t="n"/>
+      <c r="O18" s="23" t="n"/>
+      <c r="P18" s="23" t="n"/>
+      <c r="Q18" s="23" t="n"/>
+      <c r="R18" s="23" t="n"/>
+      <c r="S18" s="23" t="n"/>
+      <c r="T18" s="23" t="n"/>
+      <c r="U18" s="23" t="n"/>
+      <c r="V18" s="23" t="n"/>
+      <c r="W18" s="23" t="n"/>
+      <c r="X18" s="23" t="n"/>
+      <c r="Y18" s="23" t="n"/>
+      <c r="Z18" s="23" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="21" t="n"/>
-      <c r="B19" s="21" t="n"/>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
-      <c r="F19" s="21" t="n"/>
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="21" t="n"/>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
-      <c r="P19" s="21" t="n"/>
-      <c r="Q19" s="21" t="n"/>
-      <c r="R19" s="21" t="n"/>
-      <c r="S19" s="21" t="n"/>
-      <c r="T19" s="21" t="n"/>
-      <c r="U19" s="21" t="n"/>
-      <c r="V19" s="21" t="n"/>
-      <c r="W19" s="21" t="n"/>
+      <c r="A19" s="23" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="23" t="n"/>
+      <c r="I19" s="23" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="23" t="n"/>
+      <c r="L19" s="23" t="n"/>
+      <c r="M19" s="23" t="n"/>
+      <c r="N19" s="23" t="n"/>
+      <c r="O19" s="23" t="n"/>
+      <c r="P19" s="23" t="n"/>
+      <c r="Q19" s="23" t="n"/>
+      <c r="R19" s="23" t="n"/>
+      <c r="S19" s="23" t="n"/>
+      <c r="T19" s="23" t="n"/>
+      <c r="U19" s="23" t="n"/>
+      <c r="V19" s="23" t="n"/>
+      <c r="W19" s="23" t="n"/>
+      <c r="X19" s="23" t="n"/>
+      <c r="Y19" s="23" t="n"/>
+      <c r="Z19" s="23" t="n"/>
     </row>
     <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="21" t="n"/>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="21" t="n"/>
-      <c r="S20" s="21" t="n"/>
-      <c r="T20" s="21" t="n"/>
-      <c r="U20" s="21" t="n"/>
-      <c r="V20" s="21" t="n"/>
-      <c r="W20" s="21" t="n"/>
+      <c r="A20" s="23" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="23" t="n"/>
+      <c r="I20" s="23" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="23" t="n"/>
+      <c r="L20" s="23" t="n"/>
+      <c r="M20" s="23" t="n"/>
+      <c r="N20" s="23" t="n"/>
+      <c r="O20" s="23" t="n"/>
+      <c r="P20" s="23" t="n"/>
+      <c r="Q20" s="23" t="n"/>
+      <c r="R20" s="23" t="n"/>
+      <c r="S20" s="23" t="n"/>
+      <c r="T20" s="23" t="n"/>
+      <c r="U20" s="23" t="n"/>
+      <c r="V20" s="23" t="n"/>
+      <c r="W20" s="23" t="n"/>
+      <c r="X20" s="23" t="n"/>
+      <c r="Y20" s="23" t="n"/>
+      <c r="Z20" s="23" t="n"/>
     </row>
     <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="21" t="n"/>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="21" t="n"/>
-      <c r="G21" s="21" t="n"/>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="21" t="n"/>
-      <c r="K21" s="21" t="n"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="21" t="n"/>
-      <c r="P21" s="21" t="n"/>
-      <c r="Q21" s="21" t="n"/>
-      <c r="R21" s="21" t="n"/>
-      <c r="S21" s="21" t="n"/>
-      <c r="T21" s="21" t="n"/>
-      <c r="U21" s="21" t="n"/>
-      <c r="V21" s="21" t="n"/>
-      <c r="W21" s="21" t="n"/>
+      <c r="A21" s="23" t="n"/>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="23" t="n"/>
+      <c r="I21" s="23" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="23" t="n"/>
+      <c r="L21" s="23" t="n"/>
+      <c r="M21" s="23" t="n"/>
+      <c r="N21" s="23" t="n"/>
+      <c r="O21" s="23" t="n"/>
+      <c r="P21" s="23" t="n"/>
+      <c r="Q21" s="23" t="n"/>
+      <c r="R21" s="23" t="n"/>
+      <c r="S21" s="23" t="n"/>
+      <c r="T21" s="23" t="n"/>
+      <c r="U21" s="23" t="n"/>
+      <c r="V21" s="23" t="n"/>
+      <c r="W21" s="23" t="n"/>
+      <c r="X21" s="23" t="n"/>
+      <c r="Y21" s="23" t="n"/>
+      <c r="Z21" s="23" t="n"/>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="21" t="n"/>
-      <c r="B22" s="21" t="n"/>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
-      <c r="F22" s="21" t="n"/>
-      <c r="G22" s="21" t="n"/>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
-      <c r="P22" s="21" t="n"/>
-      <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="21" t="n"/>
-      <c r="S22" s="21" t="n"/>
-      <c r="T22" s="21" t="n"/>
-      <c r="U22" s="21" t="n"/>
-      <c r="V22" s="21" t="n"/>
-      <c r="W22" s="21" t="n"/>
+      <c r="A22" s="23" t="n"/>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="23" t="n"/>
+      <c r="L22" s="23" t="n"/>
+      <c r="M22" s="23" t="n"/>
+      <c r="N22" s="23" t="n"/>
+      <c r="O22" s="23" t="n"/>
+      <c r="P22" s="23" t="n"/>
+      <c r="Q22" s="23" t="n"/>
+      <c r="R22" s="23" t="n"/>
+      <c r="S22" s="23" t="n"/>
+      <c r="T22" s="23" t="n"/>
+      <c r="U22" s="23" t="n"/>
+      <c r="V22" s="23" t="n"/>
+      <c r="W22" s="23" t="n"/>
+      <c r="X22" s="23" t="n"/>
+      <c r="Y22" s="23" t="n"/>
+      <c r="Z22" s="23" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="21" t="n"/>
-      <c r="B23" s="21" t="n"/>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="F23" s="21" t="n"/>
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
-      <c r="K23" s="21" t="n"/>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="21" t="n"/>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="21" t="n"/>
-      <c r="P23" s="21" t="n"/>
-      <c r="Q23" s="21" t="n"/>
-      <c r="R23" s="21" t="n"/>
-      <c r="S23" s="21" t="n"/>
-      <c r="T23" s="21" t="n"/>
-      <c r="U23" s="21" t="n"/>
-      <c r="V23" s="21" t="n"/>
-      <c r="W23" s="21" t="n"/>
+      <c r="A23" s="23" t="n"/>
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="23" t="n"/>
+      <c r="I23" s="23" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="23" t="n"/>
+      <c r="L23" s="23" t="n"/>
+      <c r="M23" s="23" t="n"/>
+      <c r="N23" s="23" t="n"/>
+      <c r="O23" s="23" t="n"/>
+      <c r="P23" s="23" t="n"/>
+      <c r="Q23" s="23" t="n"/>
+      <c r="R23" s="23" t="n"/>
+      <c r="S23" s="23" t="n"/>
+      <c r="T23" s="23" t="n"/>
+      <c r="U23" s="23" t="n"/>
+      <c r="V23" s="23" t="n"/>
+      <c r="W23" s="23" t="n"/>
+      <c r="X23" s="23" t="n"/>
+      <c r="Y23" s="23" t="n"/>
+      <c r="Z23" s="23" t="n"/>
     </row>
     <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="21" t="n"/>
-      <c r="B24" s="21" t="n"/>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
-      <c r="P24" s="21" t="n"/>
-      <c r="Q24" s="21" t="n"/>
-      <c r="R24" s="21" t="n"/>
-      <c r="S24" s="21" t="n"/>
-      <c r="T24" s="21" t="n"/>
-      <c r="U24" s="21" t="n"/>
-      <c r="V24" s="21" t="n"/>
-      <c r="W24" s="21" t="n"/>
+      <c r="A24" s="23" t="n"/>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="23" t="n"/>
+      <c r="H24" s="23" t="n"/>
+      <c r="I24" s="23" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="23" t="n"/>
+      <c r="L24" s="23" t="n"/>
+      <c r="M24" s="23" t="n"/>
+      <c r="N24" s="23" t="n"/>
+      <c r="O24" s="23" t="n"/>
+      <c r="P24" s="23" t="n"/>
+      <c r="Q24" s="23" t="n"/>
+      <c r="R24" s="23" t="n"/>
+      <c r="S24" s="23" t="n"/>
+      <c r="T24" s="23" t="n"/>
+      <c r="U24" s="23" t="n"/>
+      <c r="V24" s="23" t="n"/>
+      <c r="W24" s="23" t="n"/>
+      <c r="X24" s="23" t="n"/>
+      <c r="Y24" s="23" t="n"/>
+      <c r="Z24" s="23" t="n"/>
     </row>
     <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="21" t="n"/>
-      <c r="B25" s="21" t="n"/>
-      <c r="C25" s="21" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="21" t="n"/>
-      <c r="K25" s="21" t="n"/>
-      <c r="L25" s="21" t="n"/>
-      <c r="M25" s="21" t="n"/>
-      <c r="N25" s="21" t="n"/>
-      <c r="O25" s="21" t="n"/>
-      <c r="P25" s="21" t="n"/>
-      <c r="Q25" s="21" t="n"/>
-      <c r="R25" s="21" t="n"/>
-      <c r="S25" s="21" t="n"/>
-      <c r="T25" s="21" t="n"/>
-      <c r="U25" s="21" t="n"/>
-      <c r="V25" s="21" t="n"/>
-      <c r="W25" s="21" t="n"/>
+      <c r="A25" s="23" t="n"/>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="23" t="n"/>
+      <c r="I25" s="23" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="23" t="n"/>
+      <c r="L25" s="23" t="n"/>
+      <c r="M25" s="23" t="n"/>
+      <c r="N25" s="23" t="n"/>
+      <c r="O25" s="23" t="n"/>
+      <c r="P25" s="23" t="n"/>
+      <c r="Q25" s="23" t="n"/>
+      <c r="R25" s="23" t="n"/>
+      <c r="S25" s="23" t="n"/>
+      <c r="T25" s="23" t="n"/>
+      <c r="U25" s="23" t="n"/>
+      <c r="V25" s="23" t="n"/>
+      <c r="W25" s="23" t="n"/>
+      <c r="X25" s="23" t="n"/>
+      <c r="Y25" s="23" t="n"/>
+      <c r="Z25" s="23" t="n"/>
     </row>
     <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="21" t="n"/>
-      <c r="B26" s="21" t="n"/>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="21" t="n"/>
-      <c r="K26" s="21" t="n"/>
-      <c r="L26" s="21" t="n"/>
-      <c r="M26" s="21" t="n"/>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="21" t="n"/>
-      <c r="P26" s="21" t="n"/>
-      <c r="Q26" s="21" t="n"/>
-      <c r="R26" s="21" t="n"/>
-      <c r="S26" s="21" t="n"/>
-      <c r="T26" s="21" t="n"/>
-      <c r="U26" s="21" t="n"/>
-      <c r="V26" s="21" t="n"/>
-      <c r="W26" s="21" t="n"/>
+      <c r="A26" s="23" t="n"/>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="23" t="n"/>
+      <c r="L26" s="23" t="n"/>
+      <c r="M26" s="23" t="n"/>
+      <c r="N26" s="23" t="n"/>
+      <c r="O26" s="23" t="n"/>
+      <c r="P26" s="23" t="n"/>
+      <c r="Q26" s="23" t="n"/>
+      <c r="R26" s="23" t="n"/>
+      <c r="S26" s="23" t="n"/>
+      <c r="T26" s="23" t="n"/>
+      <c r="U26" s="23" t="n"/>
+      <c r="V26" s="23" t="n"/>
+      <c r="W26" s="23" t="n"/>
+      <c r="X26" s="23" t="n"/>
+      <c r="Y26" s="23" t="n"/>
+      <c r="Z26" s="23" t="n"/>
     </row>
     <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="21" t="n"/>
-      <c r="B27" s="21" t="n"/>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
-      <c r="F27" s="21" t="n"/>
-      <c r="G27" s="21" t="n"/>
-      <c r="H27" s="21" t="n"/>
-      <c r="I27" s="21" t="n"/>
-      <c r="J27" s="21" t="n"/>
-      <c r="K27" s="21" t="n"/>
-      <c r="L27" s="21" t="n"/>
-      <c r="M27" s="21" t="n"/>
-      <c r="N27" s="21" t="n"/>
-      <c r="O27" s="21" t="n"/>
-      <c r="P27" s="21" t="n"/>
-      <c r="Q27" s="21" t="n"/>
-      <c r="R27" s="21" t="n"/>
-      <c r="S27" s="21" t="n"/>
-      <c r="T27" s="21" t="n"/>
-      <c r="U27" s="21" t="n"/>
-      <c r="V27" s="21" t="n"/>
-      <c r="W27" s="21" t="n"/>
+      <c r="A27" s="23" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="23" t="n"/>
+      <c r="H27" s="23" t="n"/>
+      <c r="I27" s="23" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="23" t="n"/>
+      <c r="L27" s="23" t="n"/>
+      <c r="M27" s="23" t="n"/>
+      <c r="N27" s="23" t="n"/>
+      <c r="O27" s="23" t="n"/>
+      <c r="P27" s="23" t="n"/>
+      <c r="Q27" s="23" t="n"/>
+      <c r="R27" s="23" t="n"/>
+      <c r="S27" s="23" t="n"/>
+      <c r="T27" s="23" t="n"/>
+      <c r="U27" s="23" t="n"/>
+      <c r="V27" s="23" t="n"/>
+      <c r="W27" s="23" t="n"/>
+      <c r="X27" s="23" t="n"/>
+      <c r="Y27" s="23" t="n"/>
+      <c r="Z27" s="23" t="n"/>
     </row>
     <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="21" t="n"/>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="21" t="n"/>
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="21" t="n"/>
-      <c r="I28" s="21" t="n"/>
-      <c r="J28" s="21" t="n"/>
-      <c r="K28" s="21" t="n"/>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="21" t="n"/>
-      <c r="N28" s="21" t="n"/>
-      <c r="O28" s="21" t="n"/>
-      <c r="P28" s="21" t="n"/>
-      <c r="Q28" s="21" t="n"/>
-      <c r="R28" s="21" t="n"/>
-      <c r="S28" s="21" t="n"/>
-      <c r="T28" s="21" t="n"/>
-      <c r="U28" s="21" t="n"/>
-      <c r="V28" s="21" t="n"/>
-      <c r="W28" s="21" t="n"/>
+      <c r="A28" s="23" t="n"/>
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="23" t="n"/>
+      <c r="H28" s="23" t="n"/>
+      <c r="I28" s="23" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="23" t="n"/>
+      <c r="L28" s="23" t="n"/>
+      <c r="M28" s="23" t="n"/>
+      <c r="N28" s="23" t="n"/>
+      <c r="O28" s="23" t="n"/>
+      <c r="P28" s="23" t="n"/>
+      <c r="Q28" s="23" t="n"/>
+      <c r="R28" s="23" t="n"/>
+      <c r="S28" s="23" t="n"/>
+      <c r="T28" s="23" t="n"/>
+      <c r="U28" s="23" t="n"/>
+      <c r="V28" s="23" t="n"/>
+      <c r="W28" s="23" t="n"/>
+      <c r="X28" s="23" t="n"/>
+      <c r="Y28" s="23" t="n"/>
+      <c r="Z28" s="23" t="n"/>
     </row>
     <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="21" t="n"/>
-      <c r="B29" s="21" t="n"/>
-      <c r="C29" s="21" t="n"/>
-      <c r="D29" s="21" t="n"/>
-      <c r="E29" s="21" t="n"/>
-      <c r="F29" s="21" t="n"/>
-      <c r="G29" s="21" t="n"/>
-      <c r="H29" s="21" t="n"/>
-      <c r="I29" s="21" t="n"/>
-      <c r="J29" s="21" t="n"/>
-      <c r="K29" s="21" t="n"/>
-      <c r="L29" s="21" t="n"/>
-      <c r="M29" s="21" t="n"/>
-      <c r="N29" s="21" t="n"/>
-      <c r="O29" s="21" t="n"/>
-      <c r="P29" s="21" t="n"/>
-      <c r="Q29" s="21" t="n"/>
-      <c r="R29" s="21" t="n"/>
-      <c r="S29" s="21" t="n"/>
-      <c r="T29" s="21" t="n"/>
-      <c r="U29" s="21" t="n"/>
-      <c r="V29" s="21" t="n"/>
-      <c r="W29" s="21" t="n"/>
+      <c r="A29" s="23" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="23" t="n"/>
+      <c r="I29" s="23" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="23" t="n"/>
+      <c r="L29" s="23" t="n"/>
+      <c r="M29" s="23" t="n"/>
+      <c r="N29" s="23" t="n"/>
+      <c r="O29" s="23" t="n"/>
+      <c r="P29" s="23" t="n"/>
+      <c r="Q29" s="23" t="n"/>
+      <c r="R29" s="23" t="n"/>
+      <c r="S29" s="23" t="n"/>
+      <c r="T29" s="23" t="n"/>
+      <c r="U29" s="23" t="n"/>
+      <c r="V29" s="23" t="n"/>
+      <c r="W29" s="23" t="n"/>
+      <c r="X29" s="23" t="n"/>
+      <c r="Y29" s="23" t="n"/>
+      <c r="Z29" s="23" t="n"/>
     </row>
     <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="21" t="n"/>
-      <c r="B30" s="21" t="n"/>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="21" t="n"/>
-      <c r="G30" s="21" t="n"/>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
-      <c r="J30" s="21" t="n"/>
-      <c r="K30" s="21" t="n"/>
-      <c r="L30" s="21" t="n"/>
-      <c r="M30" s="21" t="n"/>
-      <c r="N30" s="21" t="n"/>
-      <c r="O30" s="21" t="n"/>
-      <c r="P30" s="21" t="n"/>
-      <c r="Q30" s="21" t="n"/>
-      <c r="R30" s="21" t="n"/>
-      <c r="S30" s="21" t="n"/>
-      <c r="T30" s="21" t="n"/>
-      <c r="U30" s="21" t="n"/>
-      <c r="V30" s="21" t="n"/>
-      <c r="W30" s="21" t="n"/>
+      <c r="A30" s="23" t="n"/>
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="23" t="n"/>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="23" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="23" t="n"/>
+      <c r="O30" s="23" t="n"/>
+      <c r="P30" s="23" t="n"/>
+      <c r="Q30" s="23" t="n"/>
+      <c r="R30" s="23" t="n"/>
+      <c r="S30" s="23" t="n"/>
+      <c r="T30" s="23" t="n"/>
+      <c r="U30" s="23" t="n"/>
+      <c r="V30" s="23" t="n"/>
+      <c r="W30" s="23" t="n"/>
+      <c r="X30" s="23" t="n"/>
+      <c r="Y30" s="23" t="n"/>
+      <c r="Z30" s="23" t="n"/>
     </row>
     <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="21" t="n"/>
-      <c r="B31" s="21" t="n"/>
-      <c r="C31" s="21" t="n"/>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="21" t="n"/>
-      <c r="F31" s="21" t="n"/>
-      <c r="G31" s="21" t="n"/>
-      <c r="H31" s="21" t="n"/>
-      <c r="I31" s="21" t="n"/>
-      <c r="J31" s="21" t="n"/>
-      <c r="K31" s="21" t="n"/>
-      <c r="L31" s="21" t="n"/>
-      <c r="M31" s="21" t="n"/>
-      <c r="N31" s="21" t="n"/>
-      <c r="O31" s="21" t="n"/>
-      <c r="P31" s="21" t="n"/>
-      <c r="Q31" s="21" t="n"/>
-      <c r="R31" s="21" t="n"/>
-      <c r="S31" s="21" t="n"/>
-      <c r="T31" s="21" t="n"/>
-      <c r="U31" s="21" t="n"/>
-      <c r="V31" s="21" t="n"/>
-      <c r="W31" s="21" t="n"/>
+      <c r="A31" s="23" t="n"/>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="23" t="n"/>
+      <c r="H31" s="23" t="n"/>
+      <c r="I31" s="23" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="23" t="n"/>
+      <c r="L31" s="23" t="n"/>
+      <c r="M31" s="23" t="n"/>
+      <c r="N31" s="23" t="n"/>
+      <c r="O31" s="23" t="n"/>
+      <c r="P31" s="23" t="n"/>
+      <c r="Q31" s="23" t="n"/>
+      <c r="R31" s="23" t="n"/>
+      <c r="S31" s="23" t="n"/>
+      <c r="T31" s="23" t="n"/>
+      <c r="U31" s="23" t="n"/>
+      <c r="V31" s="23" t="n"/>
+      <c r="W31" s="23" t="n"/>
+      <c r="X31" s="23" t="n"/>
+      <c r="Y31" s="23" t="n"/>
+      <c r="Z31" s="23" t="n"/>
     </row>
     <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="21" t="n"/>
-      <c r="B32" s="21" t="n"/>
-      <c r="C32" s="21" t="n"/>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="21" t="n"/>
-      <c r="G32" s="21" t="n"/>
-      <c r="H32" s="21" t="n"/>
-      <c r="I32" s="21" t="n"/>
-      <c r="J32" s="21" t="n"/>
-      <c r="K32" s="21" t="n"/>
-      <c r="L32" s="21" t="n"/>
-      <c r="M32" s="21" t="n"/>
-      <c r="N32" s="21" t="n"/>
-      <c r="O32" s="21" t="n"/>
-      <c r="P32" s="21" t="n"/>
-      <c r="Q32" s="21" t="n"/>
-      <c r="R32" s="21" t="n"/>
-      <c r="S32" s="21" t="n"/>
-      <c r="T32" s="21" t="n"/>
-      <c r="U32" s="21" t="n"/>
-      <c r="V32" s="21" t="n"/>
-      <c r="W32" s="21" t="n"/>
+      <c r="A32" s="23" t="n"/>
+      <c r="B32" s="23" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="23" t="n"/>
+      <c r="H32" s="23" t="n"/>
+      <c r="I32" s="23" t="n"/>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="23" t="n"/>
+      <c r="L32" s="23" t="n"/>
+      <c r="M32" s="23" t="n"/>
+      <c r="N32" s="23" t="n"/>
+      <c r="O32" s="23" t="n"/>
+      <c r="P32" s="23" t="n"/>
+      <c r="Q32" s="23" t="n"/>
+      <c r="R32" s="23" t="n"/>
+      <c r="S32" s="23" t="n"/>
+      <c r="T32" s="23" t="n"/>
+      <c r="U32" s="23" t="n"/>
+      <c r="V32" s="23" t="n"/>
+      <c r="W32" s="23" t="n"/>
+      <c r="X32" s="23" t="n"/>
+      <c r="Y32" s="23" t="n"/>
+      <c r="Z32" s="23" t="n"/>
     </row>
     <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="21" t="n"/>
-      <c r="B33" s="21" t="n"/>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-      <c r="I33" s="21" t="n"/>
-      <c r="J33" s="21" t="n"/>
-      <c r="K33" s="21" t="n"/>
-      <c r="L33" s="21" t="n"/>
-      <c r="M33" s="21" t="n"/>
-      <c r="N33" s="21" t="n"/>
-      <c r="O33" s="21" t="n"/>
-      <c r="P33" s="21" t="n"/>
-      <c r="Q33" s="21" t="n"/>
-      <c r="R33" s="21" t="n"/>
-      <c r="S33" s="21" t="n"/>
-      <c r="T33" s="21" t="n"/>
-      <c r="U33" s="21" t="n"/>
-      <c r="V33" s="21" t="n"/>
-      <c r="W33" s="21" t="n"/>
+      <c r="A33" s="23" t="n"/>
+      <c r="B33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="23" t="n"/>
+      <c r="I33" s="23" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="23" t="n"/>
+      <c r="L33" s="23" t="n"/>
+      <c r="M33" s="23" t="n"/>
+      <c r="N33" s="23" t="n"/>
+      <c r="O33" s="23" t="n"/>
+      <c r="P33" s="23" t="n"/>
+      <c r="Q33" s="23" t="n"/>
+      <c r="R33" s="23" t="n"/>
+      <c r="S33" s="23" t="n"/>
+      <c r="T33" s="23" t="n"/>
+      <c r="U33" s="23" t="n"/>
+      <c r="V33" s="23" t="n"/>
+      <c r="W33" s="23" t="n"/>
+      <c r="X33" s="23" t="n"/>
+      <c r="Y33" s="23" t="n"/>
+      <c r="Z33" s="23" t="n"/>
     </row>
     <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="21" t="n"/>
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="21" t="n"/>
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="21" t="n"/>
-      <c r="I34" s="21" t="n"/>
-      <c r="J34" s="21" t="n"/>
-      <c r="K34" s="21" t="n"/>
-      <c r="L34" s="21" t="n"/>
-      <c r="M34" s="21" t="n"/>
-      <c r="N34" s="21" t="n"/>
-      <c r="O34" s="21" t="n"/>
-      <c r="P34" s="21" t="n"/>
-      <c r="Q34" s="21" t="n"/>
-      <c r="R34" s="21" t="n"/>
-      <c r="S34" s="21" t="n"/>
-      <c r="T34" s="21" t="n"/>
-      <c r="U34" s="21" t="n"/>
-      <c r="V34" s="21" t="n"/>
-      <c r="W34" s="21" t="n"/>
+      <c r="A34" s="23" t="n"/>
+      <c r="B34" s="23" t="n"/>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="23" t="n"/>
+      <c r="I34" s="23" t="n"/>
+      <c r="J34" s="23" t="n"/>
+      <c r="K34" s="23" t="n"/>
+      <c r="L34" s="23" t="n"/>
+      <c r="M34" s="23" t="n"/>
+      <c r="N34" s="23" t="n"/>
+      <c r="O34" s="23" t="n"/>
+      <c r="P34" s="23" t="n"/>
+      <c r="Q34" s="23" t="n"/>
+      <c r="R34" s="23" t="n"/>
+      <c r="S34" s="23" t="n"/>
+      <c r="T34" s="23" t="n"/>
+      <c r="U34" s="23" t="n"/>
+      <c r="V34" s="23" t="n"/>
+      <c r="W34" s="23" t="n"/>
+      <c r="X34" s="23" t="n"/>
+      <c r="Y34" s="23" t="n"/>
+      <c r="Z34" s="23" t="n"/>
     </row>
     <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="21" t="n"/>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="21" t="n"/>
-      <c r="F35" s="21" t="n"/>
-      <c r="G35" s="21" t="n"/>
-      <c r="H35" s="21" t="n"/>
-      <c r="I35" s="21" t="n"/>
-      <c r="J35" s="21" t="n"/>
-      <c r="K35" s="21" t="n"/>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="21" t="n"/>
-      <c r="O35" s="21" t="n"/>
-      <c r="P35" s="21" t="n"/>
-      <c r="Q35" s="21" t="n"/>
-      <c r="R35" s="21" t="n"/>
-      <c r="S35" s="21" t="n"/>
-      <c r="T35" s="21" t="n"/>
-      <c r="U35" s="21" t="n"/>
-      <c r="V35" s="21" t="n"/>
-      <c r="W35" s="21" t="n"/>
+      <c r="A35" s="23" t="n"/>
+      <c r="B35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="23" t="n"/>
+      <c r="I35" s="23" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="23" t="n"/>
+      <c r="L35" s="23" t="n"/>
+      <c r="M35" s="23" t="n"/>
+      <c r="N35" s="23" t="n"/>
+      <c r="O35" s="23" t="n"/>
+      <c r="P35" s="23" t="n"/>
+      <c r="Q35" s="23" t="n"/>
+      <c r="R35" s="23" t="n"/>
+      <c r="S35" s="23" t="n"/>
+      <c r="T35" s="23" t="n"/>
+      <c r="U35" s="23" t="n"/>
+      <c r="V35" s="23" t="n"/>
+      <c r="W35" s="23" t="n"/>
+      <c r="X35" s="23" t="n"/>
+      <c r="Y35" s="23" t="n"/>
+      <c r="Z35" s="23" t="n"/>
     </row>
     <row r="36" ht="40" customHeight="1">
-      <c r="A36" s="21" t="n"/>
-      <c r="B36" s="21" t="n"/>
-      <c r="C36" s="21" t="n"/>
-      <c r="D36" s="21" t="n"/>
-      <c r="E36" s="21" t="n"/>
-      <c r="F36" s="21" t="n"/>
-      <c r="G36" s="21" t="n"/>
-      <c r="H36" s="21" t="n"/>
-      <c r="I36" s="21" t="n"/>
-      <c r="J36" s="21" t="n"/>
-      <c r="K36" s="21" t="n"/>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="21" t="n"/>
-      <c r="N36" s="21" t="n"/>
-      <c r="O36" s="21" t="n"/>
-      <c r="P36" s="21" t="n"/>
-      <c r="Q36" s="21" t="n"/>
-      <c r="R36" s="21" t="n"/>
-      <c r="S36" s="21" t="n"/>
-      <c r="T36" s="21" t="n"/>
-      <c r="U36" s="21" t="n"/>
-      <c r="V36" s="21" t="n"/>
-      <c r="W36" s="21" t="n"/>
+      <c r="A36" s="23" t="n"/>
+      <c r="B36" s="23" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="23" t="n"/>
+      <c r="H36" s="23" t="n"/>
+      <c r="I36" s="23" t="n"/>
+      <c r="J36" s="23" t="n"/>
+      <c r="K36" s="23" t="n"/>
+      <c r="L36" s="23" t="n"/>
+      <c r="M36" s="23" t="n"/>
+      <c r="N36" s="23" t="n"/>
+      <c r="O36" s="23" t="n"/>
+      <c r="P36" s="23" t="n"/>
+      <c r="Q36" s="23" t="n"/>
+      <c r="R36" s="23" t="n"/>
+      <c r="S36" s="23" t="n"/>
+      <c r="T36" s="23" t="n"/>
+      <c r="U36" s="23" t="n"/>
+      <c r="V36" s="23" t="n"/>
+      <c r="W36" s="23" t="n"/>
+      <c r="X36" s="23" t="n"/>
+      <c r="Y36" s="23" t="n"/>
+      <c r="Z36" s="23" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="R4:T4"/>
+  <mergeCells count="9">
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="N4:R4"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A1:Z1"/>
     <mergeCell ref="U4:W4"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A2:W2"/>
-    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="S4:T4"/>
   </mergeCells>
   <dataValidations count="17">
     <dataValidation sqref="C7:C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="บริษัท" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$A$4:$A$8</formula1>
     </dataValidation>
-    <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="เวลาที่ใช้กับงานนี้ตอนนี้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="เวลาที่ใช้กับงานนี้ตอนนี้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$R$4:$R$8</formula1>
     </dataValidation>
-    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มูลค่าความเสียหาย/ของเสียต่อปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มูลค่าความเสียหาย/ของเสียต่อปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$S$4:$S$8</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="O7:O36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$B$4:$B$9</formula1>
     </dataValidation>
-    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีข้อมูลย้อนหลังนานแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="P7:P36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีข้อมูลย้อนหลังนานแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$C$4:$C$7</formula1>
     </dataValidation>
-    <dataValidation sqref="O7:O36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="สิทธิ์นำข้อมูลมาใช้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="สิทธิ์นำข้อมูลมาใช้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$D$4:$D$6</formula1>
     </dataValidation>
-    <dataValidation sqref="P7:P36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$E$4:$E$7</formula1>
     </dataValidation>
-    <dataValidation sqref="Q7:Q36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีคนดูแลระบบต่อหลังส่งมอบมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีคนดูแลระบบต่อหลังส่งมอบมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$F$4:$F$6</formula1>
     </dataValidation>
-    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ถ้า AI ตอบผิด จะเกิดอะไรขึ้น" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ถ้า AI ตอบผิด จะเกิดอะไรขึ้น" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$G$4:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="V7:V36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$H$4:$H$6</formula1>
     </dataValidation>
-    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ข้อมูลชุดนี้ลับแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="W7:W36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ข้อมูลชุดนี้ลับแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$I$4:$I$7</formula1>
     </dataValidation>
-    <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความสำคัญที่แผนกอยากได้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="X7:X36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความสำคัญที่แผนกอยากได้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$J$4:$J$6</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปัญหาที่ต้องการแก้" prompt="ตอนนี้เจอปัญหาอะไร ทำไมถึงอยากได้ AI มาช่วย&#10;เช่น ตรวจด้วยตาเปล่าทำให้ของเสียหลุดถึงลูกค้าเดือนละ 2-3 ครั้ง"/>
-    <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="วิธีการทำงานปัจจุบัน" prompt="ตอนนี้ทำงานนี้ยังไง ใครเป็นคนทำ ใช้เครื่องมืออะไร บันทึกผลไว้ที่ไหน&#10;เขียนแบบที่คนนอกแผนกอ่านแล้วเห็นภาพ"/>
-    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="แนวทางหลังนำ AI มาใช้" prompt="อยากให้ AI ทำอะไรให้ และผลลัพธ์ที่อยากได้หน้าตาเป็นยังไง&#10;เช่น ติดกล้องที่สายพาน ให้ AI แยกดี/เสียอัตโนมัติ&#10;ชิ้นที่ AI ไม่มั่นใจค่อยส่งให้คนตรวจ"/>
-    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ข้อมูลที่มีอยู่ตอนนี้" prompt="มีข้อมูลอะไรบ้าง เก็บไว้ที่ไหน ใครเป็นคนเก็บ&#10;ถ้ามีสัดส่วนที่น่าสนใจให้เขียนด้วย เช่น รูปดี 3,000 / รูปเสีย 1,000"/>
-    <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปริมาณข้อมูลโดยประมาณ" prompt="นับเป็น 'รายการ' หน่วยขึ้นกับงาน :&#10;  ตรวจภาพ = กี่รูป&#10;  หาสาเหตุ/NC = กี่เคส&#10;  ค้นหาเอกสาร = กี่ไฟล์&#10;  เครื่องเสีย = กี่ครั้ง&#10;  การผลิต = กี่ล็อต&#10;&#10;นับเฉพาะที่รู้คำตอบแล้ว เช่น รูปที่มาร์คว่าดี/เสีย&#10;(รายละเอียดเต็มอยู่ในคู่มือ)"/>
+    <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปัญหาที่ต้องการแก้" prompt="ตอนนี้เจอปัญหาอะไร ทำไมถึงอยากได้ AI มาช่วย&#10;เช่น ตรวจด้วยตาเปล่าทำให้ของเสียหลุดถึงลูกค้าเดือนละ 2-3 ครั้ง"/>
+    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="วิธีการทำงานปัจจุบัน" prompt="ตอนนี้ทำงานนี้ยังไง ใครเป็นคนทำ ใช้เครื่องมืออะไร บันทึกผลไว้ที่ไหน&#10;เขียนแบบที่คนนอกแผนกอ่านแล้วเห็นภาพ"/>
+    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="แนวทางหลังนำ AI มาใช้" prompt="อยากให้ AI ทำอะไรให้ และผลลัพธ์ที่อยากได้หน้าตาเป็นยังไง&#10;เช่น ติดกล้องที่สายพาน ให้ AI แยกดี/เสียอัตโนมัติ&#10;ชิ้นที่ AI ไม่มั่นใจค่อยส่งให้คนตรวจ"/>
+    <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ข้อมูลที่มีอยู่ตอนนี้" prompt="มีข้อมูลอะไรบ้าง เก็บไว้ที่ไหน ใครเป็นคนเก็บ&#10;ถ้ามีสัดส่วนที่น่าสนใจให้เขียนด้วย เช่น รูปดี 3,000 / รูปเสีย 1,000"/>
+    <dataValidation sqref="Q7:Q36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปริมาณข้อมูลโดยประมาณ" prompt="นับเป็น 'รายการ' หน่วยขึ้นกับงาน :&#10;  ตรวจภาพ = กี่รูป&#10;  หาสาเหตุ/NC = กี่เคส&#10;  ค้นหาเอกสาร = กี่ไฟล์&#10;  เครื่องเสีย = กี่ครั้ง&#10;  การผลิต = กี่ล็อต&#10;&#10;นับเฉพาะที่รู้คำตอบแล้ว เช่น รูปที่มาร์คว่าดี/เสีย&#10;(รายละเอียดเต็มอยู่ในคู่มือ)"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2265,7 +2398,7 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
@@ -2305,161 +2438,161 @@
       </c>
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="8" t="n"/>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>โซน A : ปริมาณงาน  (แผนกกรอก)</t>
         </is>
       </c>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>โซน A : ความต้องการใช้งาน  (แผนกกรอก)</t>
         </is>
       </c>
-      <c r="K4" s="14" t="n"/>
-      <c r="L4" s="14" t="n"/>
-      <c r="M4" s="14" t="n"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="K4" s="16" t="n"/>
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="19" t="inlineStr">
         <is>
           <t>โซน A : ข้อกำหนดและงบ  (แผนกกรอก)</t>
         </is>
       </c>
-      <c r="O4" s="18" t="n"/>
-      <c r="P4" s="18" t="n"/>
-      <c r="Q4" s="18" t="n"/>
-      <c r="R4" s="22" t="inlineStr">
+      <c r="O4" s="20" t="n"/>
+      <c r="P4" s="20" t="n"/>
+      <c r="Q4" s="20" t="n"/>
+      <c r="R4" s="9" t="inlineStr">
         <is>
           <t>โซน B : ทีม AI / IT เติมให้ทีหลัง — แผนกไม่ต้องกรอก</t>
         </is>
       </c>
-      <c r="S4" s="23" t="n"/>
-      <c r="T4" s="23" t="n"/>
-      <c r="U4" s="23" t="n"/>
-      <c r="V4" s="23" t="n"/>
-      <c r="W4" s="23" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>ชื่อ Use Case</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>ฝ่าย / แผนก</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>งานนี้เริ่มทำงานยังไง</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>ข้อมูลที่ AI ต้องอ่าน/ดู เป็นแบบไหน</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>จำนวนคนที่ใช้งาน/วัน</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>ช่วงพีค มีคนใช้พร้อมกันมากสุดกี่คน</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>AI ต้องประมวลผลกี่รายการ/วัน
-(ไม่ใช่จำนวนครั้งที่สั่งงาน)</t>
-        </is>
-      </c>
-      <c r="I5" s="19" t="inlineStr">
+1 รายการ = 1 ชิ้น / ล็อต / คำถาม / เคส แล้วแต่ประเภทงาน</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>จำนวนกล้อง/จุดตรวจ
 ที่ทำงานพร้อมกัน (งานภาพ)</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>ภาษาที่ต้องการ</t>
         </is>
       </c>
-      <c r="K5" s="19" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>รอผลได้นานแค่ไหน</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t>ต้องใช้งานช่วงเวลาไหน</t>
         </is>
       </c>
-      <c r="M5" s="19" t="inlineStr">
+      <c r="M5" s="21" t="inlineStr">
         <is>
           <t>ถ้าช่วงไหนคนใช้เยอะ แล้วงานนี้ช้าลง
 จะเป็นปัญหามั้ย</t>
         </is>
       </c>
-      <c r="N5" s="19" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
         </is>
       </c>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="O5" s="21" t="inlineStr">
         <is>
           <t>งบประมาณที่ตั้งไว้ (บาท)
 - ถ้ามี</t>
         </is>
       </c>
-      <c r="P5" s="19" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t>ข้อจำกัดอื่นๆ / หมายเหตุ</t>
         </is>
       </c>
-      <c r="Q5" s="19" t="inlineStr">
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>ผู้ให้ข้อมูล (แผนก)</t>
         </is>
       </c>
-      <c r="R5" s="19" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t>ขนาดข้อมูล Input/วัน</t>
         </is>
       </c>
-      <c r="S5" s="19" t="inlineStr">
+      <c r="S5" s="21" t="inlineStr">
         <is>
           <t>ขนาดคลังเอกสารทั้งหมด
 (สำหรับงานค้นหา/RAG)</t>
         </is>
       </c>
-      <c r="T5" s="19" t="inlineStr">
+      <c r="T5" s="21" t="inlineStr">
         <is>
           <t>ความละเอียดรูป</t>
         </is>
       </c>
-      <c r="U5" s="19" t="inlineStr">
+      <c r="U5" s="21" t="inlineStr">
         <is>
           <t>ติดตั้งแบบไหน
 (server ตั้งที่เดียว ไม่ใช้ Cloud)</t>
         </is>
       </c>
-      <c r="V5" s="19" t="inlineStr">
+      <c r="V5" s="21" t="inlineStr">
         <is>
           <t>ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย</t>
         </is>
       </c>
-      <c r="W5" s="19" t="inlineStr">
+      <c r="W5" s="21" t="inlineStr">
         <is>
           <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
         </is>
@@ -2478,70 +2611,70 @@
         <f>IF('1-UseCase ทั้งหมด'!B6="","",'1-UseCase ทั้งหมด'!D6)</f>
         <v/>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>ทำงานอัตโนมัติต่อเนื่อง - ระบบสั่งเอง ไม่มีคนกด</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>รูปภาพ</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>1 - 10 คน</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>1 - 2 คน</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>1,000 - 10,000 รายการ</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>1,000 - 10,000 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>2 - 3 จุด</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>ไม่เกี่ยวกับภาษา</t>
         </is>
       </c>
-      <c r="K6" s="20" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>Real-time (0 - 2 วินาที)</t>
         </is>
       </c>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>Business Hour (8:00 - 18:00)</t>
         </is>
       </c>
-      <c r="M6" s="20" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t>เป็นปัญหา - งานนี้ช้าหรือหยุดไม่ได้เลย (อยู่ในสายการผลิต)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr">
+      <c r="N6" s="22" t="inlineStr">
         <is>
           <t>2 - 3 ปี</t>
         </is>
       </c>
-      <c r="O6" s="20" t="n">
+      <c r="O6" s="22" t="n">
         <v>500000</v>
       </c>
-      <c r="P6" s="20" t="inlineStr">
+      <c r="P6" s="22" t="inlineStr">
         <is>
           <t>ต้องติดกล้องที่สายพานเดิม มีพื้นที่จำกัด</t>
         </is>
       </c>
-      <c r="Q6" s="20" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t>คุณสมชาย</t>
         </is>
@@ -2590,20 +2723,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B7="","",'1-UseCase ทั้งหมด'!D7)</f>
         <v/>
       </c>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="21" t="n"/>
-      <c r="P7" s="21" t="n"/>
-      <c r="Q7" s="21" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="23" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="23" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
       <c r="R7" s="27" t="n"/>
       <c r="S7" s="27" t="n"/>
       <c r="T7" s="27" t="n"/>
@@ -2624,20 +2757,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B8="","",'1-UseCase ทั้งหมด'!D8)</f>
         <v/>
       </c>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="21" t="n"/>
-      <c r="G8" s="21" t="n"/>
-      <c r="H8" s="21" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
-      <c r="P8" s="21" t="n"/>
-      <c r="Q8" s="21" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="23" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="23" t="n"/>
+      <c r="M8" s="23" t="n"/>
+      <c r="N8" s="23" t="n"/>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="23" t="n"/>
+      <c r="Q8" s="23" t="n"/>
       <c r="R8" s="27" t="n"/>
       <c r="S8" s="27" t="n"/>
       <c r="T8" s="27" t="n"/>
@@ -2658,20 +2791,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B9="","",'1-UseCase ทั้งหมด'!D9)</f>
         <v/>
       </c>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="21" t="n"/>
-      <c r="P9" s="21" t="n"/>
-      <c r="Q9" s="21" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="23" t="n"/>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="23" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="n"/>
+      <c r="Q9" s="23" t="n"/>
       <c r="R9" s="27" t="n"/>
       <c r="S9" s="27" t="n"/>
       <c r="T9" s="27" t="n"/>
@@ -2692,20 +2825,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B10="","",'1-UseCase ทั้งหมด'!D10)</f>
         <v/>
       </c>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="21" t="n"/>
-      <c r="M10" s="21" t="n"/>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="21" t="n"/>
-      <c r="P10" s="21" t="n"/>
-      <c r="Q10" s="21" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="23" t="n"/>
+      <c r="L10" s="23" t="n"/>
+      <c r="M10" s="23" t="n"/>
+      <c r="N10" s="23" t="n"/>
+      <c r="O10" s="23" t="n"/>
+      <c r="P10" s="23" t="n"/>
+      <c r="Q10" s="23" t="n"/>
       <c r="R10" s="27" t="n"/>
       <c r="S10" s="27" t="n"/>
       <c r="T10" s="27" t="n"/>
@@ -2726,20 +2859,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B11="","",'1-UseCase ทั้งหมด'!D11)</f>
         <v/>
       </c>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="21" t="n"/>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="21" t="n"/>
-      <c r="P11" s="21" t="n"/>
-      <c r="Q11" s="21" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="23" t="n"/>
+      <c r="M11" s="23" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="23" t="n"/>
       <c r="R11" s="27" t="n"/>
       <c r="S11" s="27" t="n"/>
       <c r="T11" s="27" t="n"/>
@@ -2760,20 +2893,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B12="","",'1-UseCase ทั้งหมด'!D12)</f>
         <v/>
       </c>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="21" t="n"/>
-      <c r="P12" s="21" t="n"/>
-      <c r="Q12" s="21" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="23" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="23" t="n"/>
+      <c r="L12" s="23" t="n"/>
+      <c r="M12" s="23" t="n"/>
+      <c r="N12" s="23" t="n"/>
+      <c r="O12" s="23" t="n"/>
+      <c r="P12" s="23" t="n"/>
+      <c r="Q12" s="23" t="n"/>
       <c r="R12" s="27" t="n"/>
       <c r="S12" s="27" t="n"/>
       <c r="T12" s="27" t="n"/>
@@ -2794,20 +2927,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B13="","",'1-UseCase ทั้งหมด'!D13)</f>
         <v/>
       </c>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="21" t="n"/>
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="21" t="n"/>
-      <c r="P13" s="21" t="n"/>
-      <c r="Q13" s="21" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="23" t="n"/>
+      <c r="I13" s="23" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="23" t="n"/>
+      <c r="L13" s="23" t="n"/>
+      <c r="M13" s="23" t="n"/>
+      <c r="N13" s="23" t="n"/>
+      <c r="O13" s="23" t="n"/>
+      <c r="P13" s="23" t="n"/>
+      <c r="Q13" s="23" t="n"/>
       <c r="R13" s="27" t="n"/>
       <c r="S13" s="27" t="n"/>
       <c r="T13" s="27" t="n"/>
@@ -2828,20 +2961,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B14="","",'1-UseCase ทั้งหมด'!D14)</f>
         <v/>
       </c>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="21" t="n"/>
-      <c r="P14" s="21" t="n"/>
-      <c r="Q14" s="21" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="23" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="23" t="n"/>
+      <c r="I14" s="23" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="23" t="n"/>
+      <c r="M14" s="23" t="n"/>
+      <c r="N14" s="23" t="n"/>
+      <c r="O14" s="23" t="n"/>
+      <c r="P14" s="23" t="n"/>
+      <c r="Q14" s="23" t="n"/>
       <c r="R14" s="27" t="n"/>
       <c r="S14" s="27" t="n"/>
       <c r="T14" s="27" t="n"/>
@@ -2862,20 +2995,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B15="","",'1-UseCase ทั้งหมด'!D15)</f>
         <v/>
       </c>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="21" t="n"/>
-      <c r="P15" s="21" t="n"/>
-      <c r="Q15" s="21" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="23" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
       <c r="R15" s="27" t="n"/>
       <c r="S15" s="27" t="n"/>
       <c r="T15" s="27" t="n"/>
@@ -2896,20 +3029,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B16="","",'1-UseCase ทั้งหมด'!D16)</f>
         <v/>
       </c>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="21" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="n"/>
+      <c r="I16" s="23" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="23" t="n"/>
+      <c r="L16" s="23" t="n"/>
+      <c r="M16" s="23" t="n"/>
+      <c r="N16" s="23" t="n"/>
+      <c r="O16" s="23" t="n"/>
+      <c r="P16" s="23" t="n"/>
+      <c r="Q16" s="23" t="n"/>
       <c r="R16" s="27" t="n"/>
       <c r="S16" s="27" t="n"/>
       <c r="T16" s="27" t="n"/>
@@ -2930,20 +3063,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B17="","",'1-UseCase ทั้งหมด'!D17)</f>
         <v/>
       </c>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="21" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="23" t="n"/>
+      <c r="I17" s="23" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="23" t="n"/>
+      <c r="L17" s="23" t="n"/>
+      <c r="M17" s="23" t="n"/>
+      <c r="N17" s="23" t="n"/>
+      <c r="O17" s="23" t="n"/>
+      <c r="P17" s="23" t="n"/>
+      <c r="Q17" s="23" t="n"/>
       <c r="R17" s="27" t="n"/>
       <c r="S17" s="27" t="n"/>
       <c r="T17" s="27" t="n"/>
@@ -2964,20 +3097,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B18="","",'1-UseCase ทั้งหมด'!D18)</f>
         <v/>
       </c>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
-      <c r="P18" s="21" t="n"/>
-      <c r="Q18" s="21" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="n"/>
+      <c r="I18" s="23" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="23" t="n"/>
+      <c r="L18" s="23" t="n"/>
+      <c r="M18" s="23" t="n"/>
+      <c r="N18" s="23" t="n"/>
+      <c r="O18" s="23" t="n"/>
+      <c r="P18" s="23" t="n"/>
+      <c r="Q18" s="23" t="n"/>
       <c r="R18" s="27" t="n"/>
       <c r="S18" s="27" t="n"/>
       <c r="T18" s="27" t="n"/>
@@ -2998,20 +3131,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B19="","",'1-UseCase ทั้งหมด'!D19)</f>
         <v/>
       </c>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
-      <c r="F19" s="21" t="n"/>
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="21" t="n"/>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
-      <c r="P19" s="21" t="n"/>
-      <c r="Q19" s="21" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="23" t="n"/>
+      <c r="I19" s="23" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="23" t="n"/>
+      <c r="L19" s="23" t="n"/>
+      <c r="M19" s="23" t="n"/>
+      <c r="N19" s="23" t="n"/>
+      <c r="O19" s="23" t="n"/>
+      <c r="P19" s="23" t="n"/>
+      <c r="Q19" s="23" t="n"/>
       <c r="R19" s="27" t="n"/>
       <c r="S19" s="27" t="n"/>
       <c r="T19" s="27" t="n"/>
@@ -3032,20 +3165,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B20="","",'1-UseCase ทั้งหมด'!D20)</f>
         <v/>
       </c>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="21" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="23" t="n"/>
+      <c r="I20" s="23" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="23" t="n"/>
+      <c r="L20" s="23" t="n"/>
+      <c r="M20" s="23" t="n"/>
+      <c r="N20" s="23" t="n"/>
+      <c r="O20" s="23" t="n"/>
+      <c r="P20" s="23" t="n"/>
+      <c r="Q20" s="23" t="n"/>
       <c r="R20" s="27" t="n"/>
       <c r="S20" s="27" t="n"/>
       <c r="T20" s="27" t="n"/>
@@ -3066,20 +3199,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B21="","",'1-UseCase ทั้งหมด'!D21)</f>
         <v/>
       </c>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="21" t="n"/>
-      <c r="G21" s="21" t="n"/>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="21" t="n"/>
-      <c r="K21" s="21" t="n"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="21" t="n"/>
-      <c r="P21" s="21" t="n"/>
-      <c r="Q21" s="21" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="23" t="n"/>
+      <c r="I21" s="23" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="23" t="n"/>
+      <c r="L21" s="23" t="n"/>
+      <c r="M21" s="23" t="n"/>
+      <c r="N21" s="23" t="n"/>
+      <c r="O21" s="23" t="n"/>
+      <c r="P21" s="23" t="n"/>
+      <c r="Q21" s="23" t="n"/>
       <c r="R21" s="27" t="n"/>
       <c r="S21" s="27" t="n"/>
       <c r="T21" s="27" t="n"/>
@@ -3100,20 +3233,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B22="","",'1-UseCase ทั้งหมด'!D22)</f>
         <v/>
       </c>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
-      <c r="F22" s="21" t="n"/>
-      <c r="G22" s="21" t="n"/>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
-      <c r="P22" s="21" t="n"/>
-      <c r="Q22" s="21" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="23" t="n"/>
+      <c r="L22" s="23" t="n"/>
+      <c r="M22" s="23" t="n"/>
+      <c r="N22" s="23" t="n"/>
+      <c r="O22" s="23" t="n"/>
+      <c r="P22" s="23" t="n"/>
+      <c r="Q22" s="23" t="n"/>
       <c r="R22" s="27" t="n"/>
       <c r="S22" s="27" t="n"/>
       <c r="T22" s="27" t="n"/>
@@ -3134,20 +3267,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B23="","",'1-UseCase ทั้งหมด'!D23)</f>
         <v/>
       </c>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="F23" s="21" t="n"/>
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
-      <c r="K23" s="21" t="n"/>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="21" t="n"/>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="21" t="n"/>
-      <c r="P23" s="21" t="n"/>
-      <c r="Q23" s="21" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="23" t="n"/>
+      <c r="I23" s="23" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="23" t="n"/>
+      <c r="L23" s="23" t="n"/>
+      <c r="M23" s="23" t="n"/>
+      <c r="N23" s="23" t="n"/>
+      <c r="O23" s="23" t="n"/>
+      <c r="P23" s="23" t="n"/>
+      <c r="Q23" s="23" t="n"/>
       <c r="R23" s="27" t="n"/>
       <c r="S23" s="27" t="n"/>
       <c r="T23" s="27" t="n"/>
@@ -3168,20 +3301,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B24="","",'1-UseCase ทั้งหมด'!D24)</f>
         <v/>
       </c>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
-      <c r="P24" s="21" t="n"/>
-      <c r="Q24" s="21" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="23" t="n"/>
+      <c r="H24" s="23" t="n"/>
+      <c r="I24" s="23" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="23" t="n"/>
+      <c r="L24" s="23" t="n"/>
+      <c r="M24" s="23" t="n"/>
+      <c r="N24" s="23" t="n"/>
+      <c r="O24" s="23" t="n"/>
+      <c r="P24" s="23" t="n"/>
+      <c r="Q24" s="23" t="n"/>
       <c r="R24" s="27" t="n"/>
       <c r="S24" s="27" t="n"/>
       <c r="T24" s="27" t="n"/>
@@ -3202,20 +3335,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B25="","",'1-UseCase ทั้งหมด'!D25)</f>
         <v/>
       </c>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="21" t="n"/>
-      <c r="K25" s="21" t="n"/>
-      <c r="L25" s="21" t="n"/>
-      <c r="M25" s="21" t="n"/>
-      <c r="N25" s="21" t="n"/>
-      <c r="O25" s="21" t="n"/>
-      <c r="P25" s="21" t="n"/>
-      <c r="Q25" s="21" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="23" t="n"/>
+      <c r="I25" s="23" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="23" t="n"/>
+      <c r="L25" s="23" t="n"/>
+      <c r="M25" s="23" t="n"/>
+      <c r="N25" s="23" t="n"/>
+      <c r="O25" s="23" t="n"/>
+      <c r="P25" s="23" t="n"/>
+      <c r="Q25" s="23" t="n"/>
       <c r="R25" s="27" t="n"/>
       <c r="S25" s="27" t="n"/>
       <c r="T25" s="27" t="n"/>
@@ -3236,20 +3369,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B26="","",'1-UseCase ทั้งหมด'!D26)</f>
         <v/>
       </c>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="21" t="n"/>
-      <c r="K26" s="21" t="n"/>
-      <c r="L26" s="21" t="n"/>
-      <c r="M26" s="21" t="n"/>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="21" t="n"/>
-      <c r="P26" s="21" t="n"/>
-      <c r="Q26" s="21" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="23" t="n"/>
+      <c r="L26" s="23" t="n"/>
+      <c r="M26" s="23" t="n"/>
+      <c r="N26" s="23" t="n"/>
+      <c r="O26" s="23" t="n"/>
+      <c r="P26" s="23" t="n"/>
+      <c r="Q26" s="23" t="n"/>
       <c r="R26" s="27" t="n"/>
       <c r="S26" s="27" t="n"/>
       <c r="T26" s="27" t="n"/>
@@ -3270,20 +3403,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B27="","",'1-UseCase ทั้งหมด'!D27)</f>
         <v/>
       </c>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
-      <c r="F27" s="21" t="n"/>
-      <c r="G27" s="21" t="n"/>
-      <c r="H27" s="21" t="n"/>
-      <c r="I27" s="21" t="n"/>
-      <c r="J27" s="21" t="n"/>
-      <c r="K27" s="21" t="n"/>
-      <c r="L27" s="21" t="n"/>
-      <c r="M27" s="21" t="n"/>
-      <c r="N27" s="21" t="n"/>
-      <c r="O27" s="21" t="n"/>
-      <c r="P27" s="21" t="n"/>
-      <c r="Q27" s="21" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="23" t="n"/>
+      <c r="H27" s="23" t="n"/>
+      <c r="I27" s="23" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="23" t="n"/>
+      <c r="L27" s="23" t="n"/>
+      <c r="M27" s="23" t="n"/>
+      <c r="N27" s="23" t="n"/>
+      <c r="O27" s="23" t="n"/>
+      <c r="P27" s="23" t="n"/>
+      <c r="Q27" s="23" t="n"/>
       <c r="R27" s="27" t="n"/>
       <c r="S27" s="27" t="n"/>
       <c r="T27" s="27" t="n"/>
@@ -3304,20 +3437,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B28="","",'1-UseCase ทั้งหมด'!D28)</f>
         <v/>
       </c>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="21" t="n"/>
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="21" t="n"/>
-      <c r="I28" s="21" t="n"/>
-      <c r="J28" s="21" t="n"/>
-      <c r="K28" s="21" t="n"/>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="21" t="n"/>
-      <c r="N28" s="21" t="n"/>
-      <c r="O28" s="21" t="n"/>
-      <c r="P28" s="21" t="n"/>
-      <c r="Q28" s="21" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="23" t="n"/>
+      <c r="H28" s="23" t="n"/>
+      <c r="I28" s="23" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="23" t="n"/>
+      <c r="L28" s="23" t="n"/>
+      <c r="M28" s="23" t="n"/>
+      <c r="N28" s="23" t="n"/>
+      <c r="O28" s="23" t="n"/>
+      <c r="P28" s="23" t="n"/>
+      <c r="Q28" s="23" t="n"/>
       <c r="R28" s="27" t="n"/>
       <c r="S28" s="27" t="n"/>
       <c r="T28" s="27" t="n"/>
@@ -3338,20 +3471,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B29="","",'1-UseCase ทั้งหมด'!D29)</f>
         <v/>
       </c>
-      <c r="D29" s="21" t="n"/>
-      <c r="E29" s="21" t="n"/>
-      <c r="F29" s="21" t="n"/>
-      <c r="G29" s="21" t="n"/>
-      <c r="H29" s="21" t="n"/>
-      <c r="I29" s="21" t="n"/>
-      <c r="J29" s="21" t="n"/>
-      <c r="K29" s="21" t="n"/>
-      <c r="L29" s="21" t="n"/>
-      <c r="M29" s="21" t="n"/>
-      <c r="N29" s="21" t="n"/>
-      <c r="O29" s="21" t="n"/>
-      <c r="P29" s="21" t="n"/>
-      <c r="Q29" s="21" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="23" t="n"/>
+      <c r="I29" s="23" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="23" t="n"/>
+      <c r="L29" s="23" t="n"/>
+      <c r="M29" s="23" t="n"/>
+      <c r="N29" s="23" t="n"/>
+      <c r="O29" s="23" t="n"/>
+      <c r="P29" s="23" t="n"/>
+      <c r="Q29" s="23" t="n"/>
       <c r="R29" s="27" t="n"/>
       <c r="S29" s="27" t="n"/>
       <c r="T29" s="27" t="n"/>
@@ -3372,20 +3505,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B30="","",'1-UseCase ทั้งหมด'!D30)</f>
         <v/>
       </c>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="21" t="n"/>
-      <c r="G30" s="21" t="n"/>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
-      <c r="J30" s="21" t="n"/>
-      <c r="K30" s="21" t="n"/>
-      <c r="L30" s="21" t="n"/>
-      <c r="M30" s="21" t="n"/>
-      <c r="N30" s="21" t="n"/>
-      <c r="O30" s="21" t="n"/>
-      <c r="P30" s="21" t="n"/>
-      <c r="Q30" s="21" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="23" t="n"/>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="23" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="23" t="n"/>
+      <c r="O30" s="23" t="n"/>
+      <c r="P30" s="23" t="n"/>
+      <c r="Q30" s="23" t="n"/>
       <c r="R30" s="27" t="n"/>
       <c r="S30" s="27" t="n"/>
       <c r="T30" s="27" t="n"/>
@@ -3406,20 +3539,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B31="","",'1-UseCase ทั้งหมด'!D31)</f>
         <v/>
       </c>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="21" t="n"/>
-      <c r="F31" s="21" t="n"/>
-      <c r="G31" s="21" t="n"/>
-      <c r="H31" s="21" t="n"/>
-      <c r="I31" s="21" t="n"/>
-      <c r="J31" s="21" t="n"/>
-      <c r="K31" s="21" t="n"/>
-      <c r="L31" s="21" t="n"/>
-      <c r="M31" s="21" t="n"/>
-      <c r="N31" s="21" t="n"/>
-      <c r="O31" s="21" t="n"/>
-      <c r="P31" s="21" t="n"/>
-      <c r="Q31" s="21" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="23" t="n"/>
+      <c r="H31" s="23" t="n"/>
+      <c r="I31" s="23" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="23" t="n"/>
+      <c r="L31" s="23" t="n"/>
+      <c r="M31" s="23" t="n"/>
+      <c r="N31" s="23" t="n"/>
+      <c r="O31" s="23" t="n"/>
+      <c r="P31" s="23" t="n"/>
+      <c r="Q31" s="23" t="n"/>
       <c r="R31" s="27" t="n"/>
       <c r="S31" s="27" t="n"/>
       <c r="T31" s="27" t="n"/>
@@ -3440,20 +3573,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B32="","",'1-UseCase ทั้งหมด'!D32)</f>
         <v/>
       </c>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="21" t="n"/>
-      <c r="G32" s="21" t="n"/>
-      <c r="H32" s="21" t="n"/>
-      <c r="I32" s="21" t="n"/>
-      <c r="J32" s="21" t="n"/>
-      <c r="K32" s="21" t="n"/>
-      <c r="L32" s="21" t="n"/>
-      <c r="M32" s="21" t="n"/>
-      <c r="N32" s="21" t="n"/>
-      <c r="O32" s="21" t="n"/>
-      <c r="P32" s="21" t="n"/>
-      <c r="Q32" s="21" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="23" t="n"/>
+      <c r="H32" s="23" t="n"/>
+      <c r="I32" s="23" t="n"/>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="23" t="n"/>
+      <c r="L32" s="23" t="n"/>
+      <c r="M32" s="23" t="n"/>
+      <c r="N32" s="23" t="n"/>
+      <c r="O32" s="23" t="n"/>
+      <c r="P32" s="23" t="n"/>
+      <c r="Q32" s="23" t="n"/>
       <c r="R32" s="27" t="n"/>
       <c r="S32" s="27" t="n"/>
       <c r="T32" s="27" t="n"/>
@@ -3474,20 +3607,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B33="","",'1-UseCase ทั้งหมด'!D33)</f>
         <v/>
       </c>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-      <c r="I33" s="21" t="n"/>
-      <c r="J33" s="21" t="n"/>
-      <c r="K33" s="21" t="n"/>
-      <c r="L33" s="21" t="n"/>
-      <c r="M33" s="21" t="n"/>
-      <c r="N33" s="21" t="n"/>
-      <c r="O33" s="21" t="n"/>
-      <c r="P33" s="21" t="n"/>
-      <c r="Q33" s="21" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="23" t="n"/>
+      <c r="I33" s="23" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="23" t="n"/>
+      <c r="L33" s="23" t="n"/>
+      <c r="M33" s="23" t="n"/>
+      <c r="N33" s="23" t="n"/>
+      <c r="O33" s="23" t="n"/>
+      <c r="P33" s="23" t="n"/>
+      <c r="Q33" s="23" t="n"/>
       <c r="R33" s="27" t="n"/>
       <c r="S33" s="27" t="n"/>
       <c r="T33" s="27" t="n"/>
@@ -3508,20 +3641,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B34="","",'1-UseCase ทั้งหมด'!D34)</f>
         <v/>
       </c>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="21" t="n"/>
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="21" t="n"/>
-      <c r="I34" s="21" t="n"/>
-      <c r="J34" s="21" t="n"/>
-      <c r="K34" s="21" t="n"/>
-      <c r="L34" s="21" t="n"/>
-      <c r="M34" s="21" t="n"/>
-      <c r="N34" s="21" t="n"/>
-      <c r="O34" s="21" t="n"/>
-      <c r="P34" s="21" t="n"/>
-      <c r="Q34" s="21" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="23" t="n"/>
+      <c r="I34" s="23" t="n"/>
+      <c r="J34" s="23" t="n"/>
+      <c r="K34" s="23" t="n"/>
+      <c r="L34" s="23" t="n"/>
+      <c r="M34" s="23" t="n"/>
+      <c r="N34" s="23" t="n"/>
+      <c r="O34" s="23" t="n"/>
+      <c r="P34" s="23" t="n"/>
+      <c r="Q34" s="23" t="n"/>
       <c r="R34" s="27" t="n"/>
       <c r="S34" s="27" t="n"/>
       <c r="T34" s="27" t="n"/>
@@ -3542,20 +3675,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B35="","",'1-UseCase ทั้งหมด'!D35)</f>
         <v/>
       </c>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="21" t="n"/>
-      <c r="F35" s="21" t="n"/>
-      <c r="G35" s="21" t="n"/>
-      <c r="H35" s="21" t="n"/>
-      <c r="I35" s="21" t="n"/>
-      <c r="J35" s="21" t="n"/>
-      <c r="K35" s="21" t="n"/>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="21" t="n"/>
-      <c r="O35" s="21" t="n"/>
-      <c r="P35" s="21" t="n"/>
-      <c r="Q35" s="21" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="23" t="n"/>
+      <c r="I35" s="23" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="23" t="n"/>
+      <c r="L35" s="23" t="n"/>
+      <c r="M35" s="23" t="n"/>
+      <c r="N35" s="23" t="n"/>
+      <c r="O35" s="23" t="n"/>
+      <c r="P35" s="23" t="n"/>
+      <c r="Q35" s="23" t="n"/>
       <c r="R35" s="27" t="n"/>
       <c r="S35" s="27" t="n"/>
       <c r="T35" s="27" t="n"/>
@@ -3576,20 +3709,20 @@
         <f>IF('1-UseCase ทั้งหมด'!B36="","",'1-UseCase ทั้งหมด'!D36)</f>
         <v/>
       </c>
-      <c r="D36" s="21" t="n"/>
-      <c r="E36" s="21" t="n"/>
-      <c r="F36" s="21" t="n"/>
-      <c r="G36" s="21" t="n"/>
-      <c r="H36" s="21" t="n"/>
-      <c r="I36" s="21" t="n"/>
-      <c r="J36" s="21" t="n"/>
-      <c r="K36" s="21" t="n"/>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="21" t="n"/>
-      <c r="N36" s="21" t="n"/>
-      <c r="O36" s="21" t="n"/>
-      <c r="P36" s="21" t="n"/>
-      <c r="Q36" s="21" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="23" t="n"/>
+      <c r="H36" s="23" t="n"/>
+      <c r="I36" s="23" t="n"/>
+      <c r="J36" s="23" t="n"/>
+      <c r="K36" s="23" t="n"/>
+      <c r="L36" s="23" t="n"/>
+      <c r="M36" s="23" t="n"/>
+      <c r="N36" s="23" t="n"/>
+      <c r="O36" s="23" t="n"/>
+      <c r="P36" s="23" t="n"/>
+      <c r="Q36" s="23" t="n"/>
       <c r="R36" s="27" t="n"/>
       <c r="S36" s="27" t="n"/>
       <c r="T36" s="27" t="n"/>
@@ -3723,36 +3856,36 @@
       </c>
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="8" t="n"/>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Impact 35%</t>
         </is>
       </c>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Data 25%</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="n"/>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="inlineStr">
         <is>
           <t>Feasibility 25%</t>
         </is>
       </c>
-      <c r="L4" s="14" t="n"/>
-      <c r="M4" s="14" t="n"/>
-      <c r="N4" s="15" t="inlineStr">
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="17" t="inlineStr">
         <is>
           <t>Risk 15% (กลับด้าน)</t>
         </is>
       </c>
-      <c r="O4" s="16" t="n"/>
-      <c r="P4" s="16" t="n"/>
-      <c r="Q4" s="16" t="n"/>
+      <c r="O4" s="18" t="n"/>
+      <c r="P4" s="18" t="n"/>
+      <c r="Q4" s="18" t="n"/>
       <c r="R4" s="28" t="inlineStr">
         <is>
           <t>ผลลัพธ์</t>
@@ -3763,117 +3896,117 @@
       <c r="U4" s="29" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>ชื่อ Use Case</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>ฝ่าย / แผนก</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>ชม./สัปดาห์
 -&gt; คะแนน</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>มูลค่าเสียหาย
 -&gt; คะแนน</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>Impact
 (1-5)</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>รูปแบบ
 ข้อมูล</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>ย้อนหลัง</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>สิทธิ์ใช้
 ข้อมูล</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>Data
 (1-5)</t>
         </is>
       </c>
-      <c r="K5" s="19" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>ระบบเดิม</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t>คนดูแล
 ต่อ</t>
         </is>
       </c>
-      <c r="M5" s="19" t="inlineStr">
+      <c r="M5" s="21" t="inlineStr">
         <is>
           <t>Feasibility
 (1-5)</t>
         </is>
       </c>
-      <c r="N5" s="19" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t>AI ผิด</t>
         </is>
       </c>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="O5" s="21" t="inlineStr">
         <is>
           <t>ตรวจซ้ำ</t>
         </is>
       </c>
-      <c r="P5" s="19" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t>ความลับ</t>
         </is>
       </c>
-      <c r="Q5" s="19" t="inlineStr">
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>Risk
 (1-5)</t>
         </is>
       </c>
-      <c r="R5" s="19" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t>คะแนนรวม
 (20-100)</t>
         </is>
       </c>
-      <c r="S5" s="19" t="inlineStr">
+      <c r="S5" s="21" t="inlineStr">
         <is>
           <t>ระดับ</t>
         </is>
       </c>
-      <c r="T5" s="19" t="inlineStr">
+      <c r="T5" s="21" t="inlineStr">
         <is>
           <t>อันดับ</t>
         </is>
       </c>
-      <c r="U5" s="19" t="inlineStr">
+      <c r="U5" s="21" t="inlineStr">
         <is>
           <t>ช่องบังคับที่ยัง
 ไม่ได้กรอก
@@ -3895,11 +4028,11 @@
         <v/>
       </c>
       <c r="D6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I6,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L6,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J6,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M6,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F6" s="32">
@@ -3907,15 +4040,15 @@
         <v/>
       </c>
       <c r="G6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L6,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O6,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M6,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P6,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O6,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R6,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J6" s="32">
@@ -3923,11 +4056,11 @@
         <v/>
       </c>
       <c r="K6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P6,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S6,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q6,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T6,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M6" s="32">
@@ -3935,15 +4068,15 @@
         <v/>
       </c>
       <c r="N6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R6,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U6,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S6,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V6,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T6,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W6,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q6" s="32">
@@ -3964,7 +4097,7 @@
         </is>
       </c>
       <c r="U6" s="31">
-        <f>IF('1-UseCase ทั้งหมด'!B6="","",COUNTBLANK('1-UseCase ทั้งหมด'!I6)+COUNTBLANK('1-UseCase ทั้งหมด'!J6)+COUNTBLANK('1-UseCase ทั้งหมด'!L6)+COUNTBLANK('1-UseCase ทั้งหมด'!M6)+COUNTBLANK('1-UseCase ทั้งหมด'!O6)+COUNTBLANK('1-UseCase ทั้งหมด'!P6)+COUNTBLANK('1-UseCase ทั้งหมด'!Q6)+COUNTBLANK('1-UseCase ทั้งหมด'!R6)+COUNTBLANK('1-UseCase ทั้งหมด'!S6)+COUNTBLANK('1-UseCase ทั้งหมด'!T6))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B6="","",COUNTBLANK('1-UseCase ทั้งหมด'!L6)+COUNTBLANK('1-UseCase ทั้งหมด'!M6)+COUNTBLANK('1-UseCase ทั้งหมด'!O6)+COUNTBLANK('1-UseCase ทั้งหมด'!P6)+COUNTBLANK('1-UseCase ทั้งหมด'!R6)+COUNTBLANK('1-UseCase ทั้งหมด'!S6)+COUNTBLANK('1-UseCase ทั้งหมด'!T6)+COUNTBLANK('1-UseCase ทั้งหมด'!U6)+COUNTBLANK('1-UseCase ทั้งหมด'!V6)+COUNTBLANK('1-UseCase ทั้งหมด'!W6))</f>
         <v/>
       </c>
     </row>
@@ -3982,11 +4115,11 @@
         <v/>
       </c>
       <c r="D7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I7,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L7,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J7,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M7,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F7" s="35">
@@ -3994,15 +4127,15 @@
         <v/>
       </c>
       <c r="G7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L7,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O7,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M7,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P7,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O7,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R7,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J7" s="35">
@@ -4010,11 +4143,11 @@
         <v/>
       </c>
       <c r="K7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P7,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S7,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q7,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T7,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M7" s="35">
@@ -4022,15 +4155,15 @@
         <v/>
       </c>
       <c r="N7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R7,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U7,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S7,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V7,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T7,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W7,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q7" s="35">
@@ -4050,7 +4183,7 @@
         <v/>
       </c>
       <c r="U7" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B7="","",COUNTBLANK('1-UseCase ทั้งหมด'!I7)+COUNTBLANK('1-UseCase ทั้งหมด'!J7)+COUNTBLANK('1-UseCase ทั้งหมด'!L7)+COUNTBLANK('1-UseCase ทั้งหมด'!M7)+COUNTBLANK('1-UseCase ทั้งหมด'!O7)+COUNTBLANK('1-UseCase ทั้งหมด'!P7)+COUNTBLANK('1-UseCase ทั้งหมด'!Q7)+COUNTBLANK('1-UseCase ทั้งหมด'!R7)+COUNTBLANK('1-UseCase ทั้งหมด'!S7)+COUNTBLANK('1-UseCase ทั้งหมด'!T7))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B7="","",COUNTBLANK('1-UseCase ทั้งหมด'!L7)+COUNTBLANK('1-UseCase ทั้งหมด'!M7)+COUNTBLANK('1-UseCase ทั้งหมด'!O7)+COUNTBLANK('1-UseCase ทั้งหมด'!P7)+COUNTBLANK('1-UseCase ทั้งหมด'!R7)+COUNTBLANK('1-UseCase ทั้งหมด'!S7)+COUNTBLANK('1-UseCase ทั้งหมด'!T7)+COUNTBLANK('1-UseCase ทั้งหมด'!U7)+COUNTBLANK('1-UseCase ทั้งหมด'!V7)+COUNTBLANK('1-UseCase ทั้งหมด'!W7))</f>
         <v/>
       </c>
     </row>
@@ -4068,11 +4201,11 @@
         <v/>
       </c>
       <c r="D8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I8,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L8,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J8,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M8,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F8" s="35">
@@ -4080,15 +4213,15 @@
         <v/>
       </c>
       <c r="G8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L8,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O8,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M8,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P8,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O8,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R8,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J8" s="35">
@@ -4096,11 +4229,11 @@
         <v/>
       </c>
       <c r="K8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P8,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S8,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q8,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T8,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M8" s="35">
@@ -4108,15 +4241,15 @@
         <v/>
       </c>
       <c r="N8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R8,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U8,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S8,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V8,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T8,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W8,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q8" s="35">
@@ -4136,7 +4269,7 @@
         <v/>
       </c>
       <c r="U8" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B8="","",COUNTBLANK('1-UseCase ทั้งหมด'!I8)+COUNTBLANK('1-UseCase ทั้งหมด'!J8)+COUNTBLANK('1-UseCase ทั้งหมด'!L8)+COUNTBLANK('1-UseCase ทั้งหมด'!M8)+COUNTBLANK('1-UseCase ทั้งหมด'!O8)+COUNTBLANK('1-UseCase ทั้งหมด'!P8)+COUNTBLANK('1-UseCase ทั้งหมด'!Q8)+COUNTBLANK('1-UseCase ทั้งหมด'!R8)+COUNTBLANK('1-UseCase ทั้งหมด'!S8)+COUNTBLANK('1-UseCase ทั้งหมด'!T8))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B8="","",COUNTBLANK('1-UseCase ทั้งหมด'!L8)+COUNTBLANK('1-UseCase ทั้งหมด'!M8)+COUNTBLANK('1-UseCase ทั้งหมด'!O8)+COUNTBLANK('1-UseCase ทั้งหมด'!P8)+COUNTBLANK('1-UseCase ทั้งหมด'!R8)+COUNTBLANK('1-UseCase ทั้งหมด'!S8)+COUNTBLANK('1-UseCase ทั้งหมด'!T8)+COUNTBLANK('1-UseCase ทั้งหมด'!U8)+COUNTBLANK('1-UseCase ทั้งหมด'!V8)+COUNTBLANK('1-UseCase ทั้งหมด'!W8))</f>
         <v/>
       </c>
     </row>
@@ -4154,11 +4287,11 @@
         <v/>
       </c>
       <c r="D9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I9,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L9,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J9,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M9,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F9" s="35">
@@ -4166,15 +4299,15 @@
         <v/>
       </c>
       <c r="G9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L9,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O9,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M9,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P9,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O9,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R9,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J9" s="35">
@@ -4182,11 +4315,11 @@
         <v/>
       </c>
       <c r="K9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P9,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S9,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q9,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T9,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M9" s="35">
@@ -4194,15 +4327,15 @@
         <v/>
       </c>
       <c r="N9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R9,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U9,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S9,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V9,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T9,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W9,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q9" s="35">
@@ -4222,7 +4355,7 @@
         <v/>
       </c>
       <c r="U9" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B9="","",COUNTBLANK('1-UseCase ทั้งหมด'!I9)+COUNTBLANK('1-UseCase ทั้งหมด'!J9)+COUNTBLANK('1-UseCase ทั้งหมด'!L9)+COUNTBLANK('1-UseCase ทั้งหมด'!M9)+COUNTBLANK('1-UseCase ทั้งหมด'!O9)+COUNTBLANK('1-UseCase ทั้งหมด'!P9)+COUNTBLANK('1-UseCase ทั้งหมด'!Q9)+COUNTBLANK('1-UseCase ทั้งหมด'!R9)+COUNTBLANK('1-UseCase ทั้งหมด'!S9)+COUNTBLANK('1-UseCase ทั้งหมด'!T9))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B9="","",COUNTBLANK('1-UseCase ทั้งหมด'!L9)+COUNTBLANK('1-UseCase ทั้งหมด'!M9)+COUNTBLANK('1-UseCase ทั้งหมด'!O9)+COUNTBLANK('1-UseCase ทั้งหมด'!P9)+COUNTBLANK('1-UseCase ทั้งหมด'!R9)+COUNTBLANK('1-UseCase ทั้งหมด'!S9)+COUNTBLANK('1-UseCase ทั้งหมด'!T9)+COUNTBLANK('1-UseCase ทั้งหมด'!U9)+COUNTBLANK('1-UseCase ทั้งหมด'!V9)+COUNTBLANK('1-UseCase ทั้งหมด'!W9))</f>
         <v/>
       </c>
     </row>
@@ -4240,11 +4373,11 @@
         <v/>
       </c>
       <c r="D10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I10,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L10,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J10,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M10,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F10" s="35">
@@ -4252,15 +4385,15 @@
         <v/>
       </c>
       <c r="G10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L10,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O10,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M10,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P10,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O10,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R10,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J10" s="35">
@@ -4268,11 +4401,11 @@
         <v/>
       </c>
       <c r="K10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P10,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S10,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q10,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T10,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M10" s="35">
@@ -4280,15 +4413,15 @@
         <v/>
       </c>
       <c r="N10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R10,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U10,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S10,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V10,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T10,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W10,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q10" s="35">
@@ -4308,7 +4441,7 @@
         <v/>
       </c>
       <c r="U10" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B10="","",COUNTBLANK('1-UseCase ทั้งหมด'!I10)+COUNTBLANK('1-UseCase ทั้งหมด'!J10)+COUNTBLANK('1-UseCase ทั้งหมด'!L10)+COUNTBLANK('1-UseCase ทั้งหมด'!M10)+COUNTBLANK('1-UseCase ทั้งหมด'!O10)+COUNTBLANK('1-UseCase ทั้งหมด'!P10)+COUNTBLANK('1-UseCase ทั้งหมด'!Q10)+COUNTBLANK('1-UseCase ทั้งหมด'!R10)+COUNTBLANK('1-UseCase ทั้งหมด'!S10)+COUNTBLANK('1-UseCase ทั้งหมด'!T10))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B10="","",COUNTBLANK('1-UseCase ทั้งหมด'!L10)+COUNTBLANK('1-UseCase ทั้งหมด'!M10)+COUNTBLANK('1-UseCase ทั้งหมด'!O10)+COUNTBLANK('1-UseCase ทั้งหมด'!P10)+COUNTBLANK('1-UseCase ทั้งหมด'!R10)+COUNTBLANK('1-UseCase ทั้งหมด'!S10)+COUNTBLANK('1-UseCase ทั้งหมด'!T10)+COUNTBLANK('1-UseCase ทั้งหมด'!U10)+COUNTBLANK('1-UseCase ทั้งหมด'!V10)+COUNTBLANK('1-UseCase ทั้งหมด'!W10))</f>
         <v/>
       </c>
     </row>
@@ -4326,11 +4459,11 @@
         <v/>
       </c>
       <c r="D11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I11,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L11,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J11,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M11,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F11" s="35">
@@ -4338,15 +4471,15 @@
         <v/>
       </c>
       <c r="G11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L11,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O11,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M11,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P11,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O11,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R11,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J11" s="35">
@@ -4354,11 +4487,11 @@
         <v/>
       </c>
       <c r="K11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P11,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S11,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q11,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T11,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M11" s="35">
@@ -4366,15 +4499,15 @@
         <v/>
       </c>
       <c r="N11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R11,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U11,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S11,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V11,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T11,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W11,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q11" s="35">
@@ -4394,7 +4527,7 @@
         <v/>
       </c>
       <c r="U11" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B11="","",COUNTBLANK('1-UseCase ทั้งหมด'!I11)+COUNTBLANK('1-UseCase ทั้งหมด'!J11)+COUNTBLANK('1-UseCase ทั้งหมด'!L11)+COUNTBLANK('1-UseCase ทั้งหมด'!M11)+COUNTBLANK('1-UseCase ทั้งหมด'!O11)+COUNTBLANK('1-UseCase ทั้งหมด'!P11)+COUNTBLANK('1-UseCase ทั้งหมด'!Q11)+COUNTBLANK('1-UseCase ทั้งหมด'!R11)+COUNTBLANK('1-UseCase ทั้งหมด'!S11)+COUNTBLANK('1-UseCase ทั้งหมด'!T11))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B11="","",COUNTBLANK('1-UseCase ทั้งหมด'!L11)+COUNTBLANK('1-UseCase ทั้งหมด'!M11)+COUNTBLANK('1-UseCase ทั้งหมด'!O11)+COUNTBLANK('1-UseCase ทั้งหมด'!P11)+COUNTBLANK('1-UseCase ทั้งหมด'!R11)+COUNTBLANK('1-UseCase ทั้งหมด'!S11)+COUNTBLANK('1-UseCase ทั้งหมด'!T11)+COUNTBLANK('1-UseCase ทั้งหมด'!U11)+COUNTBLANK('1-UseCase ทั้งหมด'!V11)+COUNTBLANK('1-UseCase ทั้งหมด'!W11))</f>
         <v/>
       </c>
     </row>
@@ -4412,11 +4545,11 @@
         <v/>
       </c>
       <c r="D12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I12,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L12,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J12,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M12,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F12" s="35">
@@ -4424,15 +4557,15 @@
         <v/>
       </c>
       <c r="G12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L12,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O12,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M12,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P12,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O12,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R12,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J12" s="35">
@@ -4440,11 +4573,11 @@
         <v/>
       </c>
       <c r="K12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P12,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S12,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q12,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T12,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M12" s="35">
@@ -4452,15 +4585,15 @@
         <v/>
       </c>
       <c r="N12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R12,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U12,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S12,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V12,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T12,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W12,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q12" s="35">
@@ -4480,7 +4613,7 @@
         <v/>
       </c>
       <c r="U12" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B12="","",COUNTBLANK('1-UseCase ทั้งหมด'!I12)+COUNTBLANK('1-UseCase ทั้งหมด'!J12)+COUNTBLANK('1-UseCase ทั้งหมด'!L12)+COUNTBLANK('1-UseCase ทั้งหมด'!M12)+COUNTBLANK('1-UseCase ทั้งหมด'!O12)+COUNTBLANK('1-UseCase ทั้งหมด'!P12)+COUNTBLANK('1-UseCase ทั้งหมด'!Q12)+COUNTBLANK('1-UseCase ทั้งหมด'!R12)+COUNTBLANK('1-UseCase ทั้งหมด'!S12)+COUNTBLANK('1-UseCase ทั้งหมด'!T12))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B12="","",COUNTBLANK('1-UseCase ทั้งหมด'!L12)+COUNTBLANK('1-UseCase ทั้งหมด'!M12)+COUNTBLANK('1-UseCase ทั้งหมด'!O12)+COUNTBLANK('1-UseCase ทั้งหมด'!P12)+COUNTBLANK('1-UseCase ทั้งหมด'!R12)+COUNTBLANK('1-UseCase ทั้งหมด'!S12)+COUNTBLANK('1-UseCase ทั้งหมด'!T12)+COUNTBLANK('1-UseCase ทั้งหมด'!U12)+COUNTBLANK('1-UseCase ทั้งหมด'!V12)+COUNTBLANK('1-UseCase ทั้งหมด'!W12))</f>
         <v/>
       </c>
     </row>
@@ -4498,11 +4631,11 @@
         <v/>
       </c>
       <c r="D13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I13,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L13,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J13,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M13,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F13" s="35">
@@ -4510,15 +4643,15 @@
         <v/>
       </c>
       <c r="G13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L13,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O13,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M13,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P13,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O13,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R13,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J13" s="35">
@@ -4526,11 +4659,11 @@
         <v/>
       </c>
       <c r="K13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P13,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S13,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q13,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T13,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M13" s="35">
@@ -4538,15 +4671,15 @@
         <v/>
       </c>
       <c r="N13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R13,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U13,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S13,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V13,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T13,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W13,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q13" s="35">
@@ -4566,7 +4699,7 @@
         <v/>
       </c>
       <c r="U13" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B13="","",COUNTBLANK('1-UseCase ทั้งหมด'!I13)+COUNTBLANK('1-UseCase ทั้งหมด'!J13)+COUNTBLANK('1-UseCase ทั้งหมด'!L13)+COUNTBLANK('1-UseCase ทั้งหมด'!M13)+COUNTBLANK('1-UseCase ทั้งหมด'!O13)+COUNTBLANK('1-UseCase ทั้งหมด'!P13)+COUNTBLANK('1-UseCase ทั้งหมด'!Q13)+COUNTBLANK('1-UseCase ทั้งหมด'!R13)+COUNTBLANK('1-UseCase ทั้งหมด'!S13)+COUNTBLANK('1-UseCase ทั้งหมด'!T13))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B13="","",COUNTBLANK('1-UseCase ทั้งหมด'!L13)+COUNTBLANK('1-UseCase ทั้งหมด'!M13)+COUNTBLANK('1-UseCase ทั้งหมด'!O13)+COUNTBLANK('1-UseCase ทั้งหมด'!P13)+COUNTBLANK('1-UseCase ทั้งหมด'!R13)+COUNTBLANK('1-UseCase ทั้งหมด'!S13)+COUNTBLANK('1-UseCase ทั้งหมด'!T13)+COUNTBLANK('1-UseCase ทั้งหมด'!U13)+COUNTBLANK('1-UseCase ทั้งหมด'!V13)+COUNTBLANK('1-UseCase ทั้งหมด'!W13))</f>
         <v/>
       </c>
     </row>
@@ -4584,11 +4717,11 @@
         <v/>
       </c>
       <c r="D14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I14,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L14,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J14,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M14,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F14" s="35">
@@ -4596,15 +4729,15 @@
         <v/>
       </c>
       <c r="G14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L14,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O14,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M14,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P14,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O14,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R14,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J14" s="35">
@@ -4612,11 +4745,11 @@
         <v/>
       </c>
       <c r="K14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P14,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S14,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q14,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T14,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M14" s="35">
@@ -4624,15 +4757,15 @@
         <v/>
       </c>
       <c r="N14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R14,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U14,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S14,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V14,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T14,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W14,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q14" s="35">
@@ -4652,7 +4785,7 @@
         <v/>
       </c>
       <c r="U14" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B14="","",COUNTBLANK('1-UseCase ทั้งหมด'!I14)+COUNTBLANK('1-UseCase ทั้งหมด'!J14)+COUNTBLANK('1-UseCase ทั้งหมด'!L14)+COUNTBLANK('1-UseCase ทั้งหมด'!M14)+COUNTBLANK('1-UseCase ทั้งหมด'!O14)+COUNTBLANK('1-UseCase ทั้งหมด'!P14)+COUNTBLANK('1-UseCase ทั้งหมด'!Q14)+COUNTBLANK('1-UseCase ทั้งหมด'!R14)+COUNTBLANK('1-UseCase ทั้งหมด'!S14)+COUNTBLANK('1-UseCase ทั้งหมด'!T14))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B14="","",COUNTBLANK('1-UseCase ทั้งหมด'!L14)+COUNTBLANK('1-UseCase ทั้งหมด'!M14)+COUNTBLANK('1-UseCase ทั้งหมด'!O14)+COUNTBLANK('1-UseCase ทั้งหมด'!P14)+COUNTBLANK('1-UseCase ทั้งหมด'!R14)+COUNTBLANK('1-UseCase ทั้งหมด'!S14)+COUNTBLANK('1-UseCase ทั้งหมด'!T14)+COUNTBLANK('1-UseCase ทั้งหมด'!U14)+COUNTBLANK('1-UseCase ทั้งหมด'!V14)+COUNTBLANK('1-UseCase ทั้งหมด'!W14))</f>
         <v/>
       </c>
     </row>
@@ -4670,11 +4803,11 @@
         <v/>
       </c>
       <c r="D15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I15,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L15,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J15,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M15,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F15" s="35">
@@ -4682,15 +4815,15 @@
         <v/>
       </c>
       <c r="G15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L15,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O15,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M15,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P15,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O15,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R15,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J15" s="35">
@@ -4698,11 +4831,11 @@
         <v/>
       </c>
       <c r="K15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P15,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S15,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q15,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T15,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M15" s="35">
@@ -4710,15 +4843,15 @@
         <v/>
       </c>
       <c r="N15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R15,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U15,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S15,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V15,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T15,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W15,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q15" s="35">
@@ -4738,7 +4871,7 @@
         <v/>
       </c>
       <c r="U15" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B15="","",COUNTBLANK('1-UseCase ทั้งหมด'!I15)+COUNTBLANK('1-UseCase ทั้งหมด'!J15)+COUNTBLANK('1-UseCase ทั้งหมด'!L15)+COUNTBLANK('1-UseCase ทั้งหมด'!M15)+COUNTBLANK('1-UseCase ทั้งหมด'!O15)+COUNTBLANK('1-UseCase ทั้งหมด'!P15)+COUNTBLANK('1-UseCase ทั้งหมด'!Q15)+COUNTBLANK('1-UseCase ทั้งหมด'!R15)+COUNTBLANK('1-UseCase ทั้งหมด'!S15)+COUNTBLANK('1-UseCase ทั้งหมด'!T15))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B15="","",COUNTBLANK('1-UseCase ทั้งหมด'!L15)+COUNTBLANK('1-UseCase ทั้งหมด'!M15)+COUNTBLANK('1-UseCase ทั้งหมด'!O15)+COUNTBLANK('1-UseCase ทั้งหมด'!P15)+COUNTBLANK('1-UseCase ทั้งหมด'!R15)+COUNTBLANK('1-UseCase ทั้งหมด'!S15)+COUNTBLANK('1-UseCase ทั้งหมด'!T15)+COUNTBLANK('1-UseCase ทั้งหมด'!U15)+COUNTBLANK('1-UseCase ทั้งหมด'!V15)+COUNTBLANK('1-UseCase ทั้งหมด'!W15))</f>
         <v/>
       </c>
     </row>
@@ -4756,11 +4889,11 @@
         <v/>
       </c>
       <c r="D16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I16,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L16,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J16,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M16,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F16" s="35">
@@ -4768,15 +4901,15 @@
         <v/>
       </c>
       <c r="G16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L16,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O16,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M16,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P16,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O16,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R16,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J16" s="35">
@@ -4784,11 +4917,11 @@
         <v/>
       </c>
       <c r="K16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P16,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S16,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q16,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T16,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M16" s="35">
@@ -4796,15 +4929,15 @@
         <v/>
       </c>
       <c r="N16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R16,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U16,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S16,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V16,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T16,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W16,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q16" s="35">
@@ -4824,7 +4957,7 @@
         <v/>
       </c>
       <c r="U16" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B16="","",COUNTBLANK('1-UseCase ทั้งหมด'!I16)+COUNTBLANK('1-UseCase ทั้งหมด'!J16)+COUNTBLANK('1-UseCase ทั้งหมด'!L16)+COUNTBLANK('1-UseCase ทั้งหมด'!M16)+COUNTBLANK('1-UseCase ทั้งหมด'!O16)+COUNTBLANK('1-UseCase ทั้งหมด'!P16)+COUNTBLANK('1-UseCase ทั้งหมด'!Q16)+COUNTBLANK('1-UseCase ทั้งหมด'!R16)+COUNTBLANK('1-UseCase ทั้งหมด'!S16)+COUNTBLANK('1-UseCase ทั้งหมด'!T16))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B16="","",COUNTBLANK('1-UseCase ทั้งหมด'!L16)+COUNTBLANK('1-UseCase ทั้งหมด'!M16)+COUNTBLANK('1-UseCase ทั้งหมด'!O16)+COUNTBLANK('1-UseCase ทั้งหมด'!P16)+COUNTBLANK('1-UseCase ทั้งหมด'!R16)+COUNTBLANK('1-UseCase ทั้งหมด'!S16)+COUNTBLANK('1-UseCase ทั้งหมด'!T16)+COUNTBLANK('1-UseCase ทั้งหมด'!U16)+COUNTBLANK('1-UseCase ทั้งหมด'!V16)+COUNTBLANK('1-UseCase ทั้งหมด'!W16))</f>
         <v/>
       </c>
     </row>
@@ -4842,11 +4975,11 @@
         <v/>
       </c>
       <c r="D17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I17,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L17,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J17,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M17,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F17" s="35">
@@ -4854,15 +4987,15 @@
         <v/>
       </c>
       <c r="G17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L17,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O17,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M17,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P17,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O17,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R17,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J17" s="35">
@@ -4870,11 +5003,11 @@
         <v/>
       </c>
       <c r="K17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P17,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S17,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q17,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T17,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M17" s="35">
@@ -4882,15 +5015,15 @@
         <v/>
       </c>
       <c r="N17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R17,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U17,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S17,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V17,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T17,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W17,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q17" s="35">
@@ -4910,7 +5043,7 @@
         <v/>
       </c>
       <c r="U17" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B17="","",COUNTBLANK('1-UseCase ทั้งหมด'!I17)+COUNTBLANK('1-UseCase ทั้งหมด'!J17)+COUNTBLANK('1-UseCase ทั้งหมด'!L17)+COUNTBLANK('1-UseCase ทั้งหมด'!M17)+COUNTBLANK('1-UseCase ทั้งหมด'!O17)+COUNTBLANK('1-UseCase ทั้งหมด'!P17)+COUNTBLANK('1-UseCase ทั้งหมด'!Q17)+COUNTBLANK('1-UseCase ทั้งหมด'!R17)+COUNTBLANK('1-UseCase ทั้งหมด'!S17)+COUNTBLANK('1-UseCase ทั้งหมด'!T17))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B17="","",COUNTBLANK('1-UseCase ทั้งหมด'!L17)+COUNTBLANK('1-UseCase ทั้งหมด'!M17)+COUNTBLANK('1-UseCase ทั้งหมด'!O17)+COUNTBLANK('1-UseCase ทั้งหมด'!P17)+COUNTBLANK('1-UseCase ทั้งหมด'!R17)+COUNTBLANK('1-UseCase ทั้งหมด'!S17)+COUNTBLANK('1-UseCase ทั้งหมด'!T17)+COUNTBLANK('1-UseCase ทั้งหมด'!U17)+COUNTBLANK('1-UseCase ทั้งหมด'!V17)+COUNTBLANK('1-UseCase ทั้งหมด'!W17))</f>
         <v/>
       </c>
     </row>
@@ -4928,11 +5061,11 @@
         <v/>
       </c>
       <c r="D18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I18,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L18,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J18,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M18,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F18" s="35">
@@ -4940,15 +5073,15 @@
         <v/>
       </c>
       <c r="G18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L18,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O18,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M18,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P18,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O18,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R18,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J18" s="35">
@@ -4956,11 +5089,11 @@
         <v/>
       </c>
       <c r="K18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P18,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S18,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q18,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T18,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M18" s="35">
@@ -4968,15 +5101,15 @@
         <v/>
       </c>
       <c r="N18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R18,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U18,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S18,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V18,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T18,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W18,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q18" s="35">
@@ -4996,7 +5129,7 @@
         <v/>
       </c>
       <c r="U18" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B18="","",COUNTBLANK('1-UseCase ทั้งหมด'!I18)+COUNTBLANK('1-UseCase ทั้งหมด'!J18)+COUNTBLANK('1-UseCase ทั้งหมด'!L18)+COUNTBLANK('1-UseCase ทั้งหมด'!M18)+COUNTBLANK('1-UseCase ทั้งหมด'!O18)+COUNTBLANK('1-UseCase ทั้งหมด'!P18)+COUNTBLANK('1-UseCase ทั้งหมด'!Q18)+COUNTBLANK('1-UseCase ทั้งหมด'!R18)+COUNTBLANK('1-UseCase ทั้งหมด'!S18)+COUNTBLANK('1-UseCase ทั้งหมด'!T18))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B18="","",COUNTBLANK('1-UseCase ทั้งหมด'!L18)+COUNTBLANK('1-UseCase ทั้งหมด'!M18)+COUNTBLANK('1-UseCase ทั้งหมด'!O18)+COUNTBLANK('1-UseCase ทั้งหมด'!P18)+COUNTBLANK('1-UseCase ทั้งหมด'!R18)+COUNTBLANK('1-UseCase ทั้งหมด'!S18)+COUNTBLANK('1-UseCase ทั้งหมด'!T18)+COUNTBLANK('1-UseCase ทั้งหมด'!U18)+COUNTBLANK('1-UseCase ทั้งหมด'!V18)+COUNTBLANK('1-UseCase ทั้งหมด'!W18))</f>
         <v/>
       </c>
     </row>
@@ -5014,11 +5147,11 @@
         <v/>
       </c>
       <c r="D19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I19,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L19,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J19,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M19,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F19" s="35">
@@ -5026,15 +5159,15 @@
         <v/>
       </c>
       <c r="G19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L19,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O19,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M19,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P19,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O19,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R19,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J19" s="35">
@@ -5042,11 +5175,11 @@
         <v/>
       </c>
       <c r="K19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P19,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S19,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q19,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T19,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M19" s="35">
@@ -5054,15 +5187,15 @@
         <v/>
       </c>
       <c r="N19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R19,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U19,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S19,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V19,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T19,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W19,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q19" s="35">
@@ -5082,7 +5215,7 @@
         <v/>
       </c>
       <c r="U19" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B19="","",COUNTBLANK('1-UseCase ทั้งหมด'!I19)+COUNTBLANK('1-UseCase ทั้งหมด'!J19)+COUNTBLANK('1-UseCase ทั้งหมด'!L19)+COUNTBLANK('1-UseCase ทั้งหมด'!M19)+COUNTBLANK('1-UseCase ทั้งหมด'!O19)+COUNTBLANK('1-UseCase ทั้งหมด'!P19)+COUNTBLANK('1-UseCase ทั้งหมด'!Q19)+COUNTBLANK('1-UseCase ทั้งหมด'!R19)+COUNTBLANK('1-UseCase ทั้งหมด'!S19)+COUNTBLANK('1-UseCase ทั้งหมด'!T19))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B19="","",COUNTBLANK('1-UseCase ทั้งหมด'!L19)+COUNTBLANK('1-UseCase ทั้งหมด'!M19)+COUNTBLANK('1-UseCase ทั้งหมด'!O19)+COUNTBLANK('1-UseCase ทั้งหมด'!P19)+COUNTBLANK('1-UseCase ทั้งหมด'!R19)+COUNTBLANK('1-UseCase ทั้งหมด'!S19)+COUNTBLANK('1-UseCase ทั้งหมด'!T19)+COUNTBLANK('1-UseCase ทั้งหมด'!U19)+COUNTBLANK('1-UseCase ทั้งหมด'!V19)+COUNTBLANK('1-UseCase ทั้งหมด'!W19))</f>
         <v/>
       </c>
     </row>
@@ -5100,11 +5233,11 @@
         <v/>
       </c>
       <c r="D20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I20,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L20,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J20,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M20,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F20" s="35">
@@ -5112,15 +5245,15 @@
         <v/>
       </c>
       <c r="G20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L20,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O20,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M20,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P20,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O20,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R20,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J20" s="35">
@@ -5128,11 +5261,11 @@
         <v/>
       </c>
       <c r="K20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P20,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S20,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q20,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T20,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M20" s="35">
@@ -5140,15 +5273,15 @@
         <v/>
       </c>
       <c r="N20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R20,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U20,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S20,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V20,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T20,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W20,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q20" s="35">
@@ -5168,7 +5301,7 @@
         <v/>
       </c>
       <c r="U20" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B20="","",COUNTBLANK('1-UseCase ทั้งหมด'!I20)+COUNTBLANK('1-UseCase ทั้งหมด'!J20)+COUNTBLANK('1-UseCase ทั้งหมด'!L20)+COUNTBLANK('1-UseCase ทั้งหมด'!M20)+COUNTBLANK('1-UseCase ทั้งหมด'!O20)+COUNTBLANK('1-UseCase ทั้งหมด'!P20)+COUNTBLANK('1-UseCase ทั้งหมด'!Q20)+COUNTBLANK('1-UseCase ทั้งหมด'!R20)+COUNTBLANK('1-UseCase ทั้งหมด'!S20)+COUNTBLANK('1-UseCase ทั้งหมด'!T20))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B20="","",COUNTBLANK('1-UseCase ทั้งหมด'!L20)+COUNTBLANK('1-UseCase ทั้งหมด'!M20)+COUNTBLANK('1-UseCase ทั้งหมด'!O20)+COUNTBLANK('1-UseCase ทั้งหมด'!P20)+COUNTBLANK('1-UseCase ทั้งหมด'!R20)+COUNTBLANK('1-UseCase ทั้งหมด'!S20)+COUNTBLANK('1-UseCase ทั้งหมด'!T20)+COUNTBLANK('1-UseCase ทั้งหมด'!U20)+COUNTBLANK('1-UseCase ทั้งหมด'!V20)+COUNTBLANK('1-UseCase ทั้งหมด'!W20))</f>
         <v/>
       </c>
     </row>
@@ -5186,11 +5319,11 @@
         <v/>
       </c>
       <c r="D21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I21,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L21,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J21,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M21,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F21" s="35">
@@ -5198,15 +5331,15 @@
         <v/>
       </c>
       <c r="G21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L21,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O21,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M21,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P21,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O21,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R21,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J21" s="35">
@@ -5214,11 +5347,11 @@
         <v/>
       </c>
       <c r="K21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P21,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S21,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q21,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T21,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M21" s="35">
@@ -5226,15 +5359,15 @@
         <v/>
       </c>
       <c r="N21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R21,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U21,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S21,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V21,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T21,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W21,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q21" s="35">
@@ -5254,7 +5387,7 @@
         <v/>
       </c>
       <c r="U21" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B21="","",COUNTBLANK('1-UseCase ทั้งหมด'!I21)+COUNTBLANK('1-UseCase ทั้งหมด'!J21)+COUNTBLANK('1-UseCase ทั้งหมด'!L21)+COUNTBLANK('1-UseCase ทั้งหมด'!M21)+COUNTBLANK('1-UseCase ทั้งหมด'!O21)+COUNTBLANK('1-UseCase ทั้งหมด'!P21)+COUNTBLANK('1-UseCase ทั้งหมด'!Q21)+COUNTBLANK('1-UseCase ทั้งหมด'!R21)+COUNTBLANK('1-UseCase ทั้งหมด'!S21)+COUNTBLANK('1-UseCase ทั้งหมด'!T21))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B21="","",COUNTBLANK('1-UseCase ทั้งหมด'!L21)+COUNTBLANK('1-UseCase ทั้งหมด'!M21)+COUNTBLANK('1-UseCase ทั้งหมด'!O21)+COUNTBLANK('1-UseCase ทั้งหมด'!P21)+COUNTBLANK('1-UseCase ทั้งหมด'!R21)+COUNTBLANK('1-UseCase ทั้งหมด'!S21)+COUNTBLANK('1-UseCase ทั้งหมด'!T21)+COUNTBLANK('1-UseCase ทั้งหมด'!U21)+COUNTBLANK('1-UseCase ทั้งหมด'!V21)+COUNTBLANK('1-UseCase ทั้งหมด'!W21))</f>
         <v/>
       </c>
     </row>
@@ -5272,11 +5405,11 @@
         <v/>
       </c>
       <c r="D22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I22,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L22,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J22,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M22,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F22" s="35">
@@ -5284,15 +5417,15 @@
         <v/>
       </c>
       <c r="G22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L22,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O22,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M22,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P22,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O22,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R22,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J22" s="35">
@@ -5300,11 +5433,11 @@
         <v/>
       </c>
       <c r="K22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P22,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S22,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q22,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T22,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M22" s="35">
@@ -5312,15 +5445,15 @@
         <v/>
       </c>
       <c r="N22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R22,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U22,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S22,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V22,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T22,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W22,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q22" s="35">
@@ -5340,7 +5473,7 @@
         <v/>
       </c>
       <c r="U22" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B22="","",COUNTBLANK('1-UseCase ทั้งหมด'!I22)+COUNTBLANK('1-UseCase ทั้งหมด'!J22)+COUNTBLANK('1-UseCase ทั้งหมด'!L22)+COUNTBLANK('1-UseCase ทั้งหมด'!M22)+COUNTBLANK('1-UseCase ทั้งหมด'!O22)+COUNTBLANK('1-UseCase ทั้งหมด'!P22)+COUNTBLANK('1-UseCase ทั้งหมด'!Q22)+COUNTBLANK('1-UseCase ทั้งหมด'!R22)+COUNTBLANK('1-UseCase ทั้งหมด'!S22)+COUNTBLANK('1-UseCase ทั้งหมด'!T22))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B22="","",COUNTBLANK('1-UseCase ทั้งหมด'!L22)+COUNTBLANK('1-UseCase ทั้งหมด'!M22)+COUNTBLANK('1-UseCase ทั้งหมด'!O22)+COUNTBLANK('1-UseCase ทั้งหมด'!P22)+COUNTBLANK('1-UseCase ทั้งหมด'!R22)+COUNTBLANK('1-UseCase ทั้งหมด'!S22)+COUNTBLANK('1-UseCase ทั้งหมด'!T22)+COUNTBLANK('1-UseCase ทั้งหมด'!U22)+COUNTBLANK('1-UseCase ทั้งหมด'!V22)+COUNTBLANK('1-UseCase ทั้งหมด'!W22))</f>
         <v/>
       </c>
     </row>
@@ -5358,11 +5491,11 @@
         <v/>
       </c>
       <c r="D23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I23,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L23,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J23,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M23,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F23" s="35">
@@ -5370,15 +5503,15 @@
         <v/>
       </c>
       <c r="G23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L23,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O23,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M23,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P23,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O23,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R23,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J23" s="35">
@@ -5386,11 +5519,11 @@
         <v/>
       </c>
       <c r="K23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P23,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S23,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q23,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T23,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M23" s="35">
@@ -5398,15 +5531,15 @@
         <v/>
       </c>
       <c r="N23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R23,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U23,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S23,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V23,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T23,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W23,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q23" s="35">
@@ -5426,7 +5559,7 @@
         <v/>
       </c>
       <c r="U23" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B23="","",COUNTBLANK('1-UseCase ทั้งหมด'!I23)+COUNTBLANK('1-UseCase ทั้งหมด'!J23)+COUNTBLANK('1-UseCase ทั้งหมด'!L23)+COUNTBLANK('1-UseCase ทั้งหมด'!M23)+COUNTBLANK('1-UseCase ทั้งหมด'!O23)+COUNTBLANK('1-UseCase ทั้งหมด'!P23)+COUNTBLANK('1-UseCase ทั้งหมด'!Q23)+COUNTBLANK('1-UseCase ทั้งหมด'!R23)+COUNTBLANK('1-UseCase ทั้งหมด'!S23)+COUNTBLANK('1-UseCase ทั้งหมด'!T23))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B23="","",COUNTBLANK('1-UseCase ทั้งหมด'!L23)+COUNTBLANK('1-UseCase ทั้งหมด'!M23)+COUNTBLANK('1-UseCase ทั้งหมด'!O23)+COUNTBLANK('1-UseCase ทั้งหมด'!P23)+COUNTBLANK('1-UseCase ทั้งหมด'!R23)+COUNTBLANK('1-UseCase ทั้งหมด'!S23)+COUNTBLANK('1-UseCase ทั้งหมด'!T23)+COUNTBLANK('1-UseCase ทั้งหมด'!U23)+COUNTBLANK('1-UseCase ทั้งหมด'!V23)+COUNTBLANK('1-UseCase ทั้งหมด'!W23))</f>
         <v/>
       </c>
     </row>
@@ -5444,11 +5577,11 @@
         <v/>
       </c>
       <c r="D24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I24,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L24,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J24,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M24,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F24" s="35">
@@ -5456,15 +5589,15 @@
         <v/>
       </c>
       <c r="G24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L24,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O24,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M24,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P24,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O24,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R24,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J24" s="35">
@@ -5472,11 +5605,11 @@
         <v/>
       </c>
       <c r="K24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P24,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S24,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q24,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T24,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M24" s="35">
@@ -5484,15 +5617,15 @@
         <v/>
       </c>
       <c r="N24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R24,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U24,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S24,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V24,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T24,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W24,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q24" s="35">
@@ -5512,7 +5645,7 @@
         <v/>
       </c>
       <c r="U24" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B24="","",COUNTBLANK('1-UseCase ทั้งหมด'!I24)+COUNTBLANK('1-UseCase ทั้งหมด'!J24)+COUNTBLANK('1-UseCase ทั้งหมด'!L24)+COUNTBLANK('1-UseCase ทั้งหมด'!M24)+COUNTBLANK('1-UseCase ทั้งหมด'!O24)+COUNTBLANK('1-UseCase ทั้งหมด'!P24)+COUNTBLANK('1-UseCase ทั้งหมด'!Q24)+COUNTBLANK('1-UseCase ทั้งหมด'!R24)+COUNTBLANK('1-UseCase ทั้งหมด'!S24)+COUNTBLANK('1-UseCase ทั้งหมด'!T24))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B24="","",COUNTBLANK('1-UseCase ทั้งหมด'!L24)+COUNTBLANK('1-UseCase ทั้งหมด'!M24)+COUNTBLANK('1-UseCase ทั้งหมด'!O24)+COUNTBLANK('1-UseCase ทั้งหมด'!P24)+COUNTBLANK('1-UseCase ทั้งหมด'!R24)+COUNTBLANK('1-UseCase ทั้งหมด'!S24)+COUNTBLANK('1-UseCase ทั้งหมด'!T24)+COUNTBLANK('1-UseCase ทั้งหมด'!U24)+COUNTBLANK('1-UseCase ทั้งหมด'!V24)+COUNTBLANK('1-UseCase ทั้งหมด'!W24))</f>
         <v/>
       </c>
     </row>
@@ -5530,11 +5663,11 @@
         <v/>
       </c>
       <c r="D25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I25,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L25,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J25,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M25,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F25" s="35">
@@ -5542,15 +5675,15 @@
         <v/>
       </c>
       <c r="G25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L25,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O25,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M25,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P25,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O25,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R25,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J25" s="35">
@@ -5558,11 +5691,11 @@
         <v/>
       </c>
       <c r="K25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P25,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S25,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q25,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T25,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M25" s="35">
@@ -5570,15 +5703,15 @@
         <v/>
       </c>
       <c r="N25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R25,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U25,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S25,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V25,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T25,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W25,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q25" s="35">
@@ -5598,7 +5731,7 @@
         <v/>
       </c>
       <c r="U25" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B25="","",COUNTBLANK('1-UseCase ทั้งหมด'!I25)+COUNTBLANK('1-UseCase ทั้งหมด'!J25)+COUNTBLANK('1-UseCase ทั้งหมด'!L25)+COUNTBLANK('1-UseCase ทั้งหมด'!M25)+COUNTBLANK('1-UseCase ทั้งหมด'!O25)+COUNTBLANK('1-UseCase ทั้งหมด'!P25)+COUNTBLANK('1-UseCase ทั้งหมด'!Q25)+COUNTBLANK('1-UseCase ทั้งหมด'!R25)+COUNTBLANK('1-UseCase ทั้งหมด'!S25)+COUNTBLANK('1-UseCase ทั้งหมด'!T25))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B25="","",COUNTBLANK('1-UseCase ทั้งหมด'!L25)+COUNTBLANK('1-UseCase ทั้งหมด'!M25)+COUNTBLANK('1-UseCase ทั้งหมด'!O25)+COUNTBLANK('1-UseCase ทั้งหมด'!P25)+COUNTBLANK('1-UseCase ทั้งหมด'!R25)+COUNTBLANK('1-UseCase ทั้งหมด'!S25)+COUNTBLANK('1-UseCase ทั้งหมด'!T25)+COUNTBLANK('1-UseCase ทั้งหมด'!U25)+COUNTBLANK('1-UseCase ทั้งหมด'!V25)+COUNTBLANK('1-UseCase ทั้งหมด'!W25))</f>
         <v/>
       </c>
     </row>
@@ -5616,11 +5749,11 @@
         <v/>
       </c>
       <c r="D26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I26,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L26,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J26,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M26,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F26" s="35">
@@ -5628,15 +5761,15 @@
         <v/>
       </c>
       <c r="G26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L26,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O26,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M26,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P26,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O26,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R26,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J26" s="35">
@@ -5644,11 +5777,11 @@
         <v/>
       </c>
       <c r="K26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P26,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S26,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q26,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T26,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M26" s="35">
@@ -5656,15 +5789,15 @@
         <v/>
       </c>
       <c r="N26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R26,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U26,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S26,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V26,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T26,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W26,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q26" s="35">
@@ -5684,7 +5817,7 @@
         <v/>
       </c>
       <c r="U26" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B26="","",COUNTBLANK('1-UseCase ทั้งหมด'!I26)+COUNTBLANK('1-UseCase ทั้งหมด'!J26)+COUNTBLANK('1-UseCase ทั้งหมด'!L26)+COUNTBLANK('1-UseCase ทั้งหมด'!M26)+COUNTBLANK('1-UseCase ทั้งหมด'!O26)+COUNTBLANK('1-UseCase ทั้งหมด'!P26)+COUNTBLANK('1-UseCase ทั้งหมด'!Q26)+COUNTBLANK('1-UseCase ทั้งหมด'!R26)+COUNTBLANK('1-UseCase ทั้งหมด'!S26)+COUNTBLANK('1-UseCase ทั้งหมด'!T26))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B26="","",COUNTBLANK('1-UseCase ทั้งหมด'!L26)+COUNTBLANK('1-UseCase ทั้งหมด'!M26)+COUNTBLANK('1-UseCase ทั้งหมด'!O26)+COUNTBLANK('1-UseCase ทั้งหมด'!P26)+COUNTBLANK('1-UseCase ทั้งหมด'!R26)+COUNTBLANK('1-UseCase ทั้งหมด'!S26)+COUNTBLANK('1-UseCase ทั้งหมด'!T26)+COUNTBLANK('1-UseCase ทั้งหมด'!U26)+COUNTBLANK('1-UseCase ทั้งหมด'!V26)+COUNTBLANK('1-UseCase ทั้งหมด'!W26))</f>
         <v/>
       </c>
     </row>
@@ -5702,11 +5835,11 @@
         <v/>
       </c>
       <c r="D27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I27,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L27,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J27,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M27,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F27" s="35">
@@ -5714,15 +5847,15 @@
         <v/>
       </c>
       <c r="G27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L27,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O27,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M27,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P27,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O27,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R27,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J27" s="35">
@@ -5730,11 +5863,11 @@
         <v/>
       </c>
       <c r="K27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P27,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S27,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q27,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T27,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M27" s="35">
@@ -5742,15 +5875,15 @@
         <v/>
       </c>
       <c r="N27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R27,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U27,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S27,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V27,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T27,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W27,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q27" s="35">
@@ -5770,7 +5903,7 @@
         <v/>
       </c>
       <c r="U27" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B27="","",COUNTBLANK('1-UseCase ทั้งหมด'!I27)+COUNTBLANK('1-UseCase ทั้งหมด'!J27)+COUNTBLANK('1-UseCase ทั้งหมด'!L27)+COUNTBLANK('1-UseCase ทั้งหมด'!M27)+COUNTBLANK('1-UseCase ทั้งหมด'!O27)+COUNTBLANK('1-UseCase ทั้งหมด'!P27)+COUNTBLANK('1-UseCase ทั้งหมด'!Q27)+COUNTBLANK('1-UseCase ทั้งหมด'!R27)+COUNTBLANK('1-UseCase ทั้งหมด'!S27)+COUNTBLANK('1-UseCase ทั้งหมด'!T27))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B27="","",COUNTBLANK('1-UseCase ทั้งหมด'!L27)+COUNTBLANK('1-UseCase ทั้งหมด'!M27)+COUNTBLANK('1-UseCase ทั้งหมด'!O27)+COUNTBLANK('1-UseCase ทั้งหมด'!P27)+COUNTBLANK('1-UseCase ทั้งหมด'!R27)+COUNTBLANK('1-UseCase ทั้งหมด'!S27)+COUNTBLANK('1-UseCase ทั้งหมด'!T27)+COUNTBLANK('1-UseCase ทั้งหมด'!U27)+COUNTBLANK('1-UseCase ทั้งหมด'!V27)+COUNTBLANK('1-UseCase ทั้งหมด'!W27))</f>
         <v/>
       </c>
     </row>
@@ -5788,11 +5921,11 @@
         <v/>
       </c>
       <c r="D28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I28,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L28,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J28,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M28,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F28" s="35">
@@ -5800,15 +5933,15 @@
         <v/>
       </c>
       <c r="G28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L28,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O28,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M28,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P28,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O28,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R28,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J28" s="35">
@@ -5816,11 +5949,11 @@
         <v/>
       </c>
       <c r="K28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P28,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S28,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q28,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T28,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M28" s="35">
@@ -5828,15 +5961,15 @@
         <v/>
       </c>
       <c r="N28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R28,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U28,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S28,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V28,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T28,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W28,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q28" s="35">
@@ -5856,7 +5989,7 @@
         <v/>
       </c>
       <c r="U28" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B28="","",COUNTBLANK('1-UseCase ทั้งหมด'!I28)+COUNTBLANK('1-UseCase ทั้งหมด'!J28)+COUNTBLANK('1-UseCase ทั้งหมด'!L28)+COUNTBLANK('1-UseCase ทั้งหมด'!M28)+COUNTBLANK('1-UseCase ทั้งหมด'!O28)+COUNTBLANK('1-UseCase ทั้งหมด'!P28)+COUNTBLANK('1-UseCase ทั้งหมด'!Q28)+COUNTBLANK('1-UseCase ทั้งหมด'!R28)+COUNTBLANK('1-UseCase ทั้งหมด'!S28)+COUNTBLANK('1-UseCase ทั้งหมด'!T28))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B28="","",COUNTBLANK('1-UseCase ทั้งหมด'!L28)+COUNTBLANK('1-UseCase ทั้งหมด'!M28)+COUNTBLANK('1-UseCase ทั้งหมด'!O28)+COUNTBLANK('1-UseCase ทั้งหมด'!P28)+COUNTBLANK('1-UseCase ทั้งหมด'!R28)+COUNTBLANK('1-UseCase ทั้งหมด'!S28)+COUNTBLANK('1-UseCase ทั้งหมด'!T28)+COUNTBLANK('1-UseCase ทั้งหมด'!U28)+COUNTBLANK('1-UseCase ทั้งหมด'!V28)+COUNTBLANK('1-UseCase ทั้งหมด'!W28))</f>
         <v/>
       </c>
     </row>
@@ -5874,11 +6007,11 @@
         <v/>
       </c>
       <c r="D29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I29,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L29,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J29,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M29,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F29" s="35">
@@ -5886,15 +6019,15 @@
         <v/>
       </c>
       <c r="G29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L29,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O29,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M29,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P29,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O29,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R29,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J29" s="35">
@@ -5902,11 +6035,11 @@
         <v/>
       </c>
       <c r="K29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P29,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S29,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q29,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T29,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M29" s="35">
@@ -5914,15 +6047,15 @@
         <v/>
       </c>
       <c r="N29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R29,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U29,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S29,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V29,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T29,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W29,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q29" s="35">
@@ -5942,7 +6075,7 @@
         <v/>
       </c>
       <c r="U29" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B29="","",COUNTBLANK('1-UseCase ทั้งหมด'!I29)+COUNTBLANK('1-UseCase ทั้งหมด'!J29)+COUNTBLANK('1-UseCase ทั้งหมด'!L29)+COUNTBLANK('1-UseCase ทั้งหมด'!M29)+COUNTBLANK('1-UseCase ทั้งหมด'!O29)+COUNTBLANK('1-UseCase ทั้งหมด'!P29)+COUNTBLANK('1-UseCase ทั้งหมด'!Q29)+COUNTBLANK('1-UseCase ทั้งหมด'!R29)+COUNTBLANK('1-UseCase ทั้งหมด'!S29)+COUNTBLANK('1-UseCase ทั้งหมด'!T29))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B29="","",COUNTBLANK('1-UseCase ทั้งหมด'!L29)+COUNTBLANK('1-UseCase ทั้งหมด'!M29)+COUNTBLANK('1-UseCase ทั้งหมด'!O29)+COUNTBLANK('1-UseCase ทั้งหมด'!P29)+COUNTBLANK('1-UseCase ทั้งหมด'!R29)+COUNTBLANK('1-UseCase ทั้งหมด'!S29)+COUNTBLANK('1-UseCase ทั้งหมด'!T29)+COUNTBLANK('1-UseCase ทั้งหมด'!U29)+COUNTBLANK('1-UseCase ทั้งหมด'!V29)+COUNTBLANK('1-UseCase ทั้งหมด'!W29))</f>
         <v/>
       </c>
     </row>
@@ -5960,11 +6093,11 @@
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I30,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L30,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J30,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M30,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F30" s="35">
@@ -5972,15 +6105,15 @@
         <v/>
       </c>
       <c r="G30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L30,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O30,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M30,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P30,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O30,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R30,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J30" s="35">
@@ -5988,11 +6121,11 @@
         <v/>
       </c>
       <c r="K30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P30,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S30,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q30,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T30,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M30" s="35">
@@ -6000,15 +6133,15 @@
         <v/>
       </c>
       <c r="N30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R30,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U30,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S30,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V30,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T30,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W30,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q30" s="35">
@@ -6028,7 +6161,7 @@
         <v/>
       </c>
       <c r="U30" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B30="","",COUNTBLANK('1-UseCase ทั้งหมด'!I30)+COUNTBLANK('1-UseCase ทั้งหมด'!J30)+COUNTBLANK('1-UseCase ทั้งหมด'!L30)+COUNTBLANK('1-UseCase ทั้งหมด'!M30)+COUNTBLANK('1-UseCase ทั้งหมด'!O30)+COUNTBLANK('1-UseCase ทั้งหมด'!P30)+COUNTBLANK('1-UseCase ทั้งหมด'!Q30)+COUNTBLANK('1-UseCase ทั้งหมด'!R30)+COUNTBLANK('1-UseCase ทั้งหมด'!S30)+COUNTBLANK('1-UseCase ทั้งหมด'!T30))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B30="","",COUNTBLANK('1-UseCase ทั้งหมด'!L30)+COUNTBLANK('1-UseCase ทั้งหมด'!M30)+COUNTBLANK('1-UseCase ทั้งหมด'!O30)+COUNTBLANK('1-UseCase ทั้งหมด'!P30)+COUNTBLANK('1-UseCase ทั้งหมด'!R30)+COUNTBLANK('1-UseCase ทั้งหมด'!S30)+COUNTBLANK('1-UseCase ทั้งหมด'!T30)+COUNTBLANK('1-UseCase ทั้งหมด'!U30)+COUNTBLANK('1-UseCase ทั้งหมด'!V30)+COUNTBLANK('1-UseCase ทั้งหมด'!W30))</f>
         <v/>
       </c>
     </row>
@@ -6046,11 +6179,11 @@
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I31,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L31,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J31,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M31,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F31" s="35">
@@ -6058,15 +6191,15 @@
         <v/>
       </c>
       <c r="G31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L31,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O31,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M31,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P31,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O31,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R31,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J31" s="35">
@@ -6074,11 +6207,11 @@
         <v/>
       </c>
       <c r="K31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P31,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S31,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q31,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T31,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M31" s="35">
@@ -6086,15 +6219,15 @@
         <v/>
       </c>
       <c r="N31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R31,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U31,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S31,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V31,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T31,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W31,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q31" s="35">
@@ -6114,7 +6247,7 @@
         <v/>
       </c>
       <c r="U31" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B31="","",COUNTBLANK('1-UseCase ทั้งหมด'!I31)+COUNTBLANK('1-UseCase ทั้งหมด'!J31)+COUNTBLANK('1-UseCase ทั้งหมด'!L31)+COUNTBLANK('1-UseCase ทั้งหมด'!M31)+COUNTBLANK('1-UseCase ทั้งหมด'!O31)+COUNTBLANK('1-UseCase ทั้งหมด'!P31)+COUNTBLANK('1-UseCase ทั้งหมด'!Q31)+COUNTBLANK('1-UseCase ทั้งหมด'!R31)+COUNTBLANK('1-UseCase ทั้งหมด'!S31)+COUNTBLANK('1-UseCase ทั้งหมด'!T31))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B31="","",COUNTBLANK('1-UseCase ทั้งหมด'!L31)+COUNTBLANK('1-UseCase ทั้งหมด'!M31)+COUNTBLANK('1-UseCase ทั้งหมด'!O31)+COUNTBLANK('1-UseCase ทั้งหมด'!P31)+COUNTBLANK('1-UseCase ทั้งหมด'!R31)+COUNTBLANK('1-UseCase ทั้งหมด'!S31)+COUNTBLANK('1-UseCase ทั้งหมด'!T31)+COUNTBLANK('1-UseCase ทั้งหมด'!U31)+COUNTBLANK('1-UseCase ทั้งหมด'!V31)+COUNTBLANK('1-UseCase ทั้งหมด'!W31))</f>
         <v/>
       </c>
     </row>
@@ -6132,11 +6265,11 @@
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I32,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L32,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J32,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M32,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F32" s="35">
@@ -6144,15 +6277,15 @@
         <v/>
       </c>
       <c r="G32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L32,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O32,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M32,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P32,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O32,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R32,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J32" s="35">
@@ -6160,11 +6293,11 @@
         <v/>
       </c>
       <c r="K32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P32,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S32,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q32,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T32,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M32" s="35">
@@ -6172,15 +6305,15 @@
         <v/>
       </c>
       <c r="N32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R32,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U32,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S32,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V32,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T32,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W32,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q32" s="35">
@@ -6200,7 +6333,7 @@
         <v/>
       </c>
       <c r="U32" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B32="","",COUNTBLANK('1-UseCase ทั้งหมด'!I32)+COUNTBLANK('1-UseCase ทั้งหมด'!J32)+COUNTBLANK('1-UseCase ทั้งหมด'!L32)+COUNTBLANK('1-UseCase ทั้งหมด'!M32)+COUNTBLANK('1-UseCase ทั้งหมด'!O32)+COUNTBLANK('1-UseCase ทั้งหมด'!P32)+COUNTBLANK('1-UseCase ทั้งหมด'!Q32)+COUNTBLANK('1-UseCase ทั้งหมด'!R32)+COUNTBLANK('1-UseCase ทั้งหมด'!S32)+COUNTBLANK('1-UseCase ทั้งหมด'!T32))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B32="","",COUNTBLANK('1-UseCase ทั้งหมด'!L32)+COUNTBLANK('1-UseCase ทั้งหมด'!M32)+COUNTBLANK('1-UseCase ทั้งหมด'!O32)+COUNTBLANK('1-UseCase ทั้งหมด'!P32)+COUNTBLANK('1-UseCase ทั้งหมด'!R32)+COUNTBLANK('1-UseCase ทั้งหมด'!S32)+COUNTBLANK('1-UseCase ทั้งหมด'!T32)+COUNTBLANK('1-UseCase ทั้งหมด'!U32)+COUNTBLANK('1-UseCase ทั้งหมด'!V32)+COUNTBLANK('1-UseCase ทั้งหมด'!W32))</f>
         <v/>
       </c>
     </row>
@@ -6218,11 +6351,11 @@
         <v/>
       </c>
       <c r="D33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I33,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L33,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J33,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M33,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F33" s="35">
@@ -6230,15 +6363,15 @@
         <v/>
       </c>
       <c r="G33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L33,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O33,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M33,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P33,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O33,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R33,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J33" s="35">
@@ -6246,11 +6379,11 @@
         <v/>
       </c>
       <c r="K33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P33,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S33,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q33,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T33,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M33" s="35">
@@ -6258,15 +6391,15 @@
         <v/>
       </c>
       <c r="N33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R33,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U33,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S33,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V33,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T33,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W33,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q33" s="35">
@@ -6286,7 +6419,7 @@
         <v/>
       </c>
       <c r="U33" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B33="","",COUNTBLANK('1-UseCase ทั้งหมด'!I33)+COUNTBLANK('1-UseCase ทั้งหมด'!J33)+COUNTBLANK('1-UseCase ทั้งหมด'!L33)+COUNTBLANK('1-UseCase ทั้งหมด'!M33)+COUNTBLANK('1-UseCase ทั้งหมด'!O33)+COUNTBLANK('1-UseCase ทั้งหมด'!P33)+COUNTBLANK('1-UseCase ทั้งหมด'!Q33)+COUNTBLANK('1-UseCase ทั้งหมด'!R33)+COUNTBLANK('1-UseCase ทั้งหมด'!S33)+COUNTBLANK('1-UseCase ทั้งหมด'!T33))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B33="","",COUNTBLANK('1-UseCase ทั้งหมด'!L33)+COUNTBLANK('1-UseCase ทั้งหมด'!M33)+COUNTBLANK('1-UseCase ทั้งหมด'!O33)+COUNTBLANK('1-UseCase ทั้งหมด'!P33)+COUNTBLANK('1-UseCase ทั้งหมด'!R33)+COUNTBLANK('1-UseCase ทั้งหมด'!S33)+COUNTBLANK('1-UseCase ทั้งหมด'!T33)+COUNTBLANK('1-UseCase ทั้งหมด'!U33)+COUNTBLANK('1-UseCase ทั้งหมด'!V33)+COUNTBLANK('1-UseCase ทั้งหมด'!W33))</f>
         <v/>
       </c>
     </row>
@@ -6304,11 +6437,11 @@
         <v/>
       </c>
       <c r="D34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I34,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L34,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J34,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M34,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F34" s="35">
@@ -6316,15 +6449,15 @@
         <v/>
       </c>
       <c r="G34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L34,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O34,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M34,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P34,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O34,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R34,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J34" s="35">
@@ -6332,11 +6465,11 @@
         <v/>
       </c>
       <c r="K34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P34,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S34,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q34,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T34,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M34" s="35">
@@ -6344,15 +6477,15 @@
         <v/>
       </c>
       <c r="N34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R34,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U34,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S34,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V34,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T34,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W34,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q34" s="35">
@@ -6372,7 +6505,7 @@
         <v/>
       </c>
       <c r="U34" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B34="","",COUNTBLANK('1-UseCase ทั้งหมด'!I34)+COUNTBLANK('1-UseCase ทั้งหมด'!J34)+COUNTBLANK('1-UseCase ทั้งหมด'!L34)+COUNTBLANK('1-UseCase ทั้งหมด'!M34)+COUNTBLANK('1-UseCase ทั้งหมด'!O34)+COUNTBLANK('1-UseCase ทั้งหมด'!P34)+COUNTBLANK('1-UseCase ทั้งหมด'!Q34)+COUNTBLANK('1-UseCase ทั้งหมด'!R34)+COUNTBLANK('1-UseCase ทั้งหมด'!S34)+COUNTBLANK('1-UseCase ทั้งหมด'!T34))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B34="","",COUNTBLANK('1-UseCase ทั้งหมด'!L34)+COUNTBLANK('1-UseCase ทั้งหมด'!M34)+COUNTBLANK('1-UseCase ทั้งหมด'!O34)+COUNTBLANK('1-UseCase ทั้งหมด'!P34)+COUNTBLANK('1-UseCase ทั้งหมด'!R34)+COUNTBLANK('1-UseCase ทั้งหมด'!S34)+COUNTBLANK('1-UseCase ทั้งหมด'!T34)+COUNTBLANK('1-UseCase ทั้งหมด'!U34)+COUNTBLANK('1-UseCase ทั้งหมด'!V34)+COUNTBLANK('1-UseCase ทั้งหมด'!W34))</f>
         <v/>
       </c>
     </row>
@@ -6390,11 +6523,11 @@
         <v/>
       </c>
       <c r="D35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I35,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L35,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J35,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M35,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F35" s="35">
@@ -6402,15 +6535,15 @@
         <v/>
       </c>
       <c r="G35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L35,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O35,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M35,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P35,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O35,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R35,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J35" s="35">
@@ -6418,11 +6551,11 @@
         <v/>
       </c>
       <c r="K35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P35,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S35,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q35,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T35,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M35" s="35">
@@ -6430,15 +6563,15 @@
         <v/>
       </c>
       <c r="N35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R35,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U35,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S35,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V35,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T35,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W35,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q35" s="35">
@@ -6458,7 +6591,7 @@
         <v/>
       </c>
       <c r="U35" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B35="","",COUNTBLANK('1-UseCase ทั้งหมด'!I35)+COUNTBLANK('1-UseCase ทั้งหมด'!J35)+COUNTBLANK('1-UseCase ทั้งหมด'!L35)+COUNTBLANK('1-UseCase ทั้งหมด'!M35)+COUNTBLANK('1-UseCase ทั้งหมด'!O35)+COUNTBLANK('1-UseCase ทั้งหมด'!P35)+COUNTBLANK('1-UseCase ทั้งหมด'!Q35)+COUNTBLANK('1-UseCase ทั้งหมด'!R35)+COUNTBLANK('1-UseCase ทั้งหมด'!S35)+COUNTBLANK('1-UseCase ทั้งหมด'!T35))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B35="","",COUNTBLANK('1-UseCase ทั้งหมด'!L35)+COUNTBLANK('1-UseCase ทั้งหมด'!M35)+COUNTBLANK('1-UseCase ทั้งหมด'!O35)+COUNTBLANK('1-UseCase ทั้งหมด'!P35)+COUNTBLANK('1-UseCase ทั้งหมด'!R35)+COUNTBLANK('1-UseCase ทั้งหมด'!S35)+COUNTBLANK('1-UseCase ทั้งหมด'!T35)+COUNTBLANK('1-UseCase ทั้งหมด'!U35)+COUNTBLANK('1-UseCase ทั้งหมด'!V35)+COUNTBLANK('1-UseCase ทั้งหมด'!W35))</f>
         <v/>
       </c>
     </row>
@@ -6476,11 +6609,11 @@
         <v/>
       </c>
       <c r="D36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!I36,DATA!$R$4:$R$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$R$30:$R$34,MATCH('1-UseCase ทั้งหมด'!L36,DATA!$R$4:$R$8,0)),""))</f>
         <v/>
       </c>
       <c r="E36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!J36,DATA!$S$4:$S$8,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$S$30:$S$34,MATCH('1-UseCase ทั้งหมด'!M36,DATA!$S$4:$S$8,0)),""))</f>
         <v/>
       </c>
       <c r="F36" s="35">
@@ -6488,15 +6621,15 @@
         <v/>
       </c>
       <c r="G36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!L36,DATA!$B$4:$B$9,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$B$30:$B$35,MATCH('1-UseCase ทั้งหมด'!O36,DATA!$B$4:$B$9,0)),""))</f>
         <v/>
       </c>
       <c r="H36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!M36,DATA!$C$4:$C$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$C$30:$C$33,MATCH('1-UseCase ทั้งหมด'!P36,DATA!$C$4:$C$7,0)),""))</f>
         <v/>
       </c>
       <c r="I36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!O36,DATA!$D$4:$D$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$D$30:$D$32,MATCH('1-UseCase ทั้งหมด'!R36,DATA!$D$4:$D$6,0)),""))</f>
         <v/>
       </c>
       <c r="J36" s="35">
@@ -6504,11 +6637,11 @@
         <v/>
       </c>
       <c r="K36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!P36,DATA!$E$4:$E$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$E$30:$E$33,MATCH('1-UseCase ทั้งหมด'!S36,DATA!$E$4:$E$7,0)),""))</f>
         <v/>
       </c>
       <c r="L36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!Q36,DATA!$F$4:$F$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$F$30:$F$32,MATCH('1-UseCase ทั้งหมด'!T36,DATA!$F$4:$F$6,0)),""))</f>
         <v/>
       </c>
       <c r="M36" s="35">
@@ -6516,15 +6649,15 @@
         <v/>
       </c>
       <c r="N36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!R36,DATA!$G$4:$G$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$G$30:$G$32,MATCH('1-UseCase ทั้งหมด'!U36,DATA!$G$4:$G$6,0)),""))</f>
         <v/>
       </c>
       <c r="O36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!S36,DATA!$H$4:$H$6,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$H$30:$H$32,MATCH('1-UseCase ทั้งหมด'!V36,DATA!$H$4:$H$6,0)),""))</f>
         <v/>
       </c>
       <c r="P36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!T36,DATA!$I$4:$I$7,0)),""))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",IFERROR(INDEX(DATA!$I$30:$I$33,MATCH('1-UseCase ทั้งหมด'!W36,DATA!$I$4:$I$7,0)),""))</f>
         <v/>
       </c>
       <c r="Q36" s="35">
@@ -6544,7 +6677,7 @@
         <v/>
       </c>
       <c r="U36" s="34">
-        <f>IF('1-UseCase ทั้งหมด'!B36="","",COUNTBLANK('1-UseCase ทั้งหมด'!I36)+COUNTBLANK('1-UseCase ทั้งหมด'!J36)+COUNTBLANK('1-UseCase ทั้งหมด'!L36)+COUNTBLANK('1-UseCase ทั้งหมด'!M36)+COUNTBLANK('1-UseCase ทั้งหมด'!O36)+COUNTBLANK('1-UseCase ทั้งหมด'!P36)+COUNTBLANK('1-UseCase ทั้งหมด'!Q36)+COUNTBLANK('1-UseCase ทั้งหมด'!R36)+COUNTBLANK('1-UseCase ทั้งหมด'!S36)+COUNTBLANK('1-UseCase ทั้งหมด'!T36))</f>
+        <f>IF('1-UseCase ทั้งหมด'!B36="","",COUNTBLANK('1-UseCase ทั้งหมด'!L36)+COUNTBLANK('1-UseCase ทั้งหมด'!M36)+COUNTBLANK('1-UseCase ทั้งหมด'!O36)+COUNTBLANK('1-UseCase ทั้งหมด'!P36)+COUNTBLANK('1-UseCase ทั้งหมด'!R36)+COUNTBLANK('1-UseCase ทั้งหมด'!S36)+COUNTBLANK('1-UseCase ทั้งหมด'!T36)+COUNTBLANK('1-UseCase ทั้งหมด'!U36)+COUNTBLANK('1-UseCase ทั้งหมด'!V36)+COUNTBLANK('1-UseCase ทั้งหมด'!W36))</f>
         <v/>
       </c>
     </row>
@@ -6586,7 +6719,7 @@
     <row r="43">
       <c r="A43" s="38" t="inlineStr">
         <is>
-          <t>•  ช่องบังคับ 10 ช่อง = เวลาที่ใช้ / มูลค่าความเสียหาย / รูปแบบข้อมูล / ข้อมูลย้อนหลัง / สิทธิ์ใช้ข้อมูล / ระบบเดิม / คนดูแลต่อ / ผลกระทบถ้า AI ผิด / การตรวจซ้ำ / ระดับความลับ</t>
+          <t>•  ช่องบังคับ 10 ช่อง (คอลัมน์ L M O P R S T U V W) = เวลาที่ใช้ / มูลค่าความเสียหาย / รูปแบบข้อมูล / ข้อมูลย้อนหลัง / สิทธิ์ใช้ข้อมูล / ระบบเดิม / คนดูแลต่อ / ผลกระทบถ้า AI ผิด / การตรวจซ้ำ / ระดับความลับ</t>
         </is>
       </c>
     </row>
@@ -6977,7 +7110,7 @@
       </c>
       <c r="V4" s="42" t="inlineStr">
         <is>
-          <t>น้อยกว่า 100 รายการ</t>
+          <t>น้อยกว่า 100 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
         </is>
       </c>
       <c r="W4" s="42" t="inlineStr">
@@ -7137,7 +7270,7 @@
       </c>
       <c r="V5" s="42" t="inlineStr">
         <is>
-          <t>100 - 1,000 รายการ</t>
+          <t>100 - 1,000 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
         </is>
       </c>
       <c r="W5" s="42" t="inlineStr">
@@ -7297,7 +7430,7 @@
       </c>
       <c r="V6" s="42" t="inlineStr">
         <is>
-          <t>1,000 - 10,000 รายการ</t>
+          <t>1,000 - 10,000 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
         </is>
       </c>
       <c r="W6" s="42" t="inlineStr">
@@ -7417,7 +7550,7 @@
       </c>
       <c r="V7" s="42" t="inlineStr">
         <is>
-          <t>10,000 - 100,000 รายการ</t>
+          <t>10,000 - 100,000 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
         </is>
       </c>
       <c r="W7" s="42" t="inlineStr">
@@ -7507,7 +7640,7 @@
       </c>
       <c r="V8" s="42" t="inlineStr">
         <is>
-          <t>มากกว่า 100,000 รายการ</t>
+          <t>มากกว่า 100,000 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
         </is>
       </c>
       <c r="X8" s="42" t="inlineStr">

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -1106,30 +1106,30 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="38" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="38" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="38" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
     <col width="34" customWidth="1" min="20" max="20"/>
-    <col width="36" customWidth="1" min="21" max="21"/>
-    <col width="34" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
-    <col width="26" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="36" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
@@ -1206,7 +1206,7 @@
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>ลำดับ</t>
         </is>
       </c>
       <c r="B5" s="21" t="inlineStr">
@@ -1221,130 +1221,123 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>ฝ่าย / แผนก</t>
+          <t>หน่วยงานที่ใช้งาน</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>ผู้รับผิดชอบ
-(Owner)</t>
+          <t>ผู้รับผิดชอบ (Owner)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t>QWP อ้างอิง
+          <t>เอกสาร QWP ที่อ้างอิง
 (รหัส / ชื่อเอกสาร)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
         <is>
-          <t>kQI / QI ที่เกี่ยวข้อง</t>
+          <t>ตัวชี้วัด kQI / QI ที่เกี่ยวข้อง</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>ขั้นตอนที่เกี่ยวข้อง
-(ขั้นตอนใน SQP ที่ use case นี้แตะ)</t>
+          <t>ขั้นตอนใน SQP ที่เกี่ยวข้อง</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
         <is>
-          <t>ปัญหาที่ต้องการแก้
-(ทำไมถึงอยากได้ AI)</t>
+          <t>ปัญหาหรือข้อจำกัดของงานในปัจจุบัน</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>วิธีการทำงานปัจจุบัน
-Existing Work
-(ตอนนี้ทำยังไง ใครทำ)</t>
+          <t>วิธีการปฏิบัติงานในปัจจุบัน
+(Existing Work)</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
         <is>
-          <t>แนวทางหลังนำ AI มาใช้
-Description for Redesign
-(อยากให้ AI ทำอะไร ผลลัพธ์ที่คาดหวัง)</t>
+          <t>แนวทางการทำงานหลังนำ AI มาใช้
+(Description for Redesign)</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t>เวลาที่ใช้กับงานนี้ตอนนี้ (ยังไม่ใช้ AI)
-นับรวมทุกคนในแผนก เช่น 3 คน x 6 ชม. = 18 ชม./สัปดาห์</t>
+          <t>ปริมาณเวลาที่ใช้กับงานนี้ในปัจจุบัน
+(รวมทุกคนในหน่วยงาน)</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
         <is>
-          <t>มูลค่าความเสียหาย/ของเสียต่อปี
-(ของเสีย เคลม งานแก้ ค่าปรับ)</t>
+          <t>มูลค่าความสูญเสียต่อปี
+(ของเสีย เคลม งานแก้ไข ค่าปรับ)</t>
         </is>
       </c>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t>ข้อมูลที่มีอยู่ตอนนี้
-Data Available
-(มีอะไร เก็บที่ไหน ใครเก็บ)</t>
+          <t>ข้อมูลที่มีอยู่ในปัจจุบัน
+(Data Available)</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
         <is>
-          <t>ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน</t>
+          <t>รูปแบบการจัดเก็บข้อมูลในปัจจุบัน</t>
         </is>
       </c>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t>มีข้อมูลย้อนหลังนานแค่ไหน</t>
+          <t>ระยะเวลาข้อมูลย้อนหลังที่มี</t>
         </is>
       </c>
       <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>ปริมาณข้อมูลโดยประมาณ
-นับเป็นรายการ : รูป / ใบ / ไฟล์ / ครั้ง / ล็อต แล้วแต่งาน
-(เอาเฉพาะที่รู้คำตอบแล้ว)</t>
+นับเป็นรายการ : ภาพ / ใบ / ไฟล์ / ครั้ง / ล็อต
+(เฉพาะข้อมูลที่ทราบผลลัพธ์แล้ว)</t>
         </is>
       </c>
       <c r="R5" s="21" t="inlineStr">
         <is>
-          <t>สิทธิ์นำข้อมูลมาใช้
-(เจ้าของข้อมูลยอมให้เอามาพัฒนา AI มั้ย)</t>
+          <t>สิทธิ์ในการนำข้อมูลมาใช้พัฒนา AI</t>
         </is>
       </c>
       <c r="S5" s="21" t="inlineStr">
         <is>
-          <t>ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย
-(ERP / MES / ระบบที่ใช้อยู่)</t>
+          <t>ความจำเป็นในการเชื่อมต่อกับระบบเดิม
+(ERP / MES / ระบบที่ใช้งานอยู่)</t>
         </is>
       </c>
       <c r="T5" s="21" t="inlineStr">
         <is>
-          <t>มีคนดูแลระบบต่อหลังส่งมอบมั้ย</t>
+          <t>ผู้ดูแลระบบหลังส่งมอบ</t>
         </is>
       </c>
       <c r="U5" s="21" t="inlineStr">
         <is>
-          <t>ถ้า AI ตอบผิด จะเกิดอะไรขึ้น</t>
+          <t>ผลกระทบเมื่อ AI ให้ผลลัพธ์ผิดพลาด</t>
         </is>
       </c>
       <c r="V5" s="21" t="inlineStr">
         <is>
-          <t>ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย</t>
+          <t>ความจำเป็นในการตรวจสอบผลลัพธ์โดยบุคลากร</t>
         </is>
       </c>
       <c r="W5" s="21" t="inlineStr">
         <is>
-          <t>ข้อมูลชุดนี้ลับแค่ไหน</t>
+          <t>ระดับชั้นความลับของข้อมูล</t>
         </is>
       </c>
       <c r="X5" s="21" t="inlineStr">
         <is>
-          <t>ความสำคัญที่แผนกอยากได้
-(ความเห็นแผนก ไม่นำไปคิดคะแนน)</t>
+          <t>ระดับความสำคัญตามความเห็นหน่วยงาน
+(ไม่นำไปคิดคะแนน)</t>
         </is>
       </c>
       <c r="Y5" s="21" t="inlineStr">
         <is>
-          <t>ต้องการใช้งานภายใน
-(ไตรมาส/ปี)</t>
+          <t>กำหนดเวลาที่ต้องการใช้งาน
+(ไตรมาส / ปี)</t>
         </is>
       </c>
       <c r="Z5" s="21" t="inlineStr">
@@ -1394,92 +1387,92 @@
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t>พนักงาน QC ตรวจชิ้นงานด้วยตาเปล่า เหนื่อยล้าตอนบ่าย ทำให้ของเสียหลุดไปถึงลูกค้าเดือนละ 2-3 ครั้ง</t>
+          <t>พนักงาน QC ตรวจชิ้นงานด้วยสายตา เกิดความล้าในช่วงบ่าย ทำให้ของเสียหลุดถึงลูกค้าเดือนละ 2-3 ครั้ง</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>QC 3 คน ผลัดกันตรวจทุกล็อตด้วยตาเปล่า เทียบกับตัวอย่างมาตรฐาน บันทึกผลลงกระดาษ</t>
+          <t>พนักงาน QC 3 คน ผลัดกันตรวจทุกล็อตด้วยสายตา เทียบกับชิ้นงานตัวอย่างมาตรฐาน และบันทึกผลลงแบบฟอร์มกระดาษ</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t>ติดกล้องที่สายพาน ให้ AI แยกชิ้นงานดี/เสียอัตโนมัติแบบ Real-time ชิ้นที่ AI ไม่มั่นใจค่อยส่งให้คนตรวจ และบันทึกผลลงระบบแทนกระดาษ</t>
+          <t>ติดตั้งกล้องที่สายพาน ให้ AI คัดแยกชิ้นงานดีและเสียอัตโนมัติแบบทันที ชิ้นงานที่ AI ไม่มั่นใจจึงส่งให้บุคลากรตรวจซ้ำ และบันทึกผลเข้าระบบแทนกระดาษ</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
         <is>
-          <t>มากกว่า 40 ชม./สัปดาห์  (มากกว่า 1 คนเต็มเวลา)</t>
+          <t>มากกว่า 40 ชั่วโมง/สัปดาห์ (มากกว่า 1 คนเต็มเวลา)</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>5 แสน - 2 ล้านบาท/ปี</t>
+          <t>500,000 - 2,000,000 บาท/ปี</t>
         </is>
       </c>
       <c r="N6" s="22" t="inlineStr">
         <is>
-          <t>มีรูปถ่ายชิ้นงานดี/เสียเก็บไว้ในมือถือหัวหน้ากะ ประมาณ 2 ปี และใบบันทึกผลตรวจเป็นกระดาษ</t>
+          <t>มีภาพถ่ายชิ้นงานดีและเสียจัดเก็บไว้ในโทรศัพท์ของหัวหน้ากะ ประมาณ 2 ปี และแบบฟอร์มบันทึกผลตรวจแบบกระดาษ</t>
         </is>
       </c>
       <c r="O6" s="22" t="inlineStr">
         <is>
-          <t>รูปภาพ / ภาพถ่าย</t>
+          <t>ภาพถ่าย / ไฟล์รูปภาพ</t>
         </is>
       </c>
       <c r="P6" s="22" t="inlineStr">
         <is>
-          <t>1 - 3 ปี - พอใช้ได้</t>
+          <t>1 - 3 ปี - เพียงพอในระดับหนึ่ง</t>
         </is>
       </c>
       <c r="Q6" s="22" t="inlineStr">
         <is>
-          <t>ประมาณ 4,000 รูป (ดี 3,000 / เสีย 1,000)</t>
+          <t>ประมาณ 4,000 ภาพ (ดี 3,000 / เสีย 1,000)</t>
         </is>
       </c>
       <c r="R6" s="22" t="inlineStr">
         <is>
-          <t>ได้ทันที - ข้อมูลอยู่ในมือแผนกเราเอง</t>
+          <t>ได้ทันที - ข้อมูลอยู่ในความดูแลของหน่วยงาน</t>
         </is>
       </c>
       <c r="S6" s="22" t="inlineStr">
         <is>
-          <t>ไม่มี - AI ทำงานแยกเดี่ยวได้เลย ไม่ต้องยุ่งกับระบบไหน</t>
+          <t>ไม่จำเป็น - ระบบทำงานแยกอิสระได้</t>
         </is>
       </c>
       <c r="T6" s="22" t="inlineStr">
         <is>
-          <t>มี - มีคนในแผนกรับดูแลต่อได้ (ระบุชื่อในหมายเหตุ)</t>
+          <t>มี - หน่วยงานมีผู้รับผิดชอบดูแลต่อ (ระบุชื่อในหมายเหตุ)</t>
         </is>
       </c>
       <c r="U6" s="22" t="inlineStr">
         <is>
-          <t>สูง - ของเสียหลุดถึงลูกค้า / อันตราย / ผิดกฎหมาย</t>
+          <t>สูง - ของเสียถึงมือลูกค้า เกิดอันตราย หรือผิดข้อกำหนดกฎหมาย</t>
         </is>
       </c>
       <c r="V6" s="22" t="inlineStr">
         <is>
-          <t>สุ่มตรวจบางส่วน - ตรวจเฉพาะที่ AI ไม่มั่นใจ</t>
+          <t>สุ่มตรวจบางส่วน - เฉพาะรายการที่ AI ไม่มั่นใจ</t>
         </is>
       </c>
       <c r="W6" s="22" t="inlineStr">
         <is>
-          <t>ข้อมูลภายใน - ห้ามออกนอกบริษัท</t>
+          <t>ภายในองค์กร - ห้ามเผยแพร่ออกนอกบริษัท</t>
         </is>
       </c>
       <c r="X6" s="22" t="inlineStr">
         <is>
-          <t>สูง - ต้องการด่วน</t>
+          <t>สูง - ต้องการเร่งด่วน</t>
         </is>
       </c>
       <c r="Y6" s="22" t="inlineStr">
         <is>
-          <t>Q2 2570</t>
+          <t>ไตรมาส 2 ปี 2570</t>
         </is>
       </c>
       <c r="Z6" s="22" t="inlineStr">
         <is>
-          <t>คุณสมชายเคยอบรม Python มาแล้ว</t>
+          <t>คุณสมชายผ่านการอบรม Python มาแล้ว</t>
         </is>
       </c>
     </row>
@@ -2339,37 +2332,37 @@
     <dataValidation sqref="C7:C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="บริษัท" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$A$4:$A$8</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="เวลาที่ใช้กับงานนี้ตอนนี้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="เวลาที่ใช้กับงานนี้ในปัจจุบัน" prompt="เวลาที่คนใช้ทำงานนี้ด้วยวิธีเดิม รวมทุกคนในหน่วยงาน&#10;&#10;เช่น 3 คน คนละ 6 ชั่วโมง/สัปดาห์ = 18 ชั่วโมง/สัปดาห์&#10;&#10;ยังไม่ได้ใช้ AI ช่วย" type="list">
       <formula1>DATA!$R$4:$R$8</formula1>
     </dataValidation>
-    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มูลค่าความเสียหาย/ของเสียต่อปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มูลค่าความสูญเสียต่อปี" prompt="ความสูญเสียที่เกิดจากปัญหานี้ในปัจจุบัน&#10;&#10;ถ้าประเมินเป็นตัวเงินไม่ได้ ให้เลือกตัวเลือกแรก&#10;ระบบจะใช้เฉพาะชั่วโมงคิดคะแนน ไม่ได้หักคะแนน" type="list">
       <formula1>DATA!$S$4:$S$8</formula1>
     </dataValidation>
-    <dataValidation sqref="O7:O36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="O7:O36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="รูปแบบการจัดเก็บข้อมูลปัจจุบัน" prompt="ข้อมูลที่จะใช้พัฒนา AI เก็บอยู่ในรูปแบบไหน&#10;&#10;กระดาษ = ต้องแปลงเป็นดิจิทัลก่อน ใช้เวลาเป็นเดือน&#10;ฐานข้อมูลในระบบ = ดึงอัตโนมัติได้ เริ่มได้เร็วที่สุด" type="list">
       <formula1>DATA!$B$4:$B$9</formula1>
     </dataValidation>
-    <dataValidation sqref="P7:P36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีข้อมูลย้อนหลังนานแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="P7:P36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ระยะเวลาข้อมูลย้อนหลังที่มี" prompt="มีข้อมูลเก็บย้อนหลังมานานแค่ไหน&#10;&#10;ยิ่งนาน ยิ่งมีตัวอย่างให้ AI เรียนรู้มาก&#10;แต่ต้องดูปริมาณด้วย 3 ปีที่มีปีละ 10 รายการ ก็ยังไม่พอ" type="list">
       <formula1>DATA!$C$4:$C$7</formula1>
     </dataValidation>
-    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="สิทธิ์นำข้อมูลมาใช้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="สิทธิ์ในการนำข้อมูลมาใช้" prompt="ไม่ได้ถามว่ามีข้อมูลมั้ย แต่ถามว่าขอมาใช้ได้จริงมั้ย&#10;&#10;เจอบ่อยว่ามีข้อมูลครบแต่ใช้ไม่ได้ เพราะเป็นของลูกค้า&#10;ที่มีสัญญา หรืออยู่ในเครื่องจักรที่ผู้ขายล็อกไว้" type="list">
       <formula1>DATA!$D$4:$D$6</formula1>
     </dataValidation>
-    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="การเชื่อมต่อกับระบบเดิม" prompt="ลองถามตัวเองว่า ถ้า export เป็นไฟล์มาให้ AI ทุกเช้า&#10;แล้วเอาผลไปกรอกเข้าระบบเองทีหลัง งานนี้ยังใช้ได้มั้ย&#10;&#10;ถ้าใช้ได้ = เลือก จำเป็นบางส่วน&#10;ถ้าต้องอัตโนมัติทันทีเท่านั้น = เลือก จำเป็น" type="list">
       <formula1>DATA!$E$4:$E$7</formula1>
     </dataValidation>
-    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มีคนดูแลระบบต่อหลังส่งมอบมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ผู้ดูแลระบบหลังส่งมอบ" prompt="มีคนในหน่วยงานรับดูแลระบบต่อหลังส่งมอบหรือไม่&#10;&#10;เป็นตัวชี้ขาดว่าระบบจะอยู่รอดหลังโครงการจบ&#10;ถ้ามี ระบุชื่อไว้ในช่องหมายเหตุด้วย" type="list">
       <formula1>DATA!$F$4:$F$6</formula1>
     </dataValidation>
-    <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ถ้า AI ตอบผิด จะเกิดอะไรขึ้น" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ผลกระทบเมื่อ AI ผิดพลาด" prompt="ถ้า AI ให้ผลผิด จะเกิดผลกระทบระดับไหน&#10;&#10;chatbot ตอบผิด ต่างจากตรวจคุณภาพผิดแล้วส่งของเสียถึงลูกค้า" type="list">
       <formula1>DATA!$G$4:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="V7:V36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="V7:V36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="การตรวจสอบผลลัพธ์โดยบุคลากร" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$H$4:$H$6</formula1>
     </dataValidation>
-    <dataValidation sqref="W7:W36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ข้อมูลชุดนี้ลับแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="W7:W36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ระดับชั้นความลับของข้อมูล" prompt="ช่องนี้ถูกใช้ 2 ที่&#10;&#10;คิดคะแนนความเสี่ยง&#10;และกำหนดว่าต้องเข้ารหัส จำกัดสิทธิ์ และเก็บ log ระดับไหน" type="list">
       <formula1>DATA!$I$4:$I$7</formula1>
     </dataValidation>
-    <dataValidation sqref="X7:X36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความสำคัญที่แผนกอยากได้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="X7:X36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ระดับความสำคัญตามความเห็นผู้ใช้" prompt="ความเห็นของหน่วยงาน ไม่ได้นำไปคิดคะแนน&#10;&#10;เก็บไว้เทียบกับคะแนนที่ระบบคำนวณ&#10;ถ้าต่างกันมาก แปลว่าต้องคุยกันว่าเพราะอะไร" type="list">
       <formula1>DATA!$J$4:$J$6</formula1>
     </dataValidation>
     <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปัญหาที่ต้องการแก้" prompt="ตอนนี้เจอปัญหาอะไร ทำไมถึงอยากได้ AI มาช่วย&#10;เช่น ตรวจด้วยตาเปล่าทำให้ของเสียหลุดถึงลูกค้าเดือนละ 2-3 ครั้ง"/>
@@ -2388,32 +2381,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="44" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="30" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="42" customWidth="1" min="21" max="21"/>
-    <col width="42" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="32" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="44" customWidth="1" min="22" max="22"/>
+    <col width="44" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2440,7 +2434,7 @@
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>โซน A : ปริมาณงาน  (แผนกกรอก)</t>
+          <t>โซน A : ปริมาณงาน  (หน่วยงานผู้ใช้กรอก)</t>
         </is>
       </c>
       <c r="E4" s="12" t="n"/>
@@ -2448,37 +2442,38 @@
       <c r="G4" s="12" t="n"/>
       <c r="H4" s="12" t="n"/>
       <c r="I4" s="12" t="n"/>
-      <c r="J4" s="15" t="inlineStr">
-        <is>
-          <t>โซน A : ความต้องการใช้งาน  (แผนกกรอก)</t>
-        </is>
-      </c>
-      <c r="K4" s="16" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>โซน A : ความต้องการใช้งาน  (หน่วยงานผู้ใช้กรอก)</t>
+        </is>
+      </c>
       <c r="L4" s="16" t="n"/>
       <c r="M4" s="16" t="n"/>
-      <c r="N4" s="19" t="inlineStr">
-        <is>
-          <t>โซน A : ข้อกำหนดและงบ  (แผนกกรอก)</t>
-        </is>
-      </c>
-      <c r="O4" s="20" t="n"/>
+      <c r="N4" s="16" t="n"/>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>โซน A : ข้อกำหนดและงบประมาณ  (หน่วยงานผู้ใช้กรอก)</t>
+        </is>
+      </c>
       <c r="P4" s="20" t="n"/>
       <c r="Q4" s="20" t="n"/>
-      <c r="R4" s="9" t="inlineStr">
-        <is>
-          <t>โซน B : ทีม AI / IT เติมให้ทีหลัง — แผนกไม่ต้องกรอก</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="n"/>
+      <c r="R4" s="20" t="n"/>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>โซน B : ทีม AI / IT ดำเนินการภายหลัง — หน่วยงานผู้ใช้ไม่ต้องกรอก</t>
+        </is>
+      </c>
       <c r="T4" s="10" t="n"/>
       <c r="U4" s="10" t="n"/>
       <c r="V4" s="10" t="n"/>
       <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>ลำดับ</t>
         </is>
       </c>
       <c r="B5" s="21" t="inlineStr">
@@ -2488,113 +2483,121 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>ฝ่าย / แผนก</t>
+          <t>หน่วยงานที่ใช้งาน</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>งานนี้เริ่มทำงานยังไง</t>
+          <t>ลักษณะการเริ่มทำงานของระบบ</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>ข้อมูลที่ AI ต้องอ่าน/ดู เป็นแบบไหน</t>
+          <t>ประเภทข้อมูลนำเข้า (Input)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t>จำนวนคนที่ใช้งาน/วัน</t>
+          <t>ประเภทงาน AI
+(ระบบคำนวณให้จากช่องซ้าย)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
         <is>
-          <t>ช่วงพีค มีคนใช้พร้อมกันมากสุดกี่คน</t>
+          <t>จำนวนผู้ใช้งานต่อวัน</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>AI ต้องประมวลผลกี่รายการ/วัน
+          <t>จำนวนผู้ใช้งานพร้อมกันสูงสุด
+(Peak Concurrent)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>ปริมาณรายการที่ต้องประมวลผลต่อวัน
 1 รายการ = 1 ชิ้น / ล็อต / คำถาม / เคส แล้วแต่ประเภทงาน</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>จำนวนกล้อง/จุดตรวจ
-ที่ทำงานพร้อมกัน (งานภาพ)</t>
-        </is>
-      </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>ภาษาที่ต้องการ</t>
+          <t>จำนวนจุดตรวจหรือกล้องที่ทำงานพร้อมกัน
+(งานประมวลผลภาพ)</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
         <is>
-          <t>รอผลได้นานแค่ไหน</t>
+          <t>ภาษาที่ต้องรองรับ</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t>ต้องใช้งานช่วงเวลาไหน</t>
+          <t>เวลาตอบสนองที่ยอมรับได้</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
         <is>
-          <t>ถ้าช่วงไหนคนใช้เยอะ แล้วงานนี้ช้าลง
-จะเป็นปัญหามั้ย</t>
+          <t>ช่วงเวลาที่ต้องให้บริการ</t>
         </is>
       </c>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
+          <t>ผลกระทบเมื่อระบบตอบสนองช้าลง
+ในช่วงที่มีการใช้งานหนาแน่น</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
         <is>
+          <t>ระยะเวลาการจัดเก็บข้อมูล</t>
+        </is>
+      </c>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
           <t>งบประมาณที่ตั้งไว้ (บาท)
-- ถ้ามี</t>
-        </is>
-      </c>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t>ข้อจำกัดอื่นๆ / หมายเหตุ</t>
+หากมี</t>
         </is>
       </c>
       <c r="Q5" s="21" t="inlineStr">
         <is>
-          <t>ผู้ให้ข้อมูล (แผนก)</t>
+          <t>ข้อจำกัดอื่นๆ และหมายเหตุ</t>
         </is>
       </c>
       <c r="R5" s="21" t="inlineStr">
         <is>
-          <t>ขนาดข้อมูล Input/วัน</t>
+          <t>ผู้ให้ข้อมูล (หน่วยงาน)</t>
         </is>
       </c>
       <c r="S5" s="21" t="inlineStr">
         <is>
+          <t>ปริมาณข้อมูลนำเข้าต่อวัน</t>
+        </is>
+      </c>
+      <c r="T5" s="21" t="inlineStr">
+        <is>
           <t>ขนาดคลังเอกสารทั้งหมด
-(สำหรับงานค้นหา/RAG)</t>
-        </is>
-      </c>
-      <c r="T5" s="21" t="inlineStr">
-        <is>
-          <t>ความละเอียดรูป</t>
+(สำหรับงานสืบค้น / RAG)</t>
         </is>
       </c>
       <c r="U5" s="21" t="inlineStr">
         <is>
-          <t>ติดตั้งแบบไหน
-(server ตั้งที่เดียว ไม่ใช้ Cloud)</t>
+          <t>ความละเอียดของภาพ</t>
         </is>
       </c>
       <c r="V5" s="21" t="inlineStr">
         <is>
-          <t>ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย</t>
+          <t>รูปแบบการติดตั้ง
+(Server ภายในองค์กรเท่านั้น)</t>
         </is>
       </c>
       <c r="W5" s="21" t="inlineStr">
         <is>
-          <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
+          <t>ความจำเป็นในการปรับโมเดล
+ด้วยข้อมูลขององค์กร</t>
+        </is>
+      </c>
+      <c r="X5" s="21" t="inlineStr">
+        <is>
+          <t>ความถี่ในการฝึกโมเดลใหม่</t>
         </is>
       </c>
     </row>
@@ -2613,98 +2616,102 @@
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>ทำงานอัตโนมัติต่อเนื่อง - ระบบสั่งเอง ไม่มีคนกด</t>
+          <t>ทำงานอัตโนมัติต่อเนื่อง - ระบบทำงานเอง ไม่มีผู้เรียกใช้</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>รูปภาพ</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
+          <t>ภาพถ่าย</t>
+        </is>
+      </c>
+      <c r="F6" s="24">
+        <f>IF($E6="","",IF($E6="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E6="ภาพถ่าย","งานภาพ (Vision)",IF($E6="เสียง","งานเสียง",IF($E6="วิดีโอ","งานภาพ (Vision)",IF($E6="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E6="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>1 - 10 คน</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>1 - 2 คน</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t>1,000 - 10,000 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
-        </is>
-      </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
+          <t>1,000 - 10,000 รายการ</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
           <t>2 - 3 จุด</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
-        <is>
-          <t>ไม่เกี่ยวกับภาษา</t>
-        </is>
-      </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t>Real-time (0 - 2 วินาที)</t>
+          <t>ไม่เกี่ยวข้องกับภาษา</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
         <is>
-          <t>Business Hour (8:00 - 18:00)</t>
+          <t>ทันที - ไม่เกิน 2 วินาที (ตอบกลับในกระบวนการทันที)</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>เป็นปัญหา - งานนี้ช้าหรือหยุดไม่ได้เลย (อยู่ในสายการผลิต)</t>
+          <t>เวลาทำการ 8:00 - 18:00 น.</t>
         </is>
       </c>
       <c r="N6" s="22" t="inlineStr">
         <is>
+          <t>กระทบมาก - ไม่สามารถล่าช้าหรือหยุดได้ (อยู่ในสายการผลิต)</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
           <t>2 - 3 ปี</t>
         </is>
       </c>
-      <c r="O6" s="22" t="n">
+      <c r="P6" s="22" t="n">
         <v>500000</v>
       </c>
-      <c r="P6" s="22" t="inlineStr">
-        <is>
-          <t>ต้องติดกล้องที่สายพานเดิม มีพื้นที่จำกัด</t>
-        </is>
-      </c>
       <c r="Q6" s="22" t="inlineStr">
         <is>
+          <t>ต้องติดตั้งกล้องที่สายพานเดิม พื้นที่ติดตั้งจำกัด</t>
+        </is>
+      </c>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
           <t>คุณสมชาย</t>
         </is>
       </c>
-      <c r="R6" s="25" t="inlineStr">
+      <c r="S6" s="25" t="inlineStr">
         <is>
           <t>1 - 10 GB</t>
         </is>
       </c>
-      <c r="S6" s="25" t="inlineStr">
-        <is>
-          <t>ไม่เกี่ยวข้อง - ไม่ใช่งานค้นหาเอกสาร</t>
-        </is>
-      </c>
       <c r="T6" s="25" t="inlineStr">
         <is>
-          <t>1 - 5 MP</t>
+          <t>ไม่เกี่ยวข้อง - ไม่ใช่งานสืบค้นเอกสาร</t>
         </is>
       </c>
       <c r="U6" s="25" t="inlineStr">
         <is>
-          <t>ต้องมีเครื่องที่หน้างาน - ติดข้างเครื่องจักร/สายพาน</t>
+          <t>1 - 5 ล้านพิกเซล</t>
         </is>
       </c>
       <c r="V6" s="25" t="inlineStr">
         <is>
-          <t>ต้อง Fine-tune - สอนด้วยข้อมูล/รูปของบริษัทเอง</t>
+          <t>ต้องติดตั้งที่หน้างาน - ติดตั้งข้างเครื่องจักรหรือสายพาน</t>
         </is>
       </c>
       <c r="W6" s="25" t="inlineStr">
+        <is>
+          <t>จำเป็น - ต้อง Fine-tune ด้วยข้อมูลหรือภาพขององค์กร</t>
+        </is>
+      </c>
+      <c r="X6" s="25" t="inlineStr">
         <is>
           <t>ทุกไตรมาส</t>
         </is>
@@ -2725,7 +2732,10 @@
       </c>
       <c r="D7" s="23" t="n"/>
       <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="n"/>
+      <c r="F7" s="26">
+        <f>IF($E7="","",IF($E7="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E7="ภาพถ่าย","งานภาพ (Vision)",IF($E7="เสียง","งานเสียง",IF($E7="วิดีโอ","งานภาพ (Vision)",IF($E7="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E7="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G7" s="23" t="n"/>
       <c r="H7" s="23" t="n"/>
       <c r="I7" s="23" t="n"/>
@@ -2737,12 +2747,13 @@
       <c r="O7" s="23" t="n"/>
       <c r="P7" s="23" t="n"/>
       <c r="Q7" s="23" t="n"/>
-      <c r="R7" s="27" t="n"/>
+      <c r="R7" s="23" t="n"/>
       <c r="S7" s="27" t="n"/>
       <c r="T7" s="27" t="n"/>
       <c r="U7" s="27" t="n"/>
       <c r="V7" s="27" t="n"/>
       <c r="W7" s="27" t="n"/>
+      <c r="X7" s="27" t="n"/>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="26">
@@ -2759,7 +2770,10 @@
       </c>
       <c r="D8" s="23" t="n"/>
       <c r="E8" s="23" t="n"/>
-      <c r="F8" s="23" t="n"/>
+      <c r="F8" s="26">
+        <f>IF($E8="","",IF($E8="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E8="ภาพถ่าย","งานภาพ (Vision)",IF($E8="เสียง","งานเสียง",IF($E8="วิดีโอ","งานภาพ (Vision)",IF($E8="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E8="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G8" s="23" t="n"/>
       <c r="H8" s="23" t="n"/>
       <c r="I8" s="23" t="n"/>
@@ -2771,12 +2785,13 @@
       <c r="O8" s="23" t="n"/>
       <c r="P8" s="23" t="n"/>
       <c r="Q8" s="23" t="n"/>
-      <c r="R8" s="27" t="n"/>
+      <c r="R8" s="23" t="n"/>
       <c r="S8" s="27" t="n"/>
       <c r="T8" s="27" t="n"/>
       <c r="U8" s="27" t="n"/>
       <c r="V8" s="27" t="n"/>
       <c r="W8" s="27" t="n"/>
+      <c r="X8" s="27" t="n"/>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="26">
@@ -2793,7 +2808,10 @@
       </c>
       <c r="D9" s="23" t="n"/>
       <c r="E9" s="23" t="n"/>
-      <c r="F9" s="23" t="n"/>
+      <c r="F9" s="26">
+        <f>IF($E9="","",IF($E9="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E9="ภาพถ่าย","งานภาพ (Vision)",IF($E9="เสียง","งานเสียง",IF($E9="วิดีโอ","งานภาพ (Vision)",IF($E9="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E9="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G9" s="23" t="n"/>
       <c r="H9" s="23" t="n"/>
       <c r="I9" s="23" t="n"/>
@@ -2805,12 +2823,13 @@
       <c r="O9" s="23" t="n"/>
       <c r="P9" s="23" t="n"/>
       <c r="Q9" s="23" t="n"/>
-      <c r="R9" s="27" t="n"/>
+      <c r="R9" s="23" t="n"/>
       <c r="S9" s="27" t="n"/>
       <c r="T9" s="27" t="n"/>
       <c r="U9" s="27" t="n"/>
       <c r="V9" s="27" t="n"/>
       <c r="W9" s="27" t="n"/>
+      <c r="X9" s="27" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="26">
@@ -2827,7 +2846,10 @@
       </c>
       <c r="D10" s="23" t="n"/>
       <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n"/>
+      <c r="F10" s="26">
+        <f>IF($E10="","",IF($E10="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E10="ภาพถ่าย","งานภาพ (Vision)",IF($E10="เสียง","งานเสียง",IF($E10="วิดีโอ","งานภาพ (Vision)",IF($E10="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E10="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G10" s="23" t="n"/>
       <c r="H10" s="23" t="n"/>
       <c r="I10" s="23" t="n"/>
@@ -2839,12 +2861,13 @@
       <c r="O10" s="23" t="n"/>
       <c r="P10" s="23" t="n"/>
       <c r="Q10" s="23" t="n"/>
-      <c r="R10" s="27" t="n"/>
+      <c r="R10" s="23" t="n"/>
       <c r="S10" s="27" t="n"/>
       <c r="T10" s="27" t="n"/>
       <c r="U10" s="27" t="n"/>
       <c r="V10" s="27" t="n"/>
       <c r="W10" s="27" t="n"/>
+      <c r="X10" s="27" t="n"/>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="26">
@@ -2861,7 +2884,10 @@
       </c>
       <c r="D11" s="23" t="n"/>
       <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
+      <c r="F11" s="26">
+        <f>IF($E11="","",IF($E11="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E11="ภาพถ่าย","งานภาพ (Vision)",IF($E11="เสียง","งานเสียง",IF($E11="วิดีโอ","งานภาพ (Vision)",IF($E11="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E11="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G11" s="23" t="n"/>
       <c r="H11" s="23" t="n"/>
       <c r="I11" s="23" t="n"/>
@@ -2873,12 +2899,13 @@
       <c r="O11" s="23" t="n"/>
       <c r="P11" s="23" t="n"/>
       <c r="Q11" s="23" t="n"/>
-      <c r="R11" s="27" t="n"/>
+      <c r="R11" s="23" t="n"/>
       <c r="S11" s="27" t="n"/>
       <c r="T11" s="27" t="n"/>
       <c r="U11" s="27" t="n"/>
       <c r="V11" s="27" t="n"/>
       <c r="W11" s="27" t="n"/>
+      <c r="X11" s="27" t="n"/>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="26">
@@ -2895,7 +2922,10 @@
       </c>
       <c r="D12" s="23" t="n"/>
       <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="F12" s="26">
+        <f>IF($E12="","",IF($E12="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E12="ภาพถ่าย","งานภาพ (Vision)",IF($E12="เสียง","งานเสียง",IF($E12="วิดีโอ","งานภาพ (Vision)",IF($E12="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E12="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G12" s="23" t="n"/>
       <c r="H12" s="23" t="n"/>
       <c r="I12" s="23" t="n"/>
@@ -2907,12 +2937,13 @@
       <c r="O12" s="23" t="n"/>
       <c r="P12" s="23" t="n"/>
       <c r="Q12" s="23" t="n"/>
-      <c r="R12" s="27" t="n"/>
+      <c r="R12" s="23" t="n"/>
       <c r="S12" s="27" t="n"/>
       <c r="T12" s="27" t="n"/>
       <c r="U12" s="27" t="n"/>
       <c r="V12" s="27" t="n"/>
       <c r="W12" s="27" t="n"/>
+      <c r="X12" s="27" t="n"/>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="26">
@@ -2929,7 +2960,10 @@
       </c>
       <c r="D13" s="23" t="n"/>
       <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="F13" s="26">
+        <f>IF($E13="","",IF($E13="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E13="ภาพถ่าย","งานภาพ (Vision)",IF($E13="เสียง","งานเสียง",IF($E13="วิดีโอ","งานภาพ (Vision)",IF($E13="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E13="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G13" s="23" t="n"/>
       <c r="H13" s="23" t="n"/>
       <c r="I13" s="23" t="n"/>
@@ -2941,12 +2975,13 @@
       <c r="O13" s="23" t="n"/>
       <c r="P13" s="23" t="n"/>
       <c r="Q13" s="23" t="n"/>
-      <c r="R13" s="27" t="n"/>
+      <c r="R13" s="23" t="n"/>
       <c r="S13" s="27" t="n"/>
       <c r="T13" s="27" t="n"/>
       <c r="U13" s="27" t="n"/>
       <c r="V13" s="27" t="n"/>
       <c r="W13" s="27" t="n"/>
+      <c r="X13" s="27" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="26">
@@ -2963,7 +2998,10 @@
       </c>
       <c r="D14" s="23" t="n"/>
       <c r="E14" s="23" t="n"/>
-      <c r="F14" s="23" t="n"/>
+      <c r="F14" s="26">
+        <f>IF($E14="","",IF($E14="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E14="ภาพถ่าย","งานภาพ (Vision)",IF($E14="เสียง","งานเสียง",IF($E14="วิดีโอ","งานภาพ (Vision)",IF($E14="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E14="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G14" s="23" t="n"/>
       <c r="H14" s="23" t="n"/>
       <c r="I14" s="23" t="n"/>
@@ -2975,12 +3013,13 @@
       <c r="O14" s="23" t="n"/>
       <c r="P14" s="23" t="n"/>
       <c r="Q14" s="23" t="n"/>
-      <c r="R14" s="27" t="n"/>
+      <c r="R14" s="23" t="n"/>
       <c r="S14" s="27" t="n"/>
       <c r="T14" s="27" t="n"/>
       <c r="U14" s="27" t="n"/>
       <c r="V14" s="27" t="n"/>
       <c r="W14" s="27" t="n"/>
+      <c r="X14" s="27" t="n"/>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="26">
@@ -2997,7 +3036,10 @@
       </c>
       <c r="D15" s="23" t="n"/>
       <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
+      <c r="F15" s="26">
+        <f>IF($E15="","",IF($E15="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E15="ภาพถ่าย","งานภาพ (Vision)",IF($E15="เสียง","งานเสียง",IF($E15="วิดีโอ","งานภาพ (Vision)",IF($E15="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E15="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G15" s="23" t="n"/>
       <c r="H15" s="23" t="n"/>
       <c r="I15" s="23" t="n"/>
@@ -3009,12 +3051,13 @@
       <c r="O15" s="23" t="n"/>
       <c r="P15" s="23" t="n"/>
       <c r="Q15" s="23" t="n"/>
-      <c r="R15" s="27" t="n"/>
+      <c r="R15" s="23" t="n"/>
       <c r="S15" s="27" t="n"/>
       <c r="T15" s="27" t="n"/>
       <c r="U15" s="27" t="n"/>
       <c r="V15" s="27" t="n"/>
       <c r="W15" s="27" t="n"/>
+      <c r="X15" s="27" t="n"/>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="26">
@@ -3031,7 +3074,10 @@
       </c>
       <c r="D16" s="23" t="n"/>
       <c r="E16" s="23" t="n"/>
-      <c r="F16" s="23" t="n"/>
+      <c r="F16" s="26">
+        <f>IF($E16="","",IF($E16="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E16="ภาพถ่าย","งานภาพ (Vision)",IF($E16="เสียง","งานเสียง",IF($E16="วิดีโอ","งานภาพ (Vision)",IF($E16="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E16="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G16" s="23" t="n"/>
       <c r="H16" s="23" t="n"/>
       <c r="I16" s="23" t="n"/>
@@ -3043,12 +3089,13 @@
       <c r="O16" s="23" t="n"/>
       <c r="P16" s="23" t="n"/>
       <c r="Q16" s="23" t="n"/>
-      <c r="R16" s="27" t="n"/>
+      <c r="R16" s="23" t="n"/>
       <c r="S16" s="27" t="n"/>
       <c r="T16" s="27" t="n"/>
       <c r="U16" s="27" t="n"/>
       <c r="V16" s="27" t="n"/>
       <c r="W16" s="27" t="n"/>
+      <c r="X16" s="27" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="26">
@@ -3065,7 +3112,10 @@
       </c>
       <c r="D17" s="23" t="n"/>
       <c r="E17" s="23" t="n"/>
-      <c r="F17" s="23" t="n"/>
+      <c r="F17" s="26">
+        <f>IF($E17="","",IF($E17="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E17="ภาพถ่าย","งานภาพ (Vision)",IF($E17="เสียง","งานเสียง",IF($E17="วิดีโอ","งานภาพ (Vision)",IF($E17="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E17="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G17" s="23" t="n"/>
       <c r="H17" s="23" t="n"/>
       <c r="I17" s="23" t="n"/>
@@ -3077,12 +3127,13 @@
       <c r="O17" s="23" t="n"/>
       <c r="P17" s="23" t="n"/>
       <c r="Q17" s="23" t="n"/>
-      <c r="R17" s="27" t="n"/>
+      <c r="R17" s="23" t="n"/>
       <c r="S17" s="27" t="n"/>
       <c r="T17" s="27" t="n"/>
       <c r="U17" s="27" t="n"/>
       <c r="V17" s="27" t="n"/>
       <c r="W17" s="27" t="n"/>
+      <c r="X17" s="27" t="n"/>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="26">
@@ -3099,7 +3150,10 @@
       </c>
       <c r="D18" s="23" t="n"/>
       <c r="E18" s="23" t="n"/>
-      <c r="F18" s="23" t="n"/>
+      <c r="F18" s="26">
+        <f>IF($E18="","",IF($E18="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E18="ภาพถ่าย","งานภาพ (Vision)",IF($E18="เสียง","งานเสียง",IF($E18="วิดีโอ","งานภาพ (Vision)",IF($E18="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E18="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G18" s="23" t="n"/>
       <c r="H18" s="23" t="n"/>
       <c r="I18" s="23" t="n"/>
@@ -3111,12 +3165,13 @@
       <c r="O18" s="23" t="n"/>
       <c r="P18" s="23" t="n"/>
       <c r="Q18" s="23" t="n"/>
-      <c r="R18" s="27" t="n"/>
+      <c r="R18" s="23" t="n"/>
       <c r="S18" s="27" t="n"/>
       <c r="T18" s="27" t="n"/>
       <c r="U18" s="27" t="n"/>
       <c r="V18" s="27" t="n"/>
       <c r="W18" s="27" t="n"/>
+      <c r="X18" s="27" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="26">
@@ -3133,7 +3188,10 @@
       </c>
       <c r="D19" s="23" t="n"/>
       <c r="E19" s="23" t="n"/>
-      <c r="F19" s="23" t="n"/>
+      <c r="F19" s="26">
+        <f>IF($E19="","",IF($E19="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E19="ภาพถ่าย","งานภาพ (Vision)",IF($E19="เสียง","งานเสียง",IF($E19="วิดีโอ","งานภาพ (Vision)",IF($E19="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E19="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G19" s="23" t="n"/>
       <c r="H19" s="23" t="n"/>
       <c r="I19" s="23" t="n"/>
@@ -3145,12 +3203,13 @@
       <c r="O19" s="23" t="n"/>
       <c r="P19" s="23" t="n"/>
       <c r="Q19" s="23" t="n"/>
-      <c r="R19" s="27" t="n"/>
+      <c r="R19" s="23" t="n"/>
       <c r="S19" s="27" t="n"/>
       <c r="T19" s="27" t="n"/>
       <c r="U19" s="27" t="n"/>
       <c r="V19" s="27" t="n"/>
       <c r="W19" s="27" t="n"/>
+      <c r="X19" s="27" t="n"/>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="26">
@@ -3167,7 +3226,10 @@
       </c>
       <c r="D20" s="23" t="n"/>
       <c r="E20" s="23" t="n"/>
-      <c r="F20" s="23" t="n"/>
+      <c r="F20" s="26">
+        <f>IF($E20="","",IF($E20="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E20="ภาพถ่าย","งานภาพ (Vision)",IF($E20="เสียง","งานเสียง",IF($E20="วิดีโอ","งานภาพ (Vision)",IF($E20="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E20="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G20" s="23" t="n"/>
       <c r="H20" s="23" t="n"/>
       <c r="I20" s="23" t="n"/>
@@ -3179,12 +3241,13 @@
       <c r="O20" s="23" t="n"/>
       <c r="P20" s="23" t="n"/>
       <c r="Q20" s="23" t="n"/>
-      <c r="R20" s="27" t="n"/>
+      <c r="R20" s="23" t="n"/>
       <c r="S20" s="27" t="n"/>
       <c r="T20" s="27" t="n"/>
       <c r="U20" s="27" t="n"/>
       <c r="V20" s="27" t="n"/>
       <c r="W20" s="27" t="n"/>
+      <c r="X20" s="27" t="n"/>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="26">
@@ -3201,7 +3264,10 @@
       </c>
       <c r="D21" s="23" t="n"/>
       <c r="E21" s="23" t="n"/>
-      <c r="F21" s="23" t="n"/>
+      <c r="F21" s="26">
+        <f>IF($E21="","",IF($E21="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E21="ภาพถ่าย","งานภาพ (Vision)",IF($E21="เสียง","งานเสียง",IF($E21="วิดีโอ","งานภาพ (Vision)",IF($E21="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E21="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G21" s="23" t="n"/>
       <c r="H21" s="23" t="n"/>
       <c r="I21" s="23" t="n"/>
@@ -3213,12 +3279,13 @@
       <c r="O21" s="23" t="n"/>
       <c r="P21" s="23" t="n"/>
       <c r="Q21" s="23" t="n"/>
-      <c r="R21" s="27" t="n"/>
+      <c r="R21" s="23" t="n"/>
       <c r="S21" s="27" t="n"/>
       <c r="T21" s="27" t="n"/>
       <c r="U21" s="27" t="n"/>
       <c r="V21" s="27" t="n"/>
       <c r="W21" s="27" t="n"/>
+      <c r="X21" s="27" t="n"/>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="26">
@@ -3235,7 +3302,10 @@
       </c>
       <c r="D22" s="23" t="n"/>
       <c r="E22" s="23" t="n"/>
-      <c r="F22" s="23" t="n"/>
+      <c r="F22" s="26">
+        <f>IF($E22="","",IF($E22="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E22="ภาพถ่าย","งานภาพ (Vision)",IF($E22="เสียง","งานเสียง",IF($E22="วิดีโอ","งานภาพ (Vision)",IF($E22="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E22="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G22" s="23" t="n"/>
       <c r="H22" s="23" t="n"/>
       <c r="I22" s="23" t="n"/>
@@ -3247,12 +3317,13 @@
       <c r="O22" s="23" t="n"/>
       <c r="P22" s="23" t="n"/>
       <c r="Q22" s="23" t="n"/>
-      <c r="R22" s="27" t="n"/>
+      <c r="R22" s="23" t="n"/>
       <c r="S22" s="27" t="n"/>
       <c r="T22" s="27" t="n"/>
       <c r="U22" s="27" t="n"/>
       <c r="V22" s="27" t="n"/>
       <c r="W22" s="27" t="n"/>
+      <c r="X22" s="27" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="26">
@@ -3269,7 +3340,10 @@
       </c>
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="23" t="n"/>
-      <c r="F23" s="23" t="n"/>
+      <c r="F23" s="26">
+        <f>IF($E23="","",IF($E23="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E23="ภาพถ่าย","งานภาพ (Vision)",IF($E23="เสียง","งานเสียง",IF($E23="วิดีโอ","งานภาพ (Vision)",IF($E23="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E23="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G23" s="23" t="n"/>
       <c r="H23" s="23" t="n"/>
       <c r="I23" s="23" t="n"/>
@@ -3281,12 +3355,13 @@
       <c r="O23" s="23" t="n"/>
       <c r="P23" s="23" t="n"/>
       <c r="Q23" s="23" t="n"/>
-      <c r="R23" s="27" t="n"/>
+      <c r="R23" s="23" t="n"/>
       <c r="S23" s="27" t="n"/>
       <c r="T23" s="27" t="n"/>
       <c r="U23" s="27" t="n"/>
       <c r="V23" s="27" t="n"/>
       <c r="W23" s="27" t="n"/>
+      <c r="X23" s="27" t="n"/>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="26">
@@ -3303,7 +3378,10 @@
       </c>
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
+      <c r="F24" s="26">
+        <f>IF($E24="","",IF($E24="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E24="ภาพถ่าย","งานภาพ (Vision)",IF($E24="เสียง","งานเสียง",IF($E24="วิดีโอ","งานภาพ (Vision)",IF($E24="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E24="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G24" s="23" t="n"/>
       <c r="H24" s="23" t="n"/>
       <c r="I24" s="23" t="n"/>
@@ -3315,12 +3393,13 @@
       <c r="O24" s="23" t="n"/>
       <c r="P24" s="23" t="n"/>
       <c r="Q24" s="23" t="n"/>
-      <c r="R24" s="27" t="n"/>
+      <c r="R24" s="23" t="n"/>
       <c r="S24" s="27" t="n"/>
       <c r="T24" s="27" t="n"/>
       <c r="U24" s="27" t="n"/>
       <c r="V24" s="27" t="n"/>
       <c r="W24" s="27" t="n"/>
+      <c r="X24" s="27" t="n"/>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="26">
@@ -3337,7 +3416,10 @@
       </c>
       <c r="D25" s="23" t="n"/>
       <c r="E25" s="23" t="n"/>
-      <c r="F25" s="23" t="n"/>
+      <c r="F25" s="26">
+        <f>IF($E25="","",IF($E25="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E25="ภาพถ่าย","งานภาพ (Vision)",IF($E25="เสียง","งานเสียง",IF($E25="วิดีโอ","งานภาพ (Vision)",IF($E25="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E25="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G25" s="23" t="n"/>
       <c r="H25" s="23" t="n"/>
       <c r="I25" s="23" t="n"/>
@@ -3349,12 +3431,13 @@
       <c r="O25" s="23" t="n"/>
       <c r="P25" s="23" t="n"/>
       <c r="Q25" s="23" t="n"/>
-      <c r="R25" s="27" t="n"/>
+      <c r="R25" s="23" t="n"/>
       <c r="S25" s="27" t="n"/>
       <c r="T25" s="27" t="n"/>
       <c r="U25" s="27" t="n"/>
       <c r="V25" s="27" t="n"/>
       <c r="W25" s="27" t="n"/>
+      <c r="X25" s="27" t="n"/>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="26">
@@ -3371,7 +3454,10 @@
       </c>
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
+      <c r="F26" s="26">
+        <f>IF($E26="","",IF($E26="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E26="ภาพถ่าย","งานภาพ (Vision)",IF($E26="เสียง","งานเสียง",IF($E26="วิดีโอ","งานภาพ (Vision)",IF($E26="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E26="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G26" s="23" t="n"/>
       <c r="H26" s="23" t="n"/>
       <c r="I26" s="23" t="n"/>
@@ -3383,12 +3469,13 @@
       <c r="O26" s="23" t="n"/>
       <c r="P26" s="23" t="n"/>
       <c r="Q26" s="23" t="n"/>
-      <c r="R26" s="27" t="n"/>
+      <c r="R26" s="23" t="n"/>
       <c r="S26" s="27" t="n"/>
       <c r="T26" s="27" t="n"/>
       <c r="U26" s="27" t="n"/>
       <c r="V26" s="27" t="n"/>
       <c r="W26" s="27" t="n"/>
+      <c r="X26" s="27" t="n"/>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="26">
@@ -3405,7 +3492,10 @@
       </c>
       <c r="D27" s="23" t="n"/>
       <c r="E27" s="23" t="n"/>
-      <c r="F27" s="23" t="n"/>
+      <c r="F27" s="26">
+        <f>IF($E27="","",IF($E27="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E27="ภาพถ่าย","งานภาพ (Vision)",IF($E27="เสียง","งานเสียง",IF($E27="วิดีโอ","งานภาพ (Vision)",IF($E27="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E27="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G27" s="23" t="n"/>
       <c r="H27" s="23" t="n"/>
       <c r="I27" s="23" t="n"/>
@@ -3417,12 +3507,13 @@
       <c r="O27" s="23" t="n"/>
       <c r="P27" s="23" t="n"/>
       <c r="Q27" s="23" t="n"/>
-      <c r="R27" s="27" t="n"/>
+      <c r="R27" s="23" t="n"/>
       <c r="S27" s="27" t="n"/>
       <c r="T27" s="27" t="n"/>
       <c r="U27" s="27" t="n"/>
       <c r="V27" s="27" t="n"/>
       <c r="W27" s="27" t="n"/>
+      <c r="X27" s="27" t="n"/>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="26">
@@ -3439,7 +3530,10 @@
       </c>
       <c r="D28" s="23" t="n"/>
       <c r="E28" s="23" t="n"/>
-      <c r="F28" s="23" t="n"/>
+      <c r="F28" s="26">
+        <f>IF($E28="","",IF($E28="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E28="ภาพถ่าย","งานภาพ (Vision)",IF($E28="เสียง","งานเสียง",IF($E28="วิดีโอ","งานภาพ (Vision)",IF($E28="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E28="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G28" s="23" t="n"/>
       <c r="H28" s="23" t="n"/>
       <c r="I28" s="23" t="n"/>
@@ -3451,12 +3545,13 @@
       <c r="O28" s="23" t="n"/>
       <c r="P28" s="23" t="n"/>
       <c r="Q28" s="23" t="n"/>
-      <c r="R28" s="27" t="n"/>
+      <c r="R28" s="23" t="n"/>
       <c r="S28" s="27" t="n"/>
       <c r="T28" s="27" t="n"/>
       <c r="U28" s="27" t="n"/>
       <c r="V28" s="27" t="n"/>
       <c r="W28" s="27" t="n"/>
+      <c r="X28" s="27" t="n"/>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="26">
@@ -3473,7 +3568,10 @@
       </c>
       <c r="D29" s="23" t="n"/>
       <c r="E29" s="23" t="n"/>
-      <c r="F29" s="23" t="n"/>
+      <c r="F29" s="26">
+        <f>IF($E29="","",IF($E29="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E29="ภาพถ่าย","งานภาพ (Vision)",IF($E29="เสียง","งานเสียง",IF($E29="วิดีโอ","งานภาพ (Vision)",IF($E29="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E29="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G29" s="23" t="n"/>
       <c r="H29" s="23" t="n"/>
       <c r="I29" s="23" t="n"/>
@@ -3485,12 +3583,13 @@
       <c r="O29" s="23" t="n"/>
       <c r="P29" s="23" t="n"/>
       <c r="Q29" s="23" t="n"/>
-      <c r="R29" s="27" t="n"/>
+      <c r="R29" s="23" t="n"/>
       <c r="S29" s="27" t="n"/>
       <c r="T29" s="27" t="n"/>
       <c r="U29" s="27" t="n"/>
       <c r="V29" s="27" t="n"/>
       <c r="W29" s="27" t="n"/>
+      <c r="X29" s="27" t="n"/>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="26">
@@ -3507,7 +3606,10 @@
       </c>
       <c r="D30" s="23" t="n"/>
       <c r="E30" s="23" t="n"/>
-      <c r="F30" s="23" t="n"/>
+      <c r="F30" s="26">
+        <f>IF($E30="","",IF($E30="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E30="ภาพถ่าย","งานภาพ (Vision)",IF($E30="เสียง","งานเสียง",IF($E30="วิดีโอ","งานภาพ (Vision)",IF($E30="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E30="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G30" s="23" t="n"/>
       <c r="H30" s="23" t="n"/>
       <c r="I30" s="23" t="n"/>
@@ -3519,12 +3621,13 @@
       <c r="O30" s="23" t="n"/>
       <c r="P30" s="23" t="n"/>
       <c r="Q30" s="23" t="n"/>
-      <c r="R30" s="27" t="n"/>
+      <c r="R30" s="23" t="n"/>
       <c r="S30" s="27" t="n"/>
       <c r="T30" s="27" t="n"/>
       <c r="U30" s="27" t="n"/>
       <c r="V30" s="27" t="n"/>
       <c r="W30" s="27" t="n"/>
+      <c r="X30" s="27" t="n"/>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="26">
@@ -3541,7 +3644,10 @@
       </c>
       <c r="D31" s="23" t="n"/>
       <c r="E31" s="23" t="n"/>
-      <c r="F31" s="23" t="n"/>
+      <c r="F31" s="26">
+        <f>IF($E31="","",IF($E31="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E31="ภาพถ่าย","งานภาพ (Vision)",IF($E31="เสียง","งานเสียง",IF($E31="วิดีโอ","งานภาพ (Vision)",IF($E31="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E31="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G31" s="23" t="n"/>
       <c r="H31" s="23" t="n"/>
       <c r="I31" s="23" t="n"/>
@@ -3553,12 +3659,13 @@
       <c r="O31" s="23" t="n"/>
       <c r="P31" s="23" t="n"/>
       <c r="Q31" s="23" t="n"/>
-      <c r="R31" s="27" t="n"/>
+      <c r="R31" s="23" t="n"/>
       <c r="S31" s="27" t="n"/>
       <c r="T31" s="27" t="n"/>
       <c r="U31" s="27" t="n"/>
       <c r="V31" s="27" t="n"/>
       <c r="W31" s="27" t="n"/>
+      <c r="X31" s="27" t="n"/>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="26">
@@ -3575,7 +3682,10 @@
       </c>
       <c r="D32" s="23" t="n"/>
       <c r="E32" s="23" t="n"/>
-      <c r="F32" s="23" t="n"/>
+      <c r="F32" s="26">
+        <f>IF($E32="","",IF($E32="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E32="ภาพถ่าย","งานภาพ (Vision)",IF($E32="เสียง","งานเสียง",IF($E32="วิดีโอ","งานภาพ (Vision)",IF($E32="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E32="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G32" s="23" t="n"/>
       <c r="H32" s="23" t="n"/>
       <c r="I32" s="23" t="n"/>
@@ -3587,12 +3697,13 @@
       <c r="O32" s="23" t="n"/>
       <c r="P32" s="23" t="n"/>
       <c r="Q32" s="23" t="n"/>
-      <c r="R32" s="27" t="n"/>
+      <c r="R32" s="23" t="n"/>
       <c r="S32" s="27" t="n"/>
       <c r="T32" s="27" t="n"/>
       <c r="U32" s="27" t="n"/>
       <c r="V32" s="27" t="n"/>
       <c r="W32" s="27" t="n"/>
+      <c r="X32" s="27" t="n"/>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="26">
@@ -3609,7 +3720,10 @@
       </c>
       <c r="D33" s="23" t="n"/>
       <c r="E33" s="23" t="n"/>
-      <c r="F33" s="23" t="n"/>
+      <c r="F33" s="26">
+        <f>IF($E33="","",IF($E33="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E33="ภาพถ่าย","งานภาพ (Vision)",IF($E33="เสียง","งานเสียง",IF($E33="วิดีโอ","งานภาพ (Vision)",IF($E33="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E33="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G33" s="23" t="n"/>
       <c r="H33" s="23" t="n"/>
       <c r="I33" s="23" t="n"/>
@@ -3621,12 +3735,13 @@
       <c r="O33" s="23" t="n"/>
       <c r="P33" s="23" t="n"/>
       <c r="Q33" s="23" t="n"/>
-      <c r="R33" s="27" t="n"/>
+      <c r="R33" s="23" t="n"/>
       <c r="S33" s="27" t="n"/>
       <c r="T33" s="27" t="n"/>
       <c r="U33" s="27" t="n"/>
       <c r="V33" s="27" t="n"/>
       <c r="W33" s="27" t="n"/>
+      <c r="X33" s="27" t="n"/>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="26">
@@ -3643,7 +3758,10 @@
       </c>
       <c r="D34" s="23" t="n"/>
       <c r="E34" s="23" t="n"/>
-      <c r="F34" s="23" t="n"/>
+      <c r="F34" s="26">
+        <f>IF($E34="","",IF($E34="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E34="ภาพถ่าย","งานภาพ (Vision)",IF($E34="เสียง","งานเสียง",IF($E34="วิดีโอ","งานภาพ (Vision)",IF($E34="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E34="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G34" s="23" t="n"/>
       <c r="H34" s="23" t="n"/>
       <c r="I34" s="23" t="n"/>
@@ -3655,12 +3773,13 @@
       <c r="O34" s="23" t="n"/>
       <c r="P34" s="23" t="n"/>
       <c r="Q34" s="23" t="n"/>
-      <c r="R34" s="27" t="n"/>
+      <c r="R34" s="23" t="n"/>
       <c r="S34" s="27" t="n"/>
       <c r="T34" s="27" t="n"/>
       <c r="U34" s="27" t="n"/>
       <c r="V34" s="27" t="n"/>
       <c r="W34" s="27" t="n"/>
+      <c r="X34" s="27" t="n"/>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="26">
@@ -3677,7 +3796,10 @@
       </c>
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="23" t="n"/>
-      <c r="F35" s="23" t="n"/>
+      <c r="F35" s="26">
+        <f>IF($E35="","",IF($E35="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E35="ภาพถ่าย","งานภาพ (Vision)",IF($E35="เสียง","งานเสียง",IF($E35="วิดีโอ","งานภาพ (Vision)",IF($E35="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E35="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G35" s="23" t="n"/>
       <c r="H35" s="23" t="n"/>
       <c r="I35" s="23" t="n"/>
@@ -3689,12 +3811,13 @@
       <c r="O35" s="23" t="n"/>
       <c r="P35" s="23" t="n"/>
       <c r="Q35" s="23" t="n"/>
-      <c r="R35" s="27" t="n"/>
+      <c r="R35" s="23" t="n"/>
       <c r="S35" s="27" t="n"/>
       <c r="T35" s="27" t="n"/>
       <c r="U35" s="27" t="n"/>
       <c r="V35" s="27" t="n"/>
       <c r="W35" s="27" t="n"/>
+      <c r="X35" s="27" t="n"/>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="26">
@@ -3711,7 +3834,10 @@
       </c>
       <c r="D36" s="23" t="n"/>
       <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n"/>
+      <c r="F36" s="26">
+        <f>IF($E36="","",IF($E36="ข้อความ / เอกสาร","งานภาษา (LLM)",IF($E36="ภาพถ่าย","งานภาพ (Vision)",IF($E36="เสียง","งานเสียง",IF($E36="วิดีโอ","งานภาพ (Vision)",IF($E36="ตัวเลข / ตาราง","งานตัวเลข (ML)",IF($E36="ผสมหลายประเภท","ผสม - ต้องดูรายละเอียด","")))))))</f>
+        <v/>
+      </c>
       <c r="G36" s="23" t="n"/>
       <c r="H36" s="23" t="n"/>
       <c r="I36" s="23" t="n"/>
@@ -3723,78 +3849,79 @@
       <c r="O36" s="23" t="n"/>
       <c r="P36" s="23" t="n"/>
       <c r="Q36" s="23" t="n"/>
-      <c r="R36" s="27" t="n"/>
+      <c r="R36" s="23" t="n"/>
       <c r="S36" s="27" t="n"/>
       <c r="T36" s="27" t="n"/>
       <c r="U36" s="27" t="n"/>
       <c r="V36" s="27" t="n"/>
       <c r="W36" s="27" t="n"/>
+      <c r="X36" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="S4:X4"/>
+    <mergeCell ref="A1:X1"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="R4:W4"/>
-    <mergeCell ref="A2:W2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G7:G36">
+  <conditionalFormatting sqref="H7:H36">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(AND($F7="1 - 10 คน",OR($G7="6 - 20 คน",$G7="21 - 50 คน",$G7="มากกว่า 50 คน")),AND($F7="11 - 50 คน",OR($G7="มากกว่า 50 คน")))</formula>
+      <formula>OR(AND($G7="1 - 10 คน",OR($H7="6 - 20 คน",$H7="21 - 50 คน",$H7="มากกว่า 50 คน")),AND($G7="11 - 50 คน",OR($H7="มากกว่า 50 คน")))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="17">
-    <dataValidation sqref="D7:D36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="งานนี้เริ่มทำงานยังไง" prompt="ตอบก่อนช่องอื่น เพราะเป็นตัวบอกว่าช่องที่เหลือต้องกรอกยังไง&#10;&#10;งานที่ระบบสั่งเอง จะไม่มี 'คนใช้งาน' — ให้กรอกคนที่เข้ามาดูผลแทน" type="list">
+    <dataValidation sqref="D7:D36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ลักษณะการเริ่มทำงานของระบบ" prompt="ตอบก่อนช่องอื่น เพราะเป็นตัวบอกว่าช่องที่เหลือต้องกรอกยังไง&#10;&#10;งานที่ระบบสั่งเอง จะไม่มี 'ผู้ใช้งาน' — ให้กรอกคนที่เข้ามาดูผลแทน" type="list">
       <formula1>DATA!$AE$4:$AE$7</formula1>
     </dataValidation>
-    <dataValidation sqref="E7:E36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ประเภทข้อมูล Input" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="E7:E36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ประเภทข้อมูลนำเข้า" prompt="ข้อมูลหลักที่ AI ต้องอ่านหรือดูคืออะไร&#10;&#10;ภาพ / วิดีโอ = ต้องใช้ GPU แน่นอน&#10;ตัวเลข / ตาราง = CPU ก็เพียงพอ&#10;&#10;ช่องถัดไปจะสรุปประเภทงาน AI ให้เองจากคำตอบช่องนี้" type="list">
       <formula1>DATA!$K$4:$K$9</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวน Users/วัน" prompt="นับคนทั้งหมดที่เข้ามาใช้ตลอดทั้งวัน ไม่ใช่พร้อมกัน&#10;&#10;ถ้าเป็นงานอัตโนมัติหรือรันตามรอบ ให้นับคนที่เข้ามาดูผล" type="list">
+    <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวนผู้ใช้งานต่อวัน" prompt="นับคนทั้งหมดที่เข้ามาใช้ตลอดทั้งวัน ไม่ใช่พร้อมกัน&#10;&#10;ถ้าเป็นงานอัตโนมัติหรือรันตามรอบ ให้นับคนที่เข้ามาดูผล" type="list">
       <formula1>DATA!$T$4:$T$8</formula1>
     </dataValidation>
-    <dataValidation sqref="G7:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Peak concurrent (คนพร้อมกัน)" prompt="ช่วงที่คนใช้เยอะที่สุดของวัน มีกี่คนกดพร้อมกัน&#10;&#10;ต้องไม่เกินจำนวนคนที่ใช้งาน/วัน&#10;งานอัตโนมัติ/รันตามรอบ มักเป็น 1 - 2 คน&#10;&#10;ถ้าขึ้นพื้นสีแดง = ตัวเลขดูสูงผิดปกติ ลองทบทวนอีกครั้ง" type="list">
+    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ผู้ใช้งานพร้อมกันสูงสุด" prompt="ช่วงที่คนใช้เยอะที่สุดของวัน มีกี่คนกดพร้อมกัน&#10;&#10;ต้องไม่เกินจำนวนผู้ใช้งานต่อวัน&#10;งานอัตโนมัติหรือรันตามรอบ มักเป็น 1 - 2 คน&#10;&#10;ถ้าขึ้นพื้นสีแดง = ตัวเลขดูสูงผิดปกติ ควรทบทวน" type="list">
       <formula1>DATA!$U$4:$U$8</formula1>
     </dataValidation>
-    <dataValidation sqref="H7:H36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="AI ประมวลผลกี่รายการ/วัน" prompt="นับรายการที่ AI ต้องประมวลผลจริง ไม่ใช่จำนวนครั้งที่สั่งงาน&#10;&#10;คนกดใช้เอง = กี่คำถาม&#10;อัตโนมัติ = กี่ชิ้น กี่ภาพ&#10;รันตามรอบ = กี่ล็อต กี่แถวในรอบนั้น&#10;เมื่อมีเหตุการณ์ = กี่เคส&#10;&#10;รันคืนละครั้งแต่ประมวลผล 12,000 ล็อต = 12,000 ไม่ใช่ 1" type="list">
+    <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ปริมาณรายการที่ประมวลผลต่อวัน" prompt="นับรายการที่ AI ต้องประมวลผลจริง ไม่ใช่จำนวนครั้งที่สั่งงาน&#10;&#10;ผู้ใช้เรียกเอง = กี่คำถาม&#10;อัตโนมัติ = กี่ชิ้น กี่ภาพ&#10;ตามรอบเวลา = กี่ล็อต กี่แถวในรอบนั้น&#10;&#10;รันคืนละครั้งแต่ประมวลผล 12,000 ล็อต = 12,000 ไม่ใช่ 1" type="list">
       <formula1>DATA!$V$4:$V$8</formula1>
     </dataValidation>
-    <dataValidation sqref="I7:I36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จำนวนกล้อง/จุดตรวจพร้อมกัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="จุดตรวจที่ทำงานพร้อมกัน" prompt="นับจุดที่ต้องประมวลผลพร้อมกัน ไม่ใช่จำนวนภาพต่อวัน&#10;&#10;600 ภาพจากกล้อง 1 ตัว ใช้เครื่องเดียว&#10;600 ภาพจากกล้อง 6 ตัวที่ตรวจพร้อมกัน ต้องมี 6 สาย&#10;&#10;ช่องนี้บอกจำนวนเครื่องที่ต้องติดตั้งหน้างาน" type="list">
       <formula1>DATA!$Y$4:$Y$8</formula1>
     </dataValidation>
-    <dataValidation sqref="J7:J36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ภาษาที่ต้องการ" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ภาษาที่ต้องรองรับ" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$L$4:$L$7</formula1>
     </dataValidation>
-    <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Latency ที่รับได้" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$M$4:$M$6</formula1>
+    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="เวลาตอบสนองที่ยอมรับได้" prompt="งานนี้ต้องได้ผลลัพธ์ภายในเวลาเท่าไหร่&#10;&#10;เป็นตัวชี้ขาดว่าต้องใช้ GPU หรือ CPU เพียงพอ&#10;งานที่รอถึงรอบวันได้ ประมวลผลด้วย CPU ตอนกลางคืนได้&#10;&#10;ไม่จำเป็นต้องมีคนนั่งรอ เช่น สายพานที่ต้องคัดแยกทันที" type="list">
+      <formula1>DATA!$M$4:$M$8</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="Availability" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ช่วงเวลาที่ต้องให้บริการ" prompt="ช่วงเวลาที่ระบบต้องพร้อมใช้งาน&#10;&#10;ถ้าไม่ต้องเปิด 24 ชั่วโมง ปิดเครื่องนอกเวลาได้&#10;ลดค่าไฟลงเกินครึ่ง&#10;&#10;24x7 = ต้องมีเครื่องสำรองเผื่อเครื่องหลักเสีย" type="list">
       <formula1>DATA!$N$4:$N$6</formula1>
     </dataValidation>
-    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ถ้างานนี้ช้าลงจะเป็นปัญหามั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ผลกระทบเมื่อระบบตอบสนองช้าลง" prompt="ถามผลกระทบต่องานของหน่วยงาน ไม่ใช่เรื่องเทคนิค&#10;&#10;ทีมส่วนกลางจะแปลเป็นข้อกำหนดเองว่าต้องมี GPU แยกหรือแชร์ได้&#10;&#10;งานในสายการผลิตที่หยุดไม่ได้ ให้เลือก กระทบมาก" type="list">
       <formula1>DATA!$AD$4:$AD$7</formula1>
     </dataValidation>
-    <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเก็บข้อมูลย้อนหลังกี่ปี" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="O7:O36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ระยะเวลาการจัดเก็บข้อมูล" prompt="เก็บข้อมูลที่เกิดใหม่ไว้นานแค่ไหน&#10;ตามข้อกำหนดของลูกค้าหรือกฎหมาย&#10;&#10;คูณกับปริมาณข้อมูลนำเข้าต่อวัน = storage ที่ต้องซื้อ&#10;10 GB/วัน เก็บ 1 ปี = 3.6 TB  |  เก็บ 5 ปี = 18 TB" type="list">
       <formula1>DATA!$AB$4:$AB$7</formula1>
     </dataValidation>
-    <dataValidation sqref="R7:R36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดข้อมูล Input/วัน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ปริมาณข้อมูลนำเข้าต่อวัน" prompt="ข้อมูลใหม่ที่เกิดขึ้นต่อวัน ไม่ใช่ข้อมูลเดิมที่มีอยู่&#10;เปรียบเหมือนน้ำที่ไหลเข้าถังทุกวัน&#10;&#10;งานภาพจะสูง งานเอกสารจะต่ำ&#10;คูณกับระยะเวลาการจัดเก็บ = storage ที่ต้องซื้อ" type="list">
       <formula1>DATA!$W$4:$W$7</formula1>
     </dataValidation>
-    <dataValidation sqref="S7:S36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดคลังเอกสารทั้งหมด (RAG)" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ขนาดคลังเอกสารทั้งหมด" prompt="กองเอกสารเดิมทั้งหมดที่ให้ AI ค้นหา&#10;ไม่ใช่ข้อมูลใหม่ที่เกิดต่อวัน&#10;เปรียบเหมือนขนาดถังที่มีน้ำอยู่แล้ว&#10;&#10;งานสืบค้นเอกสารจะสูง งานภาพเลือก ไม่เกี่ยวข้อง&#10;ใช้กำหนด RAM และขนาดฐานข้อมูลค้นหา" type="list">
       <formula1>DATA!$X$4:$X$8</formula1>
     </dataValidation>
-    <dataValidation sqref="T7:T36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความละเอียดรูป" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความละเอียดของภาพ" prompt="ความละเอียดของภาพจากกล้องที่จะใช้&#10;&#10;ยิ่งละเอียด ยิ่งใช้ VRAM มาก&#10;ถ้าไม่ใช่งานประมวลผลภาพ เลือก ไม่เกี่ยวข้อง" type="list">
       <formula1>DATA!$O$4:$O$8</formula1>
     </dataValidation>
-    <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ติดตั้งแบบไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="V7:V36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="รูปแบบการติดตั้ง" prompt="รันที่ Server กลาง หรือต้องมีเครื่องข้างเครื่องจักร&#10;&#10;งานที่ต้องตัดสินใจทันทีในสายการผลิต ต้องติดตั้งหน้างาน&#10;เพราะรอส่งข้อมูลไปกลับไม่ทัน และต้องต่อกับแขนคัดแยกหรือ PLC" type="list">
       <formula1>DATA!$Z$4:$Z$6</formula1>
     </dataValidation>
-    <dataValidation sqref="V7:V36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="W7:W36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="การปรับโมเดลด้วยข้อมูลองค์กร" prompt="สำเร็จรูป = งานความรู้ทั่วไป ใช้ได้ทันที&#10;RAG = ให้อ่านเอกสารองค์กร ไม่ต้องฝึกโมเดล&#10;Fine-tune = สอนด้วยข้อมูลหรือภาพของเราเอง ต้องมี GPU ฝึก&#10;&#10;งานเอกสารส่วนใหญ่ควรเลือก RAG ไม่ใช่ Fine-tune" type="list">
       <formula1>DATA!$Q$4:$Q$7</formula1>
     </dataValidation>
-    <dataValidation sqref="W7:W36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ต้องเทรนโมเดลใหม่บ่อยแค่ไหน" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
+    <dataValidation sqref="X7:X36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความถี่ในการฝึกโมเดลใหม่" prompt="ไม่ต้องฝึก = ใช้โมเดลสำเร็จรูปหรือ RAG&#10;ครั้งเดียว = ยังต้องฝึก 1 ครั้ง ต้องหา GPU มาฝึก&#10;ถี่กว่าเดือนละครั้ง = ควรมี GPU สำหรับฝึกแยกต่างหาก" type="list">
       <formula1>DATA!$AC$4:$AC$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -6853,72 +6980,72 @@
       </c>
       <c r="B3" s="40" t="inlineStr">
         <is>
-          <t>ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน</t>
+          <t>รูปแบบการจัดเก็บข้อมูลปัจจุบัน</t>
         </is>
       </c>
       <c r="C3" s="40" t="inlineStr">
         <is>
-          <t>มีข้อมูลย้อนหลังนานแค่ไหน</t>
+          <t>ระยะเวลาข้อมูลย้อนหลังที่มี</t>
         </is>
       </c>
       <c r="D3" s="40" t="inlineStr">
         <is>
-          <t>สิทธิ์นำข้อมูลมาใช้</t>
+          <t>สิทธิ์ในการนำข้อมูลมาใช้</t>
         </is>
       </c>
       <c r="E3" s="40" t="inlineStr">
         <is>
-          <t>ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย</t>
+          <t>การเชื่อมต่อกับระบบเดิม</t>
         </is>
       </c>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>มีคนดูแลระบบต่อหลังส่งมอบมั้ย</t>
+          <t>ผู้ดูแลระบบหลังส่งมอบ</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>ถ้า AI ตอบผิด จะเกิดอะไรขึ้น</t>
+          <t>ผลกระทบเมื่อ AI ผิดพลาด</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย</t>
+          <t>การตรวจสอบผลลัพธ์โดยบุคลากร</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>ข้อมูลชุดนี้ลับแค่ไหน</t>
+          <t>ระดับชั้นความลับของข้อมูล</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>ความสำคัญที่แผนกอยากได้</t>
+          <t>ระดับความสำคัญตามความเห็นผู้ใช้</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>ประเภทข้อมูล Input</t>
+          <t>ประเภทข้อมูลนำเข้า</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
         <is>
-          <t>ภาษาที่ต้องการ</t>
+          <t>ภาษาที่ต้องรองรับ</t>
         </is>
       </c>
       <c r="M3" s="40" t="inlineStr">
         <is>
-          <t>Latency ที่รับได้</t>
+          <t>เวลาตอบสนองที่ยอมรับได้</t>
         </is>
       </c>
       <c r="N3" s="40" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>ช่วงเวลาที่ต้องให้บริการ</t>
         </is>
       </c>
       <c r="O3" s="40" t="inlineStr">
         <is>
-          <t>ความละเอียดรูป</t>
+          <t>ความละเอียดของภาพ</t>
         </is>
       </c>
       <c r="P3" s="40" t="inlineStr">
@@ -6928,72 +7055,72 @@
       </c>
       <c r="Q3" s="40" t="inlineStr">
         <is>
-          <t>ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย</t>
+          <t>การปรับโมเดลด้วยข้อมูลองค์กร</t>
         </is>
       </c>
       <c r="R3" s="40" t="inlineStr">
         <is>
-          <t>เวลาที่ใช้กับงานนี้ตอนนี้</t>
+          <t>เวลาที่ใช้กับงานนี้ในปัจจุบัน</t>
         </is>
       </c>
       <c r="S3" s="40" t="inlineStr">
         <is>
-          <t>มูลค่าความเสียหาย/ของเสียต่อปี</t>
+          <t>มูลค่าความสูญเสียต่อปี</t>
         </is>
       </c>
       <c r="T3" s="40" t="inlineStr">
         <is>
-          <t>จำนวน Users/วัน</t>
+          <t>จำนวนผู้ใช้งานต่อวัน</t>
         </is>
       </c>
       <c r="U3" s="40" t="inlineStr">
         <is>
-          <t>Peak concurrent (คนพร้อมกัน)</t>
+          <t>ผู้ใช้งานพร้อมกันสูงสุด</t>
         </is>
       </c>
       <c r="V3" s="40" t="inlineStr">
         <is>
-          <t>AI ประมวลผลกี่รายการ/วัน</t>
+          <t>ปริมาณรายการที่ประมวลผลต่อวัน</t>
         </is>
       </c>
       <c r="W3" s="40" t="inlineStr">
         <is>
-          <t>ขนาดข้อมูล Input/วัน</t>
+          <t>ปริมาณข้อมูลนำเข้าต่อวัน</t>
         </is>
       </c>
       <c r="X3" s="40" t="inlineStr">
         <is>
-          <t>ขนาดคลังเอกสารทั้งหมด (RAG)</t>
+          <t>ขนาดคลังเอกสารทั้งหมด</t>
         </is>
       </c>
       <c r="Y3" s="40" t="inlineStr">
         <is>
-          <t>จำนวนกล้อง/จุดตรวจพร้อมกัน</t>
+          <t>จุดตรวจที่ทำงานพร้อมกัน</t>
         </is>
       </c>
       <c r="Z3" s="40" t="inlineStr">
         <is>
-          <t>ติดตั้งแบบไหน</t>
+          <t>รูปแบบการติดตั้ง</t>
         </is>
       </c>
       <c r="AB3" s="40" t="inlineStr">
         <is>
-          <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
+          <t>ระยะเวลาการจัดเก็บข้อมูล</t>
         </is>
       </c>
       <c r="AC3" s="40" t="inlineStr">
         <is>
-          <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
+          <t>ความถี่ในการฝึกโมเดลใหม่</t>
         </is>
       </c>
       <c r="AD3" s="40" t="inlineStr">
         <is>
-          <t>ถ้างานนี้ช้าลงจะเป็นปัญหามั้ย</t>
+          <t>ผลกระทบเมื่อระบบตอบสนองช้าลง</t>
         </is>
       </c>
       <c r="AE3" s="40" t="inlineStr">
         <is>
-          <t>งานนี้เริ่มทำงานยังไง</t>
+          <t>ลักษณะการเริ่มทำงานของระบบ</t>
         </is>
       </c>
       <c r="AH3" s="41" t="inlineStr">
@@ -7010,47 +7137,47 @@
       </c>
       <c r="B4" s="42" t="inlineStr">
         <is>
-          <t>กระดาษ / เอกสารเขียนมือ - ต้องพิมพ์เข้าคอมก่อน</t>
+          <t>เอกสารกระดาษ / บันทึกด้วยลายมือ - ต้องแปลงเป็นดิจิทัลก่อน</t>
         </is>
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>ยังไม่มี - ต้องเริ่มเก็บใหม่</t>
+          <t>ไม่มีข้อมูลย้อนหลัง - ต้องเริ่มเก็บใหม่</t>
         </is>
       </c>
       <c r="D4" s="42" t="inlineStr">
         <is>
-          <t>ได้ทันที - ข้อมูลอยู่ในมือแผนกเราเอง</t>
+          <t>ได้ทันที - ข้อมูลอยู่ในความดูแลของหน่วยงาน</t>
         </is>
       </c>
       <c r="E4" s="42" t="inlineStr">
         <is>
-          <t>ไม่มี - AI ทำงานแยกเดี่ยวได้เลย ไม่ต้องยุ่งกับระบบไหน</t>
+          <t>ไม่จำเป็น - ระบบทำงานแยกอิสระได้</t>
         </is>
       </c>
       <c r="F4" s="42" t="inlineStr">
         <is>
-          <t>มี - มีคนในแผนกรับดูแลต่อได้ (ระบุชื่อในหมายเหตุ)</t>
+          <t>มี - หน่วยงานมีผู้รับผิดชอบดูแลต่อ (ระบุชื่อในหมายเหตุ)</t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t>ต่ำ - คนเห็นแล้วแก้ได้ทันที ไม่มีใครเดือดร้อน</t>
+          <t>ต่ำ - ตรวจพบและแก้ไขได้ทันที ไม่กระทบผู้อื่น</t>
         </is>
       </c>
       <c r="H4" s="42" t="inlineStr">
         <is>
-          <t>ไม่ต้อง - ใช้ผล AI ได้เลย</t>
+          <t>ไม่จำเป็น - ใช้ผลลัพธ์จาก AI ได้ทันที</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
-          <t>สาธารณะ - หลุดออกไปก็ไม่เป็นไร</t>
+          <t>สาธารณะ - เปิดเผยได้ ไม่มีผลกระทบ</t>
         </is>
       </c>
       <c r="J4" s="42" t="inlineStr">
         <is>
-          <t>สูง - ต้องการด่วน</t>
+          <t>สูง - ต้องการเร่งด่วน</t>
         </is>
       </c>
       <c r="K4" s="42" t="inlineStr">
@@ -7065,12 +7192,12 @@
       </c>
       <c r="M4" s="42" t="inlineStr">
         <is>
-          <t>Real-time (0 - 2 วินาที)</t>
+          <t>ทันที - ไม่เกิน 2 วินาที (ตอบกลับในกระบวนการทันที)</t>
         </is>
       </c>
       <c r="N4" s="42" t="inlineStr">
         <is>
-          <t>Business Hour (8:00 - 18:00)</t>
+          <t>เวลาทำการ 8:00 - 18:00 น.</t>
         </is>
       </c>
       <c r="O4" s="42" t="inlineStr">
@@ -7080,22 +7207,22 @@
       </c>
       <c r="P4" s="42" t="inlineStr">
         <is>
-          <t>On-premise เท่านั้น (ห้ามออกนอก)</t>
+          <t>On-premise เท่านั้น</t>
         </is>
       </c>
       <c r="Q4" s="42" t="inlineStr">
         <is>
-          <t>ไม่ต้อง - ใช้โมเดลสำเร็จรูปได้เลย (งานความรู้ทั่วไป)</t>
+          <t>ไม่จำเป็น - ใช้โมเดลสำเร็จรูปได้ (งานความรู้ทั่วไป)</t>
         </is>
       </c>
       <c r="R4" s="42" t="inlineStr">
         <is>
-          <t>น้อยกว่า 4 ชม./สัปดาห์  (ไม่ถึงครึ่งวันทำงาน)</t>
+          <t>น้อยกว่า 4 ชั่วโมง/สัปดาห์ (ไม่ถึงครึ่งวันทำงาน)</t>
         </is>
       </c>
       <c r="S4" s="42" t="inlineStr">
         <is>
-          <t>ประเมินเป็นเงินไม่ได้ / ไม่มีความเสียหายโดยตรง</t>
+          <t>ไม่สามารถประเมินเป็นตัวเงินได้ หรือไม่มีความสูญเสียโดยตรง</t>
         </is>
       </c>
       <c r="T4" s="42" t="inlineStr">
@@ -7110,7 +7237,7 @@
       </c>
       <c r="V4" s="42" t="inlineStr">
         <is>
-          <t>น้อยกว่า 100 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
+          <t>น้อยกว่า 100 รายการ</t>
         </is>
       </c>
       <c r="W4" s="42" t="inlineStr">
@@ -7120,17 +7247,17 @@
       </c>
       <c r="X4" s="42" t="inlineStr">
         <is>
-          <t>ไม่เกี่ยวข้อง - ไม่ใช่งานค้นหาเอกสาร</t>
+          <t>ไม่เกี่ยวข้อง - ไม่ใช่งานสืบค้นเอกสาร</t>
         </is>
       </c>
       <c r="Y4" s="42" t="inlineStr">
         <is>
-          <t>ไม่เกี่ยวข้อง - ไม่ใช่งานภาพ</t>
+          <t>ไม่เกี่ยวข้อง - ไม่ใช่งานประมวลผลภาพ</t>
         </is>
       </c>
       <c r="Z4" s="42" t="inlineStr">
         <is>
-          <t>รันบน server กลางได้ - ส่งข้อมูลผ่านเครือข่ายมาได้</t>
+          <t>ติดตั้งที่ Server กลาง - ส่งข้อมูลผ่านเครือข่ายได้</t>
         </is>
       </c>
       <c r="AB4" s="42" t="inlineStr">
@@ -7140,17 +7267,17 @@
       </c>
       <c r="AC4" s="42" t="inlineStr">
         <is>
-          <t>ไม่ต้องเทรนเลย - ใช้โมเดลสำเร็จรูป</t>
+          <t>ไม่ต้องฝึกโมเดล - ใช้โมเดลสำเร็จรูป</t>
         </is>
       </c>
       <c r="AD4" s="42" t="inlineStr">
         <is>
-          <t>ไม่เป็นไร - รอได้ ช้าหน่อยก็ยังใช้งานได้</t>
+          <t>ไม่กระทบ - รอได้ ใช้งานได้ตามปกติ</t>
         </is>
       </c>
       <c r="AE4" s="42" t="inlineStr">
         <is>
-          <t>คนกดใช้เอง - มีคนเปิดใช้เป็นครั้งๆ</t>
+          <t>ผู้ใช้เรียกใช้งานเอง - เปิดใช้เป็นครั้งคราว</t>
         </is>
       </c>
       <c r="AH4" s="42" t="inlineStr">
@@ -7170,52 +7297,52 @@
       </c>
       <c r="B5" s="42" t="inlineStr">
         <is>
-          <t>ไฟล์ Excel / CSV - เปิดใช้ได้เลย</t>
+          <t>ไฟล์ Excel / CSV - นำไปใช้ได้ทันที</t>
         </is>
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>น้อยกว่า 1 ปี - อาจยังไม่พอเทรน</t>
+          <t>น้อยกว่า 1 ปี - อาจไม่เพียงพอต่อการฝึกโมเดล</t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t>ต้องขออนุมัติก่อน - เป็นของแผนกอื่น / IT</t>
+          <t>ต้องขออนุมัติก่อน - อยู่ในความดูแลของหน่วยงานอื่นหรือ IT</t>
         </is>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>มี - แค่ export ไฟล์ออกมาให้ AI แล้วเอาผลกลับเข้าไปทีหลังก็พอ</t>
+          <t>จำเป็นบางส่วน - เชื่อมต่อผ่านการนำเข้า/ส่งออกไฟล์เป็นรอบ</t>
         </is>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>ยังไม่แน่ใจ - ต้องหาคนก่อน</t>
+          <t>ยังไม่แน่ใจ - อยู่ระหว่างจัดหาผู้รับผิดชอบ</t>
         </is>
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t>กลาง - เสียเวลาทำใหม่ หรือเสียต้นทุนบางส่วน</t>
+          <t>ปานกลาง - เสียเวลาดำเนินการใหม่ หรือเกิดต้นทุนเพิ่ม</t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t>สุ่มตรวจบางส่วน - ตรวจเฉพาะที่ AI ไม่มั่นใจ</t>
+          <t>สุ่มตรวจบางส่วน - เฉพาะรายการที่ AI ไม่มั่นใจ</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t>ข้อมูลภายใน - ห้ามออกนอกบริษัท</t>
+          <t>ภายในองค์กร - ห้ามเผยแพร่ออกนอกบริษัท</t>
         </is>
       </c>
       <c r="J5" s="42" t="inlineStr">
         <is>
-          <t>กลาง - (Q2 - Q3)</t>
+          <t>ปานกลาง - ภายในไตรมาส 2 ถึง 3</t>
         </is>
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
-          <t>รูปภาพ</t>
+          <t>ภาพถ่าย</t>
         </is>
       </c>
       <c r="L5" s="42" t="inlineStr">
@@ -7225,37 +7352,37 @@
       </c>
       <c r="M5" s="42" t="inlineStr">
         <is>
-          <t>Interactive (2 - 10 วินาที)</t>
+          <t>เร็ว - 2 ถึง 10 วินาที (ผู้ใช้รอที่หน้าจอได้)</t>
         </is>
       </c>
       <c r="N5" s="42" t="inlineStr">
         <is>
-          <t>Extended (6:00 - 22:00)</t>
+          <t>ขยายเวลา 6:00 - 22:00 น.</t>
         </is>
       </c>
       <c r="O5" s="42" t="inlineStr">
         <is>
-          <t>ต่ำกว่า 1 MP</t>
+          <t>ต่ำกว่า 1 ล้านพิกเซล</t>
         </is>
       </c>
       <c r="P5" s="42" t="inlineStr">
         <is>
-          <t>ใช้ Cloud / API ภายนอกได้</t>
+          <t>ใช้ Cloud ได้</t>
         </is>
       </c>
       <c r="Q5" s="42" t="inlineStr">
         <is>
-          <t>ไม่ต้องเทรน แต่ให้อ่านเอกสารบริษัท (RAG)</t>
+          <t>ไม่ต้องฝึกโมเดล แต่ให้เข้าถึงเอกสารขององค์กร (RAG)</t>
         </is>
       </c>
       <c r="R5" s="42" t="inlineStr">
         <is>
-          <t>4 - 10 ชม./สัปดาห์  (ประมาณ 1 วันทำงาน)</t>
+          <t>4 - 10 ชั่วโมง/สัปดาห์ (ประมาณ 1 วันทำงาน)</t>
         </is>
       </c>
       <c r="S5" s="42" t="inlineStr">
         <is>
-          <t>น้อยกว่า 1 แสนบาท/ปี</t>
+          <t>น้อยกว่า 100,000 บาท/ปี</t>
         </is>
       </c>
       <c r="T5" s="42" t="inlineStr">
@@ -7270,7 +7397,7 @@
       </c>
       <c r="V5" s="42" t="inlineStr">
         <is>
-          <t>100 - 1,000 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
+          <t>100 - 1,000 รายการ</t>
         </is>
       </c>
       <c r="W5" s="42" t="inlineStr">
@@ -7290,7 +7417,7 @@
       </c>
       <c r="Z5" s="42" t="inlineStr">
         <is>
-          <t>ต้องมีเครื่องที่หน้างาน - ติดข้างเครื่องจักร/สายพาน</t>
+          <t>ต้องติดตั้งที่หน้างาน - ติดตั้งข้างเครื่องจักรหรือสายพาน</t>
         </is>
       </c>
       <c r="AB5" s="42" t="inlineStr">
@@ -7300,17 +7427,17 @@
       </c>
       <c r="AC5" s="42" t="inlineStr">
         <is>
-          <t>ครั้งเดียวจบ - เทรนเสร็จใช้ยาว</t>
+          <t>ครั้งเดียว - ฝึกเสร็จแล้วใช้งานต่อเนื่อง</t>
         </is>
       </c>
       <c r="AD5" s="42" t="inlineStr">
         <is>
-          <t>พอรับได้ - แต่ช่วงเร่งด่วนต้องได้ใช้ก่อน</t>
+          <t>กระทบบ้าง - ช่วงเร่งด่วนต้องได้รับความสำคัญก่อน</t>
         </is>
       </c>
       <c r="AE5" s="42" t="inlineStr">
         <is>
-          <t>ทำงานอัตโนมัติต่อเนื่อง - ระบบสั่งเอง ไม่มีคนกด</t>
+          <t>ทำงานอัตโนมัติต่อเนื่อง - ระบบทำงานเอง ไม่มีผู้เรียกใช้</t>
         </is>
       </c>
       <c r="AH5" s="42" t="inlineStr">
@@ -7330,47 +7457,47 @@
       </c>
       <c r="B6" s="42" t="inlineStr">
         <is>
-          <t>ฐานข้อมูลในระบบ (ERP/MES/SQL) - ดึงอัตโนมัติได้</t>
+          <t>ฐานข้อมูลในระบบ (ERP / MES / SQL) - ดึงข้อมูลอัตโนมัติได้</t>
         </is>
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>1 - 3 ปี - พอใช้ได้</t>
+          <t>1 - 3 ปี - เพียงพอในระดับหนึ่ง</t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>ขอไม่ได้ / ยังไม่แน่ใจ - เป็นของลูกค้าหรือ vendor</t>
+          <t>ไม่สามารถขอได้ หรือยังไม่แน่ใจ - เป็นของลูกค้าหรือผู้ขาย</t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>มี - AI ต้องอ่าน/เขียนข้อมูลในระบบโดยตรงแบบทันที</t>
+          <t>จำเป็น - ต้องอ่านและเขียนข้อมูลกับระบบเดิมแบบทันที</t>
         </is>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>ไม่มี - ต้องพึ่งคนนอกแผนกตลอด</t>
+          <t>ไม่มี - ต้องพึ่งพาหน่วยงานภายนอกตลอด</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t>สูง - ของเสียหลุดถึงลูกค้า / อันตราย / ผิดกฎหมาย</t>
+          <t>สูง - ของเสียถึงมือลูกค้า เกิดอันตราย หรือผิดข้อกำหนดกฎหมาย</t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t>ตรวจซ้ำทุกครั้ง - คนต้องดูทุกชิ้น/ทุกรายการ</t>
+          <t>ตรวจสอบทุกรายการ - บุคลากรต้องตรวจซ้ำทั้งหมด</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>ลับ - ต้องจำกัดสิทธิ์ว่าใครเปิดดูได้บ้าง</t>
+          <t>ลับ - ต้องจำกัดสิทธิ์การเข้าถึง</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
         <is>
-          <t>ต่ำ - Nice to have</t>
+          <t>ต่ำ - ดำเนินการได้ภายหลัง</t>
         </is>
       </c>
       <c r="K6" s="42" t="inlineStr">
@@ -7380,42 +7507,42 @@
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
-          <t>ไทย + อังกฤษ</t>
+          <t>ไทยและอังกฤษ</t>
         </is>
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t>Batch (นาที - ชั่วโมง)</t>
+          <t>ภายในไม่กี่นาที</t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
         <is>
-          <t>24 ชม. x 7 วัน</t>
+          <t>ตลอด 24 ชั่วโมง ทุกวัน</t>
         </is>
       </c>
       <c r="O6" s="42" t="inlineStr">
         <is>
-          <t>1 - 5 MP</t>
+          <t>1 - 5 ล้านพิกเซล</t>
         </is>
       </c>
       <c r="P6" s="42" t="inlineStr">
         <is>
-          <t>ผสม (ข้อมูลลับอยู่ใน, ที่เหลือออกได้)</t>
+          <t>ผสม</t>
         </is>
       </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
-          <t>ต้อง Fine-tune - สอนด้วยข้อมูล/รูปของบริษัทเอง</t>
+          <t>จำเป็น - ต้อง Fine-tune ด้วยข้อมูลหรือภาพขององค์กร</t>
         </is>
       </c>
       <c r="R6" s="42" t="inlineStr">
         <is>
-          <t>10 - 20 ชม./สัปดาห์  (ประมาณ 2 วันทำงาน)</t>
+          <t>10 - 20 ชั่วโมง/สัปดาห์ (ประมาณ 2 วันทำงาน)</t>
         </is>
       </c>
       <c r="S6" s="42" t="inlineStr">
         <is>
-          <t>1 - 5 แสนบาท/ปี</t>
+          <t>100,000 - 500,000 บาท/ปี</t>
         </is>
       </c>
       <c r="T6" s="42" t="inlineStr">
@@ -7430,7 +7557,7 @@
       </c>
       <c r="V6" s="42" t="inlineStr">
         <is>
-          <t>1,000 - 10,000 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
+          <t>1,000 - 10,000 รายการ</t>
         </is>
       </c>
       <c r="W6" s="42" t="inlineStr">
@@ -7450,7 +7577,7 @@
       </c>
       <c r="Z6" s="42" t="inlineStr">
         <is>
-          <t>ยังไม่แน่ใจ</t>
+          <t>ยังไม่สามารถระบุได้</t>
         </is>
       </c>
       <c r="AB6" s="42" t="inlineStr">
@@ -7465,12 +7592,12 @@
       </c>
       <c r="AD6" s="42" t="inlineStr">
         <is>
-          <t>เป็นปัญหา - งานนี้ช้าหรือหยุดไม่ได้เลย (อยู่ในสายการผลิต)</t>
+          <t>กระทบมาก - ไม่สามารถล่าช้าหรือหยุดได้ (อยู่ในสายการผลิต)</t>
         </is>
       </c>
       <c r="AE6" s="42" t="inlineStr">
         <is>
-          <t>รันตามรอบเวลา - เช่น ทุกคืน ทุกเช้าวันจันทร์</t>
+          <t>ประมวลผลตามรอบเวลา - เช่น ทุกคืน หรือทุกสัปดาห์</t>
         </is>
       </c>
       <c r="AH6" s="42" t="inlineStr">
@@ -7490,22 +7617,22 @@
       </c>
       <c r="B7" s="42" t="inlineStr">
         <is>
-          <t>รูปภาพ / ภาพถ่าย</t>
+          <t>ภาพถ่าย / ไฟล์รูปภาพ</t>
         </is>
       </c>
       <c r="C7" s="42" t="inlineStr">
         <is>
-          <t>มากกว่า 3 ปี - เพียงพอแน่นอน</t>
+          <t>มากกว่า 3 ปี - เพียงพอ</t>
         </is>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>ยังไม่แน่ใจ - ต้องถาม IT ก่อน</t>
+          <t>ยังไม่สามารถระบุได้ - ต้องหารือกับฝ่าย IT</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t>ลับมาก - มีข้อมูลส่วนบุคคล / ผูกกับกฎหมาย PDPA</t>
+          <t>ลับที่สุด - มีข้อมูลส่วนบุคคล อยู่ภายใต้ PDPA</t>
         </is>
       </c>
       <c r="K7" s="42" t="inlineStr">
@@ -7515,27 +7642,32 @@
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
-          <t>ไม่เกี่ยวกับภาษา</t>
+          <t>ไม่เกี่ยวข้องกับภาษา</t>
+        </is>
+      </c>
+      <c r="M7" s="42" t="inlineStr">
+        <is>
+          <t>ภายใน 1 ชั่วโมง หรือภายในรอบกะ</t>
         </is>
       </c>
       <c r="O7" s="42" t="inlineStr">
         <is>
-          <t>5 - 12 MP</t>
+          <t>5 - 12 ล้านพิกเซล</t>
         </is>
       </c>
       <c r="Q7" s="42" t="inlineStr">
         <is>
-          <t>ยังไม่แน่ใจ</t>
+          <t>ยังไม่สามารถระบุได้</t>
         </is>
       </c>
       <c r="R7" s="42" t="inlineStr">
         <is>
-          <t>20 - 40 ชม./สัปดาห์  (เท่ากับใช้คน 1 คนเต็มเวลา)</t>
+          <t>20 - 40 ชั่วโมง/สัปดาห์ (เทียบเท่าบุคลากร 1 คนเต็มเวลา)</t>
         </is>
       </c>
       <c r="S7" s="42" t="inlineStr">
         <is>
-          <t>5 แสน - 2 ล้านบาท/ปี</t>
+          <t>500,000 - 2,000,000 บาท/ปี</t>
         </is>
       </c>
       <c r="T7" s="42" t="inlineStr">
@@ -7550,7 +7682,7 @@
       </c>
       <c r="V7" s="42" t="inlineStr">
         <is>
-          <t>10,000 - 100,000 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
+          <t>10,000 - 100,000 รายการ</t>
         </is>
       </c>
       <c r="W7" s="42" t="inlineStr">
@@ -7570,7 +7702,7 @@
       </c>
       <c r="AB7" s="42" t="inlineStr">
         <is>
-          <t>เก็บถาวร - ห้ามลบ (ข้อกำหนดลูกค้า/กฎหมาย)</t>
+          <t>จัดเก็บถาวร - ห้ามลบ ตามข้อกำหนดลูกค้าหรือกฎหมาย</t>
         </is>
       </c>
       <c r="AC7" s="42" t="inlineStr">
@@ -7580,12 +7712,12 @@
       </c>
       <c r="AD7" s="42" t="inlineStr">
         <is>
-          <t>ยังไม่แน่ใจ</t>
+          <t>ยังไม่สามารถระบุได้</t>
         </is>
       </c>
       <c r="AE7" s="42" t="inlineStr">
         <is>
-          <t>ทำงานเมื่อมีเหตุการณ์ - เช่น มีใบ NC เข้ามา</t>
+          <t>ทำงานเมื่อเกิดเหตุการณ์ - เช่น มีใบ NC เข้าสู่ระบบ</t>
         </is>
       </c>
       <c r="AH7" s="42" t="inlineStr">
@@ -7605,7 +7737,7 @@
       </c>
       <c r="B8" s="42" t="inlineStr">
         <is>
-          <t>เสียง / วิดีโอ</t>
+          <t>ไฟล์เสียง / วิดีโอ</t>
         </is>
       </c>
       <c r="K8" s="42" t="inlineStr">
@@ -7613,19 +7745,24 @@
           <t>ตัวเลข / ตาราง</t>
         </is>
       </c>
+      <c r="M8" s="42" t="inlineStr">
+        <is>
+          <t>ภายในรอบวัน - ประมวลผลกลางคืน เสร็จก่อนเริ่มงานเช้า</t>
+        </is>
+      </c>
       <c r="O8" s="42" t="inlineStr">
         <is>
-          <t>มากกว่า 12 MP</t>
+          <t>มากกว่า 12 ล้านพิกเซล</t>
         </is>
       </c>
       <c r="R8" s="42" t="inlineStr">
         <is>
-          <t>มากกว่า 40 ชม./สัปดาห์  (มากกว่า 1 คนเต็มเวลา)</t>
+          <t>มากกว่า 40 ชั่วโมง/สัปดาห์ (มากกว่า 1 คนเต็มเวลา)</t>
         </is>
       </c>
       <c r="S8" s="42" t="inlineStr">
         <is>
-          <t>มากกว่า 2 ล้านบาท/ปี</t>
+          <t>มากกว่า 2,000,000 บาท/ปี</t>
         </is>
       </c>
       <c r="T8" s="42" t="inlineStr">
@@ -7640,7 +7777,7 @@
       </c>
       <c r="V8" s="42" t="inlineStr">
         <is>
-          <t>มากกว่า 100,000 รายการ  (ชิ้น / ล็อต / คำถาม / เคส)</t>
+          <t>มากกว่า 100,000 รายการ</t>
         </is>
       </c>
       <c r="X8" s="42" t="inlineStr">
@@ -7655,24 +7792,24 @@
       </c>
       <c r="AC8" s="42" t="inlineStr">
         <is>
-          <t>ทุกเดือนหรือถี่กว่า</t>
+          <t>ทุกเดือนหรือถี่กว่านั้น</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="42" t="inlineStr">
         <is>
-          <t>ยังไม่มีข้อมูลเก็บไว้ - ต้องเริ่มเก็บใหม่</t>
+          <t>ยังไม่มีการจัดเก็บ - ต้องเริ่มเก็บใหม่</t>
         </is>
       </c>
       <c r="K9" s="42" t="inlineStr">
         <is>
-          <t>ผสมหลายแบบ</t>
+          <t>ผสมหลายประเภท</t>
         </is>
       </c>
       <c r="AC9" s="42" t="inlineStr">
         <is>
-          <t>ยังไม่แน่ใจ</t>
+          <t>ยังไม่สามารถระบุได้</t>
         </is>
       </c>
       <c r="AH9" s="41" t="inlineStr">
@@ -7744,72 +7881,72 @@
       </c>
       <c r="B29" s="40" t="inlineStr">
         <is>
-          <t>ตอนนี้ข้อมูลเก็บอยู่ในรูปแบบไหน</t>
+          <t>รูปแบบการจัดเก็บข้อมูลปัจจุบัน</t>
         </is>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
-          <t>มีข้อมูลย้อนหลังนานแค่ไหน</t>
+          <t>ระยะเวลาข้อมูลย้อนหลังที่มี</t>
         </is>
       </c>
       <c r="D29" s="40" t="inlineStr">
         <is>
-          <t>สิทธิ์นำข้อมูลมาใช้</t>
+          <t>สิทธิ์ในการนำข้อมูลมาใช้</t>
         </is>
       </c>
       <c r="E29" s="40" t="inlineStr">
         <is>
-          <t>ต้องเชื่อมต่อกับระบบไอทีเดิมมั้ย</t>
+          <t>การเชื่อมต่อกับระบบเดิม</t>
         </is>
       </c>
       <c r="F29" s="40" t="inlineStr">
         <is>
-          <t>มีคนดูแลระบบต่อหลังส่งมอบมั้ย</t>
+          <t>ผู้ดูแลระบบหลังส่งมอบ</t>
         </is>
       </c>
       <c r="G29" s="40" t="inlineStr">
         <is>
-          <t>ถ้า AI ตอบผิด จะเกิดอะไรขึ้น</t>
+          <t>ผลกระทบเมื่อ AI ผิดพลาด</t>
         </is>
       </c>
       <c r="H29" s="40" t="inlineStr">
         <is>
-          <t>ต้องให้คนตรวจงานที่ AI ทำซ้ำมั้ย</t>
+          <t>การตรวจสอบผลลัพธ์โดยบุคลากร</t>
         </is>
       </c>
       <c r="I29" s="40" t="inlineStr">
         <is>
-          <t>ข้อมูลชุดนี้ลับแค่ไหน</t>
+          <t>ระดับชั้นความลับของข้อมูล</t>
         </is>
       </c>
       <c r="J29" s="40" t="inlineStr">
         <is>
-          <t>ความสำคัญที่แผนกอยากได้</t>
+          <t>ระดับความสำคัญตามความเห็นผู้ใช้</t>
         </is>
       </c>
       <c r="K29" s="40" t="inlineStr">
         <is>
-          <t>ประเภทข้อมูล Input</t>
+          <t>ประเภทข้อมูลนำเข้า</t>
         </is>
       </c>
       <c r="L29" s="40" t="inlineStr">
         <is>
-          <t>ภาษาที่ต้องการ</t>
+          <t>ภาษาที่ต้องรองรับ</t>
         </is>
       </c>
       <c r="M29" s="40" t="inlineStr">
         <is>
-          <t>Latency ที่รับได้</t>
+          <t>เวลาตอบสนองที่ยอมรับได้</t>
         </is>
       </c>
       <c r="N29" s="40" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>ช่วงเวลาที่ต้องให้บริการ</t>
         </is>
       </c>
       <c r="O29" s="40" t="inlineStr">
         <is>
-          <t>ความละเอียดรูป</t>
+          <t>ความละเอียดของภาพ</t>
         </is>
       </c>
       <c r="P29" s="40" t="inlineStr">
@@ -7819,72 +7956,72 @@
       </c>
       <c r="Q29" s="40" t="inlineStr">
         <is>
-          <t>ต้องสอนโมเดลด้วยข้อมูลบริษัทมั้ย</t>
+          <t>การปรับโมเดลด้วยข้อมูลองค์กร</t>
         </is>
       </c>
       <c r="R29" s="40" t="inlineStr">
         <is>
-          <t>เวลาที่ใช้กับงานนี้ตอนนี้</t>
+          <t>เวลาที่ใช้กับงานนี้ในปัจจุบัน</t>
         </is>
       </c>
       <c r="S29" s="40" t="inlineStr">
         <is>
-          <t>มูลค่าความเสียหาย/ของเสียต่อปี</t>
+          <t>มูลค่าความสูญเสียต่อปี</t>
         </is>
       </c>
       <c r="T29" s="40" t="inlineStr">
         <is>
-          <t>จำนวน Users/วัน</t>
+          <t>จำนวนผู้ใช้งานต่อวัน</t>
         </is>
       </c>
       <c r="U29" s="40" t="inlineStr">
         <is>
-          <t>Peak concurrent (คนพร้อมกัน)</t>
+          <t>ผู้ใช้งานพร้อมกันสูงสุด</t>
         </is>
       </c>
       <c r="V29" s="40" t="inlineStr">
         <is>
-          <t>AI ประมวลผลกี่รายการ/วัน</t>
+          <t>ปริมาณรายการที่ประมวลผลต่อวัน</t>
         </is>
       </c>
       <c r="W29" s="40" t="inlineStr">
         <is>
-          <t>ขนาดข้อมูล Input/วัน</t>
+          <t>ปริมาณข้อมูลนำเข้าต่อวัน</t>
         </is>
       </c>
       <c r="X29" s="40" t="inlineStr">
         <is>
-          <t>ขนาดคลังเอกสารทั้งหมด (RAG)</t>
+          <t>ขนาดคลังเอกสารทั้งหมด</t>
         </is>
       </c>
       <c r="Y29" s="40" t="inlineStr">
         <is>
-          <t>จำนวนกล้อง/จุดตรวจพร้อมกัน</t>
+          <t>จุดตรวจที่ทำงานพร้อมกัน</t>
         </is>
       </c>
       <c r="Z29" s="40" t="inlineStr">
         <is>
-          <t>ติดตั้งแบบไหน</t>
+          <t>รูปแบบการติดตั้ง</t>
         </is>
       </c>
       <c r="AB29" s="40" t="inlineStr">
         <is>
-          <t>ต้องเก็บข้อมูลย้อนหลังกี่ปี</t>
+          <t>ระยะเวลาการจัดเก็บข้อมูล</t>
         </is>
       </c>
       <c r="AC29" s="40" t="inlineStr">
         <is>
-          <t>ต้องเทรนโมเดลใหม่บ่อยแค่ไหน</t>
+          <t>ความถี่ในการฝึกโมเดลใหม่</t>
         </is>
       </c>
       <c r="AD29" s="40" t="inlineStr">
         <is>
-          <t>ถ้างานนี้ช้าลงจะเป็นปัญหามั้ย</t>
+          <t>ผลกระทบเมื่อระบบตอบสนองช้าลง</t>
         </is>
       </c>
       <c r="AE29" s="40" t="inlineStr">
         <is>
-          <t>งานนี้เริ่มทำงานยังไง</t>
+          <t>ลักษณะการเริ่มทำงานของระบบ</t>
         </is>
       </c>
     </row>
@@ -8314,6 +8451,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="M33" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O33" s="45" t="inlineStr">
         <is>
           <t>-</t>
@@ -8391,6 +8533,11 @@
         <v>2</v>
       </c>
       <c r="K34" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M34" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -1107,7 +1107,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
@@ -2330,7 +2330,7 @@
   </mergeCells>
   <dataValidations count="17">
     <dataValidation sqref="C7:C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="บริษัท" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
-      <formula1>DATA!$A$4:$A$8</formula1>
+      <formula1>DATA!$A$4:$A$9</formula1>
     </dataValidation>
     <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="เวลาที่ใช้กับงานนี้ในปัจจุบัน" prompt="เวลาที่คนใช้ทำงานนี้ด้วยวิธีเดิม รวมทุกคนในหน่วยงาน&#10;&#10;เช่น 3 คน คนละ 6 ชั่วโมง/สัปดาห์ = 18 ชั่วโมง/สัปดาห์&#10;&#10;ยังไม่ได้ใช้ AI ช่วย" type="list">
       <formula1>DATA!$R$4:$R$8</formula1>
@@ -7132,7 +7132,7 @@
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
         <is>
-          <t>S.K.Polymer</t>
+          <t>บริษัท แกรนด์เอสเค คอร์ปอเรชั่น จำกัด</t>
         </is>
       </c>
       <c r="B4" s="42" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="5">
       <c r="A5" s="42" t="inlineStr">
         <is>
-          <t>Thairubbtech</t>
+          <t>บริษัท เอส.เค.โพลีเมอร์ จำกัด</t>
         </is>
       </c>
       <c r="B5" s="42" t="inlineStr">
@@ -7452,7 +7452,7 @@
     <row r="6">
       <c r="A6" s="42" t="inlineStr">
         <is>
-          <t>Polymate</t>
+          <t>บริษัท ไทยรับเทค จำกัด</t>
         </is>
       </c>
       <c r="B6" s="42" t="inlineStr">
@@ -7612,7 +7612,7 @@
     <row r="7">
       <c r="A7" s="42" t="inlineStr">
         <is>
-          <t>GTK</t>
+          <t>บริษัท โพลีเมท จำกัด</t>
         </is>
       </c>
       <c r="B7" s="42" t="inlineStr">
@@ -7732,71 +7732,76 @@
     <row r="8">
       <c r="A8" s="42" t="inlineStr">
         <is>
+          <t>บริษัท จีทีเค สมาร์ท โซลูชั่น จำกัด</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t>ไฟล์เสียง / วิดีโอ</t>
+        </is>
+      </c>
+      <c r="K8" s="42" t="inlineStr">
+        <is>
+          <t>ตัวเลข / ตาราง</t>
+        </is>
+      </c>
+      <c r="M8" s="42" t="inlineStr">
+        <is>
+          <t>ภายในรอบวัน - ประมวลผลกลางคืน เสร็จก่อนเริ่มงานเช้า</t>
+        </is>
+      </c>
+      <c r="O8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 12 ล้านพิกเซล</t>
+        </is>
+      </c>
+      <c r="R8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 40 ชั่วโมง/สัปดาห์ (มากกว่า 1 คนเต็มเวลา)</t>
+        </is>
+      </c>
+      <c r="S8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 2,000,000 บาท/ปี</t>
+        </is>
+      </c>
+      <c r="T8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 1,000 คน</t>
+        </is>
+      </c>
+      <c r="U8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 50 คน</t>
+        </is>
+      </c>
+      <c r="V8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 100,000 รายการ</t>
+        </is>
+      </c>
+      <c r="X8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 100 GB</t>
+        </is>
+      </c>
+      <c r="Y8" s="42" t="inlineStr">
+        <is>
+          <t>มากกว่า 8 จุด</t>
+        </is>
+      </c>
+      <c r="AC8" s="42" t="inlineStr">
+        <is>
+          <t>ทุกเดือนหรือถี่กว่านั้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
           <t>อื่นๆ</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
-        <is>
-          <t>ไฟล์เสียง / วิดีโอ</t>
-        </is>
-      </c>
-      <c r="K8" s="42" t="inlineStr">
-        <is>
-          <t>ตัวเลข / ตาราง</t>
-        </is>
-      </c>
-      <c r="M8" s="42" t="inlineStr">
-        <is>
-          <t>ภายในรอบวัน - ประมวลผลกลางคืน เสร็จก่อนเริ่มงานเช้า</t>
-        </is>
-      </c>
-      <c r="O8" s="42" t="inlineStr">
-        <is>
-          <t>มากกว่า 12 ล้านพิกเซล</t>
-        </is>
-      </c>
-      <c r="R8" s="42" t="inlineStr">
-        <is>
-          <t>มากกว่า 40 ชั่วโมง/สัปดาห์ (มากกว่า 1 คนเต็มเวลา)</t>
-        </is>
-      </c>
-      <c r="S8" s="42" t="inlineStr">
-        <is>
-          <t>มากกว่า 2,000,000 บาท/ปี</t>
-        </is>
-      </c>
-      <c r="T8" s="42" t="inlineStr">
-        <is>
-          <t>มากกว่า 1,000 คน</t>
-        </is>
-      </c>
-      <c r="U8" s="42" t="inlineStr">
-        <is>
-          <t>มากกว่า 50 คน</t>
-        </is>
-      </c>
-      <c r="V8" s="42" t="inlineStr">
-        <is>
-          <t>มากกว่า 100,000 รายการ</t>
-        </is>
-      </c>
-      <c r="X8" s="42" t="inlineStr">
-        <is>
-          <t>มากกว่า 100 GB</t>
-        </is>
-      </c>
-      <c r="Y8" s="42" t="inlineStr">
-        <is>
-          <t>มากกว่า 8 จุด</t>
-        </is>
-      </c>
-      <c r="AC8" s="42" t="inlineStr">
-        <is>
-          <t>ทุกเดือนหรือถี่กว่านั้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
       <c r="B9" s="42" t="inlineStr">
         <is>
           <t>ยังไม่มีการจัดเก็บ - ต้องเริ่มเก็บใหม่</t>
@@ -8585,6 +8590,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="B35" s="46" t="n">
         <v>1</v>
       </c>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C34"/>
+  <dimension ref="B2:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -941,142 +941,154 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="B21" s="2" t="inlineStr">
+    <row r="21" ht="48" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>สถานที่ตั้ง (คอลัมน์ AA)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>บริษัทเดียวมีหลายที่ตั้งได้ — ที่ตั้งคนละที่ถือว่าใช้ Server คนละเครื่อง ไม่มี Server กลางข้ามที่ตั้ง จึงต้องพิมพ์ชื่อที่ตั้งให้เหมือนกันทุกครั้ง (ไม่ได้คิดคะแนน) ที่ตั้งเดียวเว้นว่างได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>คอลัมน์ที่ตรงกับ Excel Template เดิม (ยกมาครบ ไม่ได้ตัดทิ้ง)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Existing Work</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>-&gt; คอลัมน์ G 'วิธีการทำงานปัจจุบัน' ในชั้นที่ 1</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Description for Redesign</t>
+          <t>Existing Work</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>-&gt; คอลัมน์ H 'แนวทางหลังนำ AI มาใช้' ในชั้นที่ 1</t>
+          <t>-&gt; คอลัมน์ G 'วิธีการทำงานปัจจุบัน' ในชั้นที่ 1</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Data Available from &amp; by …</t>
+          <t>Description for Redesign</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>-&gt; คอลัมน์ K 'ข้อมูลที่มีอยู่ตอนนี้' ในชั้นที่ 1</t>
+          <t>-&gt; คอลัมน์ H 'แนวทางหลังนำ AI มาใช้' ในชั้นที่ 1</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>Data Available from &amp; by …</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; คอลัมน์ K 'ข้อมูลที่มีอยู่ตอนนี้' ในชั้นที่ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>ปัญหาที่ต้องการแก้ / Output ที่คาดหวัง (แบบ GSK)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>-&gt; คอลัมน์ F และ H ในชั้นที่ 1</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
+    <row r="27" ht="48" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>ข้อมูลเชิงปริมาณ + ความต้องการเชิงเทคนิค (แบบ GSK)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>-&gt; ย้ายไปอยู่ชั้นที่ 2 ทั้งหมด พร้อมเพิ่มที่ขาด เช่น Peak concurrent, ประเภทข้อมูล Input, ขนาดคลังเอกสาร, ความต้องการ Fine-tune</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="2" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>ข้อมูลแต่ละกลุ่มถูกนำไปใช้ทำอะไร</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>ผลกระทบ (สีส้ม)</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>ชั่วโมง/สัปดาห์ + มูลค่าความเสียหาย -&gt; คะแนน Impact (น้ำหนัก 35%)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>ความพร้อมข้อมูล (สีเขียว)</t>
+          <t>ผลกระทบ (สีส้ม)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>รูปแบบ + ย้อนหลัง + สิทธิ์ใช้ข้อมูล -&gt; คะแนน Data (น้ำหนัก 25%)</t>
+          <t>ชั่วโมง/สัปดาห์ + มูลค่าความเสียหาย -&gt; คะแนน Impact (น้ำหนัก 35%)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>ความเป็นไปได้ (สีม่วง)</t>
+          <t>ความพร้อมข้อมูล (สีเขียว)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>ระบบเดิมที่ต้องเชื่อม + คนดูแลต่อ -&gt; คะแนน Feasibility (น้ำหนัก 25%)</t>
+          <t>รูปแบบ + ย้อนหลัง + สิทธิ์ใช้ข้อมูล -&gt; คะแนน Data (น้ำหนัก 25%)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="B31" s="3" t="inlineStr">
         <is>
+          <t>ความเป็นไปได้ (สีม่วง)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>ระบบเดิมที่ต้องเชื่อม + คนดูแลต่อ -&gt; คะแนน Feasibility (น้ำหนัก 25%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
           <t>ความเสี่ยง (สีแดง)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>ผลถ้า AI ผิด + การตรวจซ้ำ + ความลับข้อมูล -&gt; คะแนน Risk (น้ำหนัก 15% กลับด้าน)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="33" ht="48" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>ชั้นที่ 2 ทั้งหมด</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>ใช้กำหนด Spec Hardware : Latency + ประเภทข้อมูล -&gt; ตัดสินว่าต้องใช้ GPU หรือ CPU  |  Peak concurrent + Requests -&gt; ตัดสินขนาดเครื่อง  |  ระดับความลับ + ที่ตั้งระบบ -&gt; ตัดสินว่า On-premise หรือ Cloud</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>หมายเหตุ : ข้อมูลในแถวตัวอย่าง (แถวสีเทา) เป็นตัวเลขสมมติเพื่อแสดงรูปแบบการกรอกเท่านั้น ไม่ใช่ข้อมูลจริงของบริษัท</t>
         </is>
@@ -1084,12 +1096,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1102,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:AA36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1131,6 +1143,7 @@
     <col width="30" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1202,6 +1215,11 @@
       </c>
       <c r="Y4" s="20" t="n"/>
       <c r="Z4" s="20" t="n"/>
+      <c r="AA4" s="7" t="inlineStr">
+        <is>
+          <t>สถานที่ตั้ง</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
@@ -1345,6 +1363,12 @@
           <t>หมายเหตุ</t>
         </is>
       </c>
+      <c r="AA5" s="21" t="inlineStr">
+        <is>
+          <t>สถานที่ตั้งที่ใช้งาน
+(โรงงาน / สาขา)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="22" t="n">
@@ -1475,22 +1499,67 @@
           <t>คุณสมชายผ่านการอบรม Python มาแล้ว</t>
         </is>
       </c>
+      <c r="AA6" s="22" t="inlineStr">
+        <is>
+          <t>โรงงานระยอง</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="23" t="n"/>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
+      <c r="A7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Auto Inspection ตรวจสอบคุณภาพชิ้นงานด้วย Machine Learning (แยกสินค้าดี/เสีย)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>บริษัท เอส.เค.โพลีเมอร์ จำกัด</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Production (MOLDING)</t>
+        </is>
+      </c>
       <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="23" t="n"/>
-      <c r="H7" s="23" t="n"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>QWP-A07 การวางแผนและควบคุมการผลิต MOLDING</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>% สินค้าโอนขึ้นคลัง &gt; 98%
+% งานจบตามแผน &gt; 98%
+% OEE &gt; 80%</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>ขั้นตอนที่ 11 ผลิตและควบคุมติดตามแผนการผลิต › 5 การตรวจสอบคุณภาพชิ้นงาน</t>
+        </is>
+      </c>
       <c r="I7" s="23" t="n"/>
-      <c r="J7" s="23" t="n"/>
-      <c r="K7" s="23" t="n"/>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>การตรวจสอบชิ้นงาน ตรวจสอบคุณภาพชิ้นงาน โดย ใช้การตรวจสอบด้วยสายตา</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>ใช้เครื่อง Auto Inspection ในการตรวจสอบคุณภาพสินค้า โดยใช้ Machine Learning ในการทำให้เกิดการจดจำ สินค้า ดี และ เสีย เพื่อแยกออกจากกัน</t>
+        </is>
+      </c>
       <c r="L7" s="23" t="n"/>
       <c r="M7" s="23" t="n"/>
-      <c r="N7" s="23" t="n"/>
+      <c r="N7" s="23" t="inlineStr">
+        <is>
+          <t>- รุปของสินค้าทั้งานดีและงานเสีย</t>
+        </is>
+      </c>
       <c r="O7" s="23" t="n"/>
       <c r="P7" s="23" t="n"/>
       <c r="Q7" s="23" t="n"/>
@@ -1502,23 +1571,77 @@
       <c r="W7" s="23" t="n"/>
       <c r="X7" s="23" t="n"/>
       <c r="Y7" s="23" t="n"/>
-      <c r="Z7" s="23" t="n"/>
+      <c r="Z7" s="23" t="inlineStr">
+        <is>
+          <t>แหล่งข้อมูล: ไฟล์ AI Transformation Plan (Prod) E&amp;E.xlsx ชีต Prod (3)</t>
+        </is>
+      </c>
+      <c r="AA7" s="23" t="n"/>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="23" t="n"/>
-      <c r="B8" s="23" t="n"/>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="23" t="n"/>
+      <c r="A8" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>AI จัดคนเข้าเครื่องตาม Skill Matrix แทนหัวหน้างาน (AI-Driven Manpower Allocation)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>บริษัท เอส.เค.โพลีเมอร์ จำกัด</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Production (MOLDING)</t>
+        </is>
+      </c>
       <c r="E8" s="23" t="n"/>
-      <c r="F8" s="23" t="n"/>
-      <c r="G8" s="23" t="n"/>
-      <c r="H8" s="23" t="n"/>
-      <c r="I8" s="23" t="n"/>
-      <c r="J8" s="23" t="n"/>
-      <c r="K8" s="23" t="n"/>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>QWP-A07 การวางแผนและควบคุมการผลิต MOLDING</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>% สินค้าโอนขึ้นคลัง &gt; 98%
+% งานจบตามแผน &gt; 98%
+% OEE &gt; 80%</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>ขั้นตอนที่ 11 ผลิตและควบคุมติดตามแผนการผลิต › 7 การจัดคนเข้าทำงาน</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>ไม่มีการ Optimizations ให้เกิด ประสิทธิภาพสูงสุด</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>หัวหน้างาน จะจัดคนแบบ Mannual โดยใช้ข้อมูลการ Fix คน Fix เครื่อง และ ข้อมูล Part Training ที่ผูกไว้ด้วย Excel
+และใช้ระบบเตือน หลังจากที่เลือกไปแล้วโดย จะรู้ว่า พนักงานที่จัดไปอยู่ระดับใหน</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>ให้ AI จัดคนแทนหัวหน้างานโดย ให้พิจารณาจาก ข้อมูล การ Fix คน Fix เครื่อง , ข้อมูล Part Training , ข้อมูลแผนการผลิตจาก MPS , ข้อมูลการมาทำงาน จาก Payroll
+และ และข้อมูล Performance , Good rate ของพนักงานรายคน เพื่อให้การจัดคนมีประสิทธิภาพสูงสุด</t>
+        </is>
+      </c>
       <c r="L8" s="23" t="n"/>
       <c r="M8" s="23" t="n"/>
-      <c r="N8" s="23" t="n"/>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t>- Part Training
+- ตาราง Fix คน Fix เครื่อง
+- ข้อมูลการมาทำงานจาก Payroll
+- ประวัติ ผลงาน ของพนักงาน รายบุคคล</t>
+        </is>
+      </c>
       <c r="O8" s="23" t="n"/>
       <c r="P8" s="23" t="n"/>
       <c r="Q8" s="23" t="n"/>
@@ -1530,23 +1653,75 @@
       <c r="W8" s="23" t="n"/>
       <c r="X8" s="23" t="n"/>
       <c r="Y8" s="23" t="n"/>
-      <c r="Z8" s="23" t="n"/>
+      <c r="Z8" s="23" t="inlineStr">
+        <is>
+          <t>แหล่งข้อมูล: ไฟล์ AI Transformation Plan (Prod) E&amp;E.xlsx ชีต Prod (3) และชีต Man Alocation 1–3 (Workflow, Data requirement, ทางเลือกการพัฒนา 3 ระดับ)</t>
+        </is>
+      </c>
+      <c r="AA8" s="23" t="n"/>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="23" t="n"/>
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="23" t="n"/>
-      <c r="D9" s="23" t="n"/>
+      <c r="A9" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Big Data ปิด LOT การผลิตอัตโนมัติ และวิเคราะห์แนวทางแก้ปัญหาการผลิต (Close Lot Analytics)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>บริษัท เอส.เค.โพลีเมอร์ จำกัด</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Production (MOLDING)</t>
+        </is>
+      </c>
       <c r="E9" s="23" t="n"/>
-      <c r="F9" s="23" t="n"/>
-      <c r="G9" s="23" t="n"/>
-      <c r="H9" s="23" t="n"/>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>QWP-A07 การวางแผนและควบคุมการผลิต MOLDING</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>% สินค้าโอนขึ้นคลัง &gt; 98%
+% งานจบตามแผน &gt; 98%
+% OEE &gt; 80%</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>ขั้นตอนที่ 19 Close Lot Meeting › 1 ประชุมสรุปผลการผลิต</t>
+        </is>
+      </c>
       <c r="I9" s="23" t="n"/>
-      <c r="J9" s="23" t="n"/>
-      <c r="K9" s="23" t="n"/>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>ประชุมสรุปผลการผลิต โดยจะพิจารณา ผลการผลิตตามหัวข้อเหล่านี้
+- % Yeild rate
+- % Cost
+- ประวัติ NC และCCR
+- Last Mold และ Last shot เพื่อประเมินความพร้องของการผลิตในแผนถัดไป</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>สร้าง Big Data ให้มีความเชื่อมโยงกัน ทุกข้อมูล และ ให้ มีระบบการประเมิน ปิด Lot แบบ Auto และให้สามารถวิเคราะห์แนวทางการแก้ไขปัญหาที่เกิดขึ้นในการผลิต</t>
+        </is>
+      </c>
       <c r="L9" s="23" t="n"/>
       <c r="M9" s="23" t="n"/>
-      <c r="N9" s="23" t="n"/>
+      <c r="N9" s="23" t="inlineStr">
+        <is>
+          <t>- % Yeild rate
+- % Cost
+- ประวัติ NC และCCR
+- ผลการตรวจสอบ Last Mold และ Last shot</t>
+        </is>
+      </c>
       <c r="O9" s="23" t="n"/>
       <c r="P9" s="23" t="n"/>
       <c r="Q9" s="23" t="n"/>
@@ -1558,7 +1733,12 @@
       <c r="W9" s="23" t="n"/>
       <c r="X9" s="23" t="n"/>
       <c r="Y9" s="23" t="n"/>
-      <c r="Z9" s="23" t="n"/>
+      <c r="Z9" s="23" t="inlineStr">
+        <is>
+          <t>แหล่งข้อมูล: ไฟล์ AI Transformation Plan (Prod) E&amp;E.xlsx ชีต Prod (3)</t>
+        </is>
+      </c>
+      <c r="AA9" s="23" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="23" t="n"/>
@@ -1587,6 +1767,7 @@
       <c r="X10" s="23" t="n"/>
       <c r="Y10" s="23" t="n"/>
       <c r="Z10" s="23" t="n"/>
+      <c r="AA10" s="23" t="n"/>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="23" t="n"/>
@@ -1615,6 +1796,7 @@
       <c r="X11" s="23" t="n"/>
       <c r="Y11" s="23" t="n"/>
       <c r="Z11" s="23" t="n"/>
+      <c r="AA11" s="23" t="n"/>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="23" t="n"/>
@@ -1643,6 +1825,7 @@
       <c r="X12" s="23" t="n"/>
       <c r="Y12" s="23" t="n"/>
       <c r="Z12" s="23" t="n"/>
+      <c r="AA12" s="23" t="n"/>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="23" t="n"/>
@@ -1671,6 +1854,7 @@
       <c r="X13" s="23" t="n"/>
       <c r="Y13" s="23" t="n"/>
       <c r="Z13" s="23" t="n"/>
+      <c r="AA13" s="23" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="23" t="n"/>
@@ -1699,6 +1883,7 @@
       <c r="X14" s="23" t="n"/>
       <c r="Y14" s="23" t="n"/>
       <c r="Z14" s="23" t="n"/>
+      <c r="AA14" s="23" t="n"/>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="23" t="n"/>
@@ -1727,6 +1912,7 @@
       <c r="X15" s="23" t="n"/>
       <c r="Y15" s="23" t="n"/>
       <c r="Z15" s="23" t="n"/>
+      <c r="AA15" s="23" t="n"/>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="23" t="n"/>
@@ -1755,6 +1941,7 @@
       <c r="X16" s="23" t="n"/>
       <c r="Y16" s="23" t="n"/>
       <c r="Z16" s="23" t="n"/>
+      <c r="AA16" s="23" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="23" t="n"/>
@@ -1783,6 +1970,7 @@
       <c r="X17" s="23" t="n"/>
       <c r="Y17" s="23" t="n"/>
       <c r="Z17" s="23" t="n"/>
+      <c r="AA17" s="23" t="n"/>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="23" t="n"/>
@@ -1811,6 +1999,7 @@
       <c r="X18" s="23" t="n"/>
       <c r="Y18" s="23" t="n"/>
       <c r="Z18" s="23" t="n"/>
+      <c r="AA18" s="23" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="23" t="n"/>
@@ -1839,6 +2028,7 @@
       <c r="X19" s="23" t="n"/>
       <c r="Y19" s="23" t="n"/>
       <c r="Z19" s="23" t="n"/>
+      <c r="AA19" s="23" t="n"/>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="23" t="n"/>
@@ -1867,6 +2057,7 @@
       <c r="X20" s="23" t="n"/>
       <c r="Y20" s="23" t="n"/>
       <c r="Z20" s="23" t="n"/>
+      <c r="AA20" s="23" t="n"/>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="23" t="n"/>
@@ -1895,6 +2086,7 @@
       <c r="X21" s="23" t="n"/>
       <c r="Y21" s="23" t="n"/>
       <c r="Z21" s="23" t="n"/>
+      <c r="AA21" s="23" t="n"/>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="23" t="n"/>
@@ -1923,6 +2115,7 @@
       <c r="X22" s="23" t="n"/>
       <c r="Y22" s="23" t="n"/>
       <c r="Z22" s="23" t="n"/>
+      <c r="AA22" s="23" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="23" t="n"/>
@@ -1951,6 +2144,7 @@
       <c r="X23" s="23" t="n"/>
       <c r="Y23" s="23" t="n"/>
       <c r="Z23" s="23" t="n"/>
+      <c r="AA23" s="23" t="n"/>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="23" t="n"/>
@@ -1979,6 +2173,7 @@
       <c r="X24" s="23" t="n"/>
       <c r="Y24" s="23" t="n"/>
       <c r="Z24" s="23" t="n"/>
+      <c r="AA24" s="23" t="n"/>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="23" t="n"/>
@@ -2007,6 +2202,7 @@
       <c r="X25" s="23" t="n"/>
       <c r="Y25" s="23" t="n"/>
       <c r="Z25" s="23" t="n"/>
+      <c r="AA25" s="23" t="n"/>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="23" t="n"/>
@@ -2035,6 +2231,7 @@
       <c r="X26" s="23" t="n"/>
       <c r="Y26" s="23" t="n"/>
       <c r="Z26" s="23" t="n"/>
+      <c r="AA26" s="23" t="n"/>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="23" t="n"/>
@@ -2063,6 +2260,7 @@
       <c r="X27" s="23" t="n"/>
       <c r="Y27" s="23" t="n"/>
       <c r="Z27" s="23" t="n"/>
+      <c r="AA27" s="23" t="n"/>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="23" t="n"/>
@@ -2091,6 +2289,7 @@
       <c r="X28" s="23" t="n"/>
       <c r="Y28" s="23" t="n"/>
       <c r="Z28" s="23" t="n"/>
+      <c r="AA28" s="23" t="n"/>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="23" t="n"/>
@@ -2119,6 +2318,7 @@
       <c r="X29" s="23" t="n"/>
       <c r="Y29" s="23" t="n"/>
       <c r="Z29" s="23" t="n"/>
+      <c r="AA29" s="23" t="n"/>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="23" t="n"/>
@@ -2147,6 +2347,7 @@
       <c r="X30" s="23" t="n"/>
       <c r="Y30" s="23" t="n"/>
       <c r="Z30" s="23" t="n"/>
+      <c r="AA30" s="23" t="n"/>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="23" t="n"/>
@@ -2175,6 +2376,7 @@
       <c r="X31" s="23" t="n"/>
       <c r="Y31" s="23" t="n"/>
       <c r="Z31" s="23" t="n"/>
+      <c r="AA31" s="23" t="n"/>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="23" t="n"/>
@@ -2203,6 +2405,7 @@
       <c r="X32" s="23" t="n"/>
       <c r="Y32" s="23" t="n"/>
       <c r="Z32" s="23" t="n"/>
+      <c r="AA32" s="23" t="n"/>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="23" t="n"/>
@@ -2231,6 +2434,7 @@
       <c r="X33" s="23" t="n"/>
       <c r="Y33" s="23" t="n"/>
       <c r="Z33" s="23" t="n"/>
+      <c r="AA33" s="23" t="n"/>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="23" t="n"/>
@@ -2259,6 +2463,7 @@
       <c r="X34" s="23" t="n"/>
       <c r="Y34" s="23" t="n"/>
       <c r="Z34" s="23" t="n"/>
+      <c r="AA34" s="23" t="n"/>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="23" t="n"/>
@@ -2287,6 +2492,7 @@
       <c r="X35" s="23" t="n"/>
       <c r="Y35" s="23" t="n"/>
       <c r="Z35" s="23" t="n"/>
+      <c r="AA35" s="23" t="n"/>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="23" t="n"/>
@@ -2315,20 +2521,21 @@
       <c r="X36" s="23" t="n"/>
       <c r="Y36" s="23" t="n"/>
       <c r="Z36" s="23" t="n"/>
+      <c r="AA36" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="I4:M4"/>
     <mergeCell ref="N4:R4"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A2:AA2"/>
     <mergeCell ref="U4:W4"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="A1:AA1"/>
     <mergeCell ref="S4:T4"/>
   </mergeCells>
-  <dataValidations count="17">
+  <dataValidations count="18">
     <dataValidation sqref="C7:C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="บริษัท" prompt="เลือกจากรายการ — กดลูกศรด้านขวาของช่อง" type="list">
       <formula1>DATA!$A$4:$A$9</formula1>
     </dataValidation>
@@ -2370,6 +2577,7 @@
     <dataValidation sqref="K7:K36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="แนวทางหลังนำ AI มาใช้" prompt="อยากให้ AI ทำอะไรให้ และผลลัพธ์ที่อยากได้หน้าตาเป็นยังไง&#10;เช่น ติดกล้องที่สายพาน ให้ AI แยกดี/เสียอัตโนมัติ&#10;ชิ้นที่ AI ไม่มั่นใจค่อยส่งให้คนตรวจ"/>
     <dataValidation sqref="N7:N36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ข้อมูลที่มีอยู่ตอนนี้" prompt="มีข้อมูลอะไรบ้าง เก็บไว้ที่ไหน ใครเป็นคนเก็บ&#10;ถ้ามีสัดส่วนที่น่าสนใจให้เขียนด้วย เช่น รูปดี 3,000 / รูปเสีย 1,000"/>
     <dataValidation sqref="Q7:Q36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ปริมาณข้อมูลโดยประมาณ" prompt="นับเป็น 'รายการ' หน่วยขึ้นกับงาน :&#10;  ตรวจภาพ = กี่รูป&#10;  หาสาเหตุ/NC = กี่เคส&#10;  ค้นหาเอกสาร = กี่ไฟล์&#10;  เครื่องเสีย = กี่ครั้ง&#10;  การผลิต = กี่ล็อต&#10;&#10;นับเฉพาะที่รู้คำตอบแล้ว เช่น รูปที่มาร์คว่าดี/เสีย&#10;(รายละเอียดเต็มอยู่ในคู่มือ)"/>
+    <dataValidation sqref="AA7:AA36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="สถานที่ตั้งที่ใช้งาน" prompt="โรงงาน/สาขาที่ใช้งานนี้จริง (บริษัทเดียวมีหลายที่ตั้งได้)&#10;&#10;ที่ตั้งคนละที่ = ใช้ Server คนละเครื่อง ไม่มี Server กลางข้ามที่ตั้ง&#10;พิมพ์ชื่อให้เหมือนกันทุกครั้งสำหรับที่ตั้งเดียวกัน&#10;ถ้ามีที่ตั้งเดียว เว้นว่างได้"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>ใช้กำหนด Spec Hardware : Latency + ประเภทข้อมูล -&gt; ตัดสินว่าต้องใช้ GPU หรือ CPU  |  Peak concurrent + Requests -&gt; ตัดสินขนาดเครื่อง  |  ระดับความลับ + ที่ตั้งระบบ -&gt; ตัดสินว่า On-premise หรือ Cloud</t>
+          <t>ใช้กำหนด Spec Hardware : Latency + ประเภทข้อมูล -&gt; ตัดสินว่าต้องใช้ GPU หรือ CPU  |  Peak concurrent + Requests -&gt; ตัดสินขนาดเครื่อง  |  ระดับความลับ -&gt; มาตรการเข้ารหัส/จำกัดสิทธิ์ (ทุกงานรันบน On-premise ไม่ใช้ Cloud)</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Server เป็นเครื่องซื้อใหม่ ตั้งในบริษัทที่เดียว ไม่ใช้ Cloud  |  เขียว = ระบบดึงมาให้  |  เหลือง = แผนกกรอก  |  ฟ้า = ทีม AI/IT เติมให้ทีหลัง แผนกข้ามไปได้เลย</t>
+          <t>Server เป็นเครื่องซื้อใหม่ ตั้งในบริษัท ทุกที่ตั้ง (โรงงาน/สาขา) มีเครื่องของตัวเอง ไม่ใช้ Cloud  |  เขียว = ระบบดึงมาให้  |  เหลือง = แผนกกรอก  |  ฟ้า = ทีม AI/IT เติมให้ทีหลัง แผนกข้ามไปได้เลย</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
     <dataValidation sqref="U7:U36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="ความละเอียดของภาพ" prompt="ความละเอียดของภาพจากกล้องที่จะใช้&#10;&#10;ยิ่งละเอียด ยิ่งใช้ VRAM มาก&#10;ถ้าไม่ใช่งานประมวลผลภาพ เลือก ไม่เกี่ยวข้อง" type="list">
       <formula1>DATA!$O$4:$O$8</formula1>
     </dataValidation>
-    <dataValidation sqref="V7:V36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="รูปแบบการติดตั้ง" prompt="รันที่ Server กลาง หรือต้องมีเครื่องข้างเครื่องจักร&#10;&#10;งานที่ต้องตัดสินใจทันทีในสายการผลิต ต้องติดตั้งหน้างาน&#10;เพราะรอส่งข้อมูลไปกลับไม่ทัน และต้องต่อกับแขนคัดแยกหรือ PLC" type="list">
+    <dataValidation sqref="V7:V36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="รูปแบบการติดตั้ง" prompt="รันที่ Server ของที่ตั้ง หรือต้องมีเครื่องข้างเครื่องจักร&#10;&#10;งานที่ต้องตัดสินใจทันทีในสายการผลิต ต้องติดตั้งหน้างาน&#10;เพราะรอส่งข้อมูลไปกลับไม่ทัน และต้องต่อกับแขนคัดแยกหรือ PLC" type="list">
       <formula1>DATA!$Z$4:$Z$6</formula1>
     </dataValidation>
     <dataValidation sqref="W7:W36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="การปรับโมเดลด้วยข้อมูลองค์กร" prompt="สำเร็จรูป = งานความรู้ทั่วไป ใช้ได้ทันที&#10;RAG = ให้อ่านเอกสารองค์กร ไม่ต้องฝึกโมเดล&#10;Fine-tune = สอนด้วยข้อมูลหรือภาพของเราเอง ต้องมี GPU ฝึก&#10;&#10;งานเอกสารส่วนใหญ่ควรเลือก RAG ไม่ใช่ Fine-tune" type="list">
@@ -4179,7 +4179,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>ทุกช่องในหน้านี้เป็นสูตร ดึงข้อมูลจาก sheet '1-UseCase ทั้งหมด' อัตโนมัติ  |  แถวสีเทา (แถวที่ 6) คือคะแนนของ Use Case ตัวอย่าง ไม่นับเข้าการจัดอันดับ  |  ถ้าอยากปรับน้ำหนักคะแนนหรือเกณฑ์แบ่งระดับ ให้ไปแก้ที่ sheet 'DATA' คอลัมน์ S-T (ตัวเลขสีน้ำเงิน)</t>
+          <t>ทุกช่องในหน้านี้เป็นสูตร ดึงข้อมูลจาก sheet '1-UseCase ทั้งหมด' อัตโนมัติ  |  แถวสีเทา (แถวที่ 6) คือคะแนนของ Use Case ตัวอย่าง ไม่นับเข้าการจัดอันดับ  |  ถ้าอยากปรับน้ำหนักคะแนนหรือเกณฑ์แบ่งระดับ ให้ไปแก้ที่ sheet 'DATA' คอลัมน์ AH-AI (ตัวเลขสีน้ำเงิน)</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
     <row r="46">
       <c r="A46" s="38" t="inlineStr">
         <is>
-          <t>•  ค่าเกณฑ์ชั่วโมง/มูลค่า และน้ำหนักทุกตัว แก้ได้ที่ sheet DATA คอลัมน์ S-T (ตัวเลขสีน้ำเงิน)</t>
+          <t>•  ค่าเกณฑ์ชั่วโมง/มูลค่า และน้ำหนักทุกตัว แก้ได้ที่ sheet DATA คอลัมน์ AH-AI (ตัวเลขสีน้ำเงิน)</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,6 @@
     <col width="32" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
     <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="32" customWidth="1" min="17" max="17"/>
     <col width="44" customWidth="1" min="18" max="18"/>
     <col width="32" customWidth="1" min="19" max="19"/>
@@ -7256,11 +7255,6 @@
           <t>ความละเอียดของภาพ</t>
         </is>
       </c>
-      <c r="P3" s="40" t="inlineStr">
-        <is>
-          <t>ที่ตั้งระบบ</t>
-        </is>
-      </c>
       <c r="Q3" s="40" t="inlineStr">
         <is>
           <t>การปรับโมเดลด้วยข้อมูลองค์กร</t>
@@ -7413,11 +7407,6 @@
           <t>ไม่เกี่ยวข้อง</t>
         </is>
       </c>
-      <c r="P4" s="42" t="inlineStr">
-        <is>
-          <t>On-premise เท่านั้น</t>
-        </is>
-      </c>
       <c r="Q4" s="42" t="inlineStr">
         <is>
           <t>ไม่จำเป็น - ใช้โมเดลสำเร็จรูปได้ (งานความรู้ทั่วไป)</t>
@@ -7573,11 +7562,6 @@
           <t>ต่ำกว่า 1 ล้านพิกเซล</t>
         </is>
       </c>
-      <c r="P5" s="42" t="inlineStr">
-        <is>
-          <t>ใช้ Cloud ได้</t>
-        </is>
-      </c>
       <c r="Q5" s="42" t="inlineStr">
         <is>
           <t>ไม่ต้องฝึกโมเดล แต่ให้เข้าถึงเอกสารขององค์กร (RAG)</t>
@@ -7733,11 +7717,6 @@
           <t>1 - 5 ล้านพิกเซล</t>
         </is>
       </c>
-      <c r="P6" s="42" t="inlineStr">
-        <is>
-          <t>ผสม</t>
-        </is>
-      </c>
       <c r="Q6" s="42" t="inlineStr">
         <is>
           <t>จำเป็น - ต้อง Fine-tune ด้วยข้อมูลหรือภาพขององค์กร</t>
@@ -8162,11 +8141,6 @@
           <t>ความละเอียดของภาพ</t>
         </is>
       </c>
-      <c r="P29" s="40" t="inlineStr">
-        <is>
-          <t>ที่ตั้งระบบ</t>
-        </is>
-      </c>
       <c r="Q29" s="40" t="inlineStr">
         <is>
           <t>การปรับโมเดลด้วยข้อมูลองค์กร</t>
@@ -8298,11 +8272,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P30" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="Q30" s="45" t="inlineStr">
         <is>
           <t>-</t>
@@ -8432,11 +8401,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P31" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="Q31" s="45" t="inlineStr">
         <is>
           <t>-</t>
@@ -8560,11 +8524,6 @@
         </is>
       </c>
       <c r="O32" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P32" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/docs/AI_UseCase_Template_v2.xlsx
+++ b/docs/AI_UseCase_Template_v2.xlsx
@@ -2542,7 +2542,7 @@
     <dataValidation sqref="L7:L36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="เวลาที่ใช้กับงานนี้ในปัจจุบัน" prompt="เวลาที่คนใช้ทำงานนี้ด้วยวิธีเดิม รวมทุกคนในหน่วยงาน&#10;&#10;เช่น 3 คน คนละ 6 ชั่วโมง/สัปดาห์ = 18 ชั่วโมง/สัปดาห์&#10;&#10;ยังไม่ได้ใช้ AI ช่วย" type="list">
       <formula1>DATA!$R$4:$R$8</formula1>
     </dataValidation>
-    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มูลค่าความสูญเสียต่อปี" prompt="ความสูญเสียที่เกิดจากปัญหานี้ในปัจจุบัน&#10;&#10;ถ้าประเมินเป็นตัวเงินไม่ได้ ให้เลือกตัวเลือกแรก&#10;ระบบจะใช้เฉพาะชั่วโมงคิดคะแนน ไม่ได้หักคะแนน" type="list">
+    <dataValidation sqref="M7:M36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="มูลค่าความสูญเสียต่อปี" prompt="ความสูญเสียที่เกิดจากปัญหานี้ในปัจจุบัน&#10;&#10;ถ้าประเมินเป็นตัวเงินไม่ได้ ให้เลือกตัวเลือกแรก&#10;ระบบให้ 3 คะแนน (ค่ากลาง) ไม่ได้เปรียบหรือเสียเปรียบ&#10;ถ้ารู้ว่าความเสียหายน้อยจริง ให้เลือกช่วงที่ตรงความจริง" type="list">
       <formula1>DATA!$S$4:$S$8</formula1>
     </dataValidation>
     <dataValidation sqref="O7:O36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการเท่านั้น (กดลูกศรด้านขวาของช่อง)" promptTitle="รูปแบบการจัดเก็บข้อมูลปัจจุบัน" prompt="ข้อมูลที่จะใช้พัฒนา AI เก็บอยู่ในรูปแบบไหน&#10;&#10;กระดาษ = ต้องแปลงเป็นดิจิทัลก่อน ใช้เวลาเป็นเดือน&#10;ฐานข้อมูลในระบบ = ดึงอัตโนมัติได้ เริ่มได้เร็วที่สุด" type="list">
@@ -7061,7 +7061,7 @@
     <row r="44">
       <c r="A44" s="38" t="inlineStr">
         <is>
-          <t>•  ถ้าตีมูลค่าความเสียหายเป็นเงินไม่ได้ ให้เลือก 'ประเมินเป็นเงินไม่ได้' — ระบบจะใช้เฉพาะชั่วโมงคิด Impact ไม่ได้หักคะแนน (ในตารางจะขึ้นเป็น '-')</t>
+          <t>•  ถ้าตีมูลค่าความเสียหายเป็นเงินไม่ได้ ให้เลือก 'ประเมินเป็นเงินไม่ได้' — ระบบให้ 3 คะแนน (ค่ากลาง) แล้วเฉลี่ยกับคะแนนชั่วโมงตามปกติ ไม่ได้เปรียบหรือเสียเปรียบ</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z4" s="42" t="inlineStr">
         <is>
-          <t>ติดตั้งที่ Server กลาง - ส่งข้อมูลผ่านเครือข่ายได้</t>
+          <t>ติดตั้งที่ Server ของที่ตั้ง (ห้อง Server ของโรงงาน/สาขา) - ส่งข้อมูลผ่านเครือข่ายได้</t>
         </is>
       </c>
       <c r="AB4" s="42" t="inlineStr">
@@ -8054,7 +8054,7 @@
     <row r="17">
       <c r="AH17" s="42" t="inlineStr">
         <is>
-          <t>คะแนน "-" แปลว่าไม่นำมาคิดคะแนน ไม่ใช่ได้ 0</t>
+          <t>คะแนน "-" แปลว่าตัวเลือกนั้นไม่ใช้คิดคะแนน ไม่ใช่ได้ 0</t>
         </is>
       </c>
     </row>
@@ -8280,10 +8280,8 @@
       <c r="R30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="S30" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S30" s="46" t="n">
+        <v>3</v>
       </c>
       <c r="T30" s="45" t="inlineStr">
         <is>
